--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D955AA0D-DB51-4022-BF94-8DEA70C4DD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,1564 +39,1564 @@
     <t xml:space="preserve">Indeks zadnia </t>
   </si>
   <si>
-    <t xml:space="preserve">Zdanie</t>
+    <t>Zdanie</t>
   </si>
   <si>
     <t xml:space="preserve">Kolejność znaków </t>
   </si>
   <si>
-    <t xml:space="preserve">Babcia i dziadek mają stary samochód.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BABCIA DZIADEK (PARA), SAMOCHÓD STARY, MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj jestem zmęczony i chcę już iść spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA ZMĘCZONY, DZISIAJ JA CHCE, SPAĆ,  JUŻ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego wczoraj nie byłeś w szkole?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ,SZKOŁA , NIE BYŁO , DLACZEGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój brat ma duży dom i nowy samochód.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, BRAT,DOM DUŻY,SAMOCHÓD, NOWY,MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie jest mój stary telefon i samochód?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, STARY,TELEFON , SAMOCHÓD ,GDZIE? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój brat ma nowego kota, który bardzo lubi dużo spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, BRAT , KOT, NOWY , MA , KOT,LUBI,BARDZO , DUŻO SPAĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">My jesteśmy w domu i czekamy na tatę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY,DOM , JESTEŚMY , TATA , CZEKAĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego twój przyjaciel był wczoraj smutny?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWÓJ PRZYJACIEL , WCZORAJ , SMUTNY , DLACZEGO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy ty wiesz, gdzie jest moja mama i siostra?</t>
+    <t>Babcia i dziadek mają stary samochód.</t>
+  </si>
+  <si>
+    <t>BABCIA, DZIADEK, PARA, SAMOCHÓD, STARY, MA</t>
+  </si>
+  <si>
+    <t>Dzisiaj jestem zmęczony i chcę już iść spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA ZMĘCZONY, DZISIAJ, JA, CHCE, SPAĆ,  JUŻ </t>
+  </si>
+  <si>
+    <t>Dlaczego wczoraj nie byłeś w szkole?</t>
+  </si>
+  <si>
+    <t>WCZORAJ,SZKOŁA , NIE, BYŁO , DLACZEGO</t>
+  </si>
+  <si>
+    <t>Mój brat ma duży dom i nowy samochód.</t>
+  </si>
+  <si>
+    <t>MÓJ, BRAT, DOM, DUŻY, SAMOCHÓD, NOWY, MA</t>
+  </si>
+  <si>
+    <t>Gdzie jest mój stary telefon i samochód?</t>
+  </si>
+  <si>
+    <t>MÓJ, STARY, TELEFON , SAMOCHÓD ,GDZIE</t>
+  </si>
+  <si>
+    <t>Mój brat ma nowego kota, który bardzo lubi dużo spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÓJ, BRAT , KOT, NOWY , MA , KOT, LUBI, BARDZO , DUŻO, SPAĆ </t>
+  </si>
+  <si>
+    <t>My jesteśmy w domu i czekamy na tatę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MY, DOM , JESTEŚMY , TATA , CZEKAĆ </t>
+  </si>
+  <si>
+    <t>Dlaczego twój przyjaciel był wczoraj smutny?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWÓJ, PRZYJACIEL , WCZORAJ , SMUTNY , DLACZEGO </t>
+  </si>
+  <si>
+    <t>Czy ty wiesz, gdzie jest moja mama i siostra?</t>
   </si>
   <si>
     <t xml:space="preserve">TY WIESZ , GDZIE , MAMA , SIOSTRA , JEST </t>
   </si>
   <si>
-    <t xml:space="preserve">Chce mi się pić.</t>
+    <t>Chce mi się pić.</t>
   </si>
   <si>
     <t xml:space="preserve">JA,CHCE , PIĆ </t>
   </si>
   <si>
-    <t xml:space="preserve">Moja siostra uczy się migać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOJA SIOSTRA , MIGAĆ , UCZYĆ-SIĘ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co robisz w pracy?</t>
+    <t>Moja siostra uczy się migać.</t>
+  </si>
+  <si>
+    <t>MOJA SIOSTRA , MIGAĆ , UCZYĆ-SIĘ</t>
+  </si>
+  <si>
+    <t>Co robisz w pracy?</t>
   </si>
   <si>
     <t xml:space="preserve">PRACA , TY , ROBIĆ CO? </t>
   </si>
   <si>
-    <t xml:space="preserve">Wczoraj byłem w szkole i uczyłem się migać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA,WCZORAJ , SZKOŁA , BYŁO , MIGAĆ , UCZYĆ-SIĘ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie rozumiem, co ty mówisz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA,NIE ROZUMIEM , CO , MÓWIĆ, CO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wesoła kobieta idzie do domu.</t>
+    <t>Wczoraj byłem w szkole i uczyłem się migać.</t>
+  </si>
+  <si>
+    <t>JA,WCZORAJ , SZKOŁA , BYŁO , MIGAĆ , UCZYĆ-SIĘ</t>
+  </si>
+  <si>
+    <t>Nie rozumiem, co ty mówisz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA,NIE, ROZUMIEM , CO , MÓWIĆ, CO </t>
+  </si>
+  <si>
+    <t>Wesoła kobieta idzie do domu.</t>
   </si>
   <si>
     <t xml:space="preserve">KOBIETA , WESOŁA , DOM , IŚĆ </t>
   </si>
   <si>
-    <t xml:space="preserve">Zmęczony brat idzie spać.</t>
+    <t>Zmęczony brat idzie spać.</t>
   </si>
   <si>
     <t xml:space="preserve">BRAT,ZMĘCZONY , SPAĆ , IŚĆ </t>
   </si>
   <si>
-    <t xml:space="preserve">Ty lubisz uczyć się migać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY LUBISZ,MIGAĆ,UCZYĆ-SIĘ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziękuję za wodę i jedzenie.</t>
+    <t>Ty lubisz uczyć się migać.</t>
+  </si>
+  <si>
+    <t>TY, LUBISZ,MIGAĆ,UCZYĆ-SIĘ</t>
+  </si>
+  <si>
+    <t>Dziękuję za wodę i jedzenie.</t>
   </si>
   <si>
     <t xml:space="preserve">DZIĘKUJĘ , WODA, JEDZENIE </t>
   </si>
   <si>
-    <t xml:space="preserve">Dzisiaj jest poniedziałek, idę do szkoły.</t>
+    <t>Dzisiaj jest poniedziałek, idę do szkoły.</t>
   </si>
   <si>
     <t xml:space="preserve">DZIŚ , PONIEDZIAŁEK , JA , SZKOŁA , PÓJDĘ </t>
   </si>
   <si>
-    <t xml:space="preserve">Brat lubi duże psy.</t>
+    <t>Brat lubi duże psy.</t>
   </si>
   <si>
     <t xml:space="preserve">BRAT,LUBI , DUŻE , PSY </t>
   </si>
   <si>
-    <t xml:space="preserve">Smutny mężczyzna pije zimną kawę.</t>
+    <t>Smutny mężczyzna pije zimną kawę.</t>
   </si>
   <si>
     <t xml:space="preserve">MĘŻCZYZNA , SMUTNY , KAWA , ZIMNA , PIJE </t>
   </si>
   <si>
-    <t xml:space="preserve">Kolega nie rozumie, co ja mówię.</t>
+    <t>Kolega nie rozumie, co ja mówię.</t>
   </si>
   <si>
     <t xml:space="preserve">KOLEGA , NIE , ROZUMIEĆ , CO, JA, MÓWIĆ </t>
   </si>
   <si>
-    <t xml:space="preserve">Gdzie jest mój przyjaciel?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ PRZYJACIEL , GDZIE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto wczoraj widział mojego psa?</t>
+    <t>Gdzie jest mój przyjaciel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÓJ, PRZYJACIEL , GDZIE </t>
+  </si>
+  <si>
+    <t>Kto wczoraj widział mojego psa?</t>
   </si>
   <si>
     <t xml:space="preserve">KTO,WCZORAJ , MÓJ, PIES , WIDZIAŁ </t>
   </si>
   <si>
-    <t xml:space="preserve">Ile pieniędzy chcesz?</t>
+    <t>Ile pieniędzy chcesz?</t>
   </si>
   <si>
     <t xml:space="preserve">PIENIĄDZE , TY , CHCIEĆ , ILE </t>
   </si>
   <si>
-    <t xml:space="preserve">Kiedy my idziemy do pracy?</t>
+    <t>Kiedy my idziemy do pracy?</t>
   </si>
   <si>
     <t xml:space="preserve">MY , PRACA , PÓJŚĆ , KIEDY </t>
   </si>
   <si>
-    <t xml:space="preserve">Ty rozumiesz, co ona dzisiaj do ciebie mówi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego wy uczycie się migać z tym mężczyzną?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siostra wczoraj była bardzo smutna.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIOSTRA , WCZORAJ , BARDZO SMUTNA , BYŁA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">On nie słyszy, ale bardzo dobrze widzi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON,NIE SŁYSZY , ALE WIDZI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie, ja nie chcę tego starego telefonu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIE, JA NIE CHCIEĆ ,TO,STARY TELEFON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siostra i brat czekają na nowy telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIOSTRA , BRAT , NOWY TELEFON , CZEKAĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ty wczoraj nie chciałeś nam pomóc?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY,WCZORAJ , NIE CHCIEĆ , NAM POMÓC , DLACZEGO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak duży jest twój nowy dom?</t>
+    <t>Ty rozumiesz, co ona dzisiaj do ciebie mówi.</t>
+  </si>
+  <si>
+    <t>Dlaczego wy uczycie się migać z tym mężczyzną?</t>
+  </si>
+  <si>
+    <t>Siostra wczoraj była bardzo smutna.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIOSTRA , WCZORAJ , BARDZO, SMUTNA , BYŁA </t>
+  </si>
+  <si>
+    <t>On nie słyszy, ale bardzo dobrze widzi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON,NIE, SŁYSZY, ALE, WIDZI </t>
+  </si>
+  <si>
+    <t>Nie, ja nie chcę tego starego telefonu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIE, JA, NIE, CHCIEĆ, TO, STARY, TELEFON </t>
+  </si>
+  <si>
+    <t>Siostra i brat czekają na nowy telefon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIOSTRA , BRAT , NOWY, TELEFON , CZEKAĆ </t>
+  </si>
+  <si>
+    <t>Dlaczego ty wczoraj nie chciałeś nam pomóc?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TY,WCZORAJ , NIE, CHCIEĆ , NAM, POMÓC , DLACZEGO </t>
+  </si>
+  <si>
+    <t>Jak duży jest twój nowy dom?</t>
   </si>
   <si>
     <t xml:space="preserve">TY,NOWY, DOM , DUŻY , JAK </t>
   </si>
   <si>
-    <t xml:space="preserve">Dziadek nie słyszy, co mówi ta kobieta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIADEK , NIE SŁYCHAĆ , KOBIETA TA , MÓWIĆ CO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smutna siostra czeka w domu na brata.</t>
+    <t>Dziadek nie słyszy, co mówi ta kobieta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DZIADEK , NIE, SŁYCHAĆ , KOBIETA, TA , MÓWIĆ, CO </t>
+  </si>
+  <si>
+    <t>Smutna siostra czeka w domu na brata.</t>
   </si>
   <si>
     <t xml:space="preserve">SIOSTRA , SMUTNA , DOM,BRAT, CZEKAĆ </t>
   </si>
   <si>
-    <t xml:space="preserve">Ja wiem, że wy jesteście bardzo zmęczeni.</t>
+    <t>Ja wiem, że wy jesteście bardzo zmęczeni.</t>
   </si>
   <si>
     <t xml:space="preserve">JA , WIEM , WY,ZMĘCZENI, JEST </t>
   </si>
   <si>
-    <t xml:space="preserve">Ona kocha duże psy i bardzo małe koty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONA , KOCHAĆ , DUŻE PSY , MAŁE KOTY , BARDZO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzień dobry, ja idę dzisiaj rano pracować.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIEŃ DOBRY , JA , DZIŚ RANO , PRACA , PÓJŚĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wesoły kolega wczoraj pomógł mi z samochodem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOLEGA , WESOŁY , WCZORAJ , JA SAMOCHÓD , POMÓC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mężczyzna nie słyszy, ale myśli i miga.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA , NIE SŁYCHAĆ , ALE , MYŚLEĆ , MIGAĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak dobrze uczyć się migać w nowej szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIGAĆ, UCZYĆ-SIĘ , NOWA SZKOŁA , DOBRZE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego wy nie chcecie migać w szkole?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WY,NIE CHCIEĆ , SZKOŁA , MIGAĆ , DLACZEGO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziadek i babcia mają duży stary dom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIADEK , BABCIA , PARA , DUŻY STARY , DOM , MIEĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brat ma kota i chce mieć małego psa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAT КОТ МА , MAŁY PIES , CHCE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mały pies czeka na jedzenie i wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAŁY PIES, JEDZENIE , WODA , CZEKAĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">To ważne, że my jesteśmy dzisiaj zdrowi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAŻNE , MY,DZIŚ , ZDROWY , BYĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kolega z pracy uczy się migać ze mną.</t>
+    <t>Ona kocha duże psy i bardzo małe koty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONA , KOCHAĆ , DUŻE, PSY , MAŁE, KOTY , BARDZO </t>
+  </si>
+  <si>
+    <t>Dzień dobry, ja idę dzisiaj rano pracować.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DZIEŃ, DOBRY , JA , DZIŚ RANO , PRACA , PÓJŚĆ </t>
+  </si>
+  <si>
+    <t>Wesoły kolega wczoraj pomógł mi z samochodem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOLEGA , WESOŁY , WCZORAJ, JA, SAMOCHÓD , POMÓC </t>
+  </si>
+  <si>
+    <t>Mężczyzna nie słyszy, ale myśli i miga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MĘŻCZYZNA , NIE, SŁYCHAĆ , ALE , MYŚLEĆ , MIGAĆ </t>
+  </si>
+  <si>
+    <t>Jak dobrze uczyć się migać w nowej szkole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGAĆ, UCZYĆ-SIĘ , NOWA, SZKOŁA , DOBRZE </t>
+  </si>
+  <si>
+    <t>Dlaczego wy nie chcecie migać w szkole?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WY, NIE, CHCIEĆ , SZKOŁA , MIGAĆ , DLACZEGO </t>
+  </si>
+  <si>
+    <t>Dziadek i babcia mają duży stary dom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DZIADEK , BABCIA , PARA , DUŻY, STARY , DOM , MIEĆ </t>
+  </si>
+  <si>
+    <t>Brat ma kota i chce mieć małego psa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAT, КОТ, МА , MAŁY, PIES, CHCE </t>
+  </si>
+  <si>
+    <t>Mały pies czeka na jedzenie i wodę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAŁY, PIES, JEDZENIE, WODA , CZEKAĆ </t>
+  </si>
+  <si>
+    <t>To ważne, że my jesteśmy dzisiaj zdrowi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAŻNE, MY, DZIŚ, ZDROWY, BYĆ </t>
+  </si>
+  <si>
+    <t>Kolega z pracy uczy się migać ze mną.</t>
   </si>
   <si>
     <t xml:space="preserve">KOLEGA , PRACA , RAZEM , UCZYĆ-SIĘ,  MIGAĆ </t>
   </si>
   <si>
-    <t xml:space="preserve">Jestem chory i bardzo chcę dzisiaj spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA CHORY , DZIŚ , CHCĘ , SPAĆ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ty jesteś dzisiaj bardzo smutny?</t>
+    <t>Jestem chory i bardzo chcę dzisiaj spać.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA, CHORY , DZIŚ , CHCĘ , SPAĆ </t>
+  </si>
+  <si>
+    <t>Dlaczego ty jesteś dzisiaj bardzo smutny?</t>
   </si>
   <si>
     <t xml:space="preserve">TY,DZIŚ , SMUTNY , DLACZEGO </t>
   </si>
   <si>
-    <t xml:space="preserve">Chory brat nie chce dzisiaj iść do szkoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAT, CHORY, DZISIAJ, SZKOŁA, IŚĆ, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty myślisz, że ja jestem stary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, MYŚLEĆ, JA, STARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro rano idę pracować do nowej szkoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUTRO, RANO, JA, PRACA, NOWA, SZKOŁA, IŚĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty lubisz spać rano w nowym domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, LUBIĆ, RANO, SPAĆ, NOWY, DOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On pije zimną kawę rano przed pracą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, RANO, PRZED, PRACA, KAWA, ZIMNA, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mama myśli, że to jedzenie jest bardzo dobre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAMA, MYŚLEĆ, JEDZENIE, BARDZO, DOBRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wesoły mężczyzna ma dużo pieniędzy na nowy dom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, WESOŁY, PIENIĄDZE, DUŻO, NOWY, DOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My kochamy, kiedy oni są zdrowi i weseli.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, KOCHAĆ, ONI, ZDROWY, WESOŁY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty jesteś zmęczony, więc nie chcesz teraz migać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, ZMĘCZONY, TERAZ, MIGAĆ, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro rano czekam na ważny telefon w pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUTRO, RANO, JA, PRACA, TELEFON, WAŻNY, CZEKAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty wiesz, jak bardzo lubię uczyć się migać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, WIEDZIEĆ, JA, BARDZO, LUBIĆ, UCZYĆ-SIĘ, MIGAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj w nocy kolega pomógł mi w pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, NOC, KOLEGA, MI, POMÓC, PRACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My dzisiaj dużo pracujemy i nie chcemy spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, DZISIAJ, PRACOWAĆ, DUŻO, SPAĆ, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak ty dzisiaj chcesz pracować, kiedy jesteś chory?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, DZISIAJ, CHORY, PRACOWAĆ, JAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy oni uczą się migać z moim bratem?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONI, KIEDY, UCZYĆ-SIĘ, MIGAĆ, MÓJ, BRAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj rano ty byłeś bardzo zmęczony.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, RANO, TY, BARDZO, ZMĘCZONY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja chcę dzisiaj spać w moim nowym domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, DZISIAJ, CHCIEĆ, SPAĆ, MÓJ, NOWY, DOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj jest nowy dzień, więc jestem wesoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, NOWY, DZIEŃ, JA, WESOŁY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stary dziadek nie słyszy, co my mówimy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIADEK, STARY, SŁYSZEĆ, NIE, MY, MÓWIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty i twój przyjaciel macie dużo pieniędzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY+TWÓJ, PRZYJACIEL, RAZEM, PIENIĄDZE, DUŻO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten stary kot nie chce dzisiaj jeść.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOT, STARY, DZISIAJ, JEŚĆ, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego wy nie rozumiecie, co ja mówię?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WY, DLACZEGO, NIE-ROZUMIEĆ, JA, MÓWIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto z was wie, jak dobrze migać?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KTO, Z-WAS, WIEDZIEĆ, MIGAĆ, JAK, DOBRZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile pieniędzy chcesz za ten mały samochód?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMOCHÓD, MAŁY, PIENIĄDZE, ILE, CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Który telefon jest stary, a który bardzo nowy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELEFON, KTÓRY, STARY, KTÓRY, NOWY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja wiem, że ty masz dzisiaj bardzo dobry dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, WIEDZIEĆ, TY, DZISIAJ, DZIEŃ, BARDZO, DOBRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On chce mieć duży dom i dużo pieniędzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, CHCIEĆ, DOM, DUŻY, PIENIĄDZE, DUŻO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, ja wczoraj nie byłem w domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRZEPRASZAM, WCZORAJ, JA, DOM, NIE-BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój przyjaciel dzisiaj bardzo pomógł mi w pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, PRZYJACIEL, DZISIAJ, MI, BARDZO, POMÓC-MI, PRACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ty dzisiaj rano nie byłeś u babci?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, DLACZEGO, DZISIAJ, RANO, U, BABCI, NIE-BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kolega czeka na mnie w starym samochodzie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOLEGA, CZEKAĆ, NA-MNIE, SAMOCHÓD, STARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata mówi, że ten nowy dom jest bardzo duży.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TATA, MÓWIĆ, DOM, NOWY, TEN, BARDZO, DUŻY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mężczyzna i kobieta jedzą dzisiaj w szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, KOBIETA, DZISIAJ, SZKOŁA, JEŚĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My widzimy, że oni są bardzo zmęczeni i chorzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, WIDZIEĆ, ONI, BARDZO, ZMĘCZONY, CHORY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto z was kocha tego małego, smutnego kota?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KTO, Z-WAS, KOCHAĆ, KOT, MAŁY, SMUTNY, TEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My lubimy mieć dużo pieniędzy w nowym roku.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, LUBIĆ, PIENIĄDZE, DUŻO, NOWY, ROK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rano zawsze piję kawę, a w nocy piję wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RANO, ZAWSZE, JA, KAWA, PIĆ, NOC, WODA, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie my dzisiaj idziemy jeść i pić?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDZIE, MY, DZISIAJ, IŚĆ, JEŚĆ, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto wie, dlaczego ona jest dzisiaj bardzo chora?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KTO, WIEDZIEĆ, DLACZEGO, ONA, DZISIAJ, BARDZO, CHORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja nie wiem, dlaczego on nie chce dzisiaj pomóc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, WIEDZIEĆ, NIE, DLACZEGO, ON, DZISIAJ, POMÓC-MI, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, ale ja nie mam dzisiaj dużo pieniędzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRZEPRASZAM, JA, DZISIAJ, PIENIĄDZE, DUŻO, NIE-MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziękuję, że ty rozumiesz, dlaczego jestem smutny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIĘKUJĘ, TY, ROZUMIEĆ, DLACZEGO, JA, SMUTNY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Który telefon jest twój, ten stary czy ten nowy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELEFON, KTÓRY, TWÓJ, TEN, TELEFON, TEN, NOWY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak on chce migać, kiedy nie widzi i nie słyszy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, JAK, MIGAĆ, CHCIEĆ, NIE-WIEDZIEĆ, NIE-SŁYSZEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj wieczorem byłem bardzo zdrowy i wesoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, BARDZO, ZDROWY, WESOŁY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj myślę, co my chcemy jeść jutro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, JA, MYŚLEĆ, MY, JUTRO, JEŚĆ, CO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty myślisz, że ta kobieta ma dużo pieniędzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, MYŚLEĆ, KOBIETA, TA, PIENIĄDZE, DUŻO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja jestem chory i nie chcę dzisiaj jeść.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, CHORY, DZISIAJ, JEŚĆ, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On lubi gorącą herbatę w bardzo zimny dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, LUBIĆ, HERBATA, GORĄCA, DZIEŃ, BARDZO, ZIMNY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zmęczony pies nie chce dzisiaj pić i jeść.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIES, ZMĘCZONY, DZISIAJ, PIĆ, JEŚĆ, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie, on dzisiaj nie ma pieniędzy na nowy telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, ON, PIENIĄDZE, TELEFON, NOWY, NIE-MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, że ja nie chciałem wczoraj pomóc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRZEPRASZAM, WCZORAJ, JA, POMÓC-CI, NIE-CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego my nie mamy dzisiaj gorącej kawy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, DZISIAJ, KAWA, GORĄCA, NIE-MIEĆ, DLACZEGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co ty chcesz robić jutro wieczorem w domu?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, JUTRO, WIECZÓR, DOM, CO-ROBIĆ, CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My jesteśmy dzisiaj weseli, bo mamy dużo czasu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, DZISIAJ, WESOŁY, CZAS, DUŻO, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziękuję za wczoraj, to był bardzo dobry dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIĘKUJĘ, WCZORAJ, DZIEŃ, BARDZO, DOBRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze mam dobry pomysł na nową książkę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAWSZE, JA, POMYSŁ, DOBRY, NOWA, KSIĄŻKA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie mam teraz czasu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERAZ, JA, CZAS, NIE-MIEĆ, MIĘĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jestem zmęczony więc idę spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, ZMĘCZONY, SPAĆ, IŚĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie mam jutro urodzin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUTRO, JA, URODZINY, NIE-MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie jest mój klucz?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, KLUCZ, GDZIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brat ma nowy samochód.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, BRAT, SAMOCHÓD, NOWY, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twoja siostra jest bardzo wesoła.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWÓJ, RODZEŃSTWO, BARDZO, WESOŁA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Babcia i dziadek są w domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BABCIA+DZIADEK, DOM, BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moja siostra ma małego psa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, RODZEŃSTWO, PIES, MAŁY, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj był dobry dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, DZIEŃ, DOBRY, BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj jest poniedziałek.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, PONIEDZIAŁEK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Który dzisiaj jest rok?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, ROK, KTÓRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co robisz rano?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, RANO, CO-ROBIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie jest twój telefon?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWÓJ, TELEFON, GDZIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto ma mój klucz?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KTO, MÓJ, KLUCZ, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Która kobieta to Twoja siostra?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOBIETA, KTÓRA, TWOJA, RODZEŃSTWO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja muszę iść do pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, MUSIEĆ, PRACA, IŚĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy możesz mi pomóc?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, MI, POMÓC-MI, MOŻESZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kolega chce kupić nową książkę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, KOLEGA, CHCIEĆ, KUPIĆ, KSIĄŻKA, NOWA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myślę, że to dobry pomysł.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, MYŚLEĆ, POMYSŁ, DOBRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy wiesz, gdzie jest moja książka?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, WIEDZIEĆ, MOJA, KSIĄŻKA, GDZIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muszę dużo pracować, żeby mieć pieniądze.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, MUSIEĆ, PRACOWAĆ, DUŻO, PIENIĄDZE, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To jest bardzo ważny dzień w pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIEŃ, BARDZO, WAŻNY, PRACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jestem bardzo zmęczony.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, BARDZO, ZMĘCZONY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy jesteś dzisiaj zdrowy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, DZISIAJ, ZDROWY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesteś bardzo dobrym kolegą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, KOLEGA, BARDZO, DOBRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moja babcia jest już stara, ale zdrowa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOJA, BABCIA, STARA, ALE, ZDROWA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chcę kupić ten samochód.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, CHCIEĆ, KUPIĆ, SAMOCHÓD, TEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wy chcecie pić kawę czy herbatę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WY, CHCIEĆ, PIĆ, KAWA, HERBATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja nie mogę teraz iść.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, TERAZ, IŚĆ, NIE-MÓC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój kolega kupił dzisiaj telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, KOLEGA, DZISIAJ, TELEFON, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Widzę, że masz nowy samochód.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, WIDZIEĆ, TY, SAMOCHÓD, NOWY, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten mały pies zawsze czeka na mnie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIES, MAŁY, TEN, ZAWSZE, NA-MNIE, CZEKAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy ten mężczyzna to twój tata?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, TEN, TWÓJ, TATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro będę bardzo wesoły!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUTRO, JA, BARDZO, WESOŁY, BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ten stary mężczyzna zawsze pije zimną herbatę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, STARY, TEN, ZAWSZE, HERBATA, ZIMNA, PIĆ, DLACZEGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy Twój kolega chce kupić ten nowy samochód?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWÓJ, KOLEGA, KIEDY, SAMOCHÓD, NOWY, TEN, KUPIĆ, CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy ty słyszysz, co mówi do ciebie mama?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, SŁYSZEĆ, MAMA, DO-CIEBIE, MÓWIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Który pomysł mojego brata lubisz najbardziej?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POMYSŁ, BRAT, MÓJ, KTÓRY, TY, LUBIĆ, NAJBARDZIEJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego wczoraj w nocy byłeś taki smutny?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, WCZORAJ, NOC, DLACZEGO, SMUTNY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie mogę kupić dobrą i gorącą kawę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, GDZIE, KAWA, DOBRA, GORĄCA, KUPIĆ, MOŻNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W poniedziałek rano często jestem bardzo zmęczony.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PONIEDZIAŁEK, RANO, CZĘSTO, JA, BARDZO, ZMĘCZONY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj dziadek kupił mi bardzo dobrą książkę na urodziny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, DZIADEK, MI, KSIĄŻKA, BARDZO, DOBRA, URODZINY, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Często myślę o tym, co będę robić jutro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZĘSTO, JA, MYŚLEĆ, JUTRO, CO-ROBIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj jest bardzo ważny dzień dla mojego brata.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, DZIEŃ, BARDZO, WAŻNY, MÓJ, BRAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj moja siostra nie chciała iść ze mną do szkoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, MOJA, SIOSTRA, ZE-MNĄ, SZKOŁA, IŚĆ, NIE-CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Często nie pamiętam, co mówiłem wczoraj.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZĘSTO, JA, PAMIĘTAĆ, NIE, WCZORAJ, JA, MÓWIĆ, CO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj nie mogę ci pomóc, bo muszę uczyć się do szkoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, JA, CI, POMÓC, NIE-MÓC, SZKOŁA, UCZYĆ-SIĘ, MUSIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziękuję za to, że wczoraj pomogłeś mi w szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIĘKUJĘ, WCZORAJ, TY, MI, SZKOŁA, POMÓC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze muszę czekać na mojego kolegę po pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAWSZE, JA, KOLEGA, MÓJ, PRACA, PO, CZEKAĆ, MUSIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jestem smutny, że ty nie możesz dzisiaj iść z nami.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, SMUTNY, DZISIAJ, Z-NAMI, IŚĆ, NIE-MÓC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bardzo lubię, kiedy mój brat jest taki wesoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, BARDZO, LUBIĆ, MÓJ, BRAT, WESOŁY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój brat zawsze chce mieć dużo pieniędzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, BRAT, ZAWSZE, PIENIĄDZE, DUŻO, CHCIEĆ, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiem, że to jest bardzo ważny czas dla nas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, WIEDZIEĆ, CZAS, BARDZO, WAŻNY, DLA-NAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ten mężczyzna teraz chce pracować w nocy we wtorek?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, TEN, TERAZ, DLACZEGO, NOC, WTOREK, PRACA, CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile czasu musieliście wczoraj czekać na tatę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WY, WCZORAJ, TATA, ILE, CZAS, CZEKAĆ, MUSIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Która kobieta we wtorek rano już kupił ten samochód?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOBIETA, KTÓRA, WTOREK, RANO, SAMOCHÓD, TEN, JUŻ, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie w środę była mama, kiedy wy byliście już w domu?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ŚRODA, MAMA, GDZIE, BYĆ, WY, DOM, JUŻ, BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Który to był rok, kiedy dziadek kupił ten stary dom?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROK, KTÓRY, TO, DZIADEK, DOM, STARY, TEN, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy pamiętasz, co w nocy mówił twój przyjaciel?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, PAMIĘTAĆ, TWÓJ, PRZYJACIEL, NOC, MÓWIĆ, CO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile pieniędzy chcesz za ten stary telefon?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, CHCIEĆ, ILE, PIENIĄDZE, TELEFON, STARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata miał wczoraj dużo pieniędzy, więc kupił mi książkę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, TATA, PIENIĄDZE, DUŻO, MIEĆ, MI, KSIĄŻKA, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On zawsze rano dużo pracuje, ale dzisiaj jest bardzo chory.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, ZAWSZE, RANO, PRACOWAĆ, DUŻO, ALE, DZISIAJ, BARDZO, CHORY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja dzisiaj nie mam pieniędzy, więc nie mogę kupić tej herbaty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, JA, PIENIĄDZE, NIE-MIEĆ, HERBATA, KUPIĆ, NIE-MÓC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój przyjaciel ma nową pracę, więc dzisiaj jest wesoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, PRZYJACIEL, PRACA, NOWA, MIEĆ, DZISIAJ, WESOŁY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ta nowa szkoła zawsze uczy, dlaczego czas to pieniądz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SZKOŁA, NOWA, ZAWSZE, UCZYĆ, DLACZEGO, CZAS, PIENIĄDZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój dobry przyjaciel zawsze wie, kiedy ja jestem smutny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, PRZYJACIEL, DOBRY, ZAWSZE, WIEDZIEĆ, JA, KIEDY, SMUTNY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata mojego kolegi to bardzo dobry i wesoły mężczyzna.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOLEGA, MÓJ, TATA, MĘŻCZYZNA, BARDZO, DOBRY, WESOŁY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego dziadek nie chce dzisiaj pić ze mną gorącej kawy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIADEK, DLACZEGO, DZISIAJ, ZE-MNĄ, KAWA, GORĄCA, PIĆ, NIE-CHCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego woda z domu zawsze rano jest taka zimna?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WODA, DOM, ZAWSZE, RANO, DLACZEGO, ZIMNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten duży i stary samochód mojego dziadka jest bardzo dobry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMOCHÓD, DUŻY, STARY, MÓJ, DZIADEK, BARDZO, DOBRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro będzie nowy dzień, więc my teraz idziemy już spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUTRO, DZIEŃ, NOWY, TERAZ, MY, SPAĆ, IŚĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy mam w domu dużo czasu, bardzo lubię dużo myśleć.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOM, JA, CZAS, DUŻO, MIEĆ, LUBIĆ, BARDZO, MYŚLEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze dziękuję za to, że mam dzisiaj gdzie spać</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAWSZE, JA, DZIĘKOWAĆ, DZISIAJ, GDZIE, SPAĆ, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bardzo dziękuję za to, że twój brat rano uczy mnie migać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARDZO, DZIĘKUJĘ, TWÓJ, BRAT, RANO, MNIE, MIGAĆ, UCZYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My musimy wiedzieć, dlaczego on wczoraj nie chciał iść.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, MUSIEĆ, WIEDZIEĆ, DLACZEGO, ON, WCZORAJ, IŚĆ, NIE-CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten stary mężczyzna bardzo często pije rano dużo gorącej kawy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, STARY, TEN, CZĘSTO, RANO, KAWA, GORĄCA, DUŻO, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ty zawsze dobrze wiesz, gdzie był mój klucz?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, DLACZEGO, ZAWSZE, DOBRZE, WIEDZIEĆ, MÓJ, KLUCZ, GDZIE, BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kobiety są bardzo zdrowe, bo często dużo pracują w dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOBIETY, BARDZO, ZDROWE, BO, CZĘSTO, DZIEŃ, PRACOWAĆ, DUŻO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myślałem, że ty wiesz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, MYŚLEĆ, TY, WIEDZIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zostań w poniedziałek u mnie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PONIEDZIAŁEK, U-MNIE, ZOSTAŃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupiłem dla ciebie małą książkę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, DLA-CIEBIE, KSIĄŻKA, MAŁA, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mama często chce pić kawę w nocy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAMA, CZĘSTO, NOC, KAWA, PIĆ, CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy zawsze jesteś taki smutny przed pracą?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, ZAWSZE, PRACA, PRZED, SMUTNY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego on nie może pomóc mamie z psem?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, DLACZEGO, MAMA, PIES, POMÓC, NIE-MÓC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj wieczorem kobieta dziękowała temu mężczyźnie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, WIECZÓR, KOBIETA, MĘŻCZYZNA, DZIĘKOWAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uczymy się dzisiaj, a jutro idziemy spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZISIAJ, MY, UCZYĆ-SIĘ, JUTRO, SPAĆ, IŚĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twoja mama często robi mi herbatę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWOJA, MAMA, CZĘSTO, MI, ROBIĆ, HERBATA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten klucz jest dla mojego kolegi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLUCZ, TEN, KOLEGA, MÓJ, DLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie mama kupiła tę gorącą kawę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAMA, GDZIE, KAWA, GORĄCA, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak dużo pieniędzy może mieć ta kobieta?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOBIETA, PIENIĄDZE, ILE, MIEĆ, MOŻE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kocham pić herbatę z babcią i dziadkiem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, KOCHAĆ, HERBATA, PIĆ, BABCIA, DZIADEK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, że nie pamiętałem o twoich urodzinach.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRZEPRASZAM, JA, TWOJE, URODZINY, NIE, PAMIĘTAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy słyszałeś, co mówiła moja siostra?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, SŁYSZEĆ, MOJA, SIOSTRA, CO, MÓWIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Musimy pracować w nocy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, MUSIEĆ, NOC, PRACOWAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Musisz dużo jeść, żeby być zdrowym!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, MUSIEĆ, JEŚĆ, DUŻO, ZDROWY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy widzieliście, jak on miga?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WY, WIDZIEĆ, ON, MIGAĆ, JAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mam pomysł na nowy dom.</t>
+    <t>Chory brat nie chce dzisiaj iść do szkoły.</t>
+  </si>
+  <si>
+    <t>BRAT, CHORY, DZISIAJ, SZKOŁA, IŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>Ty myślisz, że ja jestem stary.</t>
+  </si>
+  <si>
+    <t>TY, MYŚLEĆ, JA, STARY</t>
+  </si>
+  <si>
+    <t>Jutro rano idę pracować do nowej szkoły.</t>
+  </si>
+  <si>
+    <t>JUTRO, RANO, JA, PRACA, NOWA, SZKOŁA, IŚĆ</t>
+  </si>
+  <si>
+    <t>Ty lubisz spać rano w nowym domu.</t>
+  </si>
+  <si>
+    <t>TY, LUBIĆ, RANO, SPAĆ, NOWY, DOM</t>
+  </si>
+  <si>
+    <t>On pije zimną kawę rano przed pracą.</t>
+  </si>
+  <si>
+    <t>ON, RANO, PRZED, PRACA, KAWA, ZIMNA, PIĆ</t>
+  </si>
+  <si>
+    <t>Mama myśli, że to jedzenie jest bardzo dobre.</t>
+  </si>
+  <si>
+    <t>MAMA, MYŚLEĆ, JEDZENIE, BARDZO, DOBRE</t>
+  </si>
+  <si>
+    <t>Wesoły mężczyzna ma dużo pieniędzy na nowy dom.</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, WESOŁY, PIENIĄDZE, DUŻO, NOWY, DOM</t>
+  </si>
+  <si>
+    <t>My kochamy, kiedy oni są zdrowi i weseli.</t>
+  </si>
+  <si>
+    <t>MY, KOCHAĆ, ONI, ZDROWY, WESOŁY</t>
+  </si>
+  <si>
+    <t>Ty jesteś zmęczony, więc nie chcesz teraz migać.</t>
+  </si>
+  <si>
+    <t>TY, ZMĘCZONY, TERAZ, MIGAĆ, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>Jutro rano czekam na ważny telefon w pracy.</t>
+  </si>
+  <si>
+    <t>JUTRO, RANO, JA, PRACA, TELEFON, WAŻNY, CZEKAĆ</t>
+  </si>
+  <si>
+    <t>Ty wiesz, jak bardzo lubię uczyć się migać.</t>
+  </si>
+  <si>
+    <t>TY, WIEDZIEĆ, JA, BARDZO, LUBIĆ, UCZYĆ-SIĘ, MIGAĆ</t>
+  </si>
+  <si>
+    <t>Wczoraj w nocy kolega pomógł mi w pracy.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, NOC, KOLEGA, MI, POMÓC, PRACA</t>
+  </si>
+  <si>
+    <t>My dzisiaj dużo pracujemy i nie chcemy spać.</t>
+  </si>
+  <si>
+    <t>MY, DZISIAJ, PRACOWAĆ, DUŻO, SPAĆ, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>Jak ty dzisiaj chcesz pracować, kiedy jesteś chory?</t>
+  </si>
+  <si>
+    <t>TY, DZISIAJ, CHORY, PRACOWAĆ, JAK</t>
+  </si>
+  <si>
+    <t>Kiedy oni uczą się migać z moim bratem?</t>
+  </si>
+  <si>
+    <t>ONI, KIEDY, UCZYĆ-SIĘ, MIGAĆ, MÓJ, BRAT</t>
+  </si>
+  <si>
+    <t>Wczoraj rano ty byłeś bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, RANO, TY, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
+    <t>Ja chcę dzisiaj spać w moim nowym domu.</t>
+  </si>
+  <si>
+    <t>JA, DZISIAJ, CHCIEĆ, SPAĆ, MÓJ, NOWY, DOM</t>
+  </si>
+  <si>
+    <t>Dzisiaj jest nowy dzień, więc jestem wesoły.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, NOWY, DZIEŃ, JA, WESOŁY</t>
+  </si>
+  <si>
+    <t>Stary dziadek nie słyszy, co my mówimy.</t>
+  </si>
+  <si>
+    <t>DZIADEK, STARY, SŁYSZEĆ, NIE, MY, MÓWIĆ</t>
+  </si>
+  <si>
+    <t>Ty i twój przyjaciel macie dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t>TY+TWÓJ, PRZYJACIEL, RAZEM, PIENIĄDZE, DUŻO</t>
+  </si>
+  <si>
+    <t>Ten stary kot nie chce dzisiaj jeść.</t>
+  </si>
+  <si>
+    <t>KOT, STARY, DZISIAJ, JEŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>Dlaczego wy nie rozumiecie, co ja mówię?</t>
+  </si>
+  <si>
+    <t>WY, DLACZEGO, NIE-ROZUMIEĆ, JA, MÓWIĆ</t>
+  </si>
+  <si>
+    <t>Kto z was wie, jak dobrze migać?</t>
+  </si>
+  <si>
+    <t>KTO, Z-WAS, WIEDZIEĆ, MIGAĆ, JAK, DOBRZE</t>
+  </si>
+  <si>
+    <t>Ile pieniędzy chcesz za ten mały samochód?</t>
+  </si>
+  <si>
+    <t>SAMOCHÓD, MAŁY, PIENIĄDZE, ILE, CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Który telefon jest stary, a który bardzo nowy?</t>
+  </si>
+  <si>
+    <t>TELEFON, KTÓRY, STARY, KTÓRY, NOWY</t>
+  </si>
+  <si>
+    <t>Ja wiem, że ty masz dzisiaj bardzo dobry dzień.</t>
+  </si>
+  <si>
+    <t>JA, WIEDZIEĆ, TY, DZISIAJ, DZIEŃ, BARDZO, DOBRY</t>
+  </si>
+  <si>
+    <t>On chce mieć duży dom i dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t>ON, CHCIEĆ, DOM, DUŻY, PIENIĄDZE, DUŻO</t>
+  </si>
+  <si>
+    <t>Przepraszam, ja wczoraj nie byłem w domu.</t>
+  </si>
+  <si>
+    <t>PRZEPRASZAM, WCZORAJ, JA, DOM, NIE-BYĆ</t>
+  </si>
+  <si>
+    <t>Mój przyjaciel dzisiaj bardzo pomógł mi w pracy.</t>
+  </si>
+  <si>
+    <t>MÓJ, PRZYJACIEL, DZISIAJ, MI, BARDZO, POMÓC-MI, PRACA</t>
+  </si>
+  <si>
+    <t>Dlaczego ty dzisiaj rano nie byłeś u babci?</t>
+  </si>
+  <si>
+    <t>TY, DLACZEGO, DZISIAJ, RANO, U, BABCI, NIE-BYĆ</t>
+  </si>
+  <si>
+    <t>Kolega czeka na mnie w starym samochodzie.</t>
+  </si>
+  <si>
+    <t>KOLEGA, CZEKAĆ, NA-MNIE, SAMOCHÓD, STARY</t>
+  </si>
+  <si>
+    <t>Tata mówi, że ten nowy dom jest bardzo duży.</t>
+  </si>
+  <si>
+    <t>TATA, MÓWIĆ, DOM, NOWY, TEN, BARDZO, DUŻY</t>
+  </si>
+  <si>
+    <t>Mężczyzna i kobieta jedzą dzisiaj w szkole.</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, KOBIETA, DZISIAJ, SZKOŁA, JEŚĆ</t>
+  </si>
+  <si>
+    <t>My widzimy, że oni są bardzo zmęczeni i chorzy.</t>
+  </si>
+  <si>
+    <t>MY, WIDZIEĆ, ONI, BARDZO, ZMĘCZONY, CHORY</t>
+  </si>
+  <si>
+    <t>Kto z was kocha tego małego, smutnego kota?</t>
+  </si>
+  <si>
+    <t>KTO, Z-WAS, KOCHAĆ, KOT, MAŁY, SMUTNY, TEN</t>
+  </si>
+  <si>
+    <t>My lubimy mieć dużo pieniędzy w nowym roku.</t>
+  </si>
+  <si>
+    <t>MY, LUBIĆ, PIENIĄDZE, DUŻO, NOWY, ROK</t>
+  </si>
+  <si>
+    <t>Rano zawsze piję kawę, a w nocy piję wodę.</t>
+  </si>
+  <si>
+    <t>RANO, ZAWSZE, JA, KAWA, PIĆ, NOC, WODA, PIĆ</t>
+  </si>
+  <si>
+    <t>Gdzie my dzisiaj idziemy jeść i pić?</t>
+  </si>
+  <si>
+    <t>GDZIE, MY, DZISIAJ, IŚĆ, JEŚĆ, PIĆ</t>
+  </si>
+  <si>
+    <t>Kto wie, dlaczego ona jest dzisiaj bardzo chora?</t>
+  </si>
+  <si>
+    <t>KTO, WIEDZIEĆ, DLACZEGO, ONA, DZISIAJ, BARDZO, CHORA</t>
+  </si>
+  <si>
+    <t>Ja nie wiem, dlaczego on nie chce dzisiaj pomóc.</t>
+  </si>
+  <si>
+    <t>JA, WIEDZIEĆ, NIE, DLACZEGO, ON, DZISIAJ, POMÓC-MI, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>Przepraszam, ale ja nie mam dzisiaj dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t>PRZEPRASZAM, JA, DZISIAJ, PIENIĄDZE, DUŻO, NIE-MIEĆ</t>
+  </si>
+  <si>
+    <t>Dziękuję, że ty rozumiesz, dlaczego jestem smutny.</t>
+  </si>
+  <si>
+    <t>DZIĘKUJĘ, TY, ROZUMIEĆ, DLACZEGO, JA, SMUTNY</t>
+  </si>
+  <si>
+    <t>Który telefon jest twój, ten stary czy ten nowy?</t>
+  </si>
+  <si>
+    <t>TELEFON, KTÓRY, TWÓJ, TEN, TELEFON, TEN, NOWY</t>
+  </si>
+  <si>
+    <t>Jak on chce migać, kiedy nie widzi i nie słyszy?</t>
+  </si>
+  <si>
+    <t>ON, JAK, MIGAĆ, CHCIEĆ, NIE-WIEDZIEĆ, NIE-SŁYSZEĆ</t>
+  </si>
+  <si>
+    <t>Wczoraj wieczorem byłem bardzo zdrowy i wesoły.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, WIECZÓR, JA, BARDZO, ZDROWY, WESOŁY</t>
+  </si>
+  <si>
+    <t>Dzisiaj myślę, co my chcemy jeść jutro.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, JA, MYŚLEĆ, MY, JUTRO, JEŚĆ, CO</t>
+  </si>
+  <si>
+    <t>Ty myślisz, że ta kobieta ma dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t>TY, MYŚLEĆ, KOBIETA, TA, PIENIĄDZE, DUŻO</t>
+  </si>
+  <si>
+    <t>Ja jestem chory i nie chcę dzisiaj jeść.</t>
+  </si>
+  <si>
+    <t>JA, CHORY, DZISIAJ, JEŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>On lubi gorącą herbatę w bardzo zimny dzień.</t>
+  </si>
+  <si>
+    <t>ON, LUBIĆ, HERBATA, GORĄCA, DZIEŃ, BARDZO, ZIMNY</t>
+  </si>
+  <si>
+    <t>Zmęczony pies nie chce dzisiaj pić i jeść.</t>
+  </si>
+  <si>
+    <t>PIES, ZMĘCZONY, DZISIAJ, PIĆ, JEŚĆ, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>Nie, on dzisiaj nie ma pieniędzy na nowy telefon.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, ON, PIENIĄDZE, TELEFON, NOWY, NIE-MA</t>
+  </si>
+  <si>
+    <t>Przepraszam, że ja nie chciałem wczoraj pomóc.</t>
+  </si>
+  <si>
+    <t>PRZEPRASZAM, WCZORAJ, JA, POMÓC-CI, NIE-CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Dlaczego my nie mamy dzisiaj gorącej kawy?</t>
+  </si>
+  <si>
+    <t>MY, DZISIAJ, KAWA, GORĄCA, NIE-MIEĆ, DLACZEGO</t>
+  </si>
+  <si>
+    <t>Co ty chcesz robić jutro wieczorem w domu?</t>
+  </si>
+  <si>
+    <t>TY, JUTRO, WIECZÓR, DOM, CO-ROBIĆ, CHCIEĆ</t>
+  </si>
+  <si>
+    <t>My jesteśmy dzisiaj weseli, bo mamy dużo czasu.</t>
+  </si>
+  <si>
+    <t>MY, DZISIAJ, WESOŁY, CZAS, DUŻO, MIEĆ</t>
+  </si>
+  <si>
+    <t>Dziękuję za wczoraj, to był bardzo dobry dzień.</t>
+  </si>
+  <si>
+    <t>DZIĘKUJĘ, WCZORAJ, DZIEŃ, BARDZO, DOBRY</t>
+  </si>
+  <si>
+    <t>Zawsze mam dobry pomysł na nową książkę.</t>
+  </si>
+  <si>
+    <t>ZAWSZE, JA, POMYSŁ, DOBRY, NOWA, KSIĄŻKA</t>
+  </si>
+  <si>
+    <t>Nie mam teraz czasu</t>
+  </si>
+  <si>
+    <t>TERAZ, JA, CZAS, NIE-MIEĆ, MIĘĆ</t>
+  </si>
+  <si>
+    <t>Jestem zmęczony więc idę spać.</t>
+  </si>
+  <si>
+    <t>JA, ZMĘCZONY, SPAĆ, IŚĆ</t>
+  </si>
+  <si>
+    <t>Nie mam jutro urodzin.</t>
+  </si>
+  <si>
+    <t>JUTRO, JA, URODZINY, NIE-MIEĆ</t>
+  </si>
+  <si>
+    <t>Gdzie jest mój klucz?</t>
+  </si>
+  <si>
+    <t>MÓJ, KLUCZ, GDZIE</t>
+  </si>
+  <si>
+    <t>Brat ma nowy samochód.</t>
+  </si>
+  <si>
+    <t>MÓJ, BRAT, SAMOCHÓD, NOWY, MIEĆ</t>
+  </si>
+  <si>
+    <t>Twoja siostra jest bardzo wesoła.</t>
+  </si>
+  <si>
+    <t>TWÓJ, RODZEŃSTWO, BARDZO, WESOŁA</t>
+  </si>
+  <si>
+    <t>Babcia i dziadek są w domu.</t>
+  </si>
+  <si>
+    <t>BABCIA+DZIADEK, DOM, BYĆ</t>
+  </si>
+  <si>
+    <t>Moja siostra ma małego psa.</t>
+  </si>
+  <si>
+    <t>MÓJ, RODZEŃSTWO, PIES, MAŁY, MIEĆ</t>
+  </si>
+  <si>
+    <t>Wczoraj był dobry dzień.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, DZIEŃ, DOBRY, BYĆ</t>
+  </si>
+  <si>
+    <t>Dzisiaj jest poniedziałek.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, PONIEDZIAŁEK</t>
+  </si>
+  <si>
+    <t>Który dzisiaj jest rok?</t>
+  </si>
+  <si>
+    <t>DZISIAJ, ROK, KTÓRY</t>
+  </si>
+  <si>
+    <t>Co robisz rano?</t>
+  </si>
+  <si>
+    <t>TY, RANO, CO-ROBIĆ</t>
+  </si>
+  <si>
+    <t>Gdzie jest twój telefon?</t>
+  </si>
+  <si>
+    <t>TWÓJ, TELEFON, GDZIE</t>
+  </si>
+  <si>
+    <t>Kto ma mój klucz?</t>
+  </si>
+  <si>
+    <t>KTO, MÓJ, KLUCZ, MIEĆ</t>
+  </si>
+  <si>
+    <t>Która kobieta to Twoja siostra?</t>
+  </si>
+  <si>
+    <t>KOBIETA, KTÓRA, TWOJA, RODZEŃSTWO</t>
+  </si>
+  <si>
+    <t>Ja muszę iść do pracy.</t>
+  </si>
+  <si>
+    <t>JA, MUSIEĆ, PRACA, IŚĆ</t>
+  </si>
+  <si>
+    <t>Czy możesz mi pomóc?</t>
+  </si>
+  <si>
+    <t>TY, MI, POMÓC-MI, MOŻESZ</t>
+  </si>
+  <si>
+    <t>Kolega chce kupić nową książkę.</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, KOLEGA, CHCIEĆ, KUPIĆ, KSIĄŻKA, NOWA</t>
+  </si>
+  <si>
+    <t>Myślę, że to dobry pomysł.</t>
+  </si>
+  <si>
+    <t>JA, MYŚLEĆ, POMYSŁ, DOBRY</t>
+  </si>
+  <si>
+    <t>Czy wiesz, gdzie jest moja książka?</t>
+  </si>
+  <si>
+    <t>TY, WIEDZIEĆ, MOJA, KSIĄŻKA, GDZIE</t>
+  </si>
+  <si>
+    <t>Muszę dużo pracować, żeby mieć pieniądze.</t>
+  </si>
+  <si>
+    <t>JA, MUSIEĆ, PRACOWAĆ, DUŻO, PIENIĄDZE, MIEĆ</t>
+  </si>
+  <si>
+    <t>To jest bardzo ważny dzień w pracy.</t>
+  </si>
+  <si>
+    <t>DZIEŃ, BARDZO, WAŻNY, PRACA</t>
+  </si>
+  <si>
+    <t>Jestem bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t>JA, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
+    <t>Czy jesteś dzisiaj zdrowy?</t>
+  </si>
+  <si>
+    <t>TY, DZISIAJ, ZDROWY</t>
+  </si>
+  <si>
+    <t>Jesteś bardzo dobrym kolegą.</t>
+  </si>
+  <si>
+    <t>TY, KOLEGA, BARDZO, DOBRY</t>
+  </si>
+  <si>
+    <t>Moja babcia jest już stara, ale zdrowa.</t>
+  </si>
+  <si>
+    <t>MOJA, BABCIA, STARA, ALE, ZDROWA</t>
+  </si>
+  <si>
+    <t>Chcę kupić ten samochód.</t>
+  </si>
+  <si>
+    <t>JA, CHCIEĆ, KUPIĆ, SAMOCHÓD, TEN</t>
+  </si>
+  <si>
+    <t>Wy chcecie pić kawę czy herbatę?</t>
+  </si>
+  <si>
+    <t>WY, CHCIEĆ, PIĆ, KAWA, HERBATA</t>
+  </si>
+  <si>
+    <t>Ja nie mogę teraz iść.</t>
+  </si>
+  <si>
+    <t>JA, TERAZ, IŚĆ, NIE-MÓC</t>
+  </si>
+  <si>
+    <t>Mój kolega kupił dzisiaj telefon.</t>
+  </si>
+  <si>
+    <t>MÓJ, KOLEGA, DZISIAJ, TELEFON, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Widzę, że masz nowy samochód.</t>
+  </si>
+  <si>
+    <t>JA, WIDZIEĆ, TY, SAMOCHÓD, NOWY, MIEĆ</t>
+  </si>
+  <si>
+    <t>Ten mały pies zawsze czeka na mnie.</t>
+  </si>
+  <si>
+    <t>PIES, MAŁY, TEN, ZAWSZE, NA-MNIE, CZEKAĆ</t>
+  </si>
+  <si>
+    <t>Czy ten mężczyzna to twój tata?</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, TEN, TWÓJ, TATA</t>
+  </si>
+  <si>
+    <t>Jutro będę bardzo wesoły!</t>
+  </si>
+  <si>
+    <t>JUTRO, JA, BARDZO, WESOŁY, BYĆ</t>
+  </si>
+  <si>
+    <t>Dlaczego ten stary mężczyzna zawsze pije zimną herbatę?</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, STARY, TEN, ZAWSZE, HERBATA, ZIMNA, PIĆ, DLACZEGO</t>
+  </si>
+  <si>
+    <t>Kiedy Twój kolega chce kupić ten nowy samochód?</t>
+  </si>
+  <si>
+    <t>TWÓJ, KOLEGA, KIEDY, SAMOCHÓD, NOWY, TEN, KUPIĆ, CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Czy ty słyszysz, co mówi do ciebie mama?</t>
+  </si>
+  <si>
+    <t>TY, SŁYSZEĆ, MAMA, DO-CIEBIE, MÓWIĆ</t>
+  </si>
+  <si>
+    <t>Który pomysł mojego brata lubisz najbardziej?</t>
+  </si>
+  <si>
+    <t>POMYSŁ, BRAT, MÓJ, KTÓRY, TY, LUBIĆ, NAJBARDZIEJ</t>
+  </si>
+  <si>
+    <t>Dlaczego wczoraj w nocy byłeś taki smutny?</t>
+  </si>
+  <si>
+    <t>TY, WCZORAJ, NOC, DLACZEGO, SMUTNY</t>
+  </si>
+  <si>
+    <t>Gdzie mogę kupić dobrą i gorącą kawę?</t>
+  </si>
+  <si>
+    <t>JA, GDZIE, KAWA, DOBRA, GORĄCA, KUPIĆ, MOŻNA</t>
+  </si>
+  <si>
+    <t>W poniedziałek rano często jestem bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t>PONIEDZIAŁEK, RANO, CZĘSTO, JA, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
+    <t>Wczoraj dziadek kupił mi bardzo dobrą książkę na urodziny.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, DZIADEK, MI, KSIĄŻKA, BARDZO, DOBRA, URODZINY, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Często myślę o tym, co będę robić jutro.</t>
+  </si>
+  <si>
+    <t>CZĘSTO, JA, MYŚLEĆ, JUTRO, CO-ROBIĆ</t>
+  </si>
+  <si>
+    <t>Dzisiaj jest bardzo ważny dzień dla mojego brata.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, DZIEŃ, BARDZO, WAŻNY, MÓJ, BRAT</t>
+  </si>
+  <si>
+    <t>Wczoraj moja siostra nie chciała iść ze mną do szkoły.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, MOJA, SIOSTRA, ZE-MNĄ, SZKOŁA, IŚĆ, NIE-CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Często nie pamiętam, co mówiłem wczoraj.</t>
+  </si>
+  <si>
+    <t>CZĘSTO, JA, PAMIĘTAĆ, NIE, WCZORAJ, JA, MÓWIĆ, CO</t>
+  </si>
+  <si>
+    <t>Dzisiaj nie mogę ci pomóc, bo muszę uczyć się do szkoły.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, JA, CI, POMÓC, NIE-MÓC, SZKOŁA, UCZYĆ-SIĘ, MUSIEĆ</t>
+  </si>
+  <si>
+    <t>Dziękuję za to, że wczoraj pomogłeś mi w szkole.</t>
+  </si>
+  <si>
+    <t>DZIĘKUJĘ, WCZORAJ, TY, MI, SZKOŁA, POMÓC</t>
+  </si>
+  <si>
+    <t>Zawsze muszę czekać na mojego kolegę po pracy.</t>
+  </si>
+  <si>
+    <t>ZAWSZE, JA, KOLEGA, MÓJ, PRACA, PO, CZEKAĆ, MUSIEĆ</t>
+  </si>
+  <si>
+    <t>Jestem smutny, że ty nie możesz dzisiaj iść z nami.</t>
+  </si>
+  <si>
+    <t>JA, SMUTNY, DZISIAJ, Z-NAMI, IŚĆ, NIE-MÓC</t>
+  </si>
+  <si>
+    <t>Bardzo lubię, kiedy mój brat jest taki wesoły.</t>
+  </si>
+  <si>
+    <t>JA, BARDZO, LUBIĆ, MÓJ, BRAT, WESOŁY</t>
+  </si>
+  <si>
+    <t>Mój brat zawsze chce mieć dużo pieniędzy.</t>
+  </si>
+  <si>
+    <t>MÓJ, BRAT, ZAWSZE, PIENIĄDZE, DUŻO, CHCIEĆ, MIEĆ</t>
+  </si>
+  <si>
+    <t>Wiem, że to jest bardzo ważny czas dla nas.</t>
+  </si>
+  <si>
+    <t>JA, WIEDZIEĆ, CZAS, BARDZO, WAŻNY, DLA-NAS</t>
+  </si>
+  <si>
+    <t>Dlaczego ten mężczyzna teraz chce pracować w nocy we wtorek?</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, TEN, TERAZ, DLACZEGO, NOC, WTOREK, PRACA, CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Ile czasu musieliście wczoraj czekać na tatę?</t>
+  </si>
+  <si>
+    <t>WY, WCZORAJ, TATA, ILE, CZAS, CZEKAĆ, MUSIEĆ</t>
+  </si>
+  <si>
+    <t>Która kobieta we wtorek rano już kupił ten samochód?</t>
+  </si>
+  <si>
+    <t>KOBIETA, KTÓRA, WTOREK, RANO, SAMOCHÓD, TEN, JUŻ, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Gdzie w środę była mama, kiedy wy byliście już w domu?</t>
+  </si>
+  <si>
+    <t>ŚRODA, MAMA, GDZIE, BYĆ, WY, DOM, JUŻ, BYĆ</t>
+  </si>
+  <si>
+    <t>Który to był rok, kiedy dziadek kupił ten stary dom?</t>
+  </si>
+  <si>
+    <t>ROK, KTÓRY, TO, DZIADEK, DOM, STARY, TEN, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Czy pamiętasz, co w nocy mówił twój przyjaciel?</t>
+  </si>
+  <si>
+    <t>TY, PAMIĘTAĆ, TWÓJ, PRZYJACIEL, NOC, MÓWIĆ, CO</t>
+  </si>
+  <si>
+    <t>Ile pieniędzy chcesz za ten stary telefon?</t>
+  </si>
+  <si>
+    <t>TY, CHCIEĆ, ILE, PIENIĄDZE, TELEFON, STARY</t>
+  </si>
+  <si>
+    <t>Tata miał wczoraj dużo pieniędzy, więc kupił mi książkę.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, TATA, PIENIĄDZE, DUŻO, MIEĆ, MI, KSIĄŻKA, KUPIĆ</t>
+  </si>
+  <si>
+    <t>On zawsze rano dużo pracuje, ale dzisiaj jest bardzo chory.</t>
+  </si>
+  <si>
+    <t>ON, ZAWSZE, RANO, PRACOWAĆ, DUŻO, ALE, DZISIAJ, BARDZO, CHORY</t>
+  </si>
+  <si>
+    <t>Ja dzisiaj nie mam pieniędzy, więc nie mogę kupić tej herbaty.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, JA, PIENIĄDZE, NIE-MIEĆ, HERBATA, KUPIĆ, NIE-MÓC</t>
+  </si>
+  <si>
+    <t>Mój przyjaciel ma nową pracę, więc dzisiaj jest wesoły.</t>
+  </si>
+  <si>
+    <t>MÓJ, PRZYJACIEL, PRACA, NOWA, MIEĆ, DZISIAJ, WESOŁY</t>
+  </si>
+  <si>
+    <t>Ta nowa szkoła zawsze uczy, dlaczego czas to pieniądz.</t>
+  </si>
+  <si>
+    <t>SZKOŁA, NOWA, ZAWSZE, UCZYĆ, DLACZEGO, CZAS, PIENIĄDZ</t>
+  </si>
+  <si>
+    <t>Mój dobry przyjaciel zawsze wie, kiedy ja jestem smutny.</t>
+  </si>
+  <si>
+    <t>MÓJ, PRZYJACIEL, DOBRY, ZAWSZE, WIEDZIEĆ, JA, KIEDY, SMUTNY</t>
+  </si>
+  <si>
+    <t>Tata mojego kolegi to bardzo dobry i wesoły mężczyzna.</t>
+  </si>
+  <si>
+    <t>KOLEGA, MÓJ, TATA, MĘŻCZYZNA, BARDZO, DOBRY, WESOŁY</t>
+  </si>
+  <si>
+    <t>Dlaczego dziadek nie chce dzisiaj pić ze mną gorącej kawy?</t>
+  </si>
+  <si>
+    <t>DZIADEK, DLACZEGO, DZISIAJ, ZE-MNĄ, KAWA, GORĄCA, PIĆ, NIE-CHCE</t>
+  </si>
+  <si>
+    <t>Dlaczego woda z domu zawsze rano jest taka zimna?</t>
+  </si>
+  <si>
+    <t>WODA, DOM, ZAWSZE, RANO, DLACZEGO, ZIMNA</t>
+  </si>
+  <si>
+    <t>Ten duży i stary samochód mojego dziadka jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t>SAMOCHÓD, DUŻY, STARY, MÓJ, DZIADEK, BARDZO, DOBRY</t>
+  </si>
+  <si>
+    <t>Jutro będzie nowy dzień, więc my teraz idziemy już spać.</t>
+  </si>
+  <si>
+    <t>JUTRO, DZIEŃ, NOWY, TERAZ, MY, SPAĆ, IŚĆ</t>
+  </si>
+  <si>
+    <t>Kiedy mam w domu dużo czasu, bardzo lubię dużo myśleć.</t>
+  </si>
+  <si>
+    <t>DOM, JA, CZAS, DUŻO, MIEĆ, LUBIĆ, BARDZO, MYŚLEĆ</t>
+  </si>
+  <si>
+    <t>Zawsze dziękuję za to, że mam dzisiaj gdzie spać</t>
+  </si>
+  <si>
+    <t>ZAWSZE, JA, DZIĘKOWAĆ, DZISIAJ, GDZIE, SPAĆ, MIEĆ</t>
+  </si>
+  <si>
+    <t>Bardzo dziękuję za to, że twój brat rano uczy mnie migać.</t>
+  </si>
+  <si>
+    <t>BARDZO, DZIĘKUJĘ, TWÓJ, BRAT, RANO, MNIE, MIGAĆ, UCZYĆ</t>
+  </si>
+  <si>
+    <t>My musimy wiedzieć, dlaczego on wczoraj nie chciał iść.</t>
+  </si>
+  <si>
+    <t>MY, MUSIEĆ, WIEDZIEĆ, DLACZEGO, ON, WCZORAJ, IŚĆ, NIE-CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Ten stary mężczyzna bardzo często pije rano dużo gorącej kawy.</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, STARY, TEN, CZĘSTO, RANO, KAWA, GORĄCA, DUŻO, PIĆ</t>
+  </si>
+  <si>
+    <t>Dlaczego ty zawsze dobrze wiesz, gdzie był mój klucz?</t>
+  </si>
+  <si>
+    <t>TY, DLACZEGO, ZAWSZE, DOBRZE, WIEDZIEĆ, MÓJ, KLUCZ, GDZIE, BYĆ</t>
+  </si>
+  <si>
+    <t>Kobiety są bardzo zdrowe, bo często dużo pracują w dzień.</t>
+  </si>
+  <si>
+    <t>KOBIETY, BARDZO, ZDROWE, BO, CZĘSTO, DZIEŃ, PRACOWAĆ, DUŻO</t>
+  </si>
+  <si>
+    <t>Myślałem, że ty wiesz.</t>
+  </si>
+  <si>
+    <t>JA, MYŚLEĆ, TY, WIEDZIEĆ</t>
+  </si>
+  <si>
+    <t>Zostań w poniedziałek u mnie.</t>
+  </si>
+  <si>
+    <t>PONIEDZIAŁEK, U-MNIE, ZOSTAŃ</t>
+  </si>
+  <si>
+    <t>Kupiłem dla ciebie małą książkę.</t>
+  </si>
+  <si>
+    <t>JA, DLA-CIEBIE, KSIĄŻKA, MAŁA, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Mama często chce pić kawę w nocy.</t>
+  </si>
+  <si>
+    <t>MAMA, CZĘSTO, NOC, KAWA, PIĆ, CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Czy zawsze jesteś taki smutny przed pracą?</t>
+  </si>
+  <si>
+    <t>TY, ZAWSZE, PRACA, PRZED, SMUTNY</t>
+  </si>
+  <si>
+    <t>Dlaczego on nie może pomóc mamie z psem?</t>
+  </si>
+  <si>
+    <t>ON, DLACZEGO, MAMA, PIES, POMÓC, NIE-MÓC</t>
+  </si>
+  <si>
+    <t>Wczoraj wieczorem kobieta dziękowała temu mężczyźnie.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, WIECZÓR, KOBIETA, MĘŻCZYZNA, DZIĘKOWAĆ</t>
+  </si>
+  <si>
+    <t>Uczymy się dzisiaj, a jutro idziemy spać.</t>
+  </si>
+  <si>
+    <t>DZISIAJ, MY, UCZYĆ-SIĘ, JUTRO, SPAĆ, IŚĆ</t>
+  </si>
+  <si>
+    <t>Twoja mama często robi mi herbatę.</t>
+  </si>
+  <si>
+    <t>TWOJA, MAMA, CZĘSTO, MI, ROBIĆ, HERBATA</t>
+  </si>
+  <si>
+    <t>Ten klucz jest dla mojego kolegi.</t>
+  </si>
+  <si>
+    <t>KLUCZ, TEN, KOLEGA, MÓJ, DLA</t>
+  </si>
+  <si>
+    <t>Gdzie mama kupiła tę gorącą kawę?</t>
+  </si>
+  <si>
+    <t>MAMA, GDZIE, KAWA, GORĄCA, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Jak dużo pieniędzy może mieć ta kobieta?</t>
+  </si>
+  <si>
+    <t>KOBIETA, PIENIĄDZE, ILE, MIEĆ, MOŻE</t>
+  </si>
+  <si>
+    <t>Kocham pić herbatę z babcią i dziadkiem.</t>
+  </si>
+  <si>
+    <t>JA, KOCHAĆ, HERBATA, PIĆ, BABCIA, DZIADEK</t>
+  </si>
+  <si>
+    <t>Przepraszam, że nie pamiętałem o twoich urodzinach.</t>
+  </si>
+  <si>
+    <t>PRZEPRASZAM, JA, TWOJE, URODZINY, NIE, PAMIĘTAĆ</t>
+  </si>
+  <si>
+    <t>Czy słyszałeś, co mówiła moja siostra?</t>
+  </si>
+  <si>
+    <t>TY, SŁYSZEĆ, MOJA, SIOSTRA, CO, MÓWIĆ</t>
+  </si>
+  <si>
+    <t>Musimy pracować w nocy.</t>
+  </si>
+  <si>
+    <t>MY, MUSIEĆ, NOC, PRACOWAĆ</t>
+  </si>
+  <si>
+    <t>Musisz dużo jeść, żeby być zdrowym!</t>
+  </si>
+  <si>
+    <t>TY, MUSIEĆ, JEŚĆ, DUŻO, ZDROWY</t>
+  </si>
+  <si>
+    <t>Czy widzieliście, jak on miga?</t>
+  </si>
+  <si>
+    <t>WY, WIDZIEĆ, ON, MIGAĆ, JAK</t>
+  </si>
+  <si>
+    <t>Mam pomysł na nowy dom.</t>
   </si>
   <si>
     <t xml:space="preserve">MIEĆ, POMYSŁ, DOM, NOWY, </t>
   </si>
   <si>
-    <t xml:space="preserve">Brat często ma dużo czasu dla mamy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAT, CZĘSTO, CZAS, DUŻO, DLA, MAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ta kobieta czeka na klucz przy szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOBIETA, SZKOŁA, KLUCZ, CZEKAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze w poniedziałek piję zimną wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAWSZE, PONIEDZIAŁEK, JA, WODA, ZIMNA, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro nie mogę pracować, bo jestem bardzo chory.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUTRO, JA, PRACOWAĆ, NIE-MÓC, JA, BARDZO, CHORY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten rok jest dla nas bardzo dobry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROK, DLA-NAS, BARDZO, DOBRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój przyjaciel zawsze rozumie, co mówię.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, PRZYJACIEL, ZAWSZE, ROZUMIEĆ, JA, MÓWIĆ, CO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj dużo myślałem o tej książce.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCZORAJ, JA, MYŚLEĆ, DUŻO, TA, KSIĄŻKA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego twój tata kupił taki stary samochód?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWÓJ, TATA, DLACZEGO, SAMOCHÓD, STARY, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie lubię, kiedy jesteś bardzo zmęczony po szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, LUBIĆ, NIE, TY, SZKOŁA, BARDZO, ZMĘCZONY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To był mój stary telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, TELEFON, STARY, BYĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziękuję ci za ten dobry dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIĘKUJĘ, CI, DZIEŃ, DOBRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto ma klucz do domu?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KTO, KLUCZ, DOM, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mężczyzna czekał na ciebie przed szkołą wczoraj rano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MĘŻCZYZNA, WCZORAJ, RANO, SZKOŁA, PRZED, NA-CIEBIE, CZEKAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kobiety często piją kawę rano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOBIETY, CZĘSTO, RANO, KAWA, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój mały kot śpi pod starym samochodem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, KOT, MAŁY, SAMOCHÓD, STARY, POD, SPAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W nocy słyszałem psa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC, JA, PIES, SŁYSZEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego w poniedziałek pijesz zimną kawę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, PONIEDZIAŁEK, DLACZEGO, KAWA, ZIMNA, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy masz czas na pracę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, KIEDY, CZAS, PRACA, MIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile książek wczoraj kupiłeś?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, WCZORAJ, KSIĄŻKA, ILE, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My lubimy dużo spać w dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, DZIEŃ, SPAĆ, DUŻO, LUBIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twoja nowa praca jest bardzo ważna.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWOJA, PRACA, NOWA, BARDZO, WAŻNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziadek i babcia zawsze mają dla mnie czas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIADEK+BABCIA, ZAWSZE, MI, CZAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja i mój brat chcemy zostać u kolegi na noc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA+MÓJ, BRAT, KOLEGA, U, NOC, ZOSTAĆ, CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie chcę pić wody z tobą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, Z-TOBĄ, WODA, PIĆ, NIE-CHCIEĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty zawsze wiesz, gdzie są moje pieniądze!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, ZAWSZE, WIEDZIEĆ, MOJE, PIENIĄDZE, GDZIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W poniedziałek rano kupiłem ten samochód dla mamy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PONIEDZIAŁEK, RANO, JA, SAMOCHÓD, TEN, DLA, MAMA, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy ty się uczysz, ja lubię spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, UCZYĆ-SIĘ, KIEDY, JA, SPAĆ, LUBIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze myślę, żeby kupić nowy telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAWSZE, JA, MYŚLEĆ, TELEFON, NOWY, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On czeka w domu na ciebie i na tatę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, DOM, NA-CIEBIE, TATA, CZEKAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy twój pies lubi mojego małego kota?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWÓJ, PIES, MÓJ, KOT, MAŁY, LUBIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ta zimna noc była dla mnie bardzo smutna.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC, ZIMNA, DLA-MNIE, SMUTNA, BARDZO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Widzę cię dzisiaj przed moją pracą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA, DZISIAJ, CIĘ, WIDZIEĆ, PRACA, MOJA, PRZED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czego ty wczoraj nie rozumiałeś?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, WCZORAJ, CO, ROZUMIEĆ, NIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy możemy iść do ciebie wieczorem?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MY, WIECZÓR, DO-CIEBIE, MOŻNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziadek zawsze pije gorącą herbatę w nocy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZIADEK, ZAWSZE, NOC, HERBATA, GORĄCA, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto ci kupił tego psa i kota?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KTO, CI, PIES, TEN, KOT, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam cię za wczoraj.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRZEPRASZAM, CI, WCZORAJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ty zawsze dużo mówisz?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY, DLACZEGO, ZAWSZE, MÓWIĆ, DUŻO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mam bardzo dobry pomysł na jutro.</t>
+    <t>Brat często ma dużo czasu dla mamy.</t>
+  </si>
+  <si>
+    <t>BRAT, CZĘSTO, CZAS, DUŻO, DLA, MAMA</t>
+  </si>
+  <si>
+    <t>Ta kobieta czeka na klucz przy szkole.</t>
+  </si>
+  <si>
+    <t>KOBIETA, SZKOŁA, KLUCZ, CZEKAĆ</t>
+  </si>
+  <si>
+    <t>Zawsze w poniedziałek piję zimną wodę.</t>
+  </si>
+  <si>
+    <t>ZAWSZE, PONIEDZIAŁEK, JA, WODA, ZIMNA, PIĆ</t>
+  </si>
+  <si>
+    <t>Jutro nie mogę pracować, bo jestem bardzo chory.</t>
+  </si>
+  <si>
+    <t>JUTRO, JA, PRACOWAĆ, NIE-MÓC, JA, BARDZO, CHORY</t>
+  </si>
+  <si>
+    <t>Ten rok jest dla nas bardzo dobry.</t>
+  </si>
+  <si>
+    <t>ROK, DLA-NAS, BARDZO, DOBRY</t>
+  </si>
+  <si>
+    <t>Mój przyjaciel zawsze rozumie, co mówię.</t>
+  </si>
+  <si>
+    <t>MÓJ, PRZYJACIEL, ZAWSZE, ROZUMIEĆ, JA, MÓWIĆ, CO</t>
+  </si>
+  <si>
+    <t>Wczoraj dużo myślałem o tej książce.</t>
+  </si>
+  <si>
+    <t>WCZORAJ, JA, MYŚLEĆ, DUŻO, TA, KSIĄŻKA</t>
+  </si>
+  <si>
+    <t>Dlaczego twój tata kupił taki stary samochód?</t>
+  </si>
+  <si>
+    <t>TWÓJ, TATA, DLACZEGO, SAMOCHÓD, STARY, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Nie lubię, kiedy jesteś bardzo zmęczony po szkole.</t>
+  </si>
+  <si>
+    <t>JA, LUBIĆ, NIE, TY, SZKOŁA, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
+    <t>To był mój stary telefon.</t>
+  </si>
+  <si>
+    <t>MÓJ, TELEFON, STARY, BYĆ</t>
+  </si>
+  <si>
+    <t>Dziękuję ci za ten dobry dzień.</t>
+  </si>
+  <si>
+    <t>DZIĘKUJĘ, CI, DZIEŃ, DOBRY</t>
+  </si>
+  <si>
+    <t>Kto ma klucz do domu?</t>
+  </si>
+  <si>
+    <t>KTO, KLUCZ, DOM, MIEĆ</t>
+  </si>
+  <si>
+    <t>Mężczyzna czekał na ciebie przed szkołą wczoraj rano.</t>
+  </si>
+  <si>
+    <t>MĘŻCZYZNA, WCZORAJ, RANO, SZKOŁA, PRZED, NA-CIEBIE, CZEKAĆ</t>
+  </si>
+  <si>
+    <t>Kobiety często piją kawę rano.</t>
+  </si>
+  <si>
+    <t>KOBIETY, CZĘSTO, RANO, KAWA, PIĆ</t>
+  </si>
+  <si>
+    <t>Mój mały kot śpi pod starym samochodem.</t>
+  </si>
+  <si>
+    <t>MÓJ, KOT, MAŁY, SAMOCHÓD, STARY, POD, SPAĆ</t>
+  </si>
+  <si>
+    <t>W nocy słyszałem psa.</t>
+  </si>
+  <si>
+    <t>NOC, JA, PIES, SŁYSZEĆ</t>
+  </si>
+  <si>
+    <t>Dlaczego w poniedziałek pijesz zimną kawę?</t>
+  </si>
+  <si>
+    <t>TY, PONIEDZIAŁEK, DLACZEGO, KAWA, ZIMNA, PIĆ</t>
+  </si>
+  <si>
+    <t>Kiedy masz czas na pracę?</t>
+  </si>
+  <si>
+    <t>TY, KIEDY, CZAS, PRACA, MIEĆ</t>
+  </si>
+  <si>
+    <t>Ile książek wczoraj kupiłeś?</t>
+  </si>
+  <si>
+    <t>TY, WCZORAJ, KSIĄŻKA, ILE, KUPIĆ</t>
+  </si>
+  <si>
+    <t>My lubimy dużo spać w dzień.</t>
+  </si>
+  <si>
+    <t>MY, DZIEŃ, SPAĆ, DUŻO, LUBIĆ</t>
+  </si>
+  <si>
+    <t>Twoja nowa praca jest bardzo ważna.</t>
+  </si>
+  <si>
+    <t>TWOJA, PRACA, NOWA, BARDZO, WAŻNA</t>
+  </si>
+  <si>
+    <t>Dziadek i babcia zawsze mają dla mnie czas.</t>
+  </si>
+  <si>
+    <t>DZIADEK+BABCIA, ZAWSZE, MI, CZAS</t>
+  </si>
+  <si>
+    <t>Ja i mój brat chcemy zostać u kolegi na noc.</t>
+  </si>
+  <si>
+    <t>JA+MÓJ, BRAT, KOLEGA, U, NOC, ZOSTAĆ, CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Nie chcę pić wody z tobą.</t>
+  </si>
+  <si>
+    <t>JA, Z-TOBĄ, WODA, PIĆ, NIE-CHCIEĆ</t>
+  </si>
+  <si>
+    <t>Ty zawsze wiesz, gdzie są moje pieniądze!</t>
+  </si>
+  <si>
+    <t>TY, ZAWSZE, WIEDZIEĆ, MOJE, PIENIĄDZE, GDZIE</t>
+  </si>
+  <si>
+    <t>W poniedziałek rano kupiłem ten samochód dla mamy.</t>
+  </si>
+  <si>
+    <t>PONIEDZIAŁEK, RANO, JA, SAMOCHÓD, TEN, DLA, MAMA, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Kiedy ty się uczysz, ja lubię spać.</t>
+  </si>
+  <si>
+    <t>TY, UCZYĆ-SIĘ, KIEDY, JA, SPAĆ, LUBIĆ</t>
+  </si>
+  <si>
+    <t>Zawsze myślę, żeby kupić nowy telefon.</t>
+  </si>
+  <si>
+    <t>ZAWSZE, JA, MYŚLEĆ, TELEFON, NOWY, KUPIĆ</t>
+  </si>
+  <si>
+    <t>On czeka w domu na ciebie i na tatę.</t>
+  </si>
+  <si>
+    <t>ON, DOM, NA-CIEBIE, TATA, CZEKAĆ</t>
+  </si>
+  <si>
+    <t>Czy twój pies lubi mojego małego kota?</t>
+  </si>
+  <si>
+    <t>TWÓJ, PIES, MÓJ, KOT, MAŁY, LUBIĆ</t>
+  </si>
+  <si>
+    <t>Ta zimna noc była dla mnie bardzo smutna.</t>
+  </si>
+  <si>
+    <t>NOC, ZIMNA, DLA-MNIE, SMUTNA, BARDZO</t>
+  </si>
+  <si>
+    <t>Widzę cię dzisiaj przed moją pracą.</t>
+  </si>
+  <si>
+    <t>JA, DZISIAJ, CIĘ, WIDZIEĆ, PRACA, MOJA, PRZED</t>
+  </si>
+  <si>
+    <t>Czego ty wczoraj nie rozumiałeś?</t>
+  </si>
+  <si>
+    <t>TY, WCZORAJ, CO, ROZUMIEĆ, NIE</t>
+  </si>
+  <si>
+    <t>Czy możemy iść do ciebie wieczorem?</t>
+  </si>
+  <si>
+    <t>MY, WIECZÓR, DO-CIEBIE, MOŻNA</t>
+  </si>
+  <si>
+    <t>Dziadek zawsze pije gorącą herbatę w nocy.</t>
+  </si>
+  <si>
+    <t>DZIADEK, ZAWSZE, NOC, HERBATA, GORĄCA, PIĆ</t>
+  </si>
+  <si>
+    <t>Kto ci kupił tego psa i kota?</t>
+  </si>
+  <si>
+    <t>KTO, CI, PIES, TEN, KOT, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Przepraszam cię za wczoraj.</t>
+  </si>
+  <si>
+    <t>PRZEPRASZAM, CI, WCZORAJ</t>
+  </si>
+  <si>
+    <t>Dlaczego ty zawsze dużo mówisz?</t>
+  </si>
+  <si>
+    <t>TY, DLACZEGO, ZAWSZE, MÓWIĆ, DUŻO</t>
+  </si>
+  <si>
+    <t>Mam bardzo dobry pomysł na jutro.</t>
   </si>
   <si>
     <t xml:space="preserve">JA, MIEĆ, POMYSŁ, BARDZO, DOBRY, JUTRO </t>
   </si>
   <si>
-    <t xml:space="preserve">W szkole musimy uczyć się migać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SZKOŁA, MY, MUSIEĆ, UCZYĆ-SIĘ, MIGAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twój kolega wczoraj pił ze mną kawę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TWÓJ, KOLEGA, WCZORAJ, ZE-MNĄ, KAWA, PIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie są moje pieniądze z poniedziałku?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOJE, PIENIĄDZE, PONIEDZIAŁEK, GDZIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój tata bardzo kocha mojego brata.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MÓJ, TATA, BARDZO, KOCHAĆ, MÓJ, BRAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kobieta przed szkołą kupiła herbatę i kawę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOBIETA, SZKOŁA, PRZED, HERBATA, I, KAWA, KUPIĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty masz czas, żeby ze mną mówić?</t>
+    <t>W szkole musimy uczyć się migać.</t>
+  </si>
+  <si>
+    <t>SZKOŁA, MY, MUSIEĆ, UCZYĆ-SIĘ, MIGAĆ</t>
+  </si>
+  <si>
+    <t>Twój kolega wczoraj pił ze mną kawę.</t>
+  </si>
+  <si>
+    <t>TWÓJ, KOLEGA, WCZORAJ, ZE-MNĄ, KAWA, PIĆ</t>
+  </si>
+  <si>
+    <t>Gdzie są moje pieniądze z poniedziałku?</t>
+  </si>
+  <si>
+    <t>MOJE, PIENIĄDZE, PONIEDZIAŁEK, GDZIE</t>
+  </si>
+  <si>
+    <t>Mój tata bardzo kocha mojego brata.</t>
+  </si>
+  <si>
+    <t>MÓJ, TATA, BARDZO, KOCHAĆ, MÓJ, BRAT</t>
+  </si>
+  <si>
+    <t>Kobieta przed szkołą kupiła herbatę i kawę.</t>
+  </si>
+  <si>
+    <t>KOBIETA, SZKOŁA, PRZED, HERBATA, I, KAWA, KUPIĆ</t>
+  </si>
+  <si>
+    <t>Ty masz czas, żeby ze mną mówić?</t>
   </si>
   <si>
     <t xml:space="preserve">TY, MIEĆ, CZAS, MÓWIĆ, ZE-MNĄ </t>
   </si>
   <si>
-    <t xml:space="preserve">Jutro zostaniemy w starym domu dziadka.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUTRO, MY, DOM, STARY, DZIADEK, ZOSTAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile czasu masz dzisiaj na tę książkę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy to jest ten nowy telefon z mojej pracy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wesoły mężczyzna kupił małego psa i kota.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie pamiętam, kiedy ty pracowałeś w poniedziałek.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myślę, że on będzie bardzo chory jutro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To jest bardzo wesoły dzień dla nas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego jesteś dla mnie taki zimny?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zostałem przed szkołą, bo czekałem na babcię.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chcę być dobrym przyjacielem dla ciebie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy słyszycie tego kota przed szkołą?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja wczoraj w nocy myślałem o mojej pracy.</t>
+    <t>Jutro zostaniemy w starym domu dziadka.</t>
+  </si>
+  <si>
+    <t>JUTRO, MY, DOM, STARY, DZIADEK, ZOSTAĆ</t>
+  </si>
+  <si>
+    <t>Ile czasu masz dzisiaj na tę książkę?</t>
+  </si>
+  <si>
+    <t>Czy to jest ten nowy telefon z mojej pracy?</t>
+  </si>
+  <si>
+    <t>Wesoły mężczyzna kupił małego psa i kota.</t>
+  </si>
+  <si>
+    <t>Nie pamiętam, kiedy ty pracowałeś w poniedziałek.</t>
+  </si>
+  <si>
+    <t>Myślę, że on będzie bardzo chory jutro.</t>
+  </si>
+  <si>
+    <t>To jest bardzo wesoły dzień dla nas.</t>
+  </si>
+  <si>
+    <t>Dlaczego jesteś dla mnie taki zimny?</t>
+  </si>
+  <si>
+    <t>Zostałem przed szkołą, bo czekałem na babcię.</t>
+  </si>
+  <si>
+    <t>Chcę być dobrym przyjacielem dla ciebie.</t>
+  </si>
+  <si>
+    <t>Czy słyszycie tego kota przed szkołą?</t>
+  </si>
+  <si>
+    <t>Ja wczoraj w nocy myślałem o mojej pracy.</t>
   </si>
   <si>
     <t xml:space="preserve">Przepraszam, mój ważny klucz już został u taty w samochodzie. </t>
   </si>
   <si>
-    <t xml:space="preserve">Kiedy ty idziesz do domu, ja idę spać.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uczę się migać w poniedziałek po szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupiłem dla ciebie dużo książek na urodziny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze wesoła siostra już bardzo lubi pracować rano w środę i w czwartek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy wiesz, jak kupić ten duży dom?</t>
+    <t>Kiedy ty idziesz do domu, ja idę spać.</t>
+  </si>
+  <si>
+    <t>Uczę się migać w poniedziałek po szkole.</t>
+  </si>
+  <si>
+    <t>Kupiłem dla ciebie dużo książek na urodziny.</t>
+  </si>
+  <si>
+    <t>Zawsze wesoła siostra już bardzo lubi pracować rano w środę i w czwartek</t>
+  </si>
+  <si>
+    <t>Czy wiesz, jak kupić ten duży dom?</t>
   </si>
   <si>
     <t xml:space="preserve">Przepraszam, gdzie jest woda dla małego psa, który jest chory? </t>
   </si>
   <si>
-    <t xml:space="preserve">Wczoraj wieczorem widziałam mojego starego kolegę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niech ten pies zostanie w domu z kotem!</t>
+    <t>Wczoraj wieczorem widziałam mojego starego kolegę.</t>
+  </si>
+  <si>
+    <t>Niech ten pies zostanie w domu z kotem!</t>
   </si>
   <si>
     <t xml:space="preserve">Czy wy rozumiecie, że jutro będzie bardzo zimny i smutny dzień dla mamy? </t>
@@ -1591,115 +1605,115 @@
     <t xml:space="preserve">Piję teraz herbatę w tę środę, bo często w taki gorący dzień musimy dużo pić. </t>
   </si>
   <si>
-    <t xml:space="preserve">Czy masz dla mnie nowy pomysł na urodziny?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Praca w noc nie jest dobra dla mnie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Babcia zawsze kocha mojego małego brata.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty nie masz dla mnie czasu, żeby mówić.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ona wczoraj bardzo dużo jadła?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój telefon jest mały, a twój samochód jest duży.</t>
+    <t>Czy masz dla mnie nowy pomysł na urodziny?</t>
+  </si>
+  <si>
+    <t>Praca w noc nie jest dobra dla mnie.</t>
+  </si>
+  <si>
+    <t>Babcia zawsze kocha mojego małego brata.</t>
+  </si>
+  <si>
+    <t>Ty nie masz dla mnie czasu, żeby mówić.</t>
+  </si>
+  <si>
+    <t>Dlaczego ona wczoraj bardzo dużo jadła?</t>
+  </si>
+  <si>
+    <t>Mój telefon jest mały, a twój samochód jest duży.</t>
   </si>
   <si>
     <t xml:space="preserve">Jutro z tobą idę po herbatę, bo to taki zdrowy pomysł na ten zimny wtorek. </t>
   </si>
   <si>
-    <t xml:space="preserve">Przepraszam, że nie mogę ci dzisiaj pomóc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Będę ci dziękować, że on chce dzisiaj być.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamiętaj, żeby jeść dużo i pić dużo wody.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamiętam, żeby zawsze dziękować za dobrą pracę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten rok to czas, kiedy już bardzo dużo pracujemy w domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brat ma ten nowy telefon już rok i jest bardzo dobry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Już od roku zawsze rano lubię pić gorącą wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy on wczoraj kupił tego małego kota?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy wiesz, dlaczego twoja siostra jest dzisiaj smutna?</t>
+    <t>Przepraszam, że nie mogę ci dzisiaj pomóc.</t>
+  </si>
+  <si>
+    <t>Będę ci dziękować, że on chce dzisiaj być.</t>
+  </si>
+  <si>
+    <t>Pamiętaj, żeby jeść dużo i pić dużo wody.</t>
+  </si>
+  <si>
+    <t>Pamiętam, żeby zawsze dziękować za dobrą pracę.</t>
+  </si>
+  <si>
+    <t>Ten rok to czas, kiedy już bardzo dużo pracujemy w domu.</t>
+  </si>
+  <si>
+    <t>Brat ma ten nowy telefon już rok i jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t>Już od roku zawsze rano lubię pić gorącą wodę.</t>
+  </si>
+  <si>
+    <t>Kiedy on wczoraj kupił tego małego kota?</t>
+  </si>
+  <si>
+    <t>Czy wiesz, dlaczego twoja siostra jest dzisiaj smutna?</t>
   </si>
   <si>
     <t xml:space="preserve">Dziadek, który jest chory, już rok nie był w szkole </t>
   </si>
   <si>
-    <t xml:space="preserve">W poniedziałek wieczorem będę na ciebie czekać przed domem.</t>
+    <t>W poniedziałek wieczorem będę na ciebie czekać przed domem.</t>
   </si>
   <si>
     <t xml:space="preserve">Ty nie rozumiesz, że ja jestem zmęczony i muszę teraz dużo spać. </t>
   </si>
   <si>
-    <t xml:space="preserve">Kobiety lubią gorącą herbatę, a mężczyźni zimną wodę.</t>
+    <t>Kobiety lubią gorącą herbatę, a mężczyźni zimną wodę.</t>
   </si>
   <si>
     <t xml:space="preserve">Wczoraj wieczorem kupiłem nową książkę dla chorej mamy na jej urodziny. </t>
   </si>
   <si>
-    <t xml:space="preserve">Mój kolega z pracy ma dzisiaj urodziny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziękuję, że pomogłeś mojemu psu wczoraj.</t>
+    <t>Mój kolega z pracy ma dzisiaj urodziny.</t>
+  </si>
+  <si>
+    <t>Dziękuję, że pomogłeś mojemu psu wczoraj.</t>
   </si>
   <si>
     <t xml:space="preserve">Ile w roku się to robi, żeby być zdrowym? </t>
   </si>
   <si>
-    <t xml:space="preserve">Ja nie mam teraz pieniędzy na tę dużą książkę dla siostry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ten mężczyzna z psem idzie do szkoły?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W nocy kot mojego brata bardzo często pije wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie pamiętam, o czym ty do mnie mówiłeś rano.</t>
+    <t>Ja nie mam teraz pieniędzy na tę dużą książkę dla siostry</t>
+  </si>
+  <si>
+    <t>Dlaczego ten mężczyzna z psem idzie do szkoły?</t>
+  </si>
+  <si>
+    <t>W nocy kot mojego brata bardzo często pije wodę.</t>
+  </si>
+  <si>
+    <t>Nie pamiętam, o czym ty do mnie mówiłeś rano.</t>
   </si>
   <si>
     <t xml:space="preserve">Zostań u nas na herbatę we wtorek </t>
   </si>
   <si>
-    <t xml:space="preserve">Przepraszam, że wczoraj rano nie było mnie w domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy twój mały brat lubi się uczyć?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamiętaj, żeby rano kupić gorącą kawę dla dziadka.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My bardzo często myślimy o twoim nowym pomyśle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ty zawsze musisz być taki zmęczony?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Widziałem wczoraj twoją babcię w starym samochodzie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chcę wiedzieć, kto ma ten klucz od domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesteś bardzo zdrowy, bo nie jesz w nocy.</t>
+    <t>Przepraszam, że wczoraj rano nie było mnie w domu.</t>
+  </si>
+  <si>
+    <t>Czy twój mały brat lubi się uczyć?</t>
+  </si>
+  <si>
+    <t>Pamiętaj, żeby rano kupić gorącą kawę dla dziadka.</t>
+  </si>
+  <si>
+    <t>My bardzo często myślimy o twoim nowym pomyśle.</t>
+  </si>
+  <si>
+    <t>Dlaczego ty zawsze musisz być taki zmęczony?</t>
+  </si>
+  <si>
+    <t>Widziałem wczoraj twoją babcię w starym samochodzie.</t>
+  </si>
+  <si>
+    <t>Chcę wiedzieć, kto ma ten klucz od domu.</t>
+  </si>
+  <si>
+    <t>Jesteś bardzo zdrowy, bo nie jesz w nocy.</t>
   </si>
   <si>
     <t xml:space="preserve">W środę i w czwartek to jest ważny klucz. </t>
@@ -1708,433 +1722,433 @@
     <t xml:space="preserve">Przepraszam, czy wy w środę to robicie? </t>
   </si>
   <si>
-    <t xml:space="preserve">Czekam, żeby z tobą iść na kawę.</t>
+    <t>Czekam, żeby z tobą iść na kawę.</t>
   </si>
   <si>
     <t xml:space="preserve">Czy zdrowym jest robić to z roku na rok, i ile? </t>
   </si>
   <si>
-    <t xml:space="preserve">Uczę się dużo, żeby móc pracować w szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy kupisz ten stary dom dla dziadka?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woda w noc była bardzo zimna dla mojego psa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze w poniedziałek rano jestem bardzo wesoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kocham moją mamę i mojego tatę za ten nowy dom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twój pies zawsze chce dużo jeść rano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mężczyzna czekał pod domem, żeby mi pomóc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty dobrze wiesz, jak kupić taki samochód bez pieniędzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj w nocy myślałem, żeby kupić dużego kota.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Babcia robiła gorącą herbatę dla ciebie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie jest ten mały kot mojej siostry?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro rano idę do szkoły z moim nowym telefonem.</t>
+    <t>Uczę się dużo, żeby móc pracować w szkole.</t>
+  </si>
+  <si>
+    <t>Kiedy kupisz ten stary dom dla dziadka?</t>
+  </si>
+  <si>
+    <t>Woda w noc była bardzo zimna dla mojego psa.</t>
+  </si>
+  <si>
+    <t>Zawsze w poniedziałek rano jestem bardzo wesoły.</t>
+  </si>
+  <si>
+    <t>Kocham moją mamę i mojego tatę za ten nowy dom.</t>
+  </si>
+  <si>
+    <t>Twój pies zawsze chce dużo jeść rano.</t>
+  </si>
+  <si>
+    <t>Mężczyzna czekał pod domem, żeby mi pomóc.</t>
+  </si>
+  <si>
+    <t>Ty dobrze wiesz, jak kupić taki samochód bez pieniędzy.</t>
+  </si>
+  <si>
+    <t>Wczoraj w nocy myślałem, żeby kupić dużego kota.</t>
+  </si>
+  <si>
+    <t>Babcia robiła gorącą herbatę dla ciebie.</t>
+  </si>
+  <si>
+    <t>Gdzie jest ten mały kot mojej siostry?</t>
+  </si>
+  <si>
+    <t>Jutro rano idę do szkoły z moim nowym telefonem.</t>
   </si>
   <si>
     <t xml:space="preserve">Przepraszam, ile mogę to robić w czwartek? </t>
   </si>
   <si>
-    <t xml:space="preserve">Praca w domu jest dla mnie bardzo dobra.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze pamiętam o twoich urodzinach w poniedziałek.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chcę kupić dla ciebie książkę, żebyś nie był smutny.</t>
+    <t>Praca w domu jest dla mnie bardzo dobra.</t>
+  </si>
+  <si>
+    <t>Zawsze pamiętam o twoich urodzinach w poniedziałek.</t>
+  </si>
+  <si>
+    <t>Chcę kupić dla ciebie książkę, żebyś nie był smutny.</t>
   </si>
   <si>
     <t xml:space="preserve">Czy wy rozumiecie, że to był ważny rok? </t>
   </si>
   <si>
-    <t xml:space="preserve">Ja i ty musimy dużo pracować, żeby mieć na dom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto wczoraj rano kupił ten stary samochód taty?</t>
+    <t>Ja i ty musimy dużo pracować, żeby mieć na dom.</t>
+  </si>
+  <si>
+    <t>Kto wczoraj rano kupił ten stary samochód taty?</t>
   </si>
   <si>
     <t xml:space="preserve">Ile to się robi, rok? </t>
   </si>
   <si>
-    <t xml:space="preserve">Dlaczego jesteś bardzo zimny w ten gorący dzień?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kobieta z małym psem idzie rano do pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, że nie mam czasu dla ich siostry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Często słyszę tego psa przed moją pracą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj wieczorem byłem u kolegi w starym domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twój nowy pomysł na pracę jest bardzo dobry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy idziemy na dużą kawę z kolegą?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niech mój przyjaciel czeka na mnie przed szkołą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze myślę o tym, żeby być wesołym i zdrowym.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My chcemy kupić ten stary samochód w poniedziałek.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My jesteśmy dobrymi przyjacielami od wczoraj.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro będę chory, bo nie śpię w nocy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziękuję ci za tę książkę o starym domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie jest klucz do tego małego samochodu?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja bardzo lubię, kiedy pijesz ze mną kawę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty wczoraj mówiłeś, że nie masz pieniędzy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jego tata kupił telefon dla mojej nowej szkoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj rano widziałem, jak ten mężczyzna miga.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Babcia i dziadek piją gorącą wodę rano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jej kot bardzo często śpi na tej dużej książce.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze pamiętam, żeby pić wodę przed pracą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro wieczorem idę do ciebie bez psa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty nie rozumiesz, jak bardzo jestem zmęczony w pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie my wczoraj kupiliśmy tę gorącą kawę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto chory idzie rano do szkoły?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ich brat ma urodziny w poniedziałek wieczorem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile kawy dzisiaj rano piła twoja mama?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czekam na ciebie, żeby iść do starych przyjaciół.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy ty widziałeś rano mojego małego brata?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj bardzo chcę uczyć się z twoją siostrą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mężczyzna bez samochodu idzie do pracy w nocy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ta książka, którą ma ta kobieta, jest dla ciebie taka ważna?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten dzień był dla mojego przyjaciela bardzo smutny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty zawsze myślisz, że ich dom jest twój.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dziadek nie słyszy, co babcia do niego mówi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myślę, że twój pomysł na urodziny jest wesoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zostań u dziadka na noc, bo jesteś zmęczony.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czekam na ten ważny dla mnie czas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie mam klucza, więc muszę czekać na tatę przed domem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy wiesz, gdzie brat mojego kolegi kupił telefon?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kocham ten czas, kiedy rano we wtorek piję kawę</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kup małego kota, nie tego starego psa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jej mały pies wczoraj w nocy jadł książkę taty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamiętam, że mam rano iść do szkoły z jego małym przyjacielem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze myślę o mojej starej szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jej brat kupił wczoraj dla mnie nowy telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten wesoły pies często śpi u mnie w domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro rano będę pracować z twoim przyjacielem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie mam dzisiaj czasu na kawę z tobą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy wy już wiecie, co on chce robić w ten czwartek?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego myślisz, że jestem bardzo smutny?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy kupiłeś ten duży dom dla dziadka?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój stary samochód nie chce rano pracować.</t>
+    <t>Dlaczego jesteś bardzo zimny w ten gorący dzień?</t>
+  </si>
+  <si>
+    <t>Kobieta z małym psem idzie rano do pracy.</t>
+  </si>
+  <si>
+    <t>Przepraszam, że nie mam czasu dla ich siostry.</t>
+  </si>
+  <si>
+    <t>Często słyszę tego psa przed moją pracą.</t>
+  </si>
+  <si>
+    <t>Wczoraj wieczorem byłem u kolegi w starym domu.</t>
+  </si>
+  <si>
+    <t>Twój nowy pomysł na pracę jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t>Kiedy idziemy na dużą kawę z kolegą?</t>
+  </si>
+  <si>
+    <t>Niech mój przyjaciel czeka na mnie przed szkołą.</t>
+  </si>
+  <si>
+    <t>Zawsze myślę o tym, żeby być wesołym i zdrowym.</t>
+  </si>
+  <si>
+    <t>My chcemy kupić ten stary samochód w poniedziałek.</t>
+  </si>
+  <si>
+    <t>My jesteśmy dobrymi przyjacielami od wczoraj.</t>
+  </si>
+  <si>
+    <t>Jutro będę chory, bo nie śpię w nocy.</t>
+  </si>
+  <si>
+    <t>Dziękuję ci za tę książkę o starym domu.</t>
+  </si>
+  <si>
+    <t>Gdzie jest klucz do tego małego samochodu?</t>
+  </si>
+  <si>
+    <t>Ja bardzo lubię, kiedy pijesz ze mną kawę.</t>
+  </si>
+  <si>
+    <t>Ty wczoraj mówiłeś, że nie masz pieniędzy.</t>
+  </si>
+  <si>
+    <t>Jego tata kupił telefon dla mojej nowej szkoły.</t>
+  </si>
+  <si>
+    <t>Dzisiaj rano widziałem, jak ten mężczyzna miga.</t>
+  </si>
+  <si>
+    <t>Babcia i dziadek piją gorącą wodę rano.</t>
+  </si>
+  <si>
+    <t>Jej kot bardzo często śpi na tej dużej książce.</t>
+  </si>
+  <si>
+    <t>Zawsze pamiętam, żeby pić wodę przed pracą.</t>
+  </si>
+  <si>
+    <t>Jutro wieczorem idę do ciebie bez psa.</t>
+  </si>
+  <si>
+    <t>Ty nie rozumiesz, jak bardzo jestem zmęczony w pracy.</t>
+  </si>
+  <si>
+    <t>Gdzie my wczoraj kupiliśmy tę gorącą kawę?</t>
+  </si>
+  <si>
+    <t>Kto chory idzie rano do szkoły?</t>
+  </si>
+  <si>
+    <t>Ich brat ma urodziny w poniedziałek wieczorem.</t>
+  </si>
+  <si>
+    <t>Ile kawy dzisiaj rano piła twoja mama?</t>
+  </si>
+  <si>
+    <t>Czekam na ciebie, żeby iść do starych przyjaciół.</t>
+  </si>
+  <si>
+    <t>Czy ty widziałeś rano mojego małego brata?</t>
+  </si>
+  <si>
+    <t>Dzisiaj bardzo chcę uczyć się z twoją siostrą.</t>
+  </si>
+  <si>
+    <t>Mężczyzna bez samochodu idzie do pracy w nocy.</t>
+  </si>
+  <si>
+    <t>Dlaczego ta książka, którą ma ta kobieta, jest dla ciebie taka ważna?</t>
+  </si>
+  <si>
+    <t>Ten dzień był dla mojego przyjaciela bardzo smutny.</t>
+  </si>
+  <si>
+    <t>Ty zawsze myślisz, że ich dom jest twój.</t>
+  </si>
+  <si>
+    <t>Dziadek nie słyszy, co babcia do niego mówi.</t>
+  </si>
+  <si>
+    <t>Myślę, że twój pomysł na urodziny jest wesoły.</t>
+  </si>
+  <si>
+    <t>Zostań u dziadka na noc, bo jesteś zmęczony.</t>
+  </si>
+  <si>
+    <t>Czekam na ten ważny dla mnie czas.</t>
+  </si>
+  <si>
+    <t>Nie mam klucza, więc muszę czekać na tatę przed domem.</t>
+  </si>
+  <si>
+    <t>Czy wiesz, gdzie brat mojego kolegi kupił telefon?</t>
+  </si>
+  <si>
+    <t>Kocham ten czas, kiedy rano we wtorek piję kawę</t>
+  </si>
+  <si>
+    <t>Kup małego kota, nie tego starego psa.</t>
+  </si>
+  <si>
+    <t>Jej mały pies wczoraj w nocy jadł książkę taty.</t>
+  </si>
+  <si>
+    <t>Pamiętam, że mam rano iść do szkoły z jego małym przyjacielem.</t>
+  </si>
+  <si>
+    <t>Zawsze myślę o mojej starej szkole.</t>
+  </si>
+  <si>
+    <t>Jej brat kupił wczoraj dla mnie nowy telefon.</t>
+  </si>
+  <si>
+    <t>Ten wesoły pies często śpi u mnie w domu.</t>
+  </si>
+  <si>
+    <t>Jutro rano będę pracować z twoim przyjacielem.</t>
+  </si>
+  <si>
+    <t>Nie mam dzisiaj czasu na kawę z tobą.</t>
+  </si>
+  <si>
+    <t>Czy wy już wiecie, co on chce robić w ten czwartek?</t>
+  </si>
+  <si>
+    <t>Dlaczego myślisz, że jestem bardzo smutny?</t>
+  </si>
+  <si>
+    <t>Kiedy kupiłeś ten duży dom dla dziadka?</t>
+  </si>
+  <si>
+    <t>Mój stary samochód nie chce rano pracować.</t>
   </si>
   <si>
     <t xml:space="preserve">Dziękuję ci za ten telefon, który kupiłeś na moje urodziny w czwartek. </t>
   </si>
   <si>
-    <t xml:space="preserve">Gdzie twój kolega kupił taką dobrą herbatę?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W poniedziałek wieczorem będę dużo pracował u mamy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy widziałeś rano mojego psa przed domem?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chcę wiedzieć, dlaczego nie masz pieniędzy na książkę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamiętaj, żeby uczyć się w domu w dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty zawsze masz czas, żeby pić ze mną herbatę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W nocy słyszałem, jak ten kot dużo pije.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesteś dzisiaj zmęczony, bo wczoraj dużo pracowałeś.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój tata nie lubi, kiedy pije gorącą wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My bardzo często pijemy kawę u twojej siostry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ta mała książka jest dla ciebie ważna?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie wczoraj uczyłeś się migać z moim bratem?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chcę kupić stary dom z dużym psem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie rozumiem, o czym ty do mnie rano mówiłeś.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj nie mogę iść do pracy, bo chory brat jest w domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czekam na moje pieniądze od poniedziałku.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj wieczorem widziałem, jak twój kolega pije kawę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Babcia lubi, żeby kot spał rano pod domem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten czas był dla mojego przyjaciela bardzo dobry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kocham ten wesoły dzień w szkole z moim bratem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego nie pamiętasz o moich urodzinach w poniedziałek?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siostra jest często zmęczona.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niech ta kobieta zostanie u ciebie na herbatę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze rano dziękuję tacie za dobrą pracę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W nocy mój dziadek nie słyszy, co babcia mówi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do pracy z psem?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twój telefon był wczoraj rano w moim starym samochodzie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie mam klucza, żeby być rano w domu u dziadka.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja będę na ciebie czekać z gorącą wodą rano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mama musi teraz jeść.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie jest woda dla mojego nowego psa i kota?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj w nocy myślałem, co dzisiaj robić w szkole.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro rano kupię dla ciebie ten stary samochód taty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy twój przyjaciel ma czas na kawę po pracy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Będziemy uczyć się migać o mojej starej pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zostań z bratem w domu, bo on jest smutny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja i ty musimy dużo pić, żeby nie być zmęczonymi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój nowy dom w poniedziałek rano jest bardzo zimny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego ten stary kot zawsze dużo je u babci?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mężczyzna czekał rano z psem, żeby iść do pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, że wczoraj rano kupiłem ten nowy telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Często słyszę mojego psa rano, kiedy idę do pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj wieczorem byłem z małym psem w starym domu dziadka.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My chcemy dużo spać, żeby nie być chorym rano.</t>
+    <t>Gdzie twój kolega kupił taką dobrą herbatę?</t>
+  </si>
+  <si>
+    <t>W poniedziałek wieczorem będę dużo pracował u mamy.</t>
+  </si>
+  <si>
+    <t>Czy widziałeś rano mojego psa przed domem?</t>
+  </si>
+  <si>
+    <t>Chcę wiedzieć, dlaczego nie masz pieniędzy na książkę.</t>
+  </si>
+  <si>
+    <t>Pamiętaj, żeby uczyć się w domu w dzień.</t>
+  </si>
+  <si>
+    <t>Ty zawsze masz czas, żeby pić ze mną herbatę.</t>
+  </si>
+  <si>
+    <t>W nocy słyszałem, jak ten kot dużo pije.</t>
+  </si>
+  <si>
+    <t>Jesteś dzisiaj zmęczony, bo wczoraj dużo pracowałeś.</t>
+  </si>
+  <si>
+    <t>Mój tata nie lubi, kiedy pije gorącą wodę.</t>
+  </si>
+  <si>
+    <t>My bardzo często pijemy kawę u twojej siostry.</t>
+  </si>
+  <si>
+    <t>Dlaczego ta mała książka jest dla ciebie ważna?</t>
+  </si>
+  <si>
+    <t>Gdzie wczoraj uczyłeś się migać z moim bratem?</t>
+  </si>
+  <si>
+    <t>Chcę kupić stary dom z dużym psem.</t>
+  </si>
+  <si>
+    <t>Nie rozumiem, o czym ty do mnie rano mówiłeś.</t>
+  </si>
+  <si>
+    <t>Dzisiaj nie mogę iść do pracy, bo chory brat jest w domu.</t>
+  </si>
+  <si>
+    <t>Czekam na moje pieniądze od poniedziałku.</t>
+  </si>
+  <si>
+    <t>Wczoraj wieczorem widziałem, jak twój kolega pije kawę.</t>
+  </si>
+  <si>
+    <t>Babcia lubi, żeby kot spał rano pod domem.</t>
+  </si>
+  <si>
+    <t>Ten czas był dla mojego przyjaciela bardzo dobry.</t>
+  </si>
+  <si>
+    <t>Kocham ten wesoły dzień w szkole z moim bratem.</t>
+  </si>
+  <si>
+    <t>Dlaczego nie pamiętasz o moich urodzinach w poniedziałek?</t>
+  </si>
+  <si>
+    <t>Siostra jest często zmęczona.</t>
+  </si>
+  <si>
+    <t>Niech ta kobieta zostanie u ciebie na herbatę.</t>
+  </si>
+  <si>
+    <t>Zawsze rano dziękuję tacie za dobrą pracę.</t>
+  </si>
+  <si>
+    <t>W nocy mój dziadek nie słyszy, co babcia mówi.</t>
+  </si>
+  <si>
+    <t>Kto wczoraj miał pomysł, żeby iść do pracy z psem?</t>
+  </si>
+  <si>
+    <t>Twój telefon był wczoraj rano w moim starym samochodzie.</t>
+  </si>
+  <si>
+    <t>Nie mam klucza, żeby być rano w domu u dziadka.</t>
+  </si>
+  <si>
+    <t>Ja będę na ciebie czekać z gorącą wodą rano.</t>
+  </si>
+  <si>
+    <t>Mama musi teraz jeść.</t>
+  </si>
+  <si>
+    <t>Gdzie jest woda dla mojego nowego psa i kota?</t>
+  </si>
+  <si>
+    <t>Wczoraj w nocy myślałem, co dzisiaj robić w szkole.</t>
+  </si>
+  <si>
+    <t>Jutro rano kupię dla ciebie ten stary samochód taty.</t>
+  </si>
+  <si>
+    <t>Czy twój przyjaciel ma czas na kawę po pracy?</t>
+  </si>
+  <si>
+    <t>Będziemy uczyć się migać o mojej starej pracy.</t>
+  </si>
+  <si>
+    <t>Zostań z bratem w domu, bo on jest smutny.</t>
+  </si>
+  <si>
+    <t>Ja i ty musimy dużo pić, żeby nie być zmęczonymi.</t>
+  </si>
+  <si>
+    <t>Mój nowy dom w poniedziałek rano jest bardzo zimny.</t>
+  </si>
+  <si>
+    <t>Dlaczego ten stary kot zawsze dużo je u babci?</t>
+  </si>
+  <si>
+    <t>Mężczyzna czekał rano z psem, żeby iść do pracy.</t>
+  </si>
+  <si>
+    <t>Przepraszam, że wczoraj rano kupiłem ten nowy telefon.</t>
+  </si>
+  <si>
+    <t>Często słyszę mojego psa rano, kiedy idę do pracy.</t>
+  </si>
+  <si>
+    <t>Wczoraj wieczorem byłem z małym psem w starym domu dziadka.</t>
+  </si>
+  <si>
+    <t>My chcemy dużo spać, żeby nie być chorym rano.</t>
   </si>
   <si>
     <t xml:space="preserve">No to ile będziesz to robić? </t>
   </si>
   <si>
-    <t xml:space="preserve">Niech mój przyjaciel czeka na ciebie rano u dziadka.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy to jest środa, czy czwartek?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twój wesoły tata wczoraj pił z moim dziadkiem wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My chcemy wiedzieć, gdzie wczoraj był twój samochód rano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro w nocy będę spać u brata z psem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiedy kupisz dla mnie tę książkę o starym domu?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja bardzo lubię pić z tobą dobrą gorącą herbatę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie my wczoraj widzieliśmy ten stary samochód mojego przyjaciela?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, ale to był taki ważny rok, czy wy to teraz rozumiecie?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój dziadek w poniedziałek wieczorem był zmęczony i smutny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie mogę dzisiaj iść po kawę z moim nowym przyjacielem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Babcia i dziadek dzisiaj rano pili ze mną wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twój brat zawsze bardzo lubi mówić rano o pracy w środę?</t>
+    <t>Niech mój przyjaciel czeka na ciebie rano u dziadka.</t>
+  </si>
+  <si>
+    <t>Czy to jest środa, czy czwartek?</t>
+  </si>
+  <si>
+    <t>Twój wesoły tata wczoraj pił z moim dziadkiem wodę.</t>
+  </si>
+  <si>
+    <t>My chcemy wiedzieć, gdzie wczoraj był twój samochód rano.</t>
+  </si>
+  <si>
+    <t>Jutro w nocy będę spać u brata z psem.</t>
+  </si>
+  <si>
+    <t>Kiedy kupisz dla mnie tę książkę o starym domu?</t>
+  </si>
+  <si>
+    <t>Ja bardzo lubię pić z tobą dobrą gorącą herbatę.</t>
+  </si>
+  <si>
+    <t>Gdzie my wczoraj widzieliśmy ten stary samochód mojego przyjaciela?</t>
+  </si>
+  <si>
+    <t>Przepraszam, ale to był taki ważny rok, czy wy to teraz rozumiecie?</t>
+  </si>
+  <si>
+    <t>Mój dziadek w poniedziałek wieczorem był zmęczony i smutny.</t>
+  </si>
+  <si>
+    <t>Nie mogę dzisiaj iść po kawę z moim nowym przyjacielem.</t>
+  </si>
+  <si>
+    <t>Babcia i dziadek dzisiaj rano pili ze mną wodę.</t>
+  </si>
+  <si>
+    <t>Twój brat zawsze bardzo lubi mówić rano o pracy w środę?</t>
   </si>
   <si>
     <t xml:space="preserve">Ile to było robione? </t>
   </si>
   <si>
-    <t xml:space="preserve">Pamiętam, żeby pić zimną wodę w gorący dzień.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro rano idę z małym psem do ciebie po klucz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty nie pamiętasz, dlaczego wczoraj byłem u ciebie z bratem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile kawy dzisiaj pijesz, żeby mieć na to czas?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto wesoły i zdrowy idzie z moim bratem do starej szkoły?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój stary pies ma dzisiaj urodziny rano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czekam rano przed twoim nowym domem z gorącą herbatą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dzisiaj rano chcę uczyć się migać z twoją babcią.</t>
+    <t>Pamiętam, żeby pić zimną wodę w gorący dzień.</t>
+  </si>
+  <si>
+    <t>Jutro rano idę z małym psem do ciebie po klucz.</t>
+  </si>
+  <si>
+    <t>Ty nie pamiętasz, dlaczego wczoraj byłem u ciebie z bratem.</t>
+  </si>
+  <si>
+    <t>Ile kawy dzisiaj pijesz, żeby mieć na to czas?</t>
+  </si>
+  <si>
+    <t>Kto wesoły i zdrowy idzie z moim bratem do starej szkoły?</t>
+  </si>
+  <si>
+    <t>Mój stary pies ma dzisiaj urodziny rano.</t>
+  </si>
+  <si>
+    <t>Czekam rano przed twoim nowym domem z gorącą herbatą.</t>
+  </si>
+  <si>
+    <t>Dzisiaj rano chcę uczyć się migać z twoją babcią.</t>
   </si>
   <si>
     <t xml:space="preserve">To było we wtorek i w środę, teraz już to rozumiem, to był taki ważny rok. </t>
@@ -2143,58 +2157,58 @@
     <t xml:space="preserve">Czy wy się teraz kochacie, czy to już taki nowy pomysł na ten czwartek? </t>
   </si>
   <si>
-    <t xml:space="preserve">Dziadek nie słyszy, kiedy babcia mówi do kota.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj w nocy myślałem o tej książce z moim bratem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zostań rano w domu u dziadka, bo jesteś bardzo chory.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nie mam rano klucza od twojego starego samochodu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czy wiesz, co ten duży pies jadł w poniedziałek?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kocham ten czas rano, kiedy kot śpi u mnie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj wieczorem widziałem mojego psa przed szkołą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamiętam, żeby dużo pracować i mieć pieniądze na nowy dom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten bardzo smutny mężczyzna nie lubi pić ze mną kawy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie wczoraj kupiłeś tę książkę dla przyjaciela?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój tata bardzo kocha rano pić herbatę z wesołym psem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawsze chcę być z tobą rano u ciebie w pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twój pomysł na urodziny brata w poniedziałek jest bardzo dobry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niech kot zostanie u ciebie z moim starym tatą.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do nowej szkoły rano?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj rano mój tata kupił ten stary dom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dlaczego zawsze pijesz gorącą wodę z mamą?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We wtorek rano mój brat musi iść do pracy.</t>
+    <t>Dziadek nie słyszy, kiedy babcia mówi do kota.</t>
+  </si>
+  <si>
+    <t>Wczoraj w nocy myślałem o tej książce z moim bratem.</t>
+  </si>
+  <si>
+    <t>Zostań rano w domu u dziadka, bo jesteś bardzo chory.</t>
+  </si>
+  <si>
+    <t>Nie mam rano klucza od twojego starego samochodu.</t>
+  </si>
+  <si>
+    <t>Czy wiesz, co ten duży pies jadł w poniedziałek?</t>
+  </si>
+  <si>
+    <t>Kocham ten czas rano, kiedy kot śpi u mnie.</t>
+  </si>
+  <si>
+    <t>Wczoraj wieczorem widziałem mojego psa przed szkołą.</t>
+  </si>
+  <si>
+    <t>Pamiętam, żeby dużo pracować i mieć pieniądze na nowy dom.</t>
+  </si>
+  <si>
+    <t>Ten bardzo smutny mężczyzna nie lubi pić ze mną kawy.</t>
+  </si>
+  <si>
+    <t>Gdzie wczoraj kupiłeś tę książkę dla przyjaciela?</t>
+  </si>
+  <si>
+    <t>Mój tata bardzo kocha rano pić herbatę z wesołym psem.</t>
+  </si>
+  <si>
+    <t>Zawsze chcę być z tobą rano u ciebie w pracy.</t>
+  </si>
+  <si>
+    <t>Twój pomysł na urodziny brata w poniedziałek jest bardzo dobry.</t>
+  </si>
+  <si>
+    <t>Niech kot zostanie u ciebie z moim starym tatą.</t>
+  </si>
+  <si>
+    <t>Kto wczoraj miał pomysł, żeby iść do nowej szkoły rano?</t>
+  </si>
+  <si>
+    <t>Wczoraj rano mój tata kupił ten stary dom.</t>
+  </si>
+  <si>
+    <t>Dlaczego zawsze pijesz gorącą wodę z mamą?</t>
+  </si>
+  <si>
+    <t>We wtorek rano mój brat musi iść do pracy.</t>
   </si>
   <si>
     <t xml:space="preserve">W środę ja i ty chcemy kupić nowy dom, który będzie dla nas ważny </t>
@@ -2203,52 +2217,52 @@
     <t xml:space="preserve">Czy w czwartek twój pies był chory i kto mu pomógł? </t>
   </si>
   <si>
-    <t xml:space="preserve">Dlaczego we wtorek zawsze jesteś smutny?</t>
+    <t>Dlaczego we wtorek zawsze jesteś smutny?</t>
   </si>
   <si>
     <t xml:space="preserve">W środę wieczorem dziadek pije gorącą herbatę, bo kocha ten zdrowy pomysł. </t>
   </si>
   <si>
-    <t xml:space="preserve">Już pamiętam że mój przyjaciel ma urodziny w czwartek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wczoraj był poniedziałek, a dzisiaj jest wtorek.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kto musi pracować w środę w nocy?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W czwartek rano babcia czeka na mój telefon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kobieta i mężczyzna idą do szkoły we wtorek.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja wiem, że w środę będę bardzo zmęczony.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W czwartek siostra chce mieć nową książkę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gdzie ty byłeś we wtorek rano?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mój stary kot lubi spać w środę w domu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile pieniędzy musisz mieć na czwartek?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We wtorek my nie mamy czasu na kawę.</t>
+    <t>Już pamiętam że mój przyjaciel ma urodziny w czwartek</t>
+  </si>
+  <si>
+    <t>Wczoraj był poniedziałek, a dzisiaj jest wtorek.</t>
+  </si>
+  <si>
+    <t>Kto musi pracować w środę w nocy?</t>
+  </si>
+  <si>
+    <t>W czwartek rano babcia czeka na mój telefon.</t>
+  </si>
+  <si>
+    <t>Kobieta i mężczyzna idą do szkoły we wtorek.</t>
+  </si>
+  <si>
+    <t>Ja wiem, że w środę będę bardzo zmęczony.</t>
+  </si>
+  <si>
+    <t>W czwartek siostra chce mieć nową książkę.</t>
+  </si>
+  <si>
+    <t>Gdzie ty byłeś we wtorek rano?</t>
+  </si>
+  <si>
+    <t>Mój stary kot lubi spać w środę w domu.</t>
+  </si>
+  <si>
+    <t>Ile pieniędzy musisz mieć na czwartek?</t>
+  </si>
+  <si>
+    <t>We wtorek my nie mamy czasu na kawę.</t>
   </si>
   <si>
     <t xml:space="preserve">Zawsze w środę uczę się migać, teraz już kocham to robić. </t>
   </si>
   <si>
-    <t xml:space="preserve">W czwartek wieczorem twój kolega jest wesoły.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pamiętam, co mój tata mówił we wtorek.</t>
+    <t>W czwartek wieczorem twój kolega jest wesoły.</t>
+  </si>
+  <si>
+    <t>Pamiętam, co mój tata mówił we wtorek.</t>
   </si>
   <si>
     <t xml:space="preserve">W środę ten duży samochód jest mój, a wy go już kochacie. </t>
@@ -2257,16 +2271,16 @@
     <t xml:space="preserve">Dziękuję, że chcesz mi pomóc w czwartek, to taki zdrowy pomysł. </t>
   </si>
   <si>
-    <t xml:space="preserve">Jak bardzo lubisz ten wtorek?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W środę rano muszę pić zimną wodę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jutro czwartek, więc idę do pracy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przepraszam, że nie byłem zdrowy we wtorek.</t>
+    <t>Jak bardzo lubisz ten wtorek?</t>
+  </si>
+  <si>
+    <t>W środę rano muszę pić zimną wodę.</t>
+  </si>
+  <si>
+    <t>Jutro czwartek, więc idę do pracy.</t>
+  </si>
+  <si>
+    <t>Przepraszam, że nie byłem zdrowy we wtorek.</t>
   </si>
   <si>
     <t xml:space="preserve">Teraz idę do pracy, bo muszę iść po klucz, który ma moja siostra. </t>
@@ -2278,31 +2292,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2314,7 +2310,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -2322,115 +2318,87 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -2483,23 +2451,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D501"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="84.29"/>
+    <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="60" style="1" customWidth="1"/>
+    <col min="3" max="3" width="84.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2511,8 +2478,8 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2523,8 +2490,8 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:4" ht="15.6" customHeight="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -2535,8 +2502,8 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2547,8 +2514,8 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -2559,8 +2526,8 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -2571,8 +2538,8 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2583,8 +2550,8 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -2595,8 +2562,8 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2607,8 +2574,8 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2619,8 +2586,8 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2631,8 +2598,8 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2643,8 +2610,8 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:4">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2655,8 +2622,8 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:4">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2667,8 +2634,8 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+    <row r="15" spans="1:4">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2679,8 +2646,8 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:4">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2691,8 +2658,8 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+    <row r="17" spans="1:4">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2703,8 +2670,8 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:4">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2715,8 +2682,8 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+    <row r="19" spans="1:4">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2727,8 +2694,8 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:4">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -2739,8 +2706,8 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+    <row r="21" spans="1:4">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -2751,8 +2718,8 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:4">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -2763,8 +2730,8 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+    <row r="23" spans="1:4">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -2775,8 +2742,8 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:4">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -2787,8 +2754,8 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:4">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -2799,8 +2766,8 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:4">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -2811,8 +2778,8 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:4">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -2823,8 +2790,8 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:4">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -2833,8 +2800,8 @@
       <c r="C28" s="3"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:4">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -2843,8 +2810,8 @@
       <c r="C29" s="3"/>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:4">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -2855,8 +2822,8 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="n">
+    <row r="31" spans="1:4">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -2867,8 +2834,8 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:4">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -2879,8 +2846,8 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="n">
+    <row r="33" spans="1:4">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -2891,8 +2858,8 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:4">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -2903,8 +2870,8 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="n">
+    <row r="35" spans="1:4">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -2915,8 +2882,8 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+    <row r="36" spans="1:4">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -2927,8 +2894,8 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="n">
+    <row r="37" spans="1:4">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -2939,8 +2906,8 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:4">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -2951,8 +2918,8 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="n">
+    <row r="39" spans="1:4">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -2963,8 +2930,8 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:4">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -2975,8 +2942,8 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="n">
+    <row r="41" spans="1:4">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -2987,8 +2954,8 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:4">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -2999,8 +2966,8 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="n">
+    <row r="43" spans="1:4">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -3011,8 +2978,8 @@
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+    <row r="44" spans="1:4">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -3023,8 +2990,8 @@
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="n">
+    <row r="45" spans="1:4">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -3035,8 +3002,8 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:4">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -3047,8 +3014,8 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="n">
+    <row r="47" spans="1:4">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -3059,8 +3026,8 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:4">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -3071,8 +3038,8 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="n">
+    <row r="49" spans="1:4">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -3083,8 +3050,8 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
+    <row r="50" spans="1:4">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -3095,8 +3062,8 @@
       </c>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="n">
+    <row r="51" spans="1:4">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -3107,8 +3074,8 @@
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="n">
+    <row r="52" spans="1:4">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -3119,8 +3086,8 @@
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="n">
+    <row r="53" spans="1:4">
+      <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -3131,8 +3098,8 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:4">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -3143,8 +3110,8 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="n">
+    <row r="55" spans="1:4">
+      <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -3155,8 +3122,8 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:4">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -3167,8 +3134,8 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="n">
+    <row r="57" spans="1:4">
+      <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -3179,8 +3146,8 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="n">
+    <row r="58" spans="1:4">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3191,8 +3158,8 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="n">
+    <row r="59" spans="1:4">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -3203,8 +3170,8 @@
       </c>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="n">
+    <row r="60" spans="1:4">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -3215,8 +3182,8 @@
       </c>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="n">
+    <row r="61" spans="1:4">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -3227,8 +3194,8 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="n">
+    <row r="62" spans="1:4">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -3239,8 +3206,8 @@
       </c>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="n">
+    <row r="63" spans="1:4">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -3251,8 +3218,8 @@
       </c>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="n">
+    <row r="64" spans="1:4">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -3263,8 +3230,8 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="n">
+    <row r="65" spans="1:4">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -3275,8 +3242,8 @@
       </c>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="n">
+    <row r="66" spans="1:4">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -3287,8 +3254,8 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="n">
+    <row r="67" spans="1:4">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -3299,8 +3266,8 @@
       </c>
       <c r="D67" s="2"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="n">
+    <row r="68" spans="1:4">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -3311,8 +3278,8 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="n">
+    <row r="69" spans="1:4">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -3323,8 +3290,8 @@
       </c>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="n">
+    <row r="70" spans="1:4">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -3335,8 +3302,8 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="n">
+    <row r="71" spans="1:4">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -3347,8 +3314,8 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="n">
+    <row r="72" spans="1:4">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -3359,8 +3326,8 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="n">
+    <row r="73" spans="1:4">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -3371,8 +3338,8 @@
       </c>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="n">
+    <row r="74" spans="1:4">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -3383,8 +3350,8 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="n">
+    <row r="75" spans="1:4">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -3395,8 +3362,8 @@
       </c>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="n">
+    <row r="76" spans="1:4">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -3407,8 +3374,8 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="n">
+    <row r="77" spans="1:4">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -3419,8 +3386,8 @@
       </c>
       <c r="D77" s="2"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="n">
+    <row r="78" spans="1:4">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -3431,8 +3398,8 @@
       </c>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="n">
+    <row r="79" spans="1:4">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -3443,8 +3410,8 @@
       </c>
       <c r="D79" s="2"/>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="n">
+    <row r="80" spans="1:4">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -3455,8 +3422,8 @@
       </c>
       <c r="D80" s="2"/>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="n">
+    <row r="81" spans="1:4">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -3467,8 +3434,8 @@
       </c>
       <c r="D81" s="2"/>
     </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="n">
+    <row r="82" spans="1:4">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -3479,8 +3446,8 @@
       </c>
       <c r="D82" s="2"/>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="n">
+    <row r="83" spans="1:4">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -3491,8 +3458,8 @@
       </c>
       <c r="D83" s="2"/>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="n">
+    <row r="84" spans="1:4">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -3503,8 +3470,8 @@
       </c>
       <c r="D84" s="2"/>
     </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="n">
+    <row r="85" spans="1:4">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -3515,8 +3482,8 @@
       </c>
       <c r="D85" s="2"/>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="n">
+    <row r="86" spans="1:4">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -3527,8 +3494,8 @@
       </c>
       <c r="D86" s="2"/>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="n">
+    <row r="87" spans="1:4">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -3539,8 +3506,8 @@
       </c>
       <c r="D87" s="2"/>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="n">
+    <row r="88" spans="1:4">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -3551,8 +3518,8 @@
       </c>
       <c r="D88" s="2"/>
     </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="n">
+    <row r="89" spans="1:4">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -3563,8 +3530,8 @@
       </c>
       <c r="D89" s="2"/>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="n">
+    <row r="90" spans="1:4">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -3575,8 +3542,8 @@
       </c>
       <c r="D90" s="2"/>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="n">
+    <row r="91" spans="1:4">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -3587,8 +3554,8 @@
       </c>
       <c r="D91" s="2"/>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="n">
+    <row r="92" spans="1:4">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
@@ -3599,8 +3566,8 @@
       </c>
       <c r="D92" s="2"/>
     </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="n">
+    <row r="93" spans="1:4">
+      <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
@@ -3611,8 +3578,8 @@
       </c>
       <c r="D93" s="2"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="n">
+    <row r="94" spans="1:4">
+      <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -3623,8 +3590,8 @@
       </c>
       <c r="D94" s="2"/>
     </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="n">
+    <row r="95" spans="1:4">
+      <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -3635,8 +3602,8 @@
       </c>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="n">
+    <row r="96" spans="1:4">
+      <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -3647,8 +3614,8 @@
       </c>
       <c r="D96" s="2"/>
     </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="n">
+    <row r="97" spans="1:4">
+      <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -3659,8 +3626,8 @@
       </c>
       <c r="D97" s="2"/>
     </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="n">
+    <row r="98" spans="1:4">
+      <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -3671,8 +3638,8 @@
       </c>
       <c r="D98" s="2"/>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="n">
+    <row r="99" spans="1:4">
+      <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
@@ -3683,8 +3650,8 @@
       </c>
       <c r="D99" s="2"/>
     </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="n">
+    <row r="100" spans="1:4">
+      <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
@@ -3695,8 +3662,8 @@
       </c>
       <c r="D100" s="2"/>
     </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="n">
+    <row r="101" spans="1:4">
+      <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -3707,8 +3674,8 @@
       </c>
       <c r="D101" s="2"/>
     </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="n">
+    <row r="102" spans="1:4">
+      <c r="A102" s="2">
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
@@ -3719,8 +3686,8 @@
       </c>
       <c r="D102" s="2"/>
     </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="n">
+    <row r="103" spans="1:4">
+      <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
@@ -3731,8 +3698,8 @@
       </c>
       <c r="D103" s="2"/>
     </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="n">
+    <row r="104" spans="1:4">
+      <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
@@ -3743,8 +3710,8 @@
       </c>
       <c r="D104" s="2"/>
     </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="n">
+    <row r="105" spans="1:4">
+      <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
@@ -3755,8 +3722,8 @@
       </c>
       <c r="D105" s="2"/>
     </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="n">
+    <row r="106" spans="1:4">
+      <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
@@ -3767,8 +3734,8 @@
       </c>
       <c r="D106" s="2"/>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="n">
+    <row r="107" spans="1:4">
+      <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
@@ -3779,8 +3746,8 @@
       </c>
       <c r="D107" s="2"/>
     </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="n">
+    <row r="108" spans="1:4">
+      <c r="A108" s="2">
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
@@ -3791,8 +3758,8 @@
       </c>
       <c r="D108" s="2"/>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="n">
+    <row r="109" spans="1:4">
+      <c r="A109" s="2">
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
@@ -3803,8 +3770,8 @@
       </c>
       <c r="D109" s="2"/>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="n">
+    <row r="110" spans="1:4">
+      <c r="A110" s="2">
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
@@ -3815,8 +3782,8 @@
       </c>
       <c r="D110" s="2"/>
     </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="n">
+    <row r="111" spans="1:4">
+      <c r="A111" s="2">
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
@@ -3827,8 +3794,8 @@
       </c>
       <c r="D111" s="2"/>
     </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="n">
+    <row r="112" spans="1:4">
+      <c r="A112" s="2">
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
@@ -3839,8 +3806,8 @@
       </c>
       <c r="D112" s="2"/>
     </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="n">
+    <row r="113" spans="1:4">
+      <c r="A113" s="2">
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
@@ -3851,8 +3818,8 @@
       </c>
       <c r="D113" s="2"/>
     </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="n">
+    <row r="114" spans="1:4">
+      <c r="A114" s="2">
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
@@ -3863,8 +3830,8 @@
       </c>
       <c r="D114" s="2"/>
     </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="n">
+    <row r="115" spans="1:4">
+      <c r="A115" s="2">
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
@@ -3875,8 +3842,8 @@
       </c>
       <c r="D115" s="2"/>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="n">
+    <row r="116" spans="1:4">
+      <c r="A116" s="2">
         <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
@@ -3887,8 +3854,8 @@
       </c>
       <c r="D116" s="2"/>
     </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="n">
+    <row r="117" spans="1:4">
+      <c r="A117" s="2">
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
@@ -3899,8 +3866,8 @@
       </c>
       <c r="D117" s="2"/>
     </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="n">
+    <row r="118" spans="1:4">
+      <c r="A118" s="2">
         <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
@@ -3911,8 +3878,8 @@
       </c>
       <c r="D118" s="2"/>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="n">
+    <row r="119" spans="1:4">
+      <c r="A119" s="2">
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
@@ -3923,8 +3890,8 @@
       </c>
       <c r="D119" s="2"/>
     </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="n">
+    <row r="120" spans="1:4">
+      <c r="A120" s="2">
         <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
@@ -3935,8 +3902,8 @@
       </c>
       <c r="D120" s="2"/>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="n">
+    <row r="121" spans="1:4">
+      <c r="A121" s="2">
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
@@ -3947,8 +3914,8 @@
       </c>
       <c r="D121" s="2"/>
     </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="n">
+    <row r="122" spans="1:4">
+      <c r="A122" s="2">
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
@@ -3959,8 +3926,8 @@
       </c>
       <c r="D122" s="2"/>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="n">
+    <row r="123" spans="1:4">
+      <c r="A123" s="2">
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
@@ -3971,8 +3938,8 @@
       </c>
       <c r="D123" s="2"/>
     </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="n">
+    <row r="124" spans="1:4">
+      <c r="A124" s="2">
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
@@ -3983,8 +3950,8 @@
       </c>
       <c r="D124" s="2"/>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="n">
+    <row r="125" spans="1:4">
+      <c r="A125" s="2">
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
@@ -3995,8 +3962,8 @@
       </c>
       <c r="D125" s="2"/>
     </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="n">
+    <row r="126" spans="1:4">
+      <c r="A126" s="2">
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
@@ -4007,8 +3974,8 @@
       </c>
       <c r="D126" s="2"/>
     </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="n">
+    <row r="127" spans="1:4">
+      <c r="A127" s="2">
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
@@ -4019,8 +3986,8 @@
       </c>
       <c r="D127" s="2"/>
     </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="n">
+    <row r="128" spans="1:4">
+      <c r="A128" s="2">
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
@@ -4031,8 +3998,8 @@
       </c>
       <c r="D128" s="2"/>
     </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="n">
+    <row r="129" spans="1:4">
+      <c r="A129" s="2">
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
@@ -4043,8 +4010,8 @@
       </c>
       <c r="D129" s="2"/>
     </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="n">
+    <row r="130" spans="1:4">
+      <c r="A130" s="2">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
@@ -4055,8 +4022,8 @@
       </c>
       <c r="D130" s="2"/>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="2" t="n">
+    <row r="131" spans="1:4">
+      <c r="A131" s="2">
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
@@ -4067,8 +4034,8 @@
       </c>
       <c r="D131" s="2"/>
     </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="n">
+    <row r="132" spans="1:4">
+      <c r="A132" s="2">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
@@ -4079,8 +4046,8 @@
       </c>
       <c r="D132" s="2"/>
     </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="2" t="n">
+    <row r="133" spans="1:4">
+      <c r="A133" s="2">
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
@@ -4091,8 +4058,8 @@
       </c>
       <c r="D133" s="2"/>
     </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="n">
+    <row r="134" spans="1:4">
+      <c r="A134" s="2">
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
@@ -4103,8 +4070,8 @@
       </c>
       <c r="D134" s="2"/>
     </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="2" t="n">
+    <row r="135" spans="1:4">
+      <c r="A135" s="2">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
@@ -4115,8 +4082,8 @@
       </c>
       <c r="D135" s="2"/>
     </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="2" t="n">
+    <row r="136" spans="1:4">
+      <c r="A136" s="2">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
@@ -4127,8 +4094,8 @@
       </c>
       <c r="D136" s="2"/>
     </row>
-    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="n">
+    <row r="137" spans="1:4">
+      <c r="A137" s="2">
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
@@ -4139,8 +4106,8 @@
       </c>
       <c r="D137" s="2"/>
     </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="n">
+    <row r="138" spans="1:4">
+      <c r="A138" s="2">
         <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
@@ -4151,8 +4118,8 @@
       </c>
       <c r="D138" s="2"/>
     </row>
-    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="2" t="n">
+    <row r="139" spans="1:4">
+      <c r="A139" s="2">
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
@@ -4163,8 +4130,8 @@
       </c>
       <c r="D139" s="2"/>
     </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="2" t="n">
+    <row r="140" spans="1:4">
+      <c r="A140" s="2">
         <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
@@ -4175,8 +4142,8 @@
       </c>
       <c r="D140" s="2"/>
     </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="n">
+    <row r="141" spans="1:4">
+      <c r="A141" s="2">
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
@@ -4187,8 +4154,8 @@
       </c>
       <c r="D141" s="2"/>
     </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2" t="n">
+    <row r="142" spans="1:4">
+      <c r="A142" s="2">
         <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
@@ -4199,8 +4166,8 @@
       </c>
       <c r="D142" s="2"/>
     </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="2" t="n">
+    <row r="143" spans="1:4">
+      <c r="A143" s="2">
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
@@ -4211,8 +4178,8 @@
       </c>
       <c r="D143" s="2"/>
     </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="2" t="n">
+    <row r="144" spans="1:4">
+      <c r="A144" s="2">
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
@@ -4223,8 +4190,8 @@
       </c>
       <c r="D144" s="2"/>
     </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="2" t="n">
+    <row r="145" spans="1:4">
+      <c r="A145" s="2">
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
@@ -4235,8 +4202,8 @@
       </c>
       <c r="D145" s="2"/>
     </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="2" t="n">
+    <row r="146" spans="1:4">
+      <c r="A146" s="2">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
@@ -4247,8 +4214,8 @@
       </c>
       <c r="D146" s="2"/>
     </row>
-    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="n">
+    <row r="147" spans="1:4">
+      <c r="A147" s="2">
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
@@ -4259,8 +4226,8 @@
       </c>
       <c r="D147" s="2"/>
     </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="2" t="n">
+    <row r="148" spans="1:4">
+      <c r="A148" s="2">
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
@@ -4271,8 +4238,8 @@
       </c>
       <c r="D148" s="2"/>
     </row>
-    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="2" t="n">
+    <row r="149" spans="1:4">
+      <c r="A149" s="2">
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
@@ -4283,8 +4250,8 @@
       </c>
       <c r="D149" s="2"/>
     </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="2" t="n">
+    <row r="150" spans="1:4">
+      <c r="A150" s="2">
         <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
@@ -4295,8 +4262,8 @@
       </c>
       <c r="D150" s="2"/>
     </row>
-    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="2" t="n">
+    <row r="151" spans="1:4">
+      <c r="A151" s="2">
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
@@ -4307,8 +4274,8 @@
       </c>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="2" t="n">
+    <row r="152" spans="1:4">
+      <c r="A152" s="2">
         <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
@@ -4319,8 +4286,8 @@
       </c>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="2" t="n">
+    <row r="153" spans="1:4">
+      <c r="A153" s="2">
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
@@ -4331,8 +4298,8 @@
       </c>
       <c r="D153" s="2"/>
     </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="2" t="n">
+    <row r="154" spans="1:4">
+      <c r="A154" s="2">
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
@@ -4343,8 +4310,8 @@
       </c>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="2" t="n">
+    <row r="155" spans="1:4">
+      <c r="A155" s="2">
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
@@ -4355,8 +4322,8 @@
       </c>
       <c r="D155" s="2"/>
     </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="2" t="n">
+    <row r="156" spans="1:4">
+      <c r="A156" s="2">
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
@@ -4367,8 +4334,8 @@
       </c>
       <c r="D156" s="2"/>
     </row>
-    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="2" t="n">
+    <row r="157" spans="1:4">
+      <c r="A157" s="2">
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
@@ -4379,8 +4346,8 @@
       </c>
       <c r="D157" s="2"/>
     </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="2" t="n">
+    <row r="158" spans="1:4">
+      <c r="A158" s="2">
         <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
@@ -4391,8 +4358,8 @@
       </c>
       <c r="D158" s="2"/>
     </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="2" t="n">
+    <row r="159" spans="1:4">
+      <c r="A159" s="2">
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
@@ -4403,8 +4370,8 @@
       </c>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="2" t="n">
+    <row r="160" spans="1:4">
+      <c r="A160" s="2">
         <v>159</v>
       </c>
       <c r="B160" s="3" t="s">
@@ -4415,8 +4382,8 @@
       </c>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="2" t="n">
+    <row r="161" spans="1:4">
+      <c r="A161" s="2">
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
@@ -4427,8 +4394,8 @@
       </c>
       <c r="D161" s="2"/>
     </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="2" t="n">
+    <row r="162" spans="1:4">
+      <c r="A162" s="2">
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
@@ -4439,8 +4406,8 @@
       </c>
       <c r="D162" s="2"/>
     </row>
-    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="2" t="n">
+    <row r="163" spans="1:4">
+      <c r="A163" s="2">
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
@@ -4451,8 +4418,8 @@
       </c>
       <c r="D163" s="2"/>
     </row>
-    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="2" t="n">
+    <row r="164" spans="1:4">
+      <c r="A164" s="2">
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
@@ -4463,8 +4430,8 @@
       </c>
       <c r="D164" s="2"/>
     </row>
-    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="2" t="n">
+    <row r="165" spans="1:4">
+      <c r="A165" s="2">
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
@@ -4475,8 +4442,8 @@
       </c>
       <c r="D165" s="2"/>
     </row>
-    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="2" t="n">
+    <row r="166" spans="1:4">
+      <c r="A166" s="2">
         <v>165</v>
       </c>
       <c r="B166" s="3" t="s">
@@ -4487,8 +4454,8 @@
       </c>
       <c r="D166" s="2"/>
     </row>
-    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="2" t="n">
+    <row r="167" spans="1:4">
+      <c r="A167" s="2">
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
@@ -4499,8 +4466,8 @@
       </c>
       <c r="D167" s="2"/>
     </row>
-    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="2" t="n">
+    <row r="168" spans="1:4">
+      <c r="A168" s="2">
         <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
@@ -4511,8 +4478,8 @@
       </c>
       <c r="D168" s="2"/>
     </row>
-    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="2" t="n">
+    <row r="169" spans="1:4">
+      <c r="A169" s="2">
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
@@ -4523,8 +4490,8 @@
       </c>
       <c r="D169" s="2"/>
     </row>
-    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="2" t="n">
+    <row r="170" spans="1:4">
+      <c r="A170" s="2">
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
@@ -4535,8 +4502,8 @@
       </c>
       <c r="D170" s="2"/>
     </row>
-    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="2" t="n">
+    <row r="171" spans="1:4">
+      <c r="A171" s="2">
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
@@ -4547,8 +4514,8 @@
       </c>
       <c r="D171" s="2"/>
     </row>
-    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="2" t="n">
+    <row r="172" spans="1:4">
+      <c r="A172" s="2">
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
@@ -4559,8 +4526,8 @@
       </c>
       <c r="D172" s="2"/>
     </row>
-    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="2" t="n">
+    <row r="173" spans="1:4">
+      <c r="A173" s="2">
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
@@ -4571,8 +4538,8 @@
       </c>
       <c r="D173" s="2"/>
     </row>
-    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="2" t="n">
+    <row r="174" spans="1:4">
+      <c r="A174" s="2">
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
@@ -4583,8 +4550,8 @@
       </c>
       <c r="D174" s="2"/>
     </row>
-    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="2" t="n">
+    <row r="175" spans="1:4">
+      <c r="A175" s="2">
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
@@ -4595,8 +4562,8 @@
       </c>
       <c r="D175" s="2"/>
     </row>
-    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="2" t="n">
+    <row r="176" spans="1:4">
+      <c r="A176" s="2">
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
@@ -4607,8 +4574,8 @@
       </c>
       <c r="D176" s="2"/>
     </row>
-    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="2" t="n">
+    <row r="177" spans="1:4">
+      <c r="A177" s="2">
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
@@ -4619,8 +4586,8 @@
       </c>
       <c r="D177" s="2"/>
     </row>
-    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="2" t="n">
+    <row r="178" spans="1:4">
+      <c r="A178" s="2">
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
@@ -4631,8 +4598,8 @@
       </c>
       <c r="D178" s="2"/>
     </row>
-    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="2" t="n">
+    <row r="179" spans="1:4">
+      <c r="A179" s="2">
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
@@ -4643,8 +4610,8 @@
       </c>
       <c r="D179" s="2"/>
     </row>
-    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="2" t="n">
+    <row r="180" spans="1:4">
+      <c r="A180" s="2">
         <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
@@ -4655,8 +4622,8 @@
       </c>
       <c r="D180" s="2"/>
     </row>
-    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="2" t="n">
+    <row r="181" spans="1:4">
+      <c r="A181" s="2">
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
@@ -4667,8 +4634,8 @@
       </c>
       <c r="D181" s="2"/>
     </row>
-    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="2" t="n">
+    <row r="182" spans="1:4">
+      <c r="A182" s="2">
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
@@ -4679,8 +4646,8 @@
       </c>
       <c r="D182" s="2"/>
     </row>
-    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="2" t="n">
+    <row r="183" spans="1:4">
+      <c r="A183" s="2">
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
@@ -4691,8 +4658,8 @@
       </c>
       <c r="D183" s="2"/>
     </row>
-    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="2" t="n">
+    <row r="184" spans="1:4">
+      <c r="A184" s="2">
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
@@ -4703,8 +4670,8 @@
       </c>
       <c r="D184" s="2"/>
     </row>
-    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="2" t="n">
+    <row r="185" spans="1:4">
+      <c r="A185" s="2">
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
@@ -4715,8 +4682,8 @@
       </c>
       <c r="D185" s="2"/>
     </row>
-    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="2" t="n">
+    <row r="186" spans="1:4">
+      <c r="A186" s="2">
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
@@ -4727,8 +4694,8 @@
       </c>
       <c r="D186" s="2"/>
     </row>
-    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="2" t="n">
+    <row r="187" spans="1:4">
+      <c r="A187" s="2">
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
@@ -4739,8 +4706,8 @@
       </c>
       <c r="D187" s="2"/>
     </row>
-    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="2" t="n">
+    <row r="188" spans="1:4">
+      <c r="A188" s="2">
         <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
@@ -4751,8 +4718,8 @@
       </c>
       <c r="D188" s="2"/>
     </row>
-    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="2" t="n">
+    <row r="189" spans="1:4">
+      <c r="A189" s="2">
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
@@ -4763,8 +4730,8 @@
       </c>
       <c r="D189" s="2"/>
     </row>
-    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="2" t="n">
+    <row r="190" spans="1:4">
+      <c r="A190" s="2">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
@@ -4775,8 +4742,8 @@
       </c>
       <c r="D190" s="2"/>
     </row>
-    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="2" t="n">
+    <row r="191" spans="1:4">
+      <c r="A191" s="2">
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
@@ -4787,8 +4754,8 @@
       </c>
       <c r="D191" s="2"/>
     </row>
-    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="2" t="n">
+    <row r="192" spans="1:4">
+      <c r="A192" s="2">
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
@@ -4799,8 +4766,8 @@
       </c>
       <c r="D192" s="2"/>
     </row>
-    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="2" t="n">
+    <row r="193" spans="1:4">
+      <c r="A193" s="2">
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
@@ -4811,8 +4778,8 @@
       </c>
       <c r="D193" s="2"/>
     </row>
-    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="2" t="n">
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
@@ -4823,8 +4790,8 @@
       </c>
       <c r="D194" s="2"/>
     </row>
-    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="2" t="n">
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
@@ -4835,8 +4802,8 @@
       </c>
       <c r="D195" s="2"/>
     </row>
-    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="2" t="n">
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
@@ -4847,8 +4814,8 @@
       </c>
       <c r="D196" s="2"/>
     </row>
-    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="2" t="n">
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
@@ -4859,8 +4826,8 @@
       </c>
       <c r="D197" s="2"/>
     </row>
-    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="2" t="n">
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
@@ -4871,8 +4838,8 @@
       </c>
       <c r="D198" s="2"/>
     </row>
-    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="2" t="n">
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
@@ -4883,8 +4850,8 @@
       </c>
       <c r="D199" s="2"/>
     </row>
-    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="2" t="n">
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
@@ -4895,8 +4862,8 @@
       </c>
       <c r="D200" s="2"/>
     </row>
-    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="2" t="n">
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
@@ -4907,8 +4874,8 @@
       </c>
       <c r="D201" s="2"/>
     </row>
-    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="2" t="n">
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
         <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
@@ -4919,8 +4886,8 @@
       </c>
       <c r="D202" s="2"/>
     </row>
-    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="2" t="n">
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
@@ -4931,8 +4898,8 @@
       </c>
       <c r="D203" s="2"/>
     </row>
-    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="2" t="n">
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
         <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
@@ -4943,8 +4910,8 @@
       </c>
       <c r="D204" s="2"/>
     </row>
-    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="2" t="n">
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
@@ -4955,8 +4922,8 @@
       </c>
       <c r="D205" s="2"/>
     </row>
-    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="2" t="n">
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
         <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
@@ -4967,8 +4934,8 @@
       </c>
       <c r="D206" s="2"/>
     </row>
-    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="2" t="n">
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
@@ -4979,8 +4946,8 @@
       </c>
       <c r="D207" s="2"/>
     </row>
-    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="2" t="n">
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
@@ -4991,8 +4958,8 @@
       </c>
       <c r="D208" s="2"/>
     </row>
-    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="2" t="n">
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
@@ -5003,8 +4970,8 @@
       </c>
       <c r="D209" s="2"/>
     </row>
-    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="2" t="n">
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
         <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
@@ -5015,8 +4982,8 @@
       </c>
       <c r="D210" s="2"/>
     </row>
-    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="2" t="n">
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
@@ -5027,8 +4994,8 @@
       </c>
       <c r="D211" s="2"/>
     </row>
-    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="2" t="n">
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
@@ -5039,8 +5006,8 @@
       </c>
       <c r="D212" s="2"/>
     </row>
-    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="2" t="n">
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
@@ -5051,8 +5018,8 @@
       </c>
       <c r="D213" s="2"/>
     </row>
-    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="2" t="n">
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
         <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
@@ -5063,8 +5030,8 @@
       </c>
       <c r="D214" s="2"/>
     </row>
-    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="2" t="n">
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
@@ -5075,8 +5042,8 @@
       </c>
       <c r="D215" s="2"/>
     </row>
-    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="2" t="n">
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
@@ -5087,8 +5054,8 @@
       </c>
       <c r="D216" s="2"/>
     </row>
-    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="2" t="n">
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
@@ -5099,8 +5066,8 @@
       </c>
       <c r="D217" s="2"/>
     </row>
-    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="2" t="n">
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
         <v>217</v>
       </c>
       <c r="B218" s="3" t="s">
@@ -5111,8 +5078,8 @@
       </c>
       <c r="D218" s="2"/>
     </row>
-    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="2" t="n">
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
@@ -5123,8 +5090,8 @@
       </c>
       <c r="D219" s="2"/>
     </row>
-    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="2" t="n">
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
         <v>219</v>
       </c>
       <c r="B220" s="3" t="s">
@@ -5135,8 +5102,8 @@
       </c>
       <c r="D220" s="2"/>
     </row>
-    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="2" t="n">
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
@@ -5147,8 +5114,8 @@
       </c>
       <c r="D221" s="2"/>
     </row>
-    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="2" t="n">
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
         <v>221</v>
       </c>
       <c r="B222" s="3" t="s">
@@ -5159,8 +5126,8 @@
       </c>
       <c r="D222" s="2"/>
     </row>
-    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="2" t="n">
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
         <v>222</v>
       </c>
       <c r="B223" s="3" t="s">
@@ -5171,8 +5138,8 @@
       </c>
       <c r="D223" s="2"/>
     </row>
-    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="2" t="n">
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
         <v>223</v>
       </c>
       <c r="B224" s="3" t="s">
@@ -5183,8 +5150,8 @@
       </c>
       <c r="D224" s="2"/>
     </row>
-    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="2" t="n">
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
         <v>224</v>
       </c>
       <c r="B225" s="3" t="s">
@@ -5195,8 +5162,8 @@
       </c>
       <c r="D225" s="2"/>
     </row>
-    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="2" t="n">
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
         <v>225</v>
       </c>
       <c r="B226" s="3" t="s">
@@ -5207,8 +5174,8 @@
       </c>
       <c r="D226" s="2"/>
     </row>
-    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="2" t="n">
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
         <v>226</v>
       </c>
       <c r="B227" s="3" t="s">
@@ -5219,8 +5186,8 @@
       </c>
       <c r="D227" s="2"/>
     </row>
-    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="2" t="n">
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
         <v>227</v>
       </c>
       <c r="B228" s="3" t="s">
@@ -5231,8 +5198,8 @@
       </c>
       <c r="D228" s="2"/>
     </row>
-    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="2" t="n">
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
         <v>228</v>
       </c>
       <c r="B229" s="3" t="s">
@@ -5243,8 +5210,8 @@
       </c>
       <c r="D229" s="2"/>
     </row>
-    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="2" t="n">
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
         <v>229</v>
       </c>
       <c r="B230" s="3" t="s">
@@ -5255,8 +5222,8 @@
       </c>
       <c r="D230" s="2"/>
     </row>
-    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="2" t="n">
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
         <v>230</v>
       </c>
       <c r="B231" s="3" t="s">
@@ -5267,8 +5234,8 @@
       </c>
       <c r="D231" s="2"/>
     </row>
-    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="2" t="n">
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
         <v>231</v>
       </c>
       <c r="B232" s="3" t="s">
@@ -5279,8 +5246,8 @@
       </c>
       <c r="D232" s="2"/>
     </row>
-    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="2" t="n">
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
         <v>232</v>
       </c>
       <c r="B233" s="3" t="s">
@@ -5291,8 +5258,8 @@
       </c>
       <c r="D233" s="2"/>
     </row>
-    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="2" t="n">
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
         <v>233</v>
       </c>
       <c r="B234" s="3" t="s">
@@ -5303,8 +5270,8 @@
       </c>
       <c r="D234" s="2"/>
     </row>
-    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="2" t="n">
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
         <v>234</v>
       </c>
       <c r="B235" s="3" t="s">
@@ -5315,8 +5282,8 @@
       </c>
       <c r="D235" s="2"/>
     </row>
-    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="2" t="n">
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
         <v>235</v>
       </c>
       <c r="B236" s="3" t="s">
@@ -5327,8 +5294,8 @@
       </c>
       <c r="D236" s="2"/>
     </row>
-    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="2" t="n">
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
         <v>236</v>
       </c>
       <c r="B237" s="3" t="s">
@@ -5339,8 +5306,8 @@
       </c>
       <c r="D237" s="2"/>
     </row>
-    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="2" t="n">
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
         <v>237</v>
       </c>
       <c r="B238" s="3" t="s">
@@ -5351,8 +5318,8 @@
       </c>
       <c r="D238" s="2"/>
     </row>
-    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="2" t="n">
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
         <v>238</v>
       </c>
       <c r="B239" s="3" t="s">
@@ -5363,8 +5330,8 @@
       </c>
       <c r="D239" s="2"/>
     </row>
-    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="2" t="n">
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
         <v>239</v>
       </c>
       <c r="B240" s="3" t="s">
@@ -5375,8 +5342,8 @@
       </c>
       <c r="D240" s="2"/>
     </row>
-    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="2" t="n">
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
         <v>240</v>
       </c>
       <c r="B241" s="3" t="s">
@@ -5387,8 +5354,8 @@
       </c>
       <c r="D241" s="2"/>
     </row>
-    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="2" t="n">
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
         <v>241</v>
       </c>
       <c r="B242" s="3" t="s">
@@ -5399,8 +5366,8 @@
       </c>
       <c r="D242" s="2"/>
     </row>
-    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="2" t="n">
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="s">
@@ -5411,8 +5378,8 @@
       </c>
       <c r="D243" s="2"/>
     </row>
-    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="2" t="n">
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
         <v>243</v>
       </c>
       <c r="B244" s="3" t="s">
@@ -5423,8 +5390,8 @@
       </c>
       <c r="D244" s="2"/>
     </row>
-    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="2" t="n">
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="s">
@@ -5435,8 +5402,8 @@
       </c>
       <c r="D245" s="2"/>
     </row>
-    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="2" t="n">
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="s">
@@ -5447,8 +5414,8 @@
       </c>
       <c r="D246" s="2"/>
     </row>
-    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="2" t="n">
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
         <v>246</v>
       </c>
       <c r="B247" s="3" t="s">
@@ -5459,8 +5426,8 @@
       </c>
       <c r="D247" s="2"/>
     </row>
-    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="2" t="n">
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
         <v>247</v>
       </c>
       <c r="B248" s="3" t="s">
@@ -5471,8 +5438,8 @@
       </c>
       <c r="D248" s="2"/>
     </row>
-    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="2" t="n">
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
         <v>248</v>
       </c>
       <c r="B249" s="3" t="s">
@@ -5483,8 +5450,8 @@
       </c>
       <c r="D249" s="2"/>
     </row>
-    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="2" t="n">
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="s">
@@ -5495,8 +5462,8 @@
       </c>
       <c r="D250" s="2"/>
     </row>
-    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="2" t="n">
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
         <v>250</v>
       </c>
       <c r="B251" s="3" t="s">
@@ -5507,8 +5474,8 @@
       </c>
       <c r="D251" s="2"/>
     </row>
-    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="2" t="n">
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
         <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
@@ -5516,8 +5483,8 @@
       </c>
       <c r="D252" s="2"/>
     </row>
-    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="2" t="n">
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
         <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
@@ -5525,8 +5492,8 @@
       </c>
       <c r="D253" s="2"/>
     </row>
-    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="2" t="n">
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
         <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
@@ -5534,8 +5501,8 @@
       </c>
       <c r="D254" s="2"/>
     </row>
-    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="2" t="n">
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
         <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
@@ -5543,8 +5510,8 @@
       </c>
       <c r="D255" s="2"/>
     </row>
-    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="2" t="n">
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
         <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
@@ -5552,8 +5519,8 @@
       </c>
       <c r="D256" s="2"/>
     </row>
-    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="2" t="n">
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
         <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
@@ -5561,8 +5528,8 @@
       </c>
       <c r="D257" s="2"/>
     </row>
-    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="2" t="n">
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
         <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
@@ -5570,8 +5537,8 @@
       </c>
       <c r="D258" s="2"/>
     </row>
-    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="2" t="n">
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
@@ -5579,8 +5546,8 @@
       </c>
       <c r="D259" s="2"/>
     </row>
-    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="2" t="n">
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
         <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
@@ -5588,8 +5555,8 @@
       </c>
       <c r="D260" s="2"/>
     </row>
-    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="2" t="n">
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
         <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
@@ -5597,8 +5564,8 @@
       </c>
       <c r="D261" s="2"/>
     </row>
-    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="2" t="n">
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
         <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
@@ -5606,8 +5573,8 @@
       </c>
       <c r="D262" s="2"/>
     </row>
-    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="2" t="n">
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
         <v>262</v>
       </c>
       <c r="B263" s="1" t="s">
@@ -5615,8 +5582,8 @@
       </c>
       <c r="D263" s="2"/>
     </row>
-    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="2" t="n">
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
         <v>263</v>
       </c>
       <c r="B264" s="1" t="s">
@@ -5624,8 +5591,8 @@
       </c>
       <c r="D264" s="2"/>
     </row>
-    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="2" t="n">
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
         <v>264</v>
       </c>
       <c r="B265" s="1" t="s">
@@ -5633,8 +5600,8 @@
       </c>
       <c r="D265" s="2"/>
     </row>
-    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="2" t="n">
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
         <v>265</v>
       </c>
       <c r="B266" s="1" t="s">
@@ -5642,8 +5609,8 @@
       </c>
       <c r="D266" s="2"/>
     </row>
-    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="2" t="n">
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
         <v>266</v>
       </c>
       <c r="B267" s="1" t="s">
@@ -5651,8 +5618,8 @@
       </c>
       <c r="D267" s="2"/>
     </row>
-    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="2" t="n">
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
         <v>267</v>
       </c>
       <c r="B268" s="1" t="s">
@@ -5660,8 +5627,8 @@
       </c>
       <c r="D268" s="2"/>
     </row>
-    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="2" t="n">
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
         <v>268</v>
       </c>
       <c r="B269" s="1" t="s">
@@ -5669,8 +5636,8 @@
       </c>
       <c r="D269" s="2"/>
     </row>
-    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="2" t="n">
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
         <v>269</v>
       </c>
       <c r="B270" s="1" t="s">
@@ -5678,8 +5645,8 @@
       </c>
       <c r="D270" s="2"/>
     </row>
-    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="2" t="n">
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
         <v>270</v>
       </c>
       <c r="B271" s="1" t="s">
@@ -5687,8 +5654,8 @@
       </c>
       <c r="D271" s="2"/>
     </row>
-    <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="2" t="n">
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
         <v>271</v>
       </c>
       <c r="B272" s="1" t="s">
@@ -5696,8 +5663,8 @@
       </c>
       <c r="D272" s="2"/>
     </row>
-    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="2" t="n">
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
         <v>272</v>
       </c>
       <c r="B273" s="1" t="s">
@@ -5705,8 +5672,8 @@
       </c>
       <c r="D273" s="2"/>
     </row>
-    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="2" t="n">
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
         <v>273</v>
       </c>
       <c r="B274" s="1" t="s">
@@ -5714,8 +5681,8 @@
       </c>
       <c r="D274" s="2"/>
     </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="2" t="n">
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
         <v>274</v>
       </c>
       <c r="B275" s="1" t="s">
@@ -5723,8 +5690,8 @@
       </c>
       <c r="D275" s="2"/>
     </row>
-    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="2" t="n">
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
         <v>275</v>
       </c>
       <c r="B276" s="1" t="s">
@@ -5732,8 +5699,8 @@
       </c>
       <c r="D276" s="2"/>
     </row>
-    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="2" t="n">
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
         <v>276</v>
       </c>
       <c r="B277" s="1" t="s">
@@ -5741,8 +5708,8 @@
       </c>
       <c r="D277" s="2"/>
     </row>
-    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="2" t="n">
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
         <v>277</v>
       </c>
       <c r="B278" s="1" t="s">
@@ -5750,8 +5717,8 @@
       </c>
       <c r="D278" s="2"/>
     </row>
-    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="2" t="n">
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
         <v>278</v>
       </c>
       <c r="B279" s="1" t="s">
@@ -5759,8 +5726,8 @@
       </c>
       <c r="D279" s="2"/>
     </row>
-    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="2" t="n">
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
         <v>279</v>
       </c>
       <c r="B280" s="1" t="s">
@@ -5768,8 +5735,8 @@
       </c>
       <c r="D280" s="2"/>
     </row>
-    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="2" t="n">
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
@@ -5777,8 +5744,8 @@
       </c>
       <c r="D281" s="2"/>
     </row>
-    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="2" t="n">
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
@@ -5786,8 +5753,8 @@
       </c>
       <c r="D282" s="2"/>
     </row>
-    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="2" t="n">
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
@@ -5795,8 +5762,8 @@
       </c>
       <c r="D283" s="2"/>
     </row>
-    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="2" t="n">
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
@@ -5804,8 +5771,8 @@
       </c>
       <c r="D284" s="2"/>
     </row>
-    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="2" t="n">
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
         <v>284</v>
       </c>
       <c r="B285" s="1" t="s">
@@ -5813,8 +5780,8 @@
       </c>
       <c r="D285" s="2"/>
     </row>
-    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="2" t="n">
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
@@ -5822,8 +5789,8 @@
       </c>
       <c r="D286" s="2"/>
     </row>
-    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="2" t="n">
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
@@ -5831,8 +5798,8 @@
       </c>
       <c r="D287" s="2"/>
     </row>
-    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="2" t="n">
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
@@ -5840,8 +5807,8 @@
       </c>
       <c r="D288" s="2"/>
     </row>
-    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="2" t="n">
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
@@ -5849,8 +5816,8 @@
       </c>
       <c r="D289" s="2"/>
     </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="2" t="n">
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
@@ -5858,8 +5825,8 @@
       </c>
       <c r="D290" s="2"/>
     </row>
-    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="2" t="n">
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
@@ -5867,8 +5834,8 @@
       </c>
       <c r="D291" s="2"/>
     </row>
-    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="2" t="n">
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
@@ -5876,8 +5843,8 @@
       </c>
       <c r="D292" s="2"/>
     </row>
-    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="2" t="n">
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
         <v>292</v>
       </c>
       <c r="B293" s="1" t="s">
@@ -5885,8 +5852,8 @@
       </c>
       <c r="D293" s="2"/>
     </row>
-    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="2" t="n">
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
         <v>293</v>
       </c>
       <c r="B294" s="1" t="s">
@@ -5894,8 +5861,8 @@
       </c>
       <c r="D294" s="2"/>
     </row>
-    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="2" t="n">
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
         <v>294</v>
       </c>
       <c r="B295" s="1" t="s">
@@ -5903,8 +5870,8 @@
       </c>
       <c r="D295" s="2"/>
     </row>
-    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="2" t="n">
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
         <v>295</v>
       </c>
       <c r="B296" s="1" t="s">
@@ -5912,8 +5879,8 @@
       </c>
       <c r="D296" s="2"/>
     </row>
-    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="2" t="n">
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
         <v>296</v>
       </c>
       <c r="B297" s="1" t="s">
@@ -5921,8 +5888,8 @@
       </c>
       <c r="D297" s="2"/>
     </row>
-    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="2" t="n">
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
         <v>297</v>
       </c>
       <c r="B298" s="1" t="s">
@@ -5930,8 +5897,8 @@
       </c>
       <c r="D298" s="2"/>
     </row>
-    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="2" t="n">
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
         <v>298</v>
       </c>
       <c r="B299" s="1" t="s">
@@ -5939,8 +5906,8 @@
       </c>
       <c r="D299" s="2"/>
     </row>
-    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="2" t="n">
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
         <v>299</v>
       </c>
       <c r="B300" s="1" t="s">
@@ -5948,8 +5915,8 @@
       </c>
       <c r="D300" s="2"/>
     </row>
-    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="2" t="n">
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
         <v>300</v>
       </c>
       <c r="B301" s="1" t="s">
@@ -5957,1600 +5924,1600 @@
       </c>
       <c r="D301" s="2"/>
     </row>
-    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="2" t="n">
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
         <v>301</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="2" t="n">
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
         <v>302</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="2" t="n">
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
         <v>303</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="2" t="n">
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
         <v>304</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="2" t="n">
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
         <v>305</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="2" t="n">
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
         <v>306</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="2" t="n">
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
         <v>307</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="2" t="n">
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
         <v>308</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="2" t="n">
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
         <v>309</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="2" t="n">
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
         <v>310</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="2" t="n">
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
         <v>311</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="2" t="n">
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
         <v>312</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="2" t="n">
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
         <v>313</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="2" t="n">
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
         <v>314</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="2" t="n">
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
         <v>315</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="2" t="n">
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
         <v>316</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="2" t="n">
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
         <v>317</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="2" t="n">
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
         <v>318</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="2" t="n">
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
         <v>319</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="2" t="n">
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
         <v>320</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="2" t="n">
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
         <v>321</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="2" t="n">
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
         <v>322</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="2" t="n">
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
         <v>323</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="2" t="n">
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
         <v>324</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="2" t="n">
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
         <v>325</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="2" t="n">
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
         <v>326</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="2" t="n">
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
         <v>327</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="2" t="n">
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
         <v>328</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="2" t="n">
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
         <v>329</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="2" t="n">
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
         <v>330</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="2" t="n">
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
         <v>331</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="2" t="n">
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
         <v>332</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="2" t="n">
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
         <v>333</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="2" t="n">
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
         <v>334</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="2" t="n">
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
         <v>335</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="2" t="n">
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
         <v>336</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="2" t="n">
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
         <v>337</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="2" t="n">
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
         <v>338</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="2" t="n">
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
         <v>339</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="2" t="n">
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
         <v>340</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="2" t="n">
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
         <v>341</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="2" t="n">
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
         <v>342</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="2" t="n">
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
         <v>343</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="2" t="n">
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
         <v>344</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="2" t="n">
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
         <v>345</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="2" t="n">
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
         <v>346</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="2" t="n">
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
         <v>347</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="2" t="n">
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
         <v>348</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="2" t="n">
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
         <v>349</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="2" t="n">
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
         <v>350</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="2" t="n">
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
         <v>351</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="2" t="n">
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
         <v>352</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="2" t="n">
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
         <v>353</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="2" t="n">
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
         <v>354</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="2" t="n">
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
         <v>355</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="2" t="n">
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
         <v>356</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="2" t="n">
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
         <v>357</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="2" t="n">
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
         <v>358</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="2" t="n">
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
         <v>359</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="2" t="n">
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
         <v>360</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="2" t="n">
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
         <v>361</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="2" t="n">
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
         <v>362</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="2" t="n">
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
         <v>363</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="2" t="n">
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
         <v>364</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="2" t="n">
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
         <v>365</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="2" t="n">
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
         <v>366</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="2" t="n">
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
         <v>367</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="2" t="n">
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
         <v>368</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="2" t="n">
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
         <v>369</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="2" t="n">
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
         <v>370</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="2" t="n">
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
         <v>371</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="2" t="n">
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
         <v>372</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="2" t="n">
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
         <v>373</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="2" t="n">
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
         <v>374</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="2" t="n">
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
         <v>375</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="2" t="n">
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
         <v>376</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="2" t="n">
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
         <v>377</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="2" t="n">
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
         <v>378</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="2" t="n">
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
         <v>379</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="2" t="n">
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
         <v>380</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="2" t="n">
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
         <v>381</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="2" t="n">
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
         <v>382</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="2" t="n">
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
         <v>383</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="2" t="n">
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
         <v>384</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="2" t="n">
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
         <v>385</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="2" t="n">
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
         <v>386</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="2" t="n">
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
         <v>387</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="2" t="n">
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
         <v>388</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="2" t="n">
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
         <v>389</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="2" t="n">
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
         <v>390</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="2" t="n">
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
         <v>391</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="2" t="n">
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
         <v>392</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="2" t="n">
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
         <v>393</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="2" t="n">
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
         <v>394</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="2" t="n">
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
         <v>395</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="2" t="n">
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
         <v>396</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="2" t="n">
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
         <v>397</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="2" t="n">
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
         <v>398</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="2" t="n">
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
         <v>399</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="2" t="n">
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
         <v>400</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="2" t="n">
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
         <v>401</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="2" t="n">
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
         <v>402</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="2" t="n">
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
         <v>403</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A405" s="2" t="n">
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
         <v>404</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A406" s="2" t="n">
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
         <v>405</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A407" s="2" t="n">
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
         <v>406</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A408" s="2" t="n">
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
         <v>407</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A409" s="2" t="n">
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
         <v>408</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A410" s="2" t="n">
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
         <v>409</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A411" s="2" t="n">
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
         <v>410</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A412" s="2" t="n">
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
         <v>411</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A413" s="2" t="n">
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
         <v>412</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A414" s="2" t="n">
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
         <v>413</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A415" s="2" t="n">
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
         <v>414</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A416" s="2" t="n">
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
         <v>415</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A417" s="2" t="n">
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
         <v>416</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A418" s="2" t="n">
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
         <v>417</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A419" s="2" t="n">
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
         <v>418</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A420" s="2" t="n">
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
         <v>419</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="2" t="n">
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
         <v>420</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="2" t="n">
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
         <v>421</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A423" s="2" t="n">
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
         <v>422</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="2" t="n">
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
         <v>423</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A425" s="2" t="n">
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
         <v>424</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A426" s="2" t="n">
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
         <v>425</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A427" s="2" t="n">
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
         <v>426</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A428" s="2" t="n">
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
         <v>427</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A429" s="2" t="n">
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
         <v>428</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A430" s="2" t="n">
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
         <v>429</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A431" s="2" t="n">
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
         <v>430</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A432" s="2" t="n">
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
         <v>431</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A433" s="2" t="n">
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
         <v>432</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A434" s="2" t="n">
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
         <v>433</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A435" s="2" t="n">
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
         <v>434</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A436" s="2" t="n">
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
         <v>435</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A437" s="2" t="n">
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
         <v>436</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="2" t="n">
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
         <v>437</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A439" s="2" t="n">
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
         <v>438</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A440" s="2" t="n">
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
         <v>439</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A441" s="2" t="n">
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
         <v>440</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A442" s="2" t="n">
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
         <v>441</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="2" t="n">
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
         <v>442</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="2" t="n">
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
         <v>443</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="2" t="n">
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
         <v>444</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="2" t="n">
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
         <v>445</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="2" t="n">
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
         <v>446</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A448" s="2" t="n">
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
         <v>447</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A449" s="2" t="n">
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
         <v>448</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A450" s="2" t="n">
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
         <v>449</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A451" s="2" t="n">
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
         <v>450</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A452" s="2" t="n">
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
         <v>451</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A453" s="2" t="n">
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
         <v>452</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A454" s="2" t="n">
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
         <v>453</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A455" s="2" t="n">
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
         <v>454</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A456" s="2" t="n">
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
         <v>455</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A457" s="2" t="n">
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
         <v>456</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A458" s="2" t="n">
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
         <v>457</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A459" s="2" t="n">
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
         <v>458</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="2" t="n">
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
         <v>459</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="2" t="n">
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
         <v>460</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="2" t="n">
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
         <v>461</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="2" t="n">
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
         <v>462</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A464" s="2" t="n">
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
         <v>463</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A465" s="2" t="n">
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
         <v>464</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A466" s="2" t="n">
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
         <v>465</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A467" s="2" t="n">
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
         <v>466</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="2" t="n">
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
         <v>467</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A469" s="2" t="n">
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
         <v>468</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="2" t="n">
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
         <v>469</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="2" t="n">
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
         <v>470</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="2" t="n">
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
         <v>471</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A473" s="2" t="n">
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
         <v>472</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A474" s="2" t="n">
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
         <v>473</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="2" t="n">
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
         <v>474</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="2" t="n">
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
         <v>475</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A477" s="2" t="n">
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
         <v>476</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A478" s="2" t="n">
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
         <v>477</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="2" t="n">
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
         <v>478</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="2" t="n">
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
         <v>479</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="2" t="n">
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
         <v>480</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A482" s="2" t="n">
+    <row r="482" spans="1:2">
+      <c r="A482" s="2">
         <v>481</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A483" s="2" t="n">
+    <row r="483" spans="1:2">
+      <c r="A483" s="2">
         <v>482</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A484" s="2" t="n">
+    <row r="484" spans="1:2">
+      <c r="A484" s="2">
         <v>483</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A485" s="2" t="n">
+    <row r="485" spans="1:2">
+      <c r="A485" s="2">
         <v>484</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A486" s="2" t="n">
+    <row r="486" spans="1:2">
+      <c r="A486" s="2">
         <v>485</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A487" s="2" t="n">
+    <row r="487" spans="1:2">
+      <c r="A487" s="2">
         <v>486</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="2" t="n">
+    <row r="488" spans="1:2">
+      <c r="A488" s="2">
         <v>487</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="2" t="n">
+    <row r="489" spans="1:2">
+      <c r="A489" s="2">
         <v>488</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="2" t="n">
+    <row r="490" spans="1:2">
+      <c r="A490" s="2">
         <v>489</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A491" s="2" t="n">
+    <row r="491" spans="1:2">
+      <c r="A491" s="2">
         <v>490</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A492" s="2" t="n">
+    <row r="492" spans="1:2">
+      <c r="A492" s="2">
         <v>491</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A493" s="2" t="n">
+    <row r="493" spans="1:2">
+      <c r="A493" s="2">
         <v>492</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A494" s="2" t="n">
+    <row r="494" spans="1:2">
+      <c r="A494" s="2">
         <v>493</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A495" s="2" t="n">
+    <row r="495" spans="1:2">
+      <c r="A495" s="2">
         <v>494</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A496" s="2" t="n">
+    <row r="496" spans="1:2">
+      <c r="A496" s="2">
         <v>495</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A497" s="2" t="n">
+    <row r="497" spans="1:2">
+      <c r="A497" s="2">
         <v>496</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A498" s="2" t="n">
+    <row r="498" spans="1:2">
+      <c r="A498" s="2">
         <v>497</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="2" t="n">
+    <row r="499" spans="1:2">
+      <c r="A499" s="2">
         <v>498</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="2" t="n">
+    <row r="500" spans="1:2">
+      <c r="A500" s="2">
         <v>499</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A501" s="2" t="n">
+    <row r="501" spans="1:2">
+      <c r="A501" s="2">
         <v>500</v>
       </c>
       <c r="B501" s="1" t="s">
@@ -7558,10 +7525,9 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>

--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -1564,7 +1564,7 @@
     <t xml:space="preserve">Dlaczego jesteś dla mnie taki zimny?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, TY, DLA-MNIE, ZIMNY?</t>
+    <t xml:space="preserve">DLACZEGO, TY, DLA-MNIE, ZIMNY</t>
   </si>
   <si>
     <t xml:space="preserve">Zostałem przed szkołą, bo czekałem na babcię.</t>
@@ -1582,7 +1582,7 @@
     <t xml:space="preserve">Czy słyszycie tego kota przed szkołą?</t>
   </si>
   <si>
-    <t xml:space="preserve">WY, SŁYSZEĆ, KOT, TEN, PRZED, SZKOŁA?</t>
+    <t xml:space="preserve">WY, SŁYSZEĆ, KOT, TEN, PRZED, SZKOŁA</t>
   </si>
   <si>
     <t xml:space="preserve">Ja wczoraj w nocy myślałem o mojej pracy.</t>
@@ -1624,13 +1624,13 @@
     <t xml:space="preserve">Czy wiesz, jak kupić ten duży dom?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, WIEDZIEĆ, JAK, KUPIĆ, DOM, DUŻY, TEN?</t>
+    <t xml:space="preserve">TY, WIEDZIEĆ, JAK, KUPIĆ, DOM, DUŻY, TEN</t>
   </si>
   <si>
     <t xml:space="preserve">Przepraszam, gdzie jest woda dla małego psa, który jest chory? </t>
   </si>
   <si>
-    <t xml:space="preserve">PRZEPRASZAM, WODA, DLA, PIES, MAŁY, CHORY, GDZIE?</t>
+    <t xml:space="preserve">PRZEPRASZAM, WODA, DLA, PIES, MAŁY, CHORY, GDZIE</t>
   </si>
   <si>
     <t xml:space="preserve">Wczoraj wieczorem widziałam mojego starego kolegę.</t>
@@ -1642,13 +1642,13 @@
     <t xml:space="preserve">Niech ten pies zostanie w domu z kotem!</t>
   </si>
   <si>
-    <t xml:space="preserve">PIES, TEN, DOM, ZOSTAĆ, RAZEM, KOT!</t>
+    <t xml:space="preserve">PIES, TEN, DOM, ZOSTAĆ, RAZEM, KOT</t>
   </si>
   <si>
     <t xml:space="preserve">Czy wy rozumiecie, że jutro będzie bardzo zimny i smutny dzień dla mamy? </t>
   </si>
   <si>
-    <t xml:space="preserve">WY, ROZUMIEĆ, JUTRO, DZIEŃ, BARDZO, ZIMNY, SMUTNY, DLA, MAMA?</t>
+    <t xml:space="preserve">WY, ROZUMIEĆ, JUTRO, DZIEŃ, BARDZO, ZIMNY, SMUTNY, DLA, MAMA</t>
   </si>
   <si>
     <t xml:space="preserve">Piję teraz herbatę w tę środę, bo często w taki gorący dzień musimy dużo pić. </t>
@@ -1660,7 +1660,7 @@
     <t xml:space="preserve">Czy masz dla mnie nowy pomysł na urodziny?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, MIEĆ, DLA-MNIE, POMYSŁ, NOWY, NA, URODZINY?</t>
+    <t xml:space="preserve">TY, MIEĆ, DLA-MNIE, POMYSŁ, NOWY, NA, URODZINY</t>
   </si>
   <si>
     <t xml:space="preserve">Praca w noc nie jest dobra dla mnie.</t>
@@ -1684,7 +1684,7 @@
     <t xml:space="preserve">Dlaczego ona wczoraj bardzo dużo jadła?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, ONA, WCZORAJ, JEŚĆ, BARDZO-DUŻO?</t>
+    <t xml:space="preserve">DLACZEGO, ONA, WCZORAJ, JEŚĆ, BARDZO-DUŻO</t>
   </si>
   <si>
     <t xml:space="preserve">Mój telefon jest mały, a twój samochód jest duży.</t>
@@ -1726,7 +1726,7 @@
     <t xml:space="preserve">Ten rok to czas, kiedy już bardzo dużo pracujemy w domu.</t>
   </si>
   <si>
-    <t xml:space="preserve">TEN, ROK, =, CZAS, MY, JUŻ, BARDZO-DUŻO, DOM, PRACOWAĆ</t>
+    <t xml:space="preserve">TEN, ROK, CZAS, MY, JUŻ, BARDZO-DUŻO, DOM, PRACOWAĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Brat ma ten nowy telefon już rok i jest bardzo dobry.</t>
@@ -1744,13 +1744,13 @@
     <t xml:space="preserve">Kiedy on wczoraj kupił tego małego kota?</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, ON, KUPIĆ, KOT, MAŁY, KIEDY?</t>
+    <t xml:space="preserve">WCZORAJ, ON, KUPIĆ, KOT, MAŁY, KIEDY</t>
   </si>
   <si>
     <t xml:space="preserve">Czy wiesz, dlaczego twoja siostra jest dzisiaj smutna?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, WIEDZIEĆ, DLACZEGO, TWOJA, SIOSTRA, DZISIAJ, SMUTNA?</t>
+    <t xml:space="preserve">TY, WIEDZIEĆ, DLACZEGO, TWOJA, SIOSTRA, DZISIAJ, SMUTNA</t>
   </si>
   <si>
     <t xml:space="preserve">Dziadek, który jest chory, już rok nie był w szkole </t>
@@ -1798,7 +1798,7 @@
     <t xml:space="preserve">Ile w roku się to robi, żeby być zdrowym? </t>
   </si>
   <si>
-    <t xml:space="preserve">ROK, W-CIĄGU, TO, ROBIĆ, ILE, ABY, ZDROWY, BYĆ?</t>
+    <t xml:space="preserve">ROK, W-CIĄGU, TO, ROBIĆ, ILE, ABY, ZDROWY, BYĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Ja nie mam teraz pieniędzy na tę dużą książkę dla siostry</t>
@@ -1810,7 +1810,7 @@
     <t xml:space="preserve">Dlaczego ten mężczyzna z psem idzie do szkoły?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, TEN, MĘŻCZYZNA, Z, PSEM, IŚĆ, SZKOŁA?</t>
+    <t xml:space="preserve">DLACZEGO, TEN, MĘŻCZYZNA, Z, PSEM, IŚĆ, SZKOŁA</t>
   </si>
   <si>
     <t xml:space="preserve">W nocy kot mojego brata bardzo często pije wodę.</t>
@@ -1840,7 +1840,7 @@
     <t xml:space="preserve">Czy twój mały brat lubi się uczyć?</t>
   </si>
   <si>
-    <t xml:space="preserve">TWÓJ, BRAT, MAŁY, LUBI, UCZYĆ-SIĘ?</t>
+    <t xml:space="preserve">TWÓJ, BRAT, MAŁY, LUBI, UCZYĆ-SIĘ</t>
   </si>
   <si>
     <t xml:space="preserve">Pamiętaj, żeby rano kupić gorącą kawę dla dziadka.</t>
@@ -1858,7 +1858,7 @@
     <t xml:space="preserve">Dlaczego ty zawsze musisz być taki zmęczony?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, TY, ZAWSZE, MUSIEĆ, ZMĘCZONY, BYĆ?</t>
+    <t xml:space="preserve">DLACZEGO, TY, ZAWSZE, MUSIEĆ, ZMĘCZONY, BYĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Widziałem wczoraj twoją babcię w starym samochodzie.</t>
@@ -1888,7 +1888,7 @@
     <t xml:space="preserve">Przepraszam, czy wy w środę to robicie? </t>
   </si>
   <si>
-    <t xml:space="preserve">PRZEPRASZAM, WY, TO, ŚRODA, ROBIĆ?</t>
+    <t xml:space="preserve">PRZEPRASZAM, WY, TO, ŚRODA, ROBIĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Czekam, żeby z tobą iść na kawę.</t>
@@ -1900,7 +1900,7 @@
     <t xml:space="preserve">Czy zdrowym jest robić to z roku na rok, i ile? </t>
   </si>
   <si>
-    <t xml:space="preserve">TO, ROBIĆ, ROK-PO-ROK, ZDROWE, ILE?</t>
+    <t xml:space="preserve">TO, ROBIĆ, ROK-PO-ROK, ZDROWE, ILE</t>
   </si>
   <si>
     <t xml:space="preserve">Uczę się dużo, żeby móc pracować w szkole.</t>
@@ -1912,7 +1912,7 @@
     <t xml:space="preserve">Kiedy kupisz ten stary dom dla dziadka?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, KUPIĆ, DOM, STARY, DLA, DZIADEK, KIEDY?</t>
+    <t xml:space="preserve">TY, KUPIĆ, DOM, STARY, DLA, DZIADEK, KIEDY</t>
   </si>
   <si>
     <t xml:space="preserve">Woda w noc była bardzo zimna dla mojego psa.</t>
@@ -1966,7 +1966,7 @@
     <t xml:space="preserve">Gdzie jest ten mały kot mojej siostry?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, KOT, MAŁY, MOJA, SIOSTRA?</t>
+    <t xml:space="preserve">GDZIE, KOT, MAŁY, MOJA, SIOSTRA</t>
   </si>
   <si>
     <t xml:space="preserve">Jutro rano idę do szkoły z moim nowym telefonem.</t>
@@ -1978,7 +1978,7 @@
     <t xml:space="preserve">Przepraszam, ile mogę to robić w czwartek? </t>
   </si>
   <si>
-    <t xml:space="preserve">PRZEPRASZAM, CZWARTEK, JA, MÓC, TO, ROBIĆ, ILE?</t>
+    <t xml:space="preserve">PRZEPRASZAM, CZWARTEK, JA, MÓC, TO, ROBIĆ, ILE</t>
   </si>
   <si>
     <t xml:space="preserve">Praca w domu jest dla mnie bardzo dobra.</t>
@@ -2002,7 +2002,7 @@
     <t xml:space="preserve">Czy wy rozumiecie, że to był ważny rok? </t>
   </si>
   <si>
-    <t xml:space="preserve">WY, ROZUMIEĆ, TO, BYĆ, ROK, WAŻNY?</t>
+    <t xml:space="preserve">WY, ROZUMIEĆ, TO, BYĆ, ROK, WAŻNY</t>
   </si>
   <si>
     <t xml:space="preserve">Ja i ty musimy dużo pracować, żeby mieć na dom.</t>
@@ -2014,19 +2014,19 @@
     <t xml:space="preserve">Kto wczoraj rano kupił ten stary samochód taty?</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, RANO, KTO, KUPIĆ, TATA, SAMOCHÓD, STARY?</t>
+    <t xml:space="preserve">WCZORAJ, RANO, KTO, KUPIĆ, TATA, SAMOCHÓD, STARY</t>
   </si>
   <si>
     <t xml:space="preserve">Ile to się robi, rok? </t>
   </si>
   <si>
-    <t xml:space="preserve">TO, ROBIĆ, ILE, ROK?</t>
+    <t xml:space="preserve">TO, ROBIĆ, ILE, ROK</t>
   </si>
   <si>
     <t xml:space="preserve">Dlaczego jesteś bardzo zimny w ten gorący dzień?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, TY, BARDZO, ZIMNY, W, TEN, DZIEŃ, GORĄCY?</t>
+    <t xml:space="preserve">DLACZEGO, TY, BARDZO, ZIMNY, W, TEN, DZIEŃ, GORĄCY</t>
   </si>
   <si>
     <t xml:space="preserve">Kobieta z małym psem idzie rano do pracy.</t>
@@ -2062,7 +2062,7 @@
     <t xml:space="preserve">Kiedy idziemy na dużą kawę z kolegą?</t>
   </si>
   <si>
-    <t xml:space="preserve">MY, IŚĆ, KIEDY, NA, KAWA, DUŻA, Z, KOLEGA?</t>
+    <t xml:space="preserve">MY, IŚĆ, KIEDY, NA, KAWA, DUŻA, Z, KOLEGA</t>
   </si>
   <si>
     <t xml:space="preserve">Niech mój przyjaciel czeka na mnie przed szkołą.</t>
@@ -2104,7 +2104,7 @@
     <t xml:space="preserve">Gdzie jest klucz do tego małego samochodu?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, KLUCZ, SAMOCHÓD, MAŁY, TEN?</t>
+    <t xml:space="preserve">GDZIE, KLUCZ, SAMOCHÓD, MAŁY, TEN</t>
   </si>
   <si>
     <t xml:space="preserve">Ja bardzo lubię, kiedy pijesz ze mną kawę.</t>
@@ -2164,13 +2164,13 @@
     <t xml:space="preserve">Gdzie my wczoraj kupiliśmy tę gorącą kawę?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, MY, WCZORAJ, KUPIĆ, KAWA, GORĄCA, TA?</t>
+    <t xml:space="preserve">GDZIE, MY, WCZORAJ, KUPIĆ, KAWA, GORĄCA, TA</t>
   </si>
   <si>
     <t xml:space="preserve">Kto chory idzie rano do szkoły?</t>
   </si>
   <si>
-    <t xml:space="preserve">KTO, CHORY, RANO, IŚĆ, SZKOŁA?</t>
+    <t xml:space="preserve">KTO, CHORY, RANO, IŚĆ, SZKOŁA</t>
   </si>
   <si>
     <t xml:space="preserve">Ich brat ma urodziny w poniedziałek wieczorem.</t>
@@ -2182,7 +2182,7 @@
     <t xml:space="preserve">Ile kawy dzisiaj rano piła twoja mama?</t>
   </si>
   <si>
-    <t xml:space="preserve">DZISIAJ, RANO, TWOJA, MAMA, PIĆ, KAWA, ILE?</t>
+    <t xml:space="preserve">DZISIAJ, RANO, TWOJA, MAMA, PIĆ, KAWA, ILE</t>
   </si>
   <si>
     <t xml:space="preserve">Czekam na ciebie, żeby iść do starych przyjaciół.</t>
@@ -2194,7 +2194,7 @@
     <t xml:space="preserve">Czy ty widziałeś rano mojego małego brata?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, WIDZIEĆ, RANO, MÓJ, BRAT, MAŁY?</t>
+    <t xml:space="preserve">TY, WIDZIEĆ, RANO, MÓJ, BRAT, MAŁY</t>
   </si>
   <si>
     <t xml:space="preserve">Dzisiaj bardzo chcę uczyć się z twoją siostrą.</t>
@@ -2212,7 +2212,7 @@
     <t xml:space="preserve">Dlaczego ta książka, którą ma ta kobieta, jest dla ciebie taka ważna?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, KSIĄŻKA, TA, KOBIETA, MIEĆ, DLA-CIEBIE, WAŻNA?</t>
+    <t xml:space="preserve">DLACZEGO, KSIĄŻKA, TA, KOBIETA, MIEĆ, DLA-CIEBIE, WAŻNA</t>
   </si>
   <si>
     <t xml:space="preserve">Ten dzień był dla mojego przyjaciela bardzo smutny.</t>
@@ -2260,7 +2260,7 @@
     <t xml:space="preserve">Czy wiesz, gdzie brat mojego kolegi kupił telefon?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, WIEDZIEĆ, GDZIE, BRAT, MOJEGO, KOLEGI, KUPIĆ, TELEFON?</t>
+    <t xml:space="preserve">TY, WIEDZIEĆ, GDZIE, BRAT, MOJEGO, KOLEGI, KUPIĆ, TELEFON</t>
   </si>
   <si>
     <t xml:space="preserve">Kocham ten czas, kiedy rano we wtorek piję kawę</t>
@@ -2320,19 +2320,19 @@
     <t xml:space="preserve">Czy wy już wiecie, co on chce robić w ten czwartek?</t>
   </si>
   <si>
-    <t xml:space="preserve">WY, JUŻ, WIEDZIEĆ, CO, ON, CHCIEĆ, ROBIĆ, CZWARTEK?</t>
+    <t xml:space="preserve">WY, JUŻ, WIEDZIEĆ, CO, ON, CHCIEĆ, ROBIĆ, CZWARTEK</t>
   </si>
   <si>
     <t xml:space="preserve">Dlaczego myślisz, że jestem bardzo smutny?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, TY, MYŚLEĆ, JA, BARDZO, SMUTNY?</t>
+    <t xml:space="preserve">DLACZEGO, TY, MYŚLEĆ, JA, BARDZO, SMUTNY</t>
   </si>
   <si>
     <t xml:space="preserve">Kiedy kupiłeś ten duży dom dla dziadka?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, KUPIĆ, DOM, DUŻY, TEN, DLA, DZIADEK, KIEDY?</t>
+    <t xml:space="preserve">TY, KUPIĆ, DOM, DUŻY, TEN, DLA, DZIADEK, KIEDY</t>
   </si>
   <si>
     <t xml:space="preserve">Mój stary samochód nie chce rano pracować.</t>
@@ -2350,7 +2350,7 @@
     <t xml:space="preserve">Gdzie twój kolega kupił taką dobrą herbatę?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, TWÓJ, KOLEGA, KUPIĆ, HERBATA, DOBRA, TAKA?</t>
+    <t xml:space="preserve">GDZIE, TWÓJ, KOLEGA, KUPIĆ, HERBATA, DOBRA, TAKA</t>
   </si>
   <si>
     <t xml:space="preserve">W poniedziałek wieczorem będę dużo pracował u mamy.</t>
@@ -2362,7 +2362,7 @@
     <t xml:space="preserve">Czy widziałeś rano mojego psa przed domem?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, WIDZIEĆ, RANO, MÓJ, PIES, PRZED, DOM?</t>
+    <t xml:space="preserve">TY, WIDZIEĆ, RANO, MÓJ, PIES, PRZED, DOM</t>
   </si>
   <si>
     <t xml:space="preserve">Chcę wiedzieć, dlaczego nie masz pieniędzy na książkę.</t>
@@ -2767,7 +2767,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2778,10 +2778,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2946,7 +2942,7 @@
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
@@ -2958,7 +2954,7 @@
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="2"/>
@@ -2970,7 +2966,7 @@
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="2"/>
@@ -2982,7 +2978,7 @@
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2"/>
@@ -2994,7 +2990,7 @@
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="2"/>
@@ -3006,7 +3002,7 @@
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="2"/>
@@ -3018,7 +3014,7 @@
       <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="2"/>
@@ -3030,7 +3026,7 @@
       <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="2"/>
@@ -3042,7 +3038,7 @@
       <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="2"/>
@@ -3054,7 +3050,7 @@
       <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="2"/>
@@ -3066,7 +3062,7 @@
       <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="2"/>
@@ -3078,7 +3074,7 @@
       <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="2"/>
@@ -3090,7 +3086,7 @@
       <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="2"/>
@@ -3102,7 +3098,7 @@
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="2"/>
@@ -3114,7 +3110,7 @@
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D16" s="2"/>
@@ -3126,7 +3122,7 @@
       <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="2"/>
@@ -3138,7 +3134,7 @@
       <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="2"/>
@@ -3150,7 +3146,7 @@
       <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D19" s="2"/>
@@ -3162,7 +3158,7 @@
       <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="2"/>
@@ -3174,7 +3170,7 @@
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="2"/>
@@ -3186,7 +3182,7 @@
       <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="2"/>
@@ -3198,7 +3194,7 @@
       <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="2"/>
@@ -3210,7 +3206,7 @@
       <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D24" s="2"/>
@@ -3222,7 +3218,7 @@
       <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="2"/>
@@ -3234,7 +3230,7 @@
       <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="2"/>
@@ -3246,7 +3242,7 @@
       <c r="B27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D27" s="2"/>
@@ -3258,7 +3254,7 @@
       <c r="B28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="3"/>
       <c r="D28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3268,7 +3264,7 @@
       <c r="B29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="4"/>
+      <c r="C29" s="3"/>
       <c r="D29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3278,7 +3274,7 @@
       <c r="B30" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="2"/>
@@ -3290,7 +3286,7 @@
       <c r="B31" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D31" s="2"/>
@@ -3302,7 +3298,7 @@
       <c r="B32" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D32" s="2"/>
@@ -3314,7 +3310,7 @@
       <c r="B33" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="2"/>
@@ -3326,7 +3322,7 @@
       <c r="B34" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D34" s="2"/>
@@ -3338,7 +3334,7 @@
       <c r="B35" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D35" s="2"/>
@@ -3350,7 +3346,7 @@
       <c r="B36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D36" s="2"/>
@@ -3362,7 +3358,7 @@
       <c r="B37" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>72</v>
       </c>
       <c r="D37" s="2"/>
@@ -3374,7 +3370,7 @@
       <c r="B38" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D38" s="2"/>
@@ -3386,7 +3382,7 @@
       <c r="B39" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>76</v>
       </c>
       <c r="D39" s="2"/>
@@ -3398,7 +3394,7 @@
       <c r="B40" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D40" s="2"/>
@@ -3410,7 +3406,7 @@
       <c r="B41" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="2"/>
@@ -3422,7 +3418,7 @@
       <c r="B42" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>82</v>
       </c>
       <c r="D42" s="2"/>
@@ -3434,7 +3430,7 @@
       <c r="B43" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D43" s="2"/>
@@ -3446,7 +3442,7 @@
       <c r="B44" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D44" s="2"/>
@@ -3458,7 +3454,7 @@
       <c r="B45" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>88</v>
       </c>
       <c r="D45" s="2"/>
@@ -3470,7 +3466,7 @@
       <c r="B46" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D46" s="2"/>
@@ -3482,7 +3478,7 @@
       <c r="B47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D47" s="2"/>
@@ -3494,7 +3490,7 @@
       <c r="B48" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D48" s="2"/>
@@ -3506,7 +3502,7 @@
       <c r="B49" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D49" s="2"/>
@@ -3518,7 +3514,7 @@
       <c r="B50" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>98</v>
       </c>
       <c r="D50" s="2"/>
@@ -3530,7 +3526,7 @@
       <c r="B51" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D51" s="2"/>
@@ -3542,7 +3538,7 @@
       <c r="B52" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D52" s="2"/>
@@ -3554,7 +3550,7 @@
       <c r="B53" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="4" t="s">
         <v>104</v>
       </c>
       <c r="D53" s="2"/>
@@ -3566,7 +3562,7 @@
       <c r="B54" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>106</v>
       </c>
       <c r="D54" s="2"/>
@@ -3578,7 +3574,7 @@
       <c r="B55" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D55" s="2"/>
@@ -3590,7 +3586,7 @@
       <c r="B56" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>110</v>
       </c>
       <c r="D56" s="2"/>
@@ -3602,7 +3598,7 @@
       <c r="B57" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>112</v>
       </c>
       <c r="D57" s="2"/>
@@ -3614,7 +3610,7 @@
       <c r="B58" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>114</v>
       </c>
       <c r="D58" s="2"/>
@@ -3626,7 +3622,7 @@
       <c r="B59" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="4" t="s">
         <v>116</v>
       </c>
       <c r="D59" s="2"/>
@@ -3638,7 +3634,7 @@
       <c r="B60" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="4" t="s">
         <v>118</v>
       </c>
       <c r="D60" s="2"/>
@@ -3650,7 +3646,7 @@
       <c r="B61" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="4" t="s">
         <v>120</v>
       </c>
       <c r="D61" s="2"/>
@@ -3662,7 +3658,7 @@
       <c r="B62" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>122</v>
       </c>
       <c r="D62" s="2"/>
@@ -3674,7 +3670,7 @@
       <c r="B63" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D63" s="2"/>
@@ -3686,7 +3682,7 @@
       <c r="B64" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="4" t="s">
         <v>126</v>
       </c>
       <c r="D64" s="2"/>
@@ -3698,7 +3694,7 @@
       <c r="B65" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="4" t="s">
         <v>128</v>
       </c>
       <c r="D65" s="2"/>
@@ -3710,7 +3706,7 @@
       <c r="B66" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D66" s="2"/>
@@ -3722,7 +3718,7 @@
       <c r="B67" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="4" t="s">
         <v>132</v>
       </c>
       <c r="D67" s="2"/>
@@ -3734,7 +3730,7 @@
       <c r="B68" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D68" s="2"/>
@@ -3746,7 +3742,7 @@
       <c r="B69" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D69" s="2"/>
@@ -3758,7 +3754,7 @@
       <c r="B70" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="4" t="s">
         <v>138</v>
       </c>
       <c r="D70" s="2"/>
@@ -3770,7 +3766,7 @@
       <c r="B71" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D71" s="2"/>
@@ -3782,7 +3778,7 @@
       <c r="B72" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="4" t="s">
         <v>142</v>
       </c>
       <c r="D72" s="2"/>
@@ -3794,7 +3790,7 @@
       <c r="B73" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="4" t="s">
         <v>144</v>
       </c>
       <c r="D73" s="2"/>
@@ -3806,7 +3802,7 @@
       <c r="B74" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>146</v>
       </c>
       <c r="D74" s="2"/>
@@ -3818,7 +3814,7 @@
       <c r="B75" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="4" t="s">
         <v>148</v>
       </c>
       <c r="D75" s="2"/>
@@ -3830,7 +3826,7 @@
       <c r="B76" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="4" t="s">
         <v>150</v>
       </c>
       <c r="D76" s="2"/>
@@ -3842,7 +3838,7 @@
       <c r="B77" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="4" t="s">
         <v>152</v>
       </c>
       <c r="D77" s="2"/>
@@ -3854,7 +3850,7 @@
       <c r="B78" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="4" t="s">
         <v>154</v>
       </c>
       <c r="D78" s="2"/>
@@ -3866,7 +3862,7 @@
       <c r="B79" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="4" t="s">
         <v>156</v>
       </c>
       <c r="D79" s="2"/>
@@ -3878,7 +3874,7 @@
       <c r="B80" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="4" t="s">
         <v>158</v>
       </c>
       <c r="D80" s="2"/>
@@ -3890,7 +3886,7 @@
       <c r="B81" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D81" s="2"/>
@@ -3902,7 +3898,7 @@
       <c r="B82" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="4" t="s">
         <v>162</v>
       </c>
       <c r="D82" s="2"/>
@@ -3914,7 +3910,7 @@
       <c r="B83" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D83" s="2"/>
@@ -3926,7 +3922,7 @@
       <c r="B84" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D84" s="2"/>
@@ -3938,7 +3934,7 @@
       <c r="B85" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D85" s="2"/>
@@ -3950,7 +3946,7 @@
       <c r="B86" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="4" t="s">
         <v>170</v>
       </c>
       <c r="D86" s="2"/>
@@ -3962,7 +3958,7 @@
       <c r="B87" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="4" t="s">
         <v>172</v>
       </c>
       <c r="D87" s="2"/>
@@ -3974,7 +3970,7 @@
       <c r="B88" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D88" s="2"/>
@@ -3986,7 +3982,7 @@
       <c r="B89" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="4" t="s">
         <v>176</v>
       </c>
       <c r="D89" s="2"/>
@@ -3998,7 +3994,7 @@
       <c r="B90" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="4" t="s">
         <v>178</v>
       </c>
       <c r="D90" s="2"/>
@@ -4010,7 +4006,7 @@
       <c r="B91" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="4" t="s">
         <v>180</v>
       </c>
       <c r="D91" s="2"/>
@@ -4022,7 +4018,7 @@
       <c r="B92" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="4" t="s">
         <v>182</v>
       </c>
       <c r="D92" s="2"/>
@@ -4034,7 +4030,7 @@
       <c r="B93" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="4" t="s">
         <v>184</v>
       </c>
       <c r="D93" s="2"/>
@@ -4046,7 +4042,7 @@
       <c r="B94" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="4" t="s">
         <v>186</v>
       </c>
       <c r="D94" s="2"/>
@@ -4058,7 +4054,7 @@
       <c r="B95" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D95" s="2"/>
@@ -4070,7 +4066,7 @@
       <c r="B96" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C96" s="4" t="s">
         <v>190</v>
       </c>
       <c r="D96" s="2"/>
@@ -4082,7 +4078,7 @@
       <c r="B97" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C97" s="4" t="s">
         <v>192</v>
       </c>
       <c r="D97" s="2"/>
@@ -4094,7 +4090,7 @@
       <c r="B98" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="4" t="s">
         <v>194</v>
       </c>
       <c r="D98" s="2"/>
@@ -4106,7 +4102,7 @@
       <c r="B99" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C99" s="4" t="s">
         <v>196</v>
       </c>
       <c r="D99" s="2"/>
@@ -4118,7 +4114,7 @@
       <c r="B100" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C100" s="4" t="s">
         <v>198</v>
       </c>
       <c r="D100" s="2"/>
@@ -4130,7 +4126,7 @@
       <c r="B101" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C101" s="5" t="s">
+      <c r="C101" s="4" t="s">
         <v>200</v>
       </c>
       <c r="D101" s="2"/>
@@ -4142,7 +4138,7 @@
       <c r="B102" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C102" s="4" t="s">
         <v>202</v>
       </c>
       <c r="D102" s="2"/>
@@ -4154,7 +4150,7 @@
       <c r="B103" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="C103" s="4" t="s">
         <v>204</v>
       </c>
       <c r="D103" s="2"/>
@@ -4166,7 +4162,7 @@
       <c r="B104" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C104" s="4" t="s">
         <v>206</v>
       </c>
       <c r="D104" s="2"/>
@@ -4178,7 +4174,7 @@
       <c r="B105" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="C105" s="4" t="s">
         <v>208</v>
       </c>
       <c r="D105" s="2"/>
@@ -4190,7 +4186,7 @@
       <c r="B106" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C106" s="4" t="s">
         <v>210</v>
       </c>
       <c r="D106" s="2"/>
@@ -4202,7 +4198,7 @@
       <c r="B107" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="C107" s="4" t="s">
         <v>212</v>
       </c>
       <c r="D107" s="2"/>
@@ -4214,7 +4210,7 @@
       <c r="B108" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C108" s="4" t="s">
         <v>214</v>
       </c>
       <c r="D108" s="2"/>
@@ -4226,7 +4222,7 @@
       <c r="B109" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C109" s="5" t="s">
+      <c r="C109" s="4" t="s">
         <v>216</v>
       </c>
       <c r="D109" s="2"/>
@@ -4238,7 +4234,7 @@
       <c r="B110" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C110" s="4" t="s">
         <v>218</v>
       </c>
       <c r="D110" s="2"/>
@@ -4250,7 +4246,7 @@
       <c r="B111" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="C111" s="4" t="s">
         <v>220</v>
       </c>
       <c r="D111" s="2"/>
@@ -4262,7 +4258,7 @@
       <c r="B112" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C112" s="4" t="s">
         <v>222</v>
       </c>
       <c r="D112" s="2"/>
@@ -4274,7 +4270,7 @@
       <c r="B113" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C113" s="4" t="s">
         <v>224</v>
       </c>
       <c r="D113" s="2"/>
@@ -4286,7 +4282,7 @@
       <c r="B114" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C114" s="4" t="s">
         <v>226</v>
       </c>
       <c r="D114" s="2"/>
@@ -4298,7 +4294,7 @@
       <c r="B115" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="C115" s="4" t="s">
         <v>228</v>
       </c>
       <c r="D115" s="2"/>
@@ -4310,7 +4306,7 @@
       <c r="B116" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C116" s="4" t="s">
         <v>230</v>
       </c>
       <c r="D116" s="2"/>
@@ -4322,7 +4318,7 @@
       <c r="B117" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="C117" s="4" t="s">
         <v>232</v>
       </c>
       <c r="D117" s="2"/>
@@ -4334,7 +4330,7 @@
       <c r="B118" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C118" s="4" t="s">
         <v>234</v>
       </c>
       <c r="D118" s="2"/>
@@ -4346,7 +4342,7 @@
       <c r="B119" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="C119" s="4" t="s">
         <v>236</v>
       </c>
       <c r="D119" s="2"/>
@@ -4358,7 +4354,7 @@
       <c r="B120" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C120" s="4" t="s">
         <v>238</v>
       </c>
       <c r="D120" s="2"/>
@@ -4370,7 +4366,7 @@
       <c r="B121" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="C121" s="4" t="s">
         <v>240</v>
       </c>
       <c r="D121" s="2"/>
@@ -4382,7 +4378,7 @@
       <c r="B122" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C122" s="4" t="s">
         <v>242</v>
       </c>
       <c r="D122" s="2"/>
@@ -4394,7 +4390,7 @@
       <c r="B123" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="C123" s="4" t="s">
         <v>244</v>
       </c>
       <c r="D123" s="2"/>
@@ -4406,7 +4402,7 @@
       <c r="B124" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="C124" s="4" t="s">
         <v>246</v>
       </c>
       <c r="D124" s="2"/>
@@ -4418,7 +4414,7 @@
       <c r="B125" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="C125" s="4" t="s">
         <v>248</v>
       </c>
       <c r="D125" s="2"/>
@@ -4430,7 +4426,7 @@
       <c r="B126" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C126" s="4" t="s">
         <v>250</v>
       </c>
       <c r="D126" s="2"/>
@@ -4442,7 +4438,7 @@
       <c r="B127" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="C127" s="4" t="s">
         <v>252</v>
       </c>
       <c r="D127" s="2"/>
@@ -4454,7 +4450,7 @@
       <c r="B128" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C128" s="4" t="s">
         <v>254</v>
       </c>
       <c r="D128" s="2"/>
@@ -4466,7 +4462,7 @@
       <c r="B129" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="C129" s="4" t="s">
         <v>256</v>
       </c>
       <c r="D129" s="2"/>
@@ -4478,7 +4474,7 @@
       <c r="B130" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="C130" s="4" t="s">
         <v>258</v>
       </c>
       <c r="D130" s="2"/>
@@ -4490,7 +4486,7 @@
       <c r="B131" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C131" s="4" t="s">
         <v>260</v>
       </c>
       <c r="D131" s="2"/>
@@ -4502,7 +4498,7 @@
       <c r="B132" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="C132" s="4" t="s">
         <v>262</v>
       </c>
       <c r="D132" s="2"/>
@@ -4514,7 +4510,7 @@
       <c r="B133" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="C133" s="4" t="s">
         <v>264</v>
       </c>
       <c r="D133" s="2"/>
@@ -4526,7 +4522,7 @@
       <c r="B134" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C134" s="4" t="s">
         <v>266</v>
       </c>
       <c r="D134" s="2"/>
@@ -4538,7 +4534,7 @@
       <c r="B135" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="C135" s="4" t="s">
         <v>268</v>
       </c>
       <c r="D135" s="2"/>
@@ -4550,7 +4546,7 @@
       <c r="B136" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C136" s="4" t="s">
         <v>270</v>
       </c>
       <c r="D136" s="2"/>
@@ -4562,7 +4558,7 @@
       <c r="B137" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="C137" s="4" t="s">
         <v>272</v>
       </c>
       <c r="D137" s="2"/>
@@ -4574,7 +4570,7 @@
       <c r="B138" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C138" s="4" t="s">
         <v>274</v>
       </c>
       <c r="D138" s="2"/>
@@ -4586,7 +4582,7 @@
       <c r="B139" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C139" s="5" t="s">
+      <c r="C139" s="4" t="s">
         <v>276</v>
       </c>
       <c r="D139" s="2"/>
@@ -4598,7 +4594,7 @@
       <c r="B140" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="C140" s="4" t="s">
         <v>278</v>
       </c>
       <c r="D140" s="2"/>
@@ -4610,7 +4606,7 @@
       <c r="B141" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C141" s="5" t="s">
+      <c r="C141" s="4" t="s">
         <v>280</v>
       </c>
       <c r="D141" s="2"/>
@@ -4622,7 +4618,7 @@
       <c r="B142" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C142" s="4" t="s">
         <v>282</v>
       </c>
       <c r="D142" s="2"/>
@@ -4634,7 +4630,7 @@
       <c r="B143" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C143" s="4" t="s">
         <v>284</v>
       </c>
       <c r="D143" s="2"/>
@@ -4646,7 +4642,7 @@
       <c r="B144" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="C144" s="4" t="s">
         <v>286</v>
       </c>
       <c r="D144" s="2"/>
@@ -4658,7 +4654,7 @@
       <c r="B145" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C145" s="4" t="s">
         <v>288</v>
       </c>
       <c r="D145" s="2"/>
@@ -4670,7 +4666,7 @@
       <c r="B146" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="C146" s="4" t="s">
         <v>290</v>
       </c>
       <c r="D146" s="2"/>
@@ -4682,7 +4678,7 @@
       <c r="B147" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C147" s="5" t="s">
+      <c r="C147" s="4" t="s">
         <v>292</v>
       </c>
       <c r="D147" s="2"/>
@@ -4694,7 +4690,7 @@
       <c r="B148" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C148" s="5" t="s">
+      <c r="C148" s="4" t="s">
         <v>294</v>
       </c>
       <c r="D148" s="2"/>
@@ -4706,7 +4702,7 @@
       <c r="B149" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C149" s="5" t="s">
+      <c r="C149" s="4" t="s">
         <v>296</v>
       </c>
       <c r="D149" s="2"/>
@@ -4718,7 +4714,7 @@
       <c r="B150" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C150" s="4" t="s">
         <v>298</v>
       </c>
       <c r="D150" s="2"/>
@@ -4730,7 +4726,7 @@
       <c r="B151" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C151" s="5" t="s">
+      <c r="C151" s="4" t="s">
         <v>300</v>
       </c>
       <c r="D151" s="2"/>
@@ -4742,7 +4738,7 @@
       <c r="B152" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C152" s="5" t="s">
+      <c r="C152" s="4" t="s">
         <v>302</v>
       </c>
       <c r="D152" s="2"/>
@@ -4754,7 +4750,7 @@
       <c r="B153" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C153" s="5" t="s">
+      <c r="C153" s="4" t="s">
         <v>304</v>
       </c>
       <c r="D153" s="2"/>
@@ -4766,7 +4762,7 @@
       <c r="B154" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C154" s="5" t="s">
+      <c r="C154" s="4" t="s">
         <v>306</v>
       </c>
       <c r="D154" s="2"/>
@@ -4778,7 +4774,7 @@
       <c r="B155" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C155" s="5" t="s">
+      <c r="C155" s="4" t="s">
         <v>308</v>
       </c>
       <c r="D155" s="2"/>
@@ -4790,7 +4786,7 @@
       <c r="B156" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C156" s="5" t="s">
+      <c r="C156" s="4" t="s">
         <v>310</v>
       </c>
       <c r="D156" s="2"/>
@@ -4802,7 +4798,7 @@
       <c r="B157" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C157" s="5" t="s">
+      <c r="C157" s="4" t="s">
         <v>312</v>
       </c>
       <c r="D157" s="2"/>
@@ -4814,7 +4810,7 @@
       <c r="B158" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C158" s="5" t="s">
+      <c r="C158" s="4" t="s">
         <v>314</v>
       </c>
       <c r="D158" s="2"/>
@@ -4826,7 +4822,7 @@
       <c r="B159" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C159" s="5" t="s">
+      <c r="C159" s="4" t="s">
         <v>316</v>
       </c>
       <c r="D159" s="2"/>
@@ -4838,7 +4834,7 @@
       <c r="B160" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C160" s="5" t="s">
+      <c r="C160" s="4" t="s">
         <v>318</v>
       </c>
       <c r="D160" s="2"/>
@@ -4850,7 +4846,7 @@
       <c r="B161" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C161" s="5" t="s">
+      <c r="C161" s="4" t="s">
         <v>320</v>
       </c>
       <c r="D161" s="2"/>
@@ -4862,7 +4858,7 @@
       <c r="B162" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C162" s="5" t="s">
+      <c r="C162" s="4" t="s">
         <v>322</v>
       </c>
       <c r="D162" s="2"/>
@@ -4874,7 +4870,7 @@
       <c r="B163" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C163" s="5" t="s">
+      <c r="C163" s="4" t="s">
         <v>324</v>
       </c>
       <c r="D163" s="2"/>
@@ -4886,7 +4882,7 @@
       <c r="B164" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C164" s="5" t="s">
+      <c r="C164" s="4" t="s">
         <v>326</v>
       </c>
       <c r="D164" s="2"/>
@@ -4898,7 +4894,7 @@
       <c r="B165" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C165" s="5" t="s">
+      <c r="C165" s="4" t="s">
         <v>328</v>
       </c>
       <c r="D165" s="2"/>
@@ -4910,7 +4906,7 @@
       <c r="B166" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="C166" s="5" t="s">
+      <c r="C166" s="4" t="s">
         <v>330</v>
       </c>
       <c r="D166" s="2"/>
@@ -4922,7 +4918,7 @@
       <c r="B167" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C167" s="5" t="s">
+      <c r="C167" s="4" t="s">
         <v>332</v>
       </c>
       <c r="D167" s="2"/>
@@ -4934,7 +4930,7 @@
       <c r="B168" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C168" s="5" t="s">
+      <c r="C168" s="4" t="s">
         <v>334</v>
       </c>
       <c r="D168" s="2"/>
@@ -4946,7 +4942,7 @@
       <c r="B169" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="C169" s="4" t="s">
         <v>336</v>
       </c>
       <c r="D169" s="2"/>
@@ -4958,7 +4954,7 @@
       <c r="B170" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="C170" s="5" t="s">
+      <c r="C170" s="4" t="s">
         <v>338</v>
       </c>
       <c r="D170" s="2"/>
@@ -4970,7 +4966,7 @@
       <c r="B171" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="C171" s="4" t="s">
         <v>340</v>
       </c>
       <c r="D171" s="2"/>
@@ -4982,7 +4978,7 @@
       <c r="B172" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C172" s="5" t="s">
+      <c r="C172" s="4" t="s">
         <v>342</v>
       </c>
       <c r="D172" s="2"/>
@@ -4994,7 +4990,7 @@
       <c r="B173" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C173" s="5" t="s">
+      <c r="C173" s="4" t="s">
         <v>344</v>
       </c>
       <c r="D173" s="2"/>
@@ -5006,7 +5002,7 @@
       <c r="B174" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C174" s="5" t="s">
+      <c r="C174" s="4" t="s">
         <v>346</v>
       </c>
       <c r="D174" s="2"/>
@@ -5018,7 +5014,7 @@
       <c r="B175" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="C175" s="5" t="s">
+      <c r="C175" s="4" t="s">
         <v>348</v>
       </c>
       <c r="D175" s="2"/>
@@ -5030,7 +5026,7 @@
       <c r="B176" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C176" s="5" t="s">
+      <c r="C176" s="4" t="s">
         <v>350</v>
       </c>
       <c r="D176" s="2"/>
@@ -5042,7 +5038,7 @@
       <c r="B177" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C177" s="5" t="s">
+      <c r="C177" s="4" t="s">
         <v>352</v>
       </c>
       <c r="D177" s="2"/>
@@ -5054,7 +5050,7 @@
       <c r="B178" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C178" s="5" t="s">
+      <c r="C178" s="4" t="s">
         <v>354</v>
       </c>
       <c r="D178" s="2"/>
@@ -5066,7 +5062,7 @@
       <c r="B179" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C179" s="5" t="s">
+      <c r="C179" s="4" t="s">
         <v>356</v>
       </c>
       <c r="D179" s="2"/>
@@ -5078,7 +5074,7 @@
       <c r="B180" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C180" s="5" t="s">
+      <c r="C180" s="4" t="s">
         <v>358</v>
       </c>
       <c r="D180" s="2"/>
@@ -5090,7 +5086,7 @@
       <c r="B181" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="C181" s="5" t="s">
+      <c r="C181" s="4" t="s">
         <v>360</v>
       </c>
       <c r="D181" s="2"/>
@@ -5102,7 +5098,7 @@
       <c r="B182" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="C182" s="4" t="s">
         <v>362</v>
       </c>
       <c r="D182" s="2"/>
@@ -5114,7 +5110,7 @@
       <c r="B183" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="C183" s="4" t="s">
         <v>364</v>
       </c>
       <c r="D183" s="2"/>
@@ -5126,7 +5122,7 @@
       <c r="B184" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C184" s="5" t="s">
+      <c r="C184" s="4" t="s">
         <v>366</v>
       </c>
       <c r="D184" s="2"/>
@@ -5138,7 +5134,7 @@
       <c r="B185" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C185" s="5" t="s">
+      <c r="C185" s="4" t="s">
         <v>368</v>
       </c>
       <c r="D185" s="2"/>
@@ -5150,7 +5146,7 @@
       <c r="B186" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C186" s="5" t="s">
+      <c r="C186" s="4" t="s">
         <v>370</v>
       </c>
       <c r="D186" s="2"/>
@@ -5162,7 +5158,7 @@
       <c r="B187" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C187" s="5" t="s">
+      <c r="C187" s="4" t="s">
         <v>372</v>
       </c>
       <c r="D187" s="2"/>
@@ -5174,7 +5170,7 @@
       <c r="B188" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C188" s="5" t="s">
+      <c r="C188" s="4" t="s">
         <v>374</v>
       </c>
       <c r="D188" s="2"/>
@@ -5186,7 +5182,7 @@
       <c r="B189" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C189" s="5" t="s">
+      <c r="C189" s="4" t="s">
         <v>376</v>
       </c>
       <c r="D189" s="2"/>
@@ -5198,7 +5194,7 @@
       <c r="B190" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C190" s="5" t="s">
+      <c r="C190" s="4" t="s">
         <v>378</v>
       </c>
       <c r="D190" s="2"/>
@@ -5210,7 +5206,7 @@
       <c r="B191" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="5" t="s">
+      <c r="C191" s="4" t="s">
         <v>380</v>
       </c>
       <c r="D191" s="2"/>
@@ -5222,7 +5218,7 @@
       <c r="B192" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C192" s="5" t="s">
+      <c r="C192" s="4" t="s">
         <v>382</v>
       </c>
       <c r="D192" s="2"/>
@@ -5234,7 +5230,7 @@
       <c r="B193" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="C193" s="5" t="s">
+      <c r="C193" s="4" t="s">
         <v>384</v>
       </c>
       <c r="D193" s="2"/>
@@ -5246,7 +5242,7 @@
       <c r="B194" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C194" s="5" t="s">
+      <c r="C194" s="4" t="s">
         <v>386</v>
       </c>
       <c r="D194" s="2"/>
@@ -5258,7 +5254,7 @@
       <c r="B195" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C195" s="5" t="s">
+      <c r="C195" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D195" s="2"/>
@@ -5270,7 +5266,7 @@
       <c r="B196" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="C196" s="5" t="s">
+      <c r="C196" s="4" t="s">
         <v>390</v>
       </c>
       <c r="D196" s="2"/>
@@ -5282,7 +5278,7 @@
       <c r="B197" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C197" s="5" t="s">
+      <c r="C197" s="4" t="s">
         <v>392</v>
       </c>
       <c r="D197" s="2"/>
@@ -5294,7 +5290,7 @@
       <c r="B198" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C198" s="5" t="s">
+      <c r="C198" s="4" t="s">
         <v>394</v>
       </c>
       <c r="D198" s="2"/>
@@ -5306,7 +5302,7 @@
       <c r="B199" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="C199" s="5" t="s">
+      <c r="C199" s="4" t="s">
         <v>396</v>
       </c>
       <c r="D199" s="2"/>
@@ -5318,7 +5314,7 @@
       <c r="B200" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C200" s="5" t="s">
+      <c r="C200" s="4" t="s">
         <v>398</v>
       </c>
       <c r="D200" s="2"/>
@@ -5330,7 +5326,7 @@
       <c r="B201" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C201" s="5" t="s">
+      <c r="C201" s="4" t="s">
         <v>400</v>
       </c>
       <c r="D201" s="2"/>
@@ -5342,7 +5338,7 @@
       <c r="B202" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C202" s="5" t="s">
+      <c r="C202" s="4" t="s">
         <v>402</v>
       </c>
       <c r="D202" s="2"/>
@@ -5354,7 +5350,7 @@
       <c r="B203" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C203" s="5" t="s">
+      <c r="C203" s="4" t="s">
         <v>404</v>
       </c>
       <c r="D203" s="2"/>
@@ -5366,7 +5362,7 @@
       <c r="B204" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C204" s="5" t="s">
+      <c r="C204" s="4" t="s">
         <v>406</v>
       </c>
       <c r="D204" s="2"/>
@@ -5378,7 +5374,7 @@
       <c r="B205" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C205" s="5" t="s">
+      <c r="C205" s="4" t="s">
         <v>408</v>
       </c>
       <c r="D205" s="2"/>
@@ -5390,7 +5386,7 @@
       <c r="B206" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C206" s="5" t="s">
+      <c r="C206" s="4" t="s">
         <v>410</v>
       </c>
       <c r="D206" s="2"/>
@@ -5402,7 +5398,7 @@
       <c r="B207" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C207" s="5" t="s">
+      <c r="C207" s="4" t="s">
         <v>412</v>
       </c>
       <c r="D207" s="2"/>
@@ -5414,7 +5410,7 @@
       <c r="B208" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C208" s="5" t="s">
+      <c r="C208" s="4" t="s">
         <v>414</v>
       </c>
       <c r="D208" s="2"/>
@@ -5426,7 +5422,7 @@
       <c r="B209" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C209" s="5" t="s">
+      <c r="C209" s="4" t="s">
         <v>416</v>
       </c>
       <c r="D209" s="2"/>
@@ -5438,7 +5434,7 @@
       <c r="B210" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C210" s="5" t="s">
+      <c r="C210" s="4" t="s">
         <v>418</v>
       </c>
       <c r="D210" s="2"/>
@@ -5450,7 +5446,7 @@
       <c r="B211" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C211" s="5" t="s">
+      <c r="C211" s="4" t="s">
         <v>420</v>
       </c>
       <c r="D211" s="2"/>
@@ -5462,7 +5458,7 @@
       <c r="B212" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C212" s="5" t="s">
+      <c r="C212" s="4" t="s">
         <v>422</v>
       </c>
       <c r="D212" s="2"/>
@@ -5474,7 +5470,7 @@
       <c r="B213" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C213" s="5" t="s">
+      <c r="C213" s="4" t="s">
         <v>424</v>
       </c>
       <c r="D213" s="2"/>
@@ -5486,7 +5482,7 @@
       <c r="B214" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C214" s="5" t="s">
+      <c r="C214" s="4" t="s">
         <v>426</v>
       </c>
       <c r="D214" s="2"/>
@@ -5498,7 +5494,7 @@
       <c r="B215" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="C215" s="5" t="s">
+      <c r="C215" s="4" t="s">
         <v>428</v>
       </c>
       <c r="D215" s="2"/>
@@ -5510,7 +5506,7 @@
       <c r="B216" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="C216" s="5" t="s">
+      <c r="C216" s="4" t="s">
         <v>430</v>
       </c>
       <c r="D216" s="2"/>
@@ -5522,7 +5518,7 @@
       <c r="B217" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C217" s="5" t="s">
+      <c r="C217" s="4" t="s">
         <v>432</v>
       </c>
       <c r="D217" s="2"/>
@@ -5534,7 +5530,7 @@
       <c r="B218" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C218" s="5" t="s">
+      <c r="C218" s="4" t="s">
         <v>434</v>
       </c>
       <c r="D218" s="2"/>
@@ -5546,7 +5542,7 @@
       <c r="B219" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C219" s="5" t="s">
+      <c r="C219" s="4" t="s">
         <v>436</v>
       </c>
       <c r="D219" s="2"/>
@@ -5558,7 +5554,7 @@
       <c r="B220" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="C220" s="5" t="s">
+      <c r="C220" s="4" t="s">
         <v>438</v>
       </c>
       <c r="D220" s="2"/>
@@ -5570,7 +5566,7 @@
       <c r="B221" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C221" s="5" t="s">
+      <c r="C221" s="4" t="s">
         <v>440</v>
       </c>
       <c r="D221" s="2"/>
@@ -5582,7 +5578,7 @@
       <c r="B222" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C222" s="5" t="s">
+      <c r="C222" s="4" t="s">
         <v>442</v>
       </c>
       <c r="D222" s="2"/>
@@ -5594,7 +5590,7 @@
       <c r="B223" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="C223" s="5" t="s">
+      <c r="C223" s="4" t="s">
         <v>444</v>
       </c>
       <c r="D223" s="2"/>
@@ -5606,7 +5602,7 @@
       <c r="B224" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C224" s="5" t="s">
+      <c r="C224" s="4" t="s">
         <v>446</v>
       </c>
       <c r="D224" s="2"/>
@@ -5618,7 +5614,7 @@
       <c r="B225" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C225" s="5" t="s">
+      <c r="C225" s="4" t="s">
         <v>448</v>
       </c>
       <c r="D225" s="2"/>
@@ -5630,7 +5626,7 @@
       <c r="B226" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C226" s="5" t="s">
+      <c r="C226" s="4" t="s">
         <v>450</v>
       </c>
       <c r="D226" s="2"/>
@@ -5642,7 +5638,7 @@
       <c r="B227" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C227" s="5" t="s">
+      <c r="C227" s="4" t="s">
         <v>452</v>
       </c>
       <c r="D227" s="2"/>
@@ -5654,7 +5650,7 @@
       <c r="B228" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C228" s="5" t="s">
+      <c r="C228" s="4" t="s">
         <v>454</v>
       </c>
       <c r="D228" s="2"/>
@@ -5666,7 +5662,7 @@
       <c r="B229" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C229" s="5" t="s">
+      <c r="C229" s="4" t="s">
         <v>456</v>
       </c>
       <c r="D229" s="2"/>
@@ -5678,7 +5674,7 @@
       <c r="B230" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="C230" s="5" t="s">
+      <c r="C230" s="4" t="s">
         <v>458</v>
       </c>
       <c r="D230" s="2"/>
@@ -5690,7 +5686,7 @@
       <c r="B231" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C231" s="5" t="s">
+      <c r="C231" s="4" t="s">
         <v>460</v>
       </c>
       <c r="D231" s="2"/>
@@ -5702,7 +5698,7 @@
       <c r="B232" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C232" s="5" t="s">
+      <c r="C232" s="4" t="s">
         <v>462</v>
       </c>
       <c r="D232" s="2"/>
@@ -5714,7 +5710,7 @@
       <c r="B233" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="C233" s="5" t="s">
+      <c r="C233" s="4" t="s">
         <v>464</v>
       </c>
       <c r="D233" s="2"/>
@@ -5726,7 +5722,7 @@
       <c r="B234" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="C234" s="5" t="s">
+      <c r="C234" s="4" t="s">
         <v>466</v>
       </c>
       <c r="D234" s="2"/>
@@ -5738,7 +5734,7 @@
       <c r="B235" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C235" s="5" t="s">
+      <c r="C235" s="4" t="s">
         <v>468</v>
       </c>
       <c r="D235" s="2"/>
@@ -5750,7 +5746,7 @@
       <c r="B236" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C236" s="5" t="s">
+      <c r="C236" s="4" t="s">
         <v>470</v>
       </c>
       <c r="D236" s="2"/>
@@ -5762,7 +5758,7 @@
       <c r="B237" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C237" s="5" t="s">
+      <c r="C237" s="4" t="s">
         <v>472</v>
       </c>
       <c r="D237" s="2"/>
@@ -5774,7 +5770,7 @@
       <c r="B238" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C238" s="5" t="s">
+      <c r="C238" s="4" t="s">
         <v>474</v>
       </c>
       <c r="D238" s="2"/>
@@ -5786,7 +5782,7 @@
       <c r="B239" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C239" s="5" t="s">
+      <c r="C239" s="4" t="s">
         <v>476</v>
       </c>
       <c r="D239" s="2"/>
@@ -5798,7 +5794,7 @@
       <c r="B240" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C240" s="5" t="s">
+      <c r="C240" s="4" t="s">
         <v>478</v>
       </c>
       <c r="D240" s="2"/>
@@ -5810,7 +5806,7 @@
       <c r="B241" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C241" s="5" t="s">
+      <c r="C241" s="4" t="s">
         <v>480</v>
       </c>
       <c r="D241" s="2"/>
@@ -5822,7 +5818,7 @@
       <c r="B242" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C242" s="5" t="s">
+      <c r="C242" s="4" t="s">
         <v>482</v>
       </c>
       <c r="D242" s="2"/>
@@ -5834,7 +5830,7 @@
       <c r="B243" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C243" s="5" t="s">
+      <c r="C243" s="4" t="s">
         <v>484</v>
       </c>
       <c r="D243" s="2"/>
@@ -5846,7 +5842,7 @@
       <c r="B244" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C244" s="5" t="s">
+      <c r="C244" s="4" t="s">
         <v>486</v>
       </c>
       <c r="D244" s="2"/>
@@ -5858,7 +5854,7 @@
       <c r="B245" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="C245" s="5" t="s">
+      <c r="C245" s="4" t="s">
         <v>488</v>
       </c>
       <c r="D245" s="2"/>
@@ -5870,7 +5866,7 @@
       <c r="B246" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C246" s="5" t="s">
+      <c r="C246" s="4" t="s">
         <v>490</v>
       </c>
       <c r="D246" s="2"/>
@@ -5882,7 +5878,7 @@
       <c r="B247" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C247" s="5" t="s">
+      <c r="C247" s="4" t="s">
         <v>492</v>
       </c>
       <c r="D247" s="2"/>
@@ -5894,7 +5890,7 @@
       <c r="B248" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C248" s="5" t="s">
+      <c r="C248" s="4" t="s">
         <v>494</v>
       </c>
       <c r="D248" s="2"/>
@@ -5906,7 +5902,7 @@
       <c r="B249" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C249" s="5" t="s">
+      <c r="C249" s="4" t="s">
         <v>496</v>
       </c>
       <c r="D249" s="2"/>
@@ -5918,7 +5914,7 @@
       <c r="B250" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C250" s="5" t="s">
+      <c r="C250" s="4" t="s">
         <v>498</v>
       </c>
       <c r="D250" s="2"/>
@@ -5930,7 +5926,7 @@
       <c r="B251" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="C251" s="5" t="s">
+      <c r="C251" s="4" t="s">
         <v>500</v>
       </c>
       <c r="D251" s="2"/>
@@ -5942,7 +5938,7 @@
       <c r="B252" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C252" s="6" t="s">
+      <c r="C252" s="4" t="s">
         <v>502</v>
       </c>
       <c r="D252" s="2"/>
@@ -5954,7 +5950,7 @@
       <c r="B253" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C253" s="6" t="s">
+      <c r="C253" s="4" t="s">
         <v>504</v>
       </c>
       <c r="D253" s="2"/>
@@ -5966,7 +5962,7 @@
       <c r="B254" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="C254" s="6" t="s">
+      <c r="C254" s="4" t="s">
         <v>506</v>
       </c>
       <c r="D254" s="2"/>
@@ -5978,7 +5974,7 @@
       <c r="B255" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C255" s="6" t="s">
+      <c r="C255" s="4" t="s">
         <v>508</v>
       </c>
       <c r="D255" s="2"/>
@@ -5990,7 +5986,7 @@
       <c r="B256" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C256" s="6" t="s">
+      <c r="C256" s="4" t="s">
         <v>510</v>
       </c>
       <c r="D256" s="2"/>
@@ -6002,7 +5998,7 @@
       <c r="B257" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C257" s="6" t="s">
+      <c r="C257" s="5" t="s">
         <v>512</v>
       </c>
       <c r="D257" s="2"/>
@@ -6014,7 +6010,7 @@
       <c r="B258" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C258" s="6" t="s">
+      <c r="C258" s="5" t="s">
         <v>514</v>
       </c>
       <c r="D258" s="2"/>
@@ -6026,7 +6022,7 @@
       <c r="B259" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C259" s="6" t="s">
+      <c r="C259" s="5" t="s">
         <v>516</v>
       </c>
       <c r="D259" s="2"/>
@@ -6038,7 +6034,7 @@
       <c r="B260" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C260" s="6" t="s">
+      <c r="C260" s="5" t="s">
         <v>518</v>
       </c>
       <c r="D260" s="2"/>
@@ -6050,7 +6046,7 @@
       <c r="B261" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C261" s="6" t="s">
+      <c r="C261" s="5" t="s">
         <v>520</v>
       </c>
       <c r="D261" s="2"/>
@@ -6062,7 +6058,7 @@
       <c r="B262" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C262" s="6" t="s">
+      <c r="C262" s="5" t="s">
         <v>522</v>
       </c>
       <c r="D262" s="2"/>
@@ -6074,7 +6070,7 @@
       <c r="B263" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C263" s="6" t="s">
+      <c r="C263" s="5" t="s">
         <v>524</v>
       </c>
       <c r="D263" s="2"/>
@@ -6086,7 +6082,7 @@
       <c r="B264" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C264" s="6" t="s">
+      <c r="C264" s="5" t="s">
         <v>526</v>
       </c>
       <c r="D264" s="2"/>
@@ -6098,7 +6094,7 @@
       <c r="B265" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C265" s="6" t="s">
+      <c r="C265" s="5" t="s">
         <v>528</v>
       </c>
       <c r="D265" s="2"/>
@@ -6110,7 +6106,7 @@
       <c r="B266" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C266" s="6" t="s">
+      <c r="C266" s="5" t="s">
         <v>530</v>
       </c>
       <c r="D266" s="2"/>
@@ -6122,7 +6118,7 @@
       <c r="B267" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C267" s="6" t="s">
+      <c r="C267" s="5" t="s">
         <v>532</v>
       </c>
       <c r="D267" s="2"/>
@@ -6134,7 +6130,7 @@
       <c r="B268" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C268" s="6" t="s">
+      <c r="C268" s="5" t="s">
         <v>534</v>
       </c>
       <c r="D268" s="2"/>
@@ -6146,7 +6142,7 @@
       <c r="B269" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C269" s="6" t="s">
+      <c r="C269" s="5" t="s">
         <v>536</v>
       </c>
       <c r="D269" s="2"/>
@@ -6158,7 +6154,7 @@
       <c r="B270" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C270" s="6" t="s">
+      <c r="C270" s="5" t="s">
         <v>538</v>
       </c>
       <c r="D270" s="2"/>
@@ -6170,7 +6166,7 @@
       <c r="B271" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C271" s="6" t="s">
+      <c r="C271" s="5" t="s">
         <v>540</v>
       </c>
       <c r="D271" s="2"/>
@@ -6182,7 +6178,7 @@
       <c r="B272" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C272" s="6" t="s">
+      <c r="C272" s="5" t="s">
         <v>542</v>
       </c>
       <c r="D272" s="2"/>
@@ -6194,7 +6190,7 @@
       <c r="B273" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C273" s="6" t="s">
+      <c r="C273" s="5" t="s">
         <v>544</v>
       </c>
       <c r="D273" s="2"/>
@@ -6206,7 +6202,7 @@
       <c r="B274" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C274" s="6" t="s">
+      <c r="C274" s="5" t="s">
         <v>546</v>
       </c>
       <c r="D274" s="2"/>
@@ -6218,7 +6214,7 @@
       <c r="B275" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C275" s="6" t="s">
+      <c r="C275" s="5" t="s">
         <v>548</v>
       </c>
       <c r="D275" s="2"/>
@@ -6230,7 +6226,7 @@
       <c r="B276" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C276" s="6" t="s">
+      <c r="C276" s="5" t="s">
         <v>550</v>
       </c>
       <c r="D276" s="2"/>
@@ -6242,7 +6238,7 @@
       <c r="B277" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C277" s="6" t="s">
+      <c r="C277" s="5" t="s">
         <v>552</v>
       </c>
       <c r="D277" s="2"/>
@@ -6254,7 +6250,7 @@
       <c r="B278" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C278" s="6" t="s">
+      <c r="C278" s="5" t="s">
         <v>554</v>
       </c>
       <c r="D278" s="2"/>
@@ -6266,7 +6262,7 @@
       <c r="B279" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C279" s="6" t="s">
+      <c r="C279" s="5" t="s">
         <v>556</v>
       </c>
       <c r="D279" s="2"/>
@@ -6278,7 +6274,7 @@
       <c r="B280" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C280" s="6" t="s">
+      <c r="C280" s="5" t="s">
         <v>558</v>
       </c>
       <c r="D280" s="2"/>
@@ -6290,7 +6286,7 @@
       <c r="B281" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C281" s="6" t="s">
+      <c r="C281" s="5" t="s">
         <v>560</v>
       </c>
       <c r="D281" s="2"/>
@@ -6302,7 +6298,7 @@
       <c r="B282" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C282" s="6" t="s">
+      <c r="C282" s="5" t="s">
         <v>562</v>
       </c>
       <c r="D282" s="2"/>
@@ -6314,7 +6310,7 @@
       <c r="B283" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C283" s="6" t="s">
+      <c r="C283" s="5" t="s">
         <v>564</v>
       </c>
       <c r="D283" s="2"/>
@@ -6326,7 +6322,7 @@
       <c r="B284" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C284" s="6" t="s">
+      <c r="C284" s="5" t="s">
         <v>566</v>
       </c>
       <c r="D284" s="2"/>
@@ -6338,7 +6334,7 @@
       <c r="B285" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C285" s="6" t="s">
+      <c r="C285" s="5" t="s">
         <v>568</v>
       </c>
       <c r="D285" s="2"/>
@@ -6350,7 +6346,7 @@
       <c r="B286" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C286" s="6" t="s">
+      <c r="C286" s="5" t="s">
         <v>570</v>
       </c>
       <c r="D286" s="2"/>
@@ -6362,7 +6358,7 @@
       <c r="B287" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C287" s="6" t="s">
+      <c r="C287" s="5" t="s">
         <v>572</v>
       </c>
       <c r="D287" s="2"/>
@@ -6374,7 +6370,7 @@
       <c r="B288" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C288" s="6" t="s">
+      <c r="C288" s="5" t="s">
         <v>574</v>
       </c>
       <c r="D288" s="2"/>
@@ -6386,7 +6382,7 @@
       <c r="B289" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C289" s="6" t="s">
+      <c r="C289" s="5" t="s">
         <v>576</v>
       </c>
       <c r="D289" s="2"/>
@@ -6398,7 +6394,7 @@
       <c r="B290" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C290" s="6" t="s">
+      <c r="C290" s="5" t="s">
         <v>578</v>
       </c>
       <c r="D290" s="2"/>
@@ -6410,7 +6406,7 @@
       <c r="B291" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C291" s="6" t="s">
+      <c r="C291" s="5" t="s">
         <v>580</v>
       </c>
       <c r="D291" s="2"/>
@@ -6422,7 +6418,7 @@
       <c r="B292" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C292" s="6" t="s">
+      <c r="C292" s="5" t="s">
         <v>582</v>
       </c>
       <c r="D292" s="2"/>
@@ -6434,7 +6430,7 @@
       <c r="B293" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C293" s="6" t="s">
+      <c r="C293" s="5" t="s">
         <v>584</v>
       </c>
       <c r="D293" s="2"/>
@@ -6446,7 +6442,7 @@
       <c r="B294" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C294" s="6" t="s">
+      <c r="C294" s="5" t="s">
         <v>586</v>
       </c>
       <c r="D294" s="2"/>
@@ -6458,7 +6454,7 @@
       <c r="B295" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C295" s="6" t="s">
+      <c r="C295" s="5" t="s">
         <v>588</v>
       </c>
       <c r="D295" s="2"/>
@@ -6470,7 +6466,7 @@
       <c r="B296" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="C296" s="6" t="s">
+      <c r="C296" s="5" t="s">
         <v>590</v>
       </c>
       <c r="D296" s="2"/>
@@ -6482,7 +6478,7 @@
       <c r="B297" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C297" s="6" t="s">
+      <c r="C297" s="5" t="s">
         <v>592</v>
       </c>
       <c r="D297" s="2"/>
@@ -6494,7 +6490,7 @@
       <c r="B298" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="C298" s="6" t="s">
+      <c r="C298" s="5" t="s">
         <v>594</v>
       </c>
       <c r="D298" s="2"/>
@@ -6506,7 +6502,7 @@
       <c r="B299" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C299" s="6" t="s">
+      <c r="C299" s="5" t="s">
         <v>596</v>
       </c>
       <c r="D299" s="2"/>
@@ -6518,7 +6514,7 @@
       <c r="B300" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C300" s="6" t="s">
+      <c r="C300" s="5" t="s">
         <v>598</v>
       </c>
       <c r="D300" s="2"/>
@@ -6530,7 +6526,7 @@
       <c r="B301" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="C301" s="6" t="s">
+      <c r="C301" s="5" t="s">
         <v>600</v>
       </c>
       <c r="D301" s="2"/>
@@ -6542,7 +6538,7 @@
       <c r="B302" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C302" s="6" t="s">
+      <c r="C302" s="5" t="s">
         <v>602</v>
       </c>
     </row>
@@ -6553,7 +6549,7 @@
       <c r="B303" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C303" s="6" t="s">
+      <c r="C303" s="5" t="s">
         <v>604</v>
       </c>
     </row>
@@ -6564,7 +6560,7 @@
       <c r="B304" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C304" s="6" t="s">
+      <c r="C304" s="5" t="s">
         <v>606</v>
       </c>
     </row>
@@ -6575,7 +6571,7 @@
       <c r="B305" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C305" s="6" t="s">
+      <c r="C305" s="5" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6586,7 +6582,7 @@
       <c r="B306" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C306" s="6" t="s">
+      <c r="C306" s="5" t="s">
         <v>610</v>
       </c>
     </row>
@@ -6597,7 +6593,7 @@
       <c r="B307" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C307" s="6" t="s">
+      <c r="C307" s="5" t="s">
         <v>612</v>
       </c>
     </row>
@@ -6608,7 +6604,7 @@
       <c r="B308" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C308" s="6" t="s">
+      <c r="C308" s="5" t="s">
         <v>614</v>
       </c>
     </row>
@@ -6619,7 +6615,7 @@
       <c r="B309" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C309" s="6" t="s">
+      <c r="C309" s="5" t="s">
         <v>616</v>
       </c>
     </row>
@@ -6630,7 +6626,7 @@
       <c r="B310" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="C310" s="6" t="s">
+      <c r="C310" s="5" t="s">
         <v>618</v>
       </c>
     </row>
@@ -6641,7 +6637,7 @@
       <c r="B311" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C311" s="6" t="s">
+      <c r="C311" s="5" t="s">
         <v>620</v>
       </c>
     </row>
@@ -6652,7 +6648,7 @@
       <c r="B312" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="C312" s="6" t="s">
+      <c r="C312" s="5" t="s">
         <v>622</v>
       </c>
     </row>
@@ -6663,7 +6659,7 @@
       <c r="B313" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C313" s="6" t="s">
+      <c r="C313" s="5" t="s">
         <v>624</v>
       </c>
     </row>
@@ -6674,7 +6670,7 @@
       <c r="B314" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C314" s="6" t="s">
+      <c r="C314" s="5" t="s">
         <v>626</v>
       </c>
     </row>
@@ -6685,7 +6681,7 @@
       <c r="B315" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="C315" s="6" t="s">
+      <c r="C315" s="5" t="s">
         <v>628</v>
       </c>
     </row>
@@ -6696,7 +6692,7 @@
       <c r="B316" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C316" s="6" t="s">
+      <c r="C316" s="5" t="s">
         <v>630</v>
       </c>
     </row>
@@ -6707,7 +6703,7 @@
       <c r="B317" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C317" s="6" t="s">
+      <c r="C317" s="5" t="s">
         <v>632</v>
       </c>
     </row>
@@ -6718,7 +6714,7 @@
       <c r="B318" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C318" s="6" t="s">
+      <c r="C318" s="5" t="s">
         <v>634</v>
       </c>
     </row>
@@ -6729,7 +6725,7 @@
       <c r="B319" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C319" s="6" t="s">
+      <c r="C319" s="5" t="s">
         <v>636</v>
       </c>
     </row>
@@ -6740,7 +6736,7 @@
       <c r="B320" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C320" s="6" t="s">
+      <c r="C320" s="5" t="s">
         <v>638</v>
       </c>
     </row>
@@ -6751,7 +6747,7 @@
       <c r="B321" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C321" s="6" t="s">
+      <c r="C321" s="5" t="s">
         <v>640</v>
       </c>
     </row>
@@ -6762,7 +6758,7 @@
       <c r="B322" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C322" s="6" t="s">
+      <c r="C322" s="5" t="s">
         <v>642</v>
       </c>
     </row>
@@ -6773,7 +6769,7 @@
       <c r="B323" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C323" s="6" t="s">
+      <c r="C323" s="5" t="s">
         <v>644</v>
       </c>
     </row>
@@ -6784,7 +6780,7 @@
       <c r="B324" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C324" s="6" t="s">
+      <c r="C324" s="5" t="s">
         <v>646</v>
       </c>
     </row>
@@ -6795,7 +6791,7 @@
       <c r="B325" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C325" s="6" t="s">
+      <c r="C325" s="5" t="s">
         <v>648</v>
       </c>
     </row>
@@ -6806,7 +6802,7 @@
       <c r="B326" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C326" s="6" t="s">
+      <c r="C326" s="5" t="s">
         <v>650</v>
       </c>
     </row>
@@ -6817,7 +6813,7 @@
       <c r="B327" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C327" s="6" t="s">
+      <c r="C327" s="5" t="s">
         <v>652</v>
       </c>
     </row>
@@ -6828,7 +6824,7 @@
       <c r="B328" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C328" s="6" t="s">
+      <c r="C328" s="5" t="s">
         <v>654</v>
       </c>
     </row>
@@ -6839,7 +6835,7 @@
       <c r="B329" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C329" s="6" t="s">
+      <c r="C329" s="5" t="s">
         <v>656</v>
       </c>
     </row>
@@ -6850,7 +6846,7 @@
       <c r="B330" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="C330" s="6" t="s">
+      <c r="C330" s="5" t="s">
         <v>658</v>
       </c>
     </row>
@@ -6861,7 +6857,7 @@
       <c r="B331" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C331" s="6" t="s">
+      <c r="C331" s="5" t="s">
         <v>660</v>
       </c>
     </row>
@@ -6872,7 +6868,7 @@
       <c r="B332" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C332" s="6" t="s">
+      <c r="C332" s="5" t="s">
         <v>662</v>
       </c>
     </row>
@@ -6883,7 +6879,7 @@
       <c r="B333" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C333" s="6" t="s">
+      <c r="C333" s="5" t="s">
         <v>664</v>
       </c>
     </row>
@@ -6894,7 +6890,7 @@
       <c r="B334" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C334" s="6" t="s">
+      <c r="C334" s="5" t="s">
         <v>666</v>
       </c>
     </row>
@@ -6905,7 +6901,7 @@
       <c r="B335" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C335" s="6" t="s">
+      <c r="C335" s="5" t="s">
         <v>668</v>
       </c>
     </row>
@@ -6916,7 +6912,7 @@
       <c r="B336" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C336" s="6" t="s">
+      <c r="C336" s="5" t="s">
         <v>670</v>
       </c>
     </row>
@@ -6927,7 +6923,7 @@
       <c r="B337" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C337" s="6" t="s">
+      <c r="C337" s="5" t="s">
         <v>672</v>
       </c>
     </row>
@@ -6938,7 +6934,7 @@
       <c r="B338" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C338" s="6" t="s">
+      <c r="C338" s="5" t="s">
         <v>674</v>
       </c>
     </row>
@@ -6949,7 +6945,7 @@
       <c r="B339" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C339" s="6" t="s">
+      <c r="C339" s="5" t="s">
         <v>676</v>
       </c>
     </row>
@@ -6960,7 +6956,7 @@
       <c r="B340" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="C340" s="6" t="s">
+      <c r="C340" s="5" t="s">
         <v>678</v>
       </c>
     </row>
@@ -6971,7 +6967,7 @@
       <c r="B341" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C341" s="6" t="s">
+      <c r="C341" s="5" t="s">
         <v>680</v>
       </c>
     </row>
@@ -6982,7 +6978,7 @@
       <c r="B342" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C342" s="6" t="s">
+      <c r="C342" s="5" t="s">
         <v>682</v>
       </c>
     </row>
@@ -6993,7 +6989,7 @@
       <c r="B343" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="C343" s="6" t="s">
+      <c r="C343" s="5" t="s">
         <v>684</v>
       </c>
     </row>
@@ -7004,7 +7000,7 @@
       <c r="B344" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C344" s="6" t="s">
+      <c r="C344" s="5" t="s">
         <v>686</v>
       </c>
     </row>
@@ -7015,7 +7011,7 @@
       <c r="B345" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="C345" s="6" t="s">
+      <c r="C345" s="5" t="s">
         <v>688</v>
       </c>
     </row>
@@ -7026,7 +7022,7 @@
       <c r="B346" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C346" s="6" t="s">
+      <c r="C346" s="5" t="s">
         <v>690</v>
       </c>
     </row>
@@ -7037,7 +7033,7 @@
       <c r="B347" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="C347" s="6" t="s">
+      <c r="C347" s="5" t="s">
         <v>692</v>
       </c>
     </row>
@@ -7048,7 +7044,7 @@
       <c r="B348" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="C348" s="6" t="s">
+      <c r="C348" s="5" t="s">
         <v>694</v>
       </c>
     </row>
@@ -7059,7 +7055,7 @@
       <c r="B349" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C349" s="6" t="s">
+      <c r="C349" s="5" t="s">
         <v>696</v>
       </c>
     </row>
@@ -7070,7 +7066,7 @@
       <c r="B350" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="C350" s="6" t="s">
+      <c r="C350" s="5" t="s">
         <v>698</v>
       </c>
     </row>
@@ -7081,7 +7077,7 @@
       <c r="B351" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C351" s="6" t="s">
+      <c r="C351" s="5" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7092,7 +7088,7 @@
       <c r="B352" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="C352" s="6" t="s">
+      <c r="C352" s="5" t="s">
         <v>702</v>
       </c>
     </row>
@@ -7103,7 +7099,7 @@
       <c r="B353" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C353" s="6" t="s">
+      <c r="C353" s="5" t="s">
         <v>704</v>
       </c>
     </row>
@@ -7114,7 +7110,7 @@
       <c r="B354" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C354" s="6" t="s">
+      <c r="C354" s="5" t="s">
         <v>706</v>
       </c>
     </row>
@@ -7125,7 +7121,7 @@
       <c r="B355" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C355" s="6" t="s">
+      <c r="C355" s="5" t="s">
         <v>708</v>
       </c>
     </row>
@@ -7136,7 +7132,7 @@
       <c r="B356" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C356" s="6" t="s">
+      <c r="C356" s="5" t="s">
         <v>710</v>
       </c>
     </row>
@@ -7147,7 +7143,7 @@
       <c r="B357" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C357" s="6" t="s">
+      <c r="C357" s="5" t="s">
         <v>712</v>
       </c>
     </row>
@@ -7158,7 +7154,7 @@
       <c r="B358" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="C358" s="6" t="s">
+      <c r="C358" s="5" t="s">
         <v>714</v>
       </c>
     </row>
@@ -7169,7 +7165,7 @@
       <c r="B359" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="C359" s="6" t="s">
+      <c r="C359" s="5" t="s">
         <v>716</v>
       </c>
     </row>
@@ -7180,7 +7176,7 @@
       <c r="B360" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C360" s="6" t="s">
+      <c r="C360" s="5" t="s">
         <v>718</v>
       </c>
     </row>
@@ -7191,7 +7187,7 @@
       <c r="B361" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="C361" s="6" t="s">
+      <c r="C361" s="5" t="s">
         <v>720</v>
       </c>
     </row>
@@ -7202,7 +7198,7 @@
       <c r="B362" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="C362" s="6" t="s">
+      <c r="C362" s="5" t="s">
         <v>722</v>
       </c>
     </row>
@@ -7213,7 +7209,7 @@
       <c r="B363" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C363" s="6" t="s">
+      <c r="C363" s="5" t="s">
         <v>724</v>
       </c>
     </row>
@@ -7224,7 +7220,7 @@
       <c r="B364" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="C364" s="6" t="s">
+      <c r="C364" s="5" t="s">
         <v>726</v>
       </c>
     </row>
@@ -7235,7 +7231,7 @@
       <c r="B365" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C365" s="6" t="s">
+      <c r="C365" s="5" t="s">
         <v>728</v>
       </c>
     </row>
@@ -7246,7 +7242,7 @@
       <c r="B366" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="C366" s="6" t="s">
+      <c r="C366" s="5" t="s">
         <v>730</v>
       </c>
     </row>
@@ -7257,7 +7253,7 @@
       <c r="B367" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C367" s="6" t="s">
+      <c r="C367" s="5" t="s">
         <v>732</v>
       </c>
     </row>
@@ -7268,7 +7264,7 @@
       <c r="B368" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C368" s="6" t="s">
+      <c r="C368" s="5" t="s">
         <v>734</v>
       </c>
     </row>
@@ -7279,7 +7275,7 @@
       <c r="B369" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="C369" s="6" t="s">
+      <c r="C369" s="5" t="s">
         <v>736</v>
       </c>
     </row>
@@ -7290,7 +7286,7 @@
       <c r="B370" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C370" s="6" t="s">
+      <c r="C370" s="5" t="s">
         <v>738</v>
       </c>
     </row>
@@ -7301,7 +7297,7 @@
       <c r="B371" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C371" s="6" t="s">
+      <c r="C371" s="5" t="s">
         <v>740</v>
       </c>
     </row>
@@ -7312,7 +7308,7 @@
       <c r="B372" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C372" s="6" t="s">
+      <c r="C372" s="5" t="s">
         <v>742</v>
       </c>
     </row>
@@ -7323,7 +7319,7 @@
       <c r="B373" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C373" s="6" t="s">
+      <c r="C373" s="5" t="s">
         <v>744</v>
       </c>
     </row>
@@ -7334,7 +7330,7 @@
       <c r="B374" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="C374" s="6" t="s">
+      <c r="C374" s="5" t="s">
         <v>746</v>
       </c>
     </row>
@@ -7345,7 +7341,7 @@
       <c r="B375" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C375" s="6" t="s">
+      <c r="C375" s="5" t="s">
         <v>748</v>
       </c>
     </row>
@@ -7356,7 +7352,7 @@
       <c r="B376" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="C376" s="6" t="s">
+      <c r="C376" s="5" t="s">
         <v>750</v>
       </c>
     </row>
@@ -7367,7 +7363,7 @@
       <c r="B377" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C377" s="6" t="s">
+      <c r="C377" s="5" t="s">
         <v>752</v>
       </c>
     </row>
@@ -7378,7 +7374,7 @@
       <c r="B378" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C378" s="6" t="s">
+      <c r="C378" s="5" t="s">
         <v>754</v>
       </c>
     </row>
@@ -7389,7 +7385,7 @@
       <c r="B379" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="C379" s="6" t="s">
+      <c r="C379" s="5" t="s">
         <v>756</v>
       </c>
     </row>
@@ -7400,7 +7396,7 @@
       <c r="B380" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="C380" s="6" t="s">
+      <c r="C380" s="5" t="s">
         <v>758</v>
       </c>
     </row>
@@ -7411,7 +7407,7 @@
       <c r="B381" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C381" s="6" t="s">
+      <c r="C381" s="5" t="s">
         <v>760</v>
       </c>
     </row>
@@ -7422,7 +7418,7 @@
       <c r="B382" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="C382" s="6" t="s">
+      <c r="C382" s="5" t="s">
         <v>762</v>
       </c>
     </row>
@@ -7433,7 +7429,7 @@
       <c r="B383" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C383" s="6" t="s">
+      <c r="C383" s="5" t="s">
         <v>764</v>
       </c>
     </row>
@@ -7444,7 +7440,7 @@
       <c r="B384" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="C384" s="6" t="s">
+      <c r="C384" s="5" t="s">
         <v>766</v>
       </c>
     </row>
@@ -7455,7 +7451,7 @@
       <c r="B385" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="C385" s="6" t="s">
+      <c r="C385" s="5" t="s">
         <v>768</v>
       </c>
     </row>
@@ -7466,7 +7462,7 @@
       <c r="B386" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="C386" s="6" t="s">
+      <c r="C386" s="5" t="s">
         <v>770</v>
       </c>
     </row>
@@ -7477,7 +7473,7 @@
       <c r="B387" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C387" s="6" t="s">
+      <c r="C387" s="5" t="s">
         <v>772</v>
       </c>
     </row>
@@ -7488,7 +7484,7 @@
       <c r="B388" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C388" s="6" t="s">
+      <c r="C388" s="5" t="s">
         <v>774</v>
       </c>
     </row>
@@ -7499,7 +7495,7 @@
       <c r="B389" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="C389" s="6" t="s">
+      <c r="C389" s="5" t="s">
         <v>776</v>
       </c>
     </row>
@@ -7510,7 +7506,7 @@
       <c r="B390" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="C390" s="6" t="s">
+      <c r="C390" s="5" t="s">
         <v>778</v>
       </c>
     </row>
@@ -7521,7 +7517,7 @@
       <c r="B391" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="C391" s="6" t="s">
+      <c r="C391" s="5" t="s">
         <v>780</v>
       </c>
     </row>

--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Dzisiaj jestem zmęczony i chcę już iść spać.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA ZMĘCZONY, DZISIAJ, JA, CHCE, SPAĆ,  JUŻ </t>
+    <t xml:space="preserve">JA, ZMĘCZONY, DZISIAJ, JA, CHCE, SPAĆ,  JUŻ </t>
   </si>
   <si>
     <t xml:space="preserve">Dlaczego wczoraj nie byłeś w szkole?</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Moja siostra uczy się migać.</t>
   </si>
   <si>
-    <t xml:space="preserve">MOJA SIOSTRA , MIGAĆ , UCZYĆ-SIĘ</t>
+    <t xml:space="preserve">MOJA, RODZEŃSTWO , MIGAĆ , UCZYĆ-SIĘ</t>
   </si>
   <si>
     <t xml:space="preserve">Co robisz w pracy?</t>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">Nie rozumiem, co ty mówisz.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA,NIE, ROZUMIEM , CO , MÓWIĆ, CO </t>
+    <t xml:space="preserve">JA,NIE, ROZUMIEM , TY, CO , MÓWIĆ, CO </t>
   </si>
   <si>
     <t xml:space="preserve">Wesoła kobieta idzie do domu.</t>
@@ -310,7 +310,7 @@
     <t xml:space="preserve">Kolega z pracy uczy się migać ze mną.</t>
   </si>
   <si>
-    <t xml:space="preserve">KOLEGA , PRACA , RAZEM , UCZYĆ-SIĘ,  MIGAĆ </t>
+    <t xml:space="preserve">MĘŻCZYZNA-KOLEGA , PRACA , RAZEM , UCZYĆ-SIĘ,  MIGAĆ </t>
   </si>
   <si>
     <t xml:space="preserve">Jestem chory i bardzo chcę dzisiaj spać.</t>
@@ -994,7 +994,7 @@
     <t xml:space="preserve">Ile czasu musieliście wczoraj czekać na tatę?</t>
   </si>
   <si>
-    <t xml:space="preserve">WY, WCZORAJ, TATA, ILE, CZAS, CZEKAĆ, MUSIEĆ</t>
+    <t xml:space="preserve">WY, WCZORAJ, TATA, ILE, CZEKAĆ, MUSIEĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Która kobieta we wtorek rano już kupił ten samochód?</t>
@@ -1168,7 +1168,7 @@
     <t xml:space="preserve">Dlaczego on nie może pomóc mamie z psem?</t>
   </si>
   <si>
-    <t xml:space="preserve">ON, DLACZEGO, MAMA, PIES, POMÓC, NIE-MÓC</t>
+    <t xml:space="preserve">ON, DLACZEGO, MAMA, PIES, POMÓC-CI, NIE-MÓC</t>
   </si>
   <si>
     <t xml:space="preserve">Wczoraj wieczorem kobieta dziękowała temu mężczyźnie.</t>
@@ -1192,7 +1192,7 @@
     <t xml:space="preserve">Ten klucz jest dla mojego kolegi.</t>
   </si>
   <si>
-    <t xml:space="preserve">KLUCZ, TEN, KOLEGA, MÓJ, DLA</t>
+    <t xml:space="preserve">KLUCZ, KOLEGA, MÓJ, DLA</t>
   </si>
   <si>
     <t xml:space="preserve">Gdzie mama kupiła tę gorącą kawę?</t>
@@ -1240,7 +1240,7 @@
     <t xml:space="preserve">Czy widzieliście, jak on miga?</t>
   </si>
   <si>
-    <t xml:space="preserve">WY, WIDZIEĆ, ON, MIGAĆ, JAK</t>
+    <t xml:space="preserve">WY, WIEDZIEĆ, ON, MIGAĆ, JAK</t>
   </si>
   <si>
     <t xml:space="preserve">Mam pomysł na nowy dom.</t>
@@ -1300,7 +1300,7 @@
     <t xml:space="preserve">Nie lubię, kiedy jesteś bardzo zmęczony po szkole.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, LUBIĆ, NIE, TY, SZKOŁA, BARDZO, ZMĘCZONY</t>
+    <t xml:space="preserve">JA, NIE-LUBIĆ, TY, SZKOŁA, BARDZO, ZMĘCZONY</t>
   </si>
   <si>
     <t xml:space="preserve">To był mój stary telefon.</t>
@@ -1312,7 +1312,7 @@
     <t xml:space="preserve">Dziękuję ci za ten dobry dzień.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZIĘKUJĘ, CI, DZIEŃ, DOBRY</t>
+    <t xml:space="preserve">DZIĘKUJĘ, CI, DOBRY, DZIEŃ</t>
   </si>
   <si>
     <t xml:space="preserve">Kto ma klucz do domu?</t>
@@ -1378,13 +1378,13 @@
     <t xml:space="preserve">Dziadek i babcia zawsze mają dla mnie czas.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZIADEK+BABCIA, ZAWSZE, MI, CZAS</t>
+    <t xml:space="preserve">DZIADEK, BABCIA, ZAWSZE, MI, CZAS, MIEĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Ja i mój brat chcemy zostać u kolegi na noc.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA+MÓJ, BRAT, KOLEGA, U, NOC, ZOSTAĆ, CHCIEĆ</t>
+    <t xml:space="preserve">JA, MÓJ, BRAT, KOLEGA, U, NOC, ZOSTAĆ, CHCIEĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Nie chcę pić wody z tobą.</t>
@@ -1480,7 +1480,7 @@
     <t xml:space="preserve">Mam bardzo dobry pomysł na jutro.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, MIEĆ, POMYSŁ, BARDZO, DOBRY, JUTRO </t>
+    <t xml:space="preserve">MIEĆ, POMYSŁ, BARDZO, DOBRY, JUTRO </t>
   </si>
   <si>
     <t xml:space="preserve">W szkole musimy uczyć się migać.</t>
@@ -1510,7 +1510,7 @@
     <t xml:space="preserve">Kobieta przed szkołą kupiła herbatę i kawę.</t>
   </si>
   <si>
-    <t xml:space="preserve">KOBIETA, SZKOŁA, PRZED, HERBATA, I, KAWA, KUPIĆ</t>
+    <t xml:space="preserve">KOBIETA, SZKOŁA, PRZED, HERBATA, KAWA, KUPIĆ</t>
   </si>
   <si>
     <t xml:space="preserve">Ty masz czas, żeby ze mną mówić?</t>
@@ -1540,7 +1540,7 @@
     <t xml:space="preserve">Wesoły mężczyzna kupił małego psa i kota.</t>
   </si>
   <si>
-    <t xml:space="preserve">MĘŻCZYZNA WESOŁY KUPIĆ PIES MAŁY PLUS KOT</t>
+    <t xml:space="preserve">MĘŻCZYZNA, WESOŁY, KUPIĆ, PIES, MAŁY, KOT</t>
   </si>
   <si>
     <t xml:space="preserve">Nie pamiętam, kiedy ty pracowałeś w poniedziałek.</t>
@@ -2767,7 +2767,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2785,10 +2785,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5998,7 +5994,7 @@
       <c r="B257" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C257" s="5" t="s">
+      <c r="C257" s="4" t="s">
         <v>512</v>
       </c>
       <c r="D257" s="2"/>
@@ -6010,7 +6006,7 @@
       <c r="B258" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C258" s="5" t="s">
+      <c r="C258" s="4" t="s">
         <v>514</v>
       </c>
       <c r="D258" s="2"/>
@@ -6022,7 +6018,7 @@
       <c r="B259" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C259" s="5" t="s">
+      <c r="C259" s="4" t="s">
         <v>516</v>
       </c>
       <c r="D259" s="2"/>
@@ -6034,7 +6030,7 @@
       <c r="B260" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C260" s="5" t="s">
+      <c r="C260" s="4" t="s">
         <v>518</v>
       </c>
       <c r="D260" s="2"/>
@@ -6046,7 +6042,7 @@
       <c r="B261" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C261" s="5" t="s">
+      <c r="C261" s="4" t="s">
         <v>520</v>
       </c>
       <c r="D261" s="2"/>
@@ -6058,7 +6054,7 @@
       <c r="B262" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C262" s="5" t="s">
+      <c r="C262" s="4" t="s">
         <v>522</v>
       </c>
       <c r="D262" s="2"/>
@@ -6070,7 +6066,7 @@
       <c r="B263" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C263" s="5" t="s">
+      <c r="C263" s="4" t="s">
         <v>524</v>
       </c>
       <c r="D263" s="2"/>
@@ -6082,7 +6078,7 @@
       <c r="B264" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C264" s="5" t="s">
+      <c r="C264" s="4" t="s">
         <v>526</v>
       </c>
       <c r="D264" s="2"/>
@@ -6094,7 +6090,7 @@
       <c r="B265" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C265" s="5" t="s">
+      <c r="C265" s="4" t="s">
         <v>528</v>
       </c>
       <c r="D265" s="2"/>
@@ -6106,7 +6102,7 @@
       <c r="B266" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C266" s="5" t="s">
+      <c r="C266" s="4" t="s">
         <v>530</v>
       </c>
       <c r="D266" s="2"/>
@@ -6118,7 +6114,7 @@
       <c r="B267" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C267" s="5" t="s">
+      <c r="C267" s="4" t="s">
         <v>532</v>
       </c>
       <c r="D267" s="2"/>
@@ -6130,7 +6126,7 @@
       <c r="B268" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C268" s="5" t="s">
+      <c r="C268" s="4" t="s">
         <v>534</v>
       </c>
       <c r="D268" s="2"/>
@@ -6142,7 +6138,7 @@
       <c r="B269" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C269" s="5" t="s">
+      <c r="C269" s="4" t="s">
         <v>536</v>
       </c>
       <c r="D269" s="2"/>
@@ -6154,7 +6150,7 @@
       <c r="B270" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C270" s="5" t="s">
+      <c r="C270" s="4" t="s">
         <v>538</v>
       </c>
       <c r="D270" s="2"/>
@@ -6166,7 +6162,7 @@
       <c r="B271" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C271" s="5" t="s">
+      <c r="C271" s="4" t="s">
         <v>540</v>
       </c>
       <c r="D271" s="2"/>
@@ -6178,7 +6174,7 @@
       <c r="B272" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C272" s="5" t="s">
+      <c r="C272" s="4" t="s">
         <v>542</v>
       </c>
       <c r="D272" s="2"/>
@@ -6190,7 +6186,7 @@
       <c r="B273" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C273" s="5" t="s">
+      <c r="C273" s="4" t="s">
         <v>544</v>
       </c>
       <c r="D273" s="2"/>
@@ -6202,7 +6198,7 @@
       <c r="B274" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C274" s="5" t="s">
+      <c r="C274" s="4" t="s">
         <v>546</v>
       </c>
       <c r="D274" s="2"/>
@@ -6214,7 +6210,7 @@
       <c r="B275" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C275" s="5" t="s">
+      <c r="C275" s="4" t="s">
         <v>548</v>
       </c>
       <c r="D275" s="2"/>
@@ -6226,7 +6222,7 @@
       <c r="B276" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C276" s="5" t="s">
+      <c r="C276" s="4" t="s">
         <v>550</v>
       </c>
       <c r="D276" s="2"/>
@@ -6238,7 +6234,7 @@
       <c r="B277" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C277" s="5" t="s">
+      <c r="C277" s="4" t="s">
         <v>552</v>
       </c>
       <c r="D277" s="2"/>
@@ -6250,7 +6246,7 @@
       <c r="B278" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C278" s="5" t="s">
+      <c r="C278" s="4" t="s">
         <v>554</v>
       </c>
       <c r="D278" s="2"/>
@@ -6262,7 +6258,7 @@
       <c r="B279" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C279" s="5" t="s">
+      <c r="C279" s="4" t="s">
         <v>556</v>
       </c>
       <c r="D279" s="2"/>
@@ -6274,7 +6270,7 @@
       <c r="B280" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C280" s="5" t="s">
+      <c r="C280" s="4" t="s">
         <v>558</v>
       </c>
       <c r="D280" s="2"/>
@@ -6286,7 +6282,7 @@
       <c r="B281" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C281" s="5" t="s">
+      <c r="C281" s="4" t="s">
         <v>560</v>
       </c>
       <c r="D281" s="2"/>
@@ -6298,7 +6294,7 @@
       <c r="B282" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C282" s="5" t="s">
+      <c r="C282" s="4" t="s">
         <v>562</v>
       </c>
       <c r="D282" s="2"/>
@@ -6310,7 +6306,7 @@
       <c r="B283" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C283" s="5" t="s">
+      <c r="C283" s="4" t="s">
         <v>564</v>
       </c>
       <c r="D283" s="2"/>
@@ -6322,7 +6318,7 @@
       <c r="B284" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C284" s="5" t="s">
+      <c r="C284" s="4" t="s">
         <v>566</v>
       </c>
       <c r="D284" s="2"/>
@@ -6334,7 +6330,7 @@
       <c r="B285" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C285" s="5" t="s">
+      <c r="C285" s="4" t="s">
         <v>568</v>
       </c>
       <c r="D285" s="2"/>
@@ -6346,7 +6342,7 @@
       <c r="B286" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C286" s="5" t="s">
+      <c r="C286" s="4" t="s">
         <v>570</v>
       </c>
       <c r="D286" s="2"/>
@@ -6358,7 +6354,7 @@
       <c r="B287" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C287" s="5" t="s">
+      <c r="C287" s="4" t="s">
         <v>572</v>
       </c>
       <c r="D287" s="2"/>
@@ -6370,7 +6366,7 @@
       <c r="B288" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C288" s="5" t="s">
+      <c r="C288" s="4" t="s">
         <v>574</v>
       </c>
       <c r="D288" s="2"/>
@@ -6382,7 +6378,7 @@
       <c r="B289" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C289" s="5" t="s">
+      <c r="C289" s="4" t="s">
         <v>576</v>
       </c>
       <c r="D289" s="2"/>
@@ -6394,7 +6390,7 @@
       <c r="B290" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C290" s="5" t="s">
+      <c r="C290" s="4" t="s">
         <v>578</v>
       </c>
       <c r="D290" s="2"/>
@@ -6406,7 +6402,7 @@
       <c r="B291" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C291" s="5" t="s">
+      <c r="C291" s="4" t="s">
         <v>580</v>
       </c>
       <c r="D291" s="2"/>
@@ -6418,7 +6414,7 @@
       <c r="B292" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C292" s="5" t="s">
+      <c r="C292" s="4" t="s">
         <v>582</v>
       </c>
       <c r="D292" s="2"/>
@@ -6430,7 +6426,7 @@
       <c r="B293" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C293" s="5" t="s">
+      <c r="C293" s="4" t="s">
         <v>584</v>
       </c>
       <c r="D293" s="2"/>
@@ -6442,7 +6438,7 @@
       <c r="B294" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C294" s="5" t="s">
+      <c r="C294" s="4" t="s">
         <v>586</v>
       </c>
       <c r="D294" s="2"/>
@@ -6454,7 +6450,7 @@
       <c r="B295" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C295" s="5" t="s">
+      <c r="C295" s="4" t="s">
         <v>588</v>
       </c>
       <c r="D295" s="2"/>
@@ -6466,7 +6462,7 @@
       <c r="B296" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="C296" s="5" t="s">
+      <c r="C296" s="4" t="s">
         <v>590</v>
       </c>
       <c r="D296" s="2"/>
@@ -6478,7 +6474,7 @@
       <c r="B297" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C297" s="5" t="s">
+      <c r="C297" s="4" t="s">
         <v>592</v>
       </c>
       <c r="D297" s="2"/>
@@ -6490,7 +6486,7 @@
       <c r="B298" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="C298" s="5" t="s">
+      <c r="C298" s="4" t="s">
         <v>594</v>
       </c>
       <c r="D298" s="2"/>
@@ -6502,7 +6498,7 @@
       <c r="B299" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C299" s="5" t="s">
+      <c r="C299" s="4" t="s">
         <v>596</v>
       </c>
       <c r="D299" s="2"/>
@@ -6514,7 +6510,7 @@
       <c r="B300" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C300" s="5" t="s">
+      <c r="C300" s="4" t="s">
         <v>598</v>
       </c>
       <c r="D300" s="2"/>
@@ -6526,7 +6522,7 @@
       <c r="B301" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="C301" s="5" t="s">
+      <c r="C301" s="4" t="s">
         <v>600</v>
       </c>
       <c r="D301" s="2"/>
@@ -6538,7 +6534,7 @@
       <c r="B302" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C302" s="5" t="s">
+      <c r="C302" s="4" t="s">
         <v>602</v>
       </c>
     </row>
@@ -6549,7 +6545,7 @@
       <c r="B303" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C303" s="5" t="s">
+      <c r="C303" s="4" t="s">
         <v>604</v>
       </c>
     </row>
@@ -6560,7 +6556,7 @@
       <c r="B304" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C304" s="5" t="s">
+      <c r="C304" s="4" t="s">
         <v>606</v>
       </c>
     </row>
@@ -6571,7 +6567,7 @@
       <c r="B305" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C305" s="5" t="s">
+      <c r="C305" s="4" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6582,7 +6578,7 @@
       <c r="B306" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C306" s="5" t="s">
+      <c r="C306" s="4" t="s">
         <v>610</v>
       </c>
     </row>
@@ -6593,7 +6589,7 @@
       <c r="B307" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C307" s="5" t="s">
+      <c r="C307" s="4" t="s">
         <v>612</v>
       </c>
     </row>
@@ -6604,7 +6600,7 @@
       <c r="B308" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C308" s="5" t="s">
+      <c r="C308" s="4" t="s">
         <v>614</v>
       </c>
     </row>
@@ -6615,7 +6611,7 @@
       <c r="B309" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C309" s="5" t="s">
+      <c r="C309" s="4" t="s">
         <v>616</v>
       </c>
     </row>
@@ -6626,7 +6622,7 @@
       <c r="B310" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="C310" s="5" t="s">
+      <c r="C310" s="4" t="s">
         <v>618</v>
       </c>
     </row>
@@ -6637,7 +6633,7 @@
       <c r="B311" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C311" s="5" t="s">
+      <c r="C311" s="4" t="s">
         <v>620</v>
       </c>
     </row>
@@ -6648,7 +6644,7 @@
       <c r="B312" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="C312" s="5" t="s">
+      <c r="C312" s="4" t="s">
         <v>622</v>
       </c>
     </row>
@@ -6659,7 +6655,7 @@
       <c r="B313" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C313" s="5" t="s">
+      <c r="C313" s="4" t="s">
         <v>624</v>
       </c>
     </row>
@@ -6670,7 +6666,7 @@
       <c r="B314" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C314" s="5" t="s">
+      <c r="C314" s="4" t="s">
         <v>626</v>
       </c>
     </row>
@@ -6681,7 +6677,7 @@
       <c r="B315" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="C315" s="5" t="s">
+      <c r="C315" s="4" t="s">
         <v>628</v>
       </c>
     </row>
@@ -6692,7 +6688,7 @@
       <c r="B316" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C316" s="5" t="s">
+      <c r="C316" s="4" t="s">
         <v>630</v>
       </c>
     </row>
@@ -6703,7 +6699,7 @@
       <c r="B317" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C317" s="5" t="s">
+      <c r="C317" s="4" t="s">
         <v>632</v>
       </c>
     </row>
@@ -6714,7 +6710,7 @@
       <c r="B318" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C318" s="5" t="s">
+      <c r="C318" s="4" t="s">
         <v>634</v>
       </c>
     </row>
@@ -6725,7 +6721,7 @@
       <c r="B319" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C319" s="5" t="s">
+      <c r="C319" s="4" t="s">
         <v>636</v>
       </c>
     </row>
@@ -6736,7 +6732,7 @@
       <c r="B320" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C320" s="5" t="s">
+      <c r="C320" s="4" t="s">
         <v>638</v>
       </c>
     </row>
@@ -6747,7 +6743,7 @@
       <c r="B321" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C321" s="5" t="s">
+      <c r="C321" s="4" t="s">
         <v>640</v>
       </c>
     </row>
@@ -6758,7 +6754,7 @@
       <c r="B322" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C322" s="5" t="s">
+      <c r="C322" s="4" t="s">
         <v>642</v>
       </c>
     </row>
@@ -6769,7 +6765,7 @@
       <c r="B323" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C323" s="5" t="s">
+      <c r="C323" s="4" t="s">
         <v>644</v>
       </c>
     </row>
@@ -6780,7 +6776,7 @@
       <c r="B324" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C324" s="5" t="s">
+      <c r="C324" s="4" t="s">
         <v>646</v>
       </c>
     </row>
@@ -6791,7 +6787,7 @@
       <c r="B325" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C325" s="5" t="s">
+      <c r="C325" s="4" t="s">
         <v>648</v>
       </c>
     </row>
@@ -6802,7 +6798,7 @@
       <c r="B326" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C326" s="5" t="s">
+      <c r="C326" s="4" t="s">
         <v>650</v>
       </c>
     </row>
@@ -6813,7 +6809,7 @@
       <c r="B327" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C327" s="5" t="s">
+      <c r="C327" s="4" t="s">
         <v>652</v>
       </c>
     </row>
@@ -6824,7 +6820,7 @@
       <c r="B328" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C328" s="5" t="s">
+      <c r="C328" s="4" t="s">
         <v>654</v>
       </c>
     </row>
@@ -6835,7 +6831,7 @@
       <c r="B329" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C329" s="5" t="s">
+      <c r="C329" s="4" t="s">
         <v>656</v>
       </c>
     </row>
@@ -6846,7 +6842,7 @@
       <c r="B330" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="C330" s="5" t="s">
+      <c r="C330" s="4" t="s">
         <v>658</v>
       </c>
     </row>
@@ -6857,7 +6853,7 @@
       <c r="B331" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C331" s="5" t="s">
+      <c r="C331" s="4" t="s">
         <v>660</v>
       </c>
     </row>
@@ -6868,7 +6864,7 @@
       <c r="B332" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C332" s="5" t="s">
+      <c r="C332" s="4" t="s">
         <v>662</v>
       </c>
     </row>
@@ -6879,7 +6875,7 @@
       <c r="B333" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C333" s="5" t="s">
+      <c r="C333" s="4" t="s">
         <v>664</v>
       </c>
     </row>
@@ -6890,7 +6886,7 @@
       <c r="B334" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C334" s="5" t="s">
+      <c r="C334" s="4" t="s">
         <v>666</v>
       </c>
     </row>
@@ -6901,7 +6897,7 @@
       <c r="B335" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C335" s="5" t="s">
+      <c r="C335" s="4" t="s">
         <v>668</v>
       </c>
     </row>
@@ -6912,7 +6908,7 @@
       <c r="B336" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C336" s="5" t="s">
+      <c r="C336" s="4" t="s">
         <v>670</v>
       </c>
     </row>
@@ -6923,7 +6919,7 @@
       <c r="B337" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C337" s="5" t="s">
+      <c r="C337" s="4" t="s">
         <v>672</v>
       </c>
     </row>
@@ -6934,7 +6930,7 @@
       <c r="B338" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C338" s="5" t="s">
+      <c r="C338" s="4" t="s">
         <v>674</v>
       </c>
     </row>
@@ -6945,7 +6941,7 @@
       <c r="B339" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C339" s="5" t="s">
+      <c r="C339" s="4" t="s">
         <v>676</v>
       </c>
     </row>
@@ -6956,7 +6952,7 @@
       <c r="B340" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="C340" s="5" t="s">
+      <c r="C340" s="4" t="s">
         <v>678</v>
       </c>
     </row>
@@ -6967,7 +6963,7 @@
       <c r="B341" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C341" s="5" t="s">
+      <c r="C341" s="4" t="s">
         <v>680</v>
       </c>
     </row>
@@ -6978,7 +6974,7 @@
       <c r="B342" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C342" s="5" t="s">
+      <c r="C342" s="4" t="s">
         <v>682</v>
       </c>
     </row>
@@ -6989,7 +6985,7 @@
       <c r="B343" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="C343" s="5" t="s">
+      <c r="C343" s="4" t="s">
         <v>684</v>
       </c>
     </row>
@@ -7000,7 +6996,7 @@
       <c r="B344" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C344" s="5" t="s">
+      <c r="C344" s="4" t="s">
         <v>686</v>
       </c>
     </row>
@@ -7011,7 +7007,7 @@
       <c r="B345" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="C345" s="5" t="s">
+      <c r="C345" s="4" t="s">
         <v>688</v>
       </c>
     </row>
@@ -7022,7 +7018,7 @@
       <c r="B346" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C346" s="5" t="s">
+      <c r="C346" s="4" t="s">
         <v>690</v>
       </c>
     </row>
@@ -7033,7 +7029,7 @@
       <c r="B347" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="C347" s="5" t="s">
+      <c r="C347" s="4" t="s">
         <v>692</v>
       </c>
     </row>
@@ -7044,7 +7040,7 @@
       <c r="B348" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="C348" s="5" t="s">
+      <c r="C348" s="4" t="s">
         <v>694</v>
       </c>
     </row>
@@ -7055,7 +7051,7 @@
       <c r="B349" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C349" s="5" t="s">
+      <c r="C349" s="4" t="s">
         <v>696</v>
       </c>
     </row>
@@ -7066,7 +7062,7 @@
       <c r="B350" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="C350" s="5" t="s">
+      <c r="C350" s="4" t="s">
         <v>698</v>
       </c>
     </row>
@@ -7077,7 +7073,7 @@
       <c r="B351" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C351" s="5" t="s">
+      <c r="C351" s="4" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7088,7 +7084,7 @@
       <c r="B352" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="C352" s="5" t="s">
+      <c r="C352" s="4" t="s">
         <v>702</v>
       </c>
     </row>
@@ -7099,7 +7095,7 @@
       <c r="B353" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C353" s="5" t="s">
+      <c r="C353" s="4" t="s">
         <v>704</v>
       </c>
     </row>
@@ -7110,7 +7106,7 @@
       <c r="B354" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C354" s="5" t="s">
+      <c r="C354" s="4" t="s">
         <v>706</v>
       </c>
     </row>
@@ -7121,7 +7117,7 @@
       <c r="B355" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C355" s="5" t="s">
+      <c r="C355" s="4" t="s">
         <v>708</v>
       </c>
     </row>
@@ -7132,7 +7128,7 @@
       <c r="B356" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C356" s="5" t="s">
+      <c r="C356" s="4" t="s">
         <v>710</v>
       </c>
     </row>
@@ -7143,7 +7139,7 @@
       <c r="B357" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C357" s="5" t="s">
+      <c r="C357" s="4" t="s">
         <v>712</v>
       </c>
     </row>
@@ -7154,7 +7150,7 @@
       <c r="B358" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="C358" s="5" t="s">
+      <c r="C358" s="4" t="s">
         <v>714</v>
       </c>
     </row>
@@ -7165,7 +7161,7 @@
       <c r="B359" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="C359" s="5" t="s">
+      <c r="C359" s="4" t="s">
         <v>716</v>
       </c>
     </row>
@@ -7176,7 +7172,7 @@
       <c r="B360" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C360" s="5" t="s">
+      <c r="C360" s="4" t="s">
         <v>718</v>
       </c>
     </row>
@@ -7187,7 +7183,7 @@
       <c r="B361" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="C361" s="5" t="s">
+      <c r="C361" s="4" t="s">
         <v>720</v>
       </c>
     </row>
@@ -7198,7 +7194,7 @@
       <c r="B362" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="C362" s="5" t="s">
+      <c r="C362" s="4" t="s">
         <v>722</v>
       </c>
     </row>
@@ -7209,7 +7205,7 @@
       <c r="B363" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C363" s="5" t="s">
+      <c r="C363" s="4" t="s">
         <v>724</v>
       </c>
     </row>
@@ -7220,7 +7216,7 @@
       <c r="B364" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="C364" s="5" t="s">
+      <c r="C364" s="4" t="s">
         <v>726</v>
       </c>
     </row>
@@ -7231,7 +7227,7 @@
       <c r="B365" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C365" s="5" t="s">
+      <c r="C365" s="4" t="s">
         <v>728</v>
       </c>
     </row>
@@ -7242,7 +7238,7 @@
       <c r="B366" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="C366" s="5" t="s">
+      <c r="C366" s="4" t="s">
         <v>730</v>
       </c>
     </row>
@@ -7253,7 +7249,7 @@
       <c r="B367" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C367" s="5" t="s">
+      <c r="C367" s="4" t="s">
         <v>732</v>
       </c>
     </row>
@@ -7264,7 +7260,7 @@
       <c r="B368" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C368" s="5" t="s">
+      <c r="C368" s="4" t="s">
         <v>734</v>
       </c>
     </row>
@@ -7275,7 +7271,7 @@
       <c r="B369" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="C369" s="5" t="s">
+      <c r="C369" s="4" t="s">
         <v>736</v>
       </c>
     </row>
@@ -7286,7 +7282,7 @@
       <c r="B370" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C370" s="5" t="s">
+      <c r="C370" s="4" t="s">
         <v>738</v>
       </c>
     </row>
@@ -7297,7 +7293,7 @@
       <c r="B371" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C371" s="5" t="s">
+      <c r="C371" s="4" t="s">
         <v>740</v>
       </c>
     </row>
@@ -7308,7 +7304,7 @@
       <c r="B372" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C372" s="5" t="s">
+      <c r="C372" s="4" t="s">
         <v>742</v>
       </c>
     </row>
@@ -7319,7 +7315,7 @@
       <c r="B373" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C373" s="5" t="s">
+      <c r="C373" s="4" t="s">
         <v>744</v>
       </c>
     </row>
@@ -7330,7 +7326,7 @@
       <c r="B374" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="C374" s="5" t="s">
+      <c r="C374" s="4" t="s">
         <v>746</v>
       </c>
     </row>
@@ -7341,7 +7337,7 @@
       <c r="B375" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C375" s="5" t="s">
+      <c r="C375" s="4" t="s">
         <v>748</v>
       </c>
     </row>
@@ -7352,7 +7348,7 @@
       <c r="B376" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="C376" s="5" t="s">
+      <c r="C376" s="4" t="s">
         <v>750</v>
       </c>
     </row>
@@ -7363,7 +7359,7 @@
       <c r="B377" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C377" s="5" t="s">
+      <c r="C377" s="4" t="s">
         <v>752</v>
       </c>
     </row>
@@ -7374,7 +7370,7 @@
       <c r="B378" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C378" s="5" t="s">
+      <c r="C378" s="4" t="s">
         <v>754</v>
       </c>
     </row>
@@ -7385,7 +7381,7 @@
       <c r="B379" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="C379" s="5" t="s">
+      <c r="C379" s="4" t="s">
         <v>756</v>
       </c>
     </row>
@@ -7396,7 +7392,7 @@
       <c r="B380" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="C380" s="5" t="s">
+      <c r="C380" s="4" t="s">
         <v>758</v>
       </c>
     </row>
@@ -7407,7 +7403,7 @@
       <c r="B381" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C381" s="5" t="s">
+      <c r="C381" s="4" t="s">
         <v>760</v>
       </c>
     </row>
@@ -7418,7 +7414,7 @@
       <c r="B382" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="C382" s="5" t="s">
+      <c r="C382" s="4" t="s">
         <v>762</v>
       </c>
     </row>
@@ -7429,7 +7425,7 @@
       <c r="B383" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C383" s="5" t="s">
+      <c r="C383" s="4" t="s">
         <v>764</v>
       </c>
     </row>
@@ -7440,7 +7436,7 @@
       <c r="B384" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="C384" s="5" t="s">
+      <c r="C384" s="4" t="s">
         <v>766</v>
       </c>
     </row>
@@ -7451,7 +7447,7 @@
       <c r="B385" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="C385" s="5" t="s">
+      <c r="C385" s="4" t="s">
         <v>768</v>
       </c>
     </row>
@@ -7462,7 +7458,7 @@
       <c r="B386" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="C386" s="5" t="s">
+      <c r="C386" s="4" t="s">
         <v>770</v>
       </c>
     </row>
@@ -7473,7 +7469,7 @@
       <c r="B387" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C387" s="5" t="s">
+      <c r="C387" s="4" t="s">
         <v>772</v>
       </c>
     </row>
@@ -7484,7 +7480,7 @@
       <c r="B388" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C388" s="5" t="s">
+      <c r="C388" s="4" t="s">
         <v>774</v>
       </c>
     </row>
@@ -7495,7 +7491,7 @@
       <c r="B389" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="C389" s="5" t="s">
+      <c r="C389" s="4" t="s">
         <v>776</v>
       </c>
     </row>
@@ -7506,7 +7502,7 @@
       <c r="B390" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="C390" s="5" t="s">
+      <c r="C390" s="4" t="s">
         <v>778</v>
       </c>
     </row>
@@ -7517,7 +7513,7 @@
       <c r="B391" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="C391" s="5" t="s">
+      <c r="C391" s="4" t="s">
         <v>780</v>
       </c>
     </row>

--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{969B918A-EBFD-4054-A732-1DA8E8F1672A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BE14D5C-B0B5-478C-B07A-3118A13CE647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
     <t>Czy ty wiesz, gdzie jest moja mama i siostra?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY WIESZ , GDZIE , MAMA , SIOSTRA , JEST </t>
+    <t xml:space="preserve">TY, WIESZ , GDZIE , MAMA , SIOSTRA , JEST </t>
   </si>
   <si>
     <t>Chce mi się pić.</t>
@@ -114,7 +114,7 @@
     <t>Co robisz w pracy?</t>
   </si>
   <si>
-    <t xml:space="preserve">PRACA , TY , ROBIĆ CO? </t>
+    <t xml:space="preserve">PRACA , TY , ROBIĆ, CO? </t>
   </si>
   <si>
     <t>Wczoraj byłem w szkole i uczyłem się migać.</t>
@@ -282,7 +282,7 @@
     <t>Mężczyzna nie słyszy, ale myśli i miga.</t>
   </si>
   <si>
-    <t>MĘŻCZYZNA , NIE, SŁYCHAĆ , ALE , MYŚLEĆ , MIGAĆ</t>
+    <t>MĘŻCZYZNA,NIE-SŁYSZY, ALE,MYŚLEĆ,MIGAĆ</t>
   </si>
   <si>
     <t>Jak dobrze uczyć się migać w nowej szkole.</t>
@@ -2741,14 +2741,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2881,5486 +2879,5484 @@
   <dimension ref="A1:D501"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60" style="1" customWidth="1"/>
-    <col min="3" max="3" width="84.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="84.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="2"/>
+      <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="2"/>
+      <c r="D29" s="1"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" s="1"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" s="1"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" s="1"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" s="1"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" s="1"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" s="1"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" s="1"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" s="1"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" s="1"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" s="1"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" s="1"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" s="1"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" s="1"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="2"/>
+      <c r="D46" s="1"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D47" s="2"/>
+      <c r="D47" s="1"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="2"/>
+      <c r="D48" s="1"/>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D49" s="2"/>
+      <c r="D49" s="1"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="D50" s="1"/>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="2"/>
+      <c r="D51" s="1"/>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="2"/>
+      <c r="D52" s="1"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" t="s">
         <v>103</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="1"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="2"/>
+      <c r="D54" s="1"/>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D55" s="2"/>
+      <c r="D55" s="1"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D56" s="2"/>
+      <c r="D56" s="1"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" s="1"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D58" s="2"/>
+      <c r="D58" s="1"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" t="s">
         <v>115</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D59" s="2"/>
+      <c r="D59" s="1"/>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D60" s="2"/>
+      <c r="D60" s="1"/>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D61" s="2"/>
+      <c r="D61" s="1"/>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D62" s="2"/>
+      <c r="D62" s="1"/>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D63" s="2"/>
+      <c r="D63" s="1"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D64" s="2"/>
+      <c r="D64" s="1"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D65" s="2"/>
+      <c r="D65" s="1"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" t="s">
         <v>129</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D66" s="2"/>
+      <c r="D66" s="1"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" t="s">
         <v>131</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D67" s="2"/>
+      <c r="D67" s="1"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D68" s="2"/>
+      <c r="D68" s="1"/>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" t="s">
         <v>135</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D69" s="2"/>
+      <c r="D69" s="1"/>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" t="s">
         <v>137</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D70" s="2"/>
+      <c r="D70" s="1"/>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" t="s">
         <v>139</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D71" s="2"/>
+      <c r="D71" s="1"/>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" t="s">
         <v>141</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D72" s="2"/>
+      <c r="D72" s="1"/>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" t="s">
         <v>143</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D73" s="2"/>
+      <c r="D73" s="1"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="2">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" t="s">
         <v>145</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D74" s="2"/>
+      <c r="D74" s="1"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="2">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" t="s">
         <v>147</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D75" s="2"/>
+      <c r="D75" s="1"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="2">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" t="s">
         <v>149</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D76" s="2"/>
+      <c r="D76" s="1"/>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="2">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" t="s">
         <v>151</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D77" s="2"/>
+      <c r="D77" s="1"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="2">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" t="s">
         <v>153</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D78" s="2"/>
+      <c r="D78" s="1"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="2">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" t="s">
         <v>155</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D79" s="2"/>
+      <c r="D79" s="1"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="2">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" t="s">
         <v>157</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D80" s="1"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="2">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" t="s">
         <v>159</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D81" s="2"/>
+      <c r="D81" s="1"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="2">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" t="s">
         <v>161</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D82" s="2"/>
+      <c r="D82" s="1"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="2">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" t="s">
         <v>163</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D83" s="2"/>
+      <c r="D83" s="1"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="2">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" t="s">
         <v>165</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D84" s="2"/>
+      <c r="D84" s="1"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="2">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" t="s">
         <v>167</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D85" s="2"/>
+      <c r="D85" s="1"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="2">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" t="s">
         <v>169</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D86" s="2"/>
+      <c r="D86" s="1"/>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="2">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" t="s">
         <v>171</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D87" s="2"/>
+      <c r="D87" s="1"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="2">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" t="s">
         <v>173</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D88" s="2"/>
+      <c r="D88" s="1"/>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="2">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" t="s">
         <v>175</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D89" s="2"/>
+      <c r="D89" s="1"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="2">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" t="s">
         <v>177</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D90" s="2"/>
+      <c r="D90" s="1"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="2">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" t="s">
         <v>179</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D91" s="2"/>
+      <c r="D91" s="1"/>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="2">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" t="s">
         <v>181</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D92" s="2"/>
+      <c r="D92" s="1"/>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="2">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" t="s">
         <v>183</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D93" s="2"/>
+      <c r="D93" s="1"/>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="2">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" t="s">
         <v>185</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D94" s="2"/>
+      <c r="D94" s="1"/>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="2">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" t="s">
         <v>187</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D95" s="2"/>
+      <c r="D95" s="1"/>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="2">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" t="s">
         <v>189</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D96" s="2"/>
+      <c r="D96" s="1"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="2">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" t="s">
         <v>191</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D97" s="2"/>
+      <c r="D97" s="1"/>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="2">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" t="s">
         <v>193</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D98" s="2"/>
+      <c r="D98" s="1"/>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="2">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" t="s">
         <v>195</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D99" s="2"/>
+      <c r="D99" s="1"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="2">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" t="s">
         <v>197</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D100" s="2"/>
+      <c r="D100" s="1"/>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="2">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" t="s">
         <v>199</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D101" s="2"/>
+      <c r="D101" s="1"/>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="2">
+      <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" t="s">
         <v>201</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D102" s="2"/>
+      <c r="D102" s="1"/>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="2">
+      <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" t="s">
         <v>203</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D103" s="2"/>
+      <c r="D103" s="1"/>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="2">
+      <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" t="s">
         <v>205</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D104" s="2"/>
+      <c r="D104" s="1"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="2">
+      <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" t="s">
         <v>207</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D105" s="2"/>
+      <c r="D105" s="1"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="2">
+      <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" t="s">
         <v>209</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D106" s="2"/>
+      <c r="D106" s="1"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="2">
+      <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" t="s">
         <v>211</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D107" s="2"/>
+      <c r="D107" s="1"/>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="2">
+      <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" t="s">
         <v>213</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D108" s="2"/>
+      <c r="D108" s="1"/>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="2">
+      <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" t="s">
         <v>215</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D109" s="2"/>
+      <c r="D109" s="1"/>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="2">
+      <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" t="s">
         <v>217</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D110" s="2"/>
+      <c r="D110" s="1"/>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="2">
+      <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" t="s">
         <v>219</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D111" s="2"/>
+      <c r="D111" s="1"/>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="2">
+      <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" t="s">
         <v>221</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D112" s="2"/>
+      <c r="D112" s="1"/>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="2">
+      <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" t="s">
         <v>223</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D113" s="2"/>
+      <c r="D113" s="1"/>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="2">
+      <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" t="s">
         <v>225</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D114" s="2"/>
+      <c r="D114" s="1"/>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="2">
+      <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" t="s">
         <v>227</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D115" s="2"/>
+      <c r="D115" s="1"/>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="2">
+      <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" t="s">
         <v>229</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D116" s="2"/>
+      <c r="D116" s="1"/>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="2">
+      <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" t="s">
         <v>231</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D117" s="2"/>
+      <c r="D117" s="1"/>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="2">
+      <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" t="s">
         <v>233</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D118" s="2"/>
+      <c r="D118" s="1"/>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="2">
+      <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" t="s">
         <v>235</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D119" s="2"/>
+      <c r="D119" s="1"/>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="2">
+      <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" t="s">
         <v>237</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D120" s="2"/>
+      <c r="D120" s="1"/>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="2">
+      <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" t="s">
         <v>239</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D121" s="2"/>
+      <c r="D121" s="1"/>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="2">
+      <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" t="s">
         <v>241</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D122" s="2"/>
+      <c r="D122" s="1"/>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="2">
+      <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" t="s">
         <v>243</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D123" s="2"/>
+      <c r="D123" s="1"/>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="2">
+      <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" t="s">
         <v>245</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D124" s="2"/>
+      <c r="D124" s="1"/>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="2">
+      <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" t="s">
         <v>247</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D125" s="2"/>
+      <c r="D125" s="1"/>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="2">
+      <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" t="s">
         <v>249</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D126" s="2"/>
+      <c r="D126" s="1"/>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="2">
+      <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" t="s">
         <v>251</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D127" s="2"/>
+      <c r="D127" s="1"/>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="2">
+      <c r="A128" s="1">
         <v>127</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" t="s">
         <v>253</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D128" s="2"/>
+      <c r="D128" s="1"/>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="2">
+      <c r="A129" s="1">
         <v>128</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" t="s">
         <v>255</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D129" s="2"/>
+      <c r="D129" s="1"/>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="2">
+      <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" t="s">
         <v>257</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D130" s="2"/>
+      <c r="D130" s="1"/>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="2">
+      <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" t="s">
         <v>259</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D131" s="2"/>
+      <c r="D131" s="1"/>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="2">
+      <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" t="s">
         <v>261</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D132" s="2"/>
+      <c r="D132" s="1"/>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="2">
+      <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" t="s">
         <v>263</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D133" s="2"/>
+      <c r="D133" s="1"/>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="2">
+      <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" t="s">
         <v>265</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D134" s="2"/>
+      <c r="D134" s="1"/>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="2">
+      <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" t="s">
         <v>267</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D135" s="2"/>
+      <c r="D135" s="1"/>
     </row>
     <row r="136" spans="1:4">
-      <c r="A136" s="2">
+      <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" t="s">
         <v>269</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D136" s="2"/>
+      <c r="D136" s="1"/>
     </row>
     <row r="137" spans="1:4">
-      <c r="A137" s="2">
+      <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" t="s">
         <v>271</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D137" s="2"/>
+      <c r="D137" s="1"/>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="2">
+      <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" t="s">
         <v>273</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D138" s="2"/>
+      <c r="D138" s="1"/>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="2">
+      <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" t="s">
         <v>275</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D139" s="2"/>
+      <c r="D139" s="1"/>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="2">
+      <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" t="s">
         <v>277</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D140" s="2"/>
+      <c r="D140" s="1"/>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="2">
+      <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" t="s">
         <v>279</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D141" s="2"/>
+      <c r="D141" s="1"/>
     </row>
     <row r="142" spans="1:4">
-      <c r="A142" s="2">
+      <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" t="s">
         <v>281</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D142" s="2"/>
+      <c r="D142" s="1"/>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="2">
+      <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" t="s">
         <v>283</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D143" s="2"/>
+      <c r="D143" s="1"/>
     </row>
     <row r="144" spans="1:4">
-      <c r="A144" s="2">
+      <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" t="s">
         <v>285</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D144" s="2"/>
+      <c r="D144" s="1"/>
     </row>
     <row r="145" spans="1:4">
-      <c r="A145" s="2">
+      <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" t="s">
         <v>287</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D145" s="2"/>
+      <c r="D145" s="1"/>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="2">
+      <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" t="s">
         <v>289</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D146" s="2"/>
+      <c r="D146" s="1"/>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="2">
+      <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" t="s">
         <v>291</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D147" s="2"/>
+      <c r="D147" s="1"/>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="2">
+      <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" t="s">
         <v>293</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D148" s="2"/>
+      <c r="D148" s="1"/>
     </row>
     <row r="149" spans="1:4">
-      <c r="A149" s="2">
+      <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" t="s">
         <v>295</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D149" s="2"/>
+      <c r="D149" s="1"/>
     </row>
     <row r="150" spans="1:4">
-      <c r="A150" s="2">
+      <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" t="s">
         <v>297</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D150" s="2"/>
+      <c r="D150" s="1"/>
     </row>
     <row r="151" spans="1:4">
-      <c r="A151" s="2">
+      <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" t="s">
         <v>299</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D151" s="2"/>
+      <c r="D151" s="1"/>
     </row>
     <row r="152" spans="1:4">
-      <c r="A152" s="2">
+      <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" t="s">
         <v>301</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D152" s="2"/>
+      <c r="D152" s="1"/>
     </row>
     <row r="153" spans="1:4">
-      <c r="A153" s="2">
+      <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" t="s">
         <v>303</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C153" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D153" s="2"/>
+      <c r="D153" s="1"/>
     </row>
     <row r="154" spans="1:4">
-      <c r="A154" s="2">
+      <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" t="s">
         <v>305</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C154" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D154" s="2"/>
+      <c r="D154" s="1"/>
     </row>
     <row r="155" spans="1:4">
-      <c r="A155" s="2">
+      <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" t="s">
         <v>307</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D155" s="2"/>
+      <c r="D155" s="1"/>
     </row>
     <row r="156" spans="1:4">
-      <c r="A156" s="2">
+      <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" t="s">
         <v>309</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D156" s="2"/>
+      <c r="D156" s="1"/>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="2">
+      <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" t="s">
         <v>311</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="D157" s="2"/>
+      <c r="D157" s="1"/>
     </row>
     <row r="158" spans="1:4">
-      <c r="A158" s="2">
+      <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" t="s">
         <v>313</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D158" s="2"/>
+      <c r="D158" s="1"/>
     </row>
     <row r="159" spans="1:4">
-      <c r="A159" s="2">
+      <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" t="s">
         <v>315</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D159" s="2"/>
+      <c r="D159" s="1"/>
     </row>
     <row r="160" spans="1:4">
-      <c r="A160" s="2">
+      <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" t="s">
         <v>317</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D160" s="2"/>
+      <c r="D160" s="1"/>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="2">
+      <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" t="s">
         <v>319</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D161" s="2"/>
+      <c r="D161" s="1"/>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="2">
+      <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" t="s">
         <v>321</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D162" s="2"/>
+      <c r="D162" s="1"/>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="2">
+      <c r="A163" s="1">
         <v>162</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" t="s">
         <v>323</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D163" s="2"/>
+      <c r="D163" s="1"/>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="2">
+      <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" t="s">
         <v>325</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D164" s="2"/>
+      <c r="D164" s="1"/>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="2">
+      <c r="A165" s="1">
         <v>164</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" t="s">
         <v>327</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D165" s="2"/>
+      <c r="D165" s="1"/>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="2">
+      <c r="A166" s="1">
         <v>165</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" t="s">
         <v>329</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D166" s="2"/>
+      <c r="D166" s="1"/>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="2">
+      <c r="A167" s="1">
         <v>166</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" t="s">
         <v>331</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D167" s="2"/>
+      <c r="D167" s="1"/>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="2">
+      <c r="A168" s="1">
         <v>167</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" t="s">
         <v>333</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D168" s="2"/>
+      <c r="D168" s="1"/>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="2">
+      <c r="A169" s="1">
         <v>168</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" t="s">
         <v>335</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D169" s="2"/>
+      <c r="D169" s="1"/>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="2">
+      <c r="A170" s="1">
         <v>169</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" t="s">
         <v>337</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D170" s="2"/>
+      <c r="D170" s="1"/>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="2">
+      <c r="A171" s="1">
         <v>170</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" t="s">
         <v>339</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D171" s="2"/>
+      <c r="D171" s="1"/>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="2">
+      <c r="A172" s="1">
         <v>171</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" t="s">
         <v>341</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C172" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D172" s="2"/>
+      <c r="D172" s="1"/>
     </row>
     <row r="173" spans="1:4">
-      <c r="A173" s="2">
+      <c r="A173" s="1">
         <v>172</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" t="s">
         <v>343</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C173" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D173" s="2"/>
+      <c r="D173" s="1"/>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="2">
+      <c r="A174" s="1">
         <v>173</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" t="s">
         <v>345</v>
       </c>
-      <c r="C174" s="4" t="s">
+      <c r="C174" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D174" s="2"/>
+      <c r="D174" s="1"/>
     </row>
     <row r="175" spans="1:4">
-      <c r="A175" s="2">
+      <c r="A175" s="1">
         <v>174</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" t="s">
         <v>347</v>
       </c>
-      <c r="C175" s="4" t="s">
+      <c r="C175" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D175" s="2"/>
+      <c r="D175" s="1"/>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="2">
+      <c r="A176" s="1">
         <v>175</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" t="s">
         <v>349</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D176" s="2"/>
+      <c r="D176" s="1"/>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="2">
+      <c r="A177" s="1">
         <v>176</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" t="s">
         <v>351</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C177" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D177" s="2"/>
+      <c r="D177" s="1"/>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="2">
+      <c r="A178" s="1">
         <v>177</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" t="s">
         <v>353</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D178" s="2"/>
+      <c r="D178" s="1"/>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="2">
+      <c r="A179" s="1">
         <v>178</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" t="s">
         <v>355</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D179" s="2"/>
+      <c r="D179" s="1"/>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="2">
+      <c r="A180" s="1">
         <v>179</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" t="s">
         <v>357</v>
       </c>
-      <c r="C180" s="4" t="s">
+      <c r="C180" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D180" s="2"/>
+      <c r="D180" s="1"/>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="2">
+      <c r="A181" s="1">
         <v>180</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" t="s">
         <v>359</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D181" s="2"/>
+      <c r="D181" s="1"/>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="2">
+      <c r="A182" s="1">
         <v>181</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" t="s">
         <v>361</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D182" s="2"/>
+      <c r="D182" s="1"/>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="2">
+      <c r="A183" s="1">
         <v>182</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" t="s">
         <v>363</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C183" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D183" s="2"/>
+      <c r="D183" s="1"/>
     </row>
     <row r="184" spans="1:4">
-      <c r="A184" s="2">
+      <c r="A184" s="1">
         <v>183</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" t="s">
         <v>365</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C184" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D184" s="2"/>
+      <c r="D184" s="1"/>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="2">
+      <c r="A185" s="1">
         <v>184</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" t="s">
         <v>367</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C185" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D185" s="2"/>
+      <c r="D185" s="1"/>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="2">
+      <c r="A186" s="1">
         <v>185</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" t="s">
         <v>369</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C186" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D186" s="2"/>
+      <c r="D186" s="1"/>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="2">
+      <c r="A187" s="1">
         <v>186</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" t="s">
         <v>371</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C187" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D187" s="2"/>
+      <c r="D187" s="1"/>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="2">
+      <c r="A188" s="1">
         <v>187</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" t="s">
         <v>373</v>
       </c>
-      <c r="C188" s="4" t="s">
+      <c r="C188" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D188" s="2"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="2">
+      <c r="A189" s="1">
         <v>188</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" t="s">
         <v>375</v>
       </c>
-      <c r="C189" s="4" t="s">
+      <c r="C189" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D189" s="2"/>
+      <c r="D189" s="1"/>
     </row>
     <row r="190" spans="1:4">
-      <c r="A190" s="2">
+      <c r="A190" s="1">
         <v>189</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" t="s">
         <v>377</v>
       </c>
-      <c r="C190" s="4" t="s">
+      <c r="C190" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D190" s="2"/>
+      <c r="D190" s="1"/>
     </row>
     <row r="191" spans="1:4">
-      <c r="A191" s="2">
+      <c r="A191" s="1">
         <v>190</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D191" s="2"/>
+      <c r="D191" s="1"/>
     </row>
     <row r="192" spans="1:4">
-      <c r="A192" s="2">
+      <c r="A192" s="1">
         <v>191</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" t="s">
         <v>381</v>
       </c>
-      <c r="C192" s="4" t="s">
+      <c r="C192" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D192" s="2"/>
+      <c r="D192" s="1"/>
     </row>
     <row r="193" spans="1:4">
-      <c r="A193" s="2">
+      <c r="A193" s="1">
         <v>192</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" t="s">
         <v>383</v>
       </c>
-      <c r="C193" s="4" t="s">
+      <c r="C193" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D193" s="2"/>
+      <c r="D193" s="1"/>
     </row>
     <row r="194" spans="1:4">
-      <c r="A194" s="2">
+      <c r="A194" s="1">
         <v>193</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" t="s">
         <v>385</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C194" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D194" s="2"/>
+      <c r="D194" s="1"/>
     </row>
     <row r="195" spans="1:4">
-      <c r="A195" s="2">
+      <c r="A195" s="1">
         <v>194</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" t="s">
         <v>387</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C195" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D195" s="2"/>
+      <c r="D195" s="1"/>
     </row>
     <row r="196" spans="1:4">
-      <c r="A196" s="2">
+      <c r="A196" s="1">
         <v>195</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" t="s">
         <v>389</v>
       </c>
-      <c r="C196" s="4" t="s">
+      <c r="C196" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D196" s="2"/>
+      <c r="D196" s="1"/>
     </row>
     <row r="197" spans="1:4">
-      <c r="A197" s="2">
+      <c r="A197" s="1">
         <v>196</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B197" t="s">
         <v>391</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D197" s="2"/>
+      <c r="D197" s="1"/>
     </row>
     <row r="198" spans="1:4">
-      <c r="A198" s="2">
+      <c r="A198" s="1">
         <v>197</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B198" t="s">
         <v>393</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C198" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D198" s="2"/>
+      <c r="D198" s="1"/>
     </row>
     <row r="199" spans="1:4">
-      <c r="A199" s="2">
+      <c r="A199" s="1">
         <v>198</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" t="s">
         <v>395</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C199" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D199" s="2"/>
+      <c r="D199" s="1"/>
     </row>
     <row r="200" spans="1:4">
-      <c r="A200" s="2">
+      <c r="A200" s="1">
         <v>199</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B200" t="s">
         <v>397</v>
       </c>
-      <c r="C200" s="4" t="s">
+      <c r="C200" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D200" s="2"/>
+      <c r="D200" s="1"/>
     </row>
     <row r="201" spans="1:4">
-      <c r="A201" s="2">
+      <c r="A201" s="1">
         <v>200</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B201" t="s">
         <v>399</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C201" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D201" s="2"/>
+      <c r="D201" s="1"/>
     </row>
     <row r="202" spans="1:4">
-      <c r="A202" s="2">
+      <c r="A202" s="1">
         <v>201</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" t="s">
         <v>401</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="C202" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D202" s="2"/>
+      <c r="D202" s="1"/>
     </row>
     <row r="203" spans="1:4">
-      <c r="A203" s="2">
+      <c r="A203" s="1">
         <v>202</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" t="s">
         <v>403</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D203" s="2"/>
+      <c r="D203" s="1"/>
     </row>
     <row r="204" spans="1:4">
-      <c r="A204" s="2">
+      <c r="A204" s="1">
         <v>203</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" t="s">
         <v>405</v>
       </c>
-      <c r="C204" s="4" t="s">
+      <c r="C204" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D204" s="2"/>
+      <c r="D204" s="1"/>
     </row>
     <row r="205" spans="1:4">
-      <c r="A205" s="2">
+      <c r="A205" s="1">
         <v>204</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" t="s">
         <v>407</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C205" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D205" s="2"/>
+      <c r="D205" s="1"/>
     </row>
     <row r="206" spans="1:4">
-      <c r="A206" s="2">
+      <c r="A206" s="1">
         <v>205</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" t="s">
         <v>409</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D206" s="2"/>
+      <c r="D206" s="1"/>
     </row>
     <row r="207" spans="1:4">
-      <c r="A207" s="2">
+      <c r="A207" s="1">
         <v>206</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" t="s">
         <v>411</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C207" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D207" s="2"/>
+      <c r="D207" s="1"/>
     </row>
     <row r="208" spans="1:4">
-      <c r="A208" s="2">
+      <c r="A208" s="1">
         <v>207</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" t="s">
         <v>413</v>
       </c>
-      <c r="C208" s="4" t="s">
+      <c r="C208" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D208" s="2"/>
+      <c r="D208" s="1"/>
     </row>
     <row r="209" spans="1:4">
-      <c r="A209" s="2">
+      <c r="A209" s="1">
         <v>208</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" t="s">
         <v>415</v>
       </c>
-      <c r="C209" s="4" t="s">
+      <c r="C209" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D209" s="2"/>
+      <c r="D209" s="1"/>
     </row>
     <row r="210" spans="1:4">
-      <c r="A210" s="2">
+      <c r="A210" s="1">
         <v>209</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B210" t="s">
         <v>417</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D210" s="2"/>
+      <c r="D210" s="1"/>
     </row>
     <row r="211" spans="1:4">
-      <c r="A211" s="2">
+      <c r="A211" s="1">
         <v>210</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" t="s">
         <v>419</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D211" s="2"/>
+      <c r="D211" s="1"/>
     </row>
     <row r="212" spans="1:4">
-      <c r="A212" s="2">
+      <c r="A212" s="1">
         <v>211</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" t="s">
         <v>421</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D212" s="2"/>
+      <c r="D212" s="1"/>
     </row>
     <row r="213" spans="1:4">
-      <c r="A213" s="2">
+      <c r="A213" s="1">
         <v>212</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" t="s">
         <v>423</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C213" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D213" s="2"/>
+      <c r="D213" s="1"/>
     </row>
     <row r="214" spans="1:4">
-      <c r="A214" s="2">
+      <c r="A214" s="1">
         <v>213</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B214" t="s">
         <v>425</v>
       </c>
-      <c r="C214" s="4" t="s">
+      <c r="C214" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D214" s="2"/>
+      <c r="D214" s="1"/>
     </row>
     <row r="215" spans="1:4">
-      <c r="A215" s="2">
+      <c r="A215" s="1">
         <v>214</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B215" t="s">
         <v>427</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D215" s="2"/>
+      <c r="D215" s="1"/>
     </row>
     <row r="216" spans="1:4">
-      <c r="A216" s="2">
+      <c r="A216" s="1">
         <v>215</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" t="s">
         <v>429</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C216" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D216" s="2"/>
+      <c r="D216" s="1"/>
     </row>
     <row r="217" spans="1:4">
-      <c r="A217" s="2">
+      <c r="A217" s="1">
         <v>216</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" t="s">
         <v>431</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="C217" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D217" s="2"/>
+      <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4">
-      <c r="A218" s="2">
+      <c r="A218" s="1">
         <v>217</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" t="s">
         <v>433</v>
       </c>
-      <c r="C218" s="4" t="s">
+      <c r="C218" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D218" s="2"/>
+      <c r="D218" s="1"/>
     </row>
     <row r="219" spans="1:4">
-      <c r="A219" s="2">
+      <c r="A219" s="1">
         <v>218</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B219" t="s">
         <v>435</v>
       </c>
-      <c r="C219" s="4" t="s">
+      <c r="C219" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D219" s="2"/>
+      <c r="D219" s="1"/>
     </row>
     <row r="220" spans="1:4">
-      <c r="A220" s="2">
+      <c r="A220" s="1">
         <v>219</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" t="s">
         <v>437</v>
       </c>
-      <c r="C220" s="4" t="s">
+      <c r="C220" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D220" s="2"/>
+      <c r="D220" s="1"/>
     </row>
     <row r="221" spans="1:4">
-      <c r="A221" s="2">
+      <c r="A221" s="1">
         <v>220</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" t="s">
         <v>439</v>
       </c>
-      <c r="C221" s="4" t="s">
+      <c r="C221" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="D221" s="2"/>
+      <c r="D221" s="1"/>
     </row>
     <row r="222" spans="1:4">
-      <c r="A222" s="2">
+      <c r="A222" s="1">
         <v>221</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B222" t="s">
         <v>441</v>
       </c>
-      <c r="C222" s="4" t="s">
+      <c r="C222" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D222" s="2"/>
+      <c r="D222" s="1"/>
     </row>
     <row r="223" spans="1:4">
-      <c r="A223" s="2">
+      <c r="A223" s="1">
         <v>222</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" t="s">
         <v>443</v>
       </c>
-      <c r="C223" s="4" t="s">
+      <c r="C223" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D223" s="2"/>
+      <c r="D223" s="1"/>
     </row>
     <row r="224" spans="1:4">
-      <c r="A224" s="2">
+      <c r="A224" s="1">
         <v>223</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" t="s">
         <v>445</v>
       </c>
-      <c r="C224" s="4" t="s">
+      <c r="C224" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D224" s="2"/>
+      <c r="D224" s="1"/>
     </row>
     <row r="225" spans="1:4">
-      <c r="A225" s="2">
+      <c r="A225" s="1">
         <v>224</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" t="s">
         <v>447</v>
       </c>
-      <c r="C225" s="4" t="s">
+      <c r="C225" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D225" s="2"/>
+      <c r="D225" s="1"/>
     </row>
     <row r="226" spans="1:4">
-      <c r="A226" s="2">
+      <c r="A226" s="1">
         <v>225</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" t="s">
         <v>449</v>
       </c>
-      <c r="C226" s="4" t="s">
+      <c r="C226" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D226" s="2"/>
+      <c r="D226" s="1"/>
     </row>
     <row r="227" spans="1:4">
-      <c r="A227" s="2">
+      <c r="A227" s="1">
         <v>226</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" t="s">
         <v>451</v>
       </c>
-      <c r="C227" s="4" t="s">
+      <c r="C227" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="D227" s="2"/>
+      <c r="D227" s="1"/>
     </row>
     <row r="228" spans="1:4">
-      <c r="A228" s="2">
+      <c r="A228" s="1">
         <v>227</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" t="s">
         <v>453</v>
       </c>
-      <c r="C228" s="4" t="s">
+      <c r="C228" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D228" s="2"/>
+      <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4">
-      <c r="A229" s="2">
+      <c r="A229" s="1">
         <v>228</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" t="s">
         <v>455</v>
       </c>
-      <c r="C229" s="4" t="s">
+      <c r="C229" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D229" s="2"/>
+      <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4">
-      <c r="A230" s="2">
+      <c r="A230" s="1">
         <v>229</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" t="s">
         <v>457</v>
       </c>
-      <c r="C230" s="4" t="s">
+      <c r="C230" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D230" s="2"/>
+      <c r="D230" s="1"/>
     </row>
     <row r="231" spans="1:4">
-      <c r="A231" s="2">
+      <c r="A231" s="1">
         <v>230</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" t="s">
         <v>459</v>
       </c>
-      <c r="C231" s="4" t="s">
+      <c r="C231" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D231" s="2"/>
+      <c r="D231" s="1"/>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="2">
+      <c r="A232" s="1">
         <v>231</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" t="s">
         <v>461</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="C232" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D232" s="2"/>
+      <c r="D232" s="1"/>
     </row>
     <row r="233" spans="1:4">
-      <c r="A233" s="2">
+      <c r="A233" s="1">
         <v>232</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B233" t="s">
         <v>463</v>
       </c>
-      <c r="C233" s="4" t="s">
+      <c r="C233" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D233" s="2"/>
+      <c r="D233" s="1"/>
     </row>
     <row r="234" spans="1:4">
-      <c r="A234" s="2">
+      <c r="A234" s="1">
         <v>233</v>
       </c>
-      <c r="B234" s="3" t="s">
+      <c r="B234" t="s">
         <v>465</v>
       </c>
-      <c r="C234" s="4" t="s">
+      <c r="C234" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D234" s="2"/>
+      <c r="D234" s="1"/>
     </row>
     <row r="235" spans="1:4">
-      <c r="A235" s="2">
+      <c r="A235" s="1">
         <v>234</v>
       </c>
-      <c r="B235" s="3" t="s">
+      <c r="B235" t="s">
         <v>467</v>
       </c>
-      <c r="C235" s="4" t="s">
+      <c r="C235" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D235" s="2"/>
+      <c r="D235" s="1"/>
     </row>
     <row r="236" spans="1:4">
-      <c r="A236" s="2">
+      <c r="A236" s="1">
         <v>235</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B236" t="s">
         <v>469</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="C236" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D236" s="2"/>
+      <c r="D236" s="1"/>
     </row>
     <row r="237" spans="1:4">
-      <c r="A237" s="2">
+      <c r="A237" s="1">
         <v>236</v>
       </c>
-      <c r="B237" s="3" t="s">
+      <c r="B237" t="s">
         <v>471</v>
       </c>
-      <c r="C237" s="4" t="s">
+      <c r="C237" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D237" s="2"/>
+      <c r="D237" s="1"/>
     </row>
     <row r="238" spans="1:4">
-      <c r="A238" s="2">
+      <c r="A238" s="1">
         <v>237</v>
       </c>
-      <c r="B238" s="3" t="s">
+      <c r="B238" t="s">
         <v>473</v>
       </c>
-      <c r="C238" s="4" t="s">
+      <c r="C238" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D238" s="2"/>
+      <c r="D238" s="1"/>
     </row>
     <row r="239" spans="1:4">
-      <c r="A239" s="2">
+      <c r="A239" s="1">
         <v>238</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="B239" t="s">
         <v>475</v>
       </c>
-      <c r="C239" s="4" t="s">
+      <c r="C239" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="D239" s="2"/>
+      <c r="D239" s="1"/>
     </row>
     <row r="240" spans="1:4">
-      <c r="A240" s="2">
+      <c r="A240" s="1">
         <v>239</v>
       </c>
-      <c r="B240" s="3" t="s">
+      <c r="B240" t="s">
         <v>477</v>
       </c>
-      <c r="C240" s="4" t="s">
+      <c r="C240" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D240" s="2"/>
+      <c r="D240" s="1"/>
     </row>
     <row r="241" spans="1:4">
-      <c r="A241" s="2">
+      <c r="A241" s="1">
         <v>240</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B241" t="s">
         <v>479</v>
       </c>
-      <c r="C241" s="4" t="s">
+      <c r="C241" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D241" s="2"/>
+      <c r="D241" s="1"/>
     </row>
     <row r="242" spans="1:4">
-      <c r="A242" s="2">
+      <c r="A242" s="1">
         <v>241</v>
       </c>
-      <c r="B242" s="3" t="s">
+      <c r="B242" t="s">
         <v>481</v>
       </c>
-      <c r="C242" s="4" t="s">
+      <c r="C242" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D242" s="2"/>
+      <c r="D242" s="1"/>
     </row>
     <row r="243" spans="1:4">
-      <c r="A243" s="2">
+      <c r="A243" s="1">
         <v>242</v>
       </c>
-      <c r="B243" s="3" t="s">
+      <c r="B243" t="s">
         <v>483</v>
       </c>
-      <c r="C243" s="4" t="s">
+      <c r="C243" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D243" s="2"/>
+      <c r="D243" s="1"/>
     </row>
     <row r="244" spans="1:4">
-      <c r="A244" s="2">
+      <c r="A244" s="1">
         <v>243</v>
       </c>
-      <c r="B244" s="3" t="s">
+      <c r="B244" t="s">
         <v>485</v>
       </c>
-      <c r="C244" s="4" t="s">
+      <c r="C244" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D244" s="2"/>
+      <c r="D244" s="1"/>
     </row>
     <row r="245" spans="1:4">
-      <c r="A245" s="2">
+      <c r="A245" s="1">
         <v>244</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B245" t="s">
         <v>487</v>
       </c>
-      <c r="C245" s="4" t="s">
+      <c r="C245" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D245" s="2"/>
+      <c r="D245" s="1"/>
     </row>
     <row r="246" spans="1:4">
-      <c r="A246" s="2">
+      <c r="A246" s="1">
         <v>245</v>
       </c>
-      <c r="B246" s="3" t="s">
+      <c r="B246" t="s">
         <v>489</v>
       </c>
-      <c r="C246" s="4" t="s">
+      <c r="C246" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D246" s="2"/>
+      <c r="D246" s="1"/>
     </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="2">
+      <c r="A247" s="1">
         <v>246</v>
       </c>
-      <c r="B247" s="3" t="s">
+      <c r="B247" t="s">
         <v>491</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C247" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D247" s="2"/>
+      <c r="D247" s="1"/>
     </row>
     <row r="248" spans="1:4">
-      <c r="A248" s="2">
+      <c r="A248" s="1">
         <v>247</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B248" t="s">
         <v>493</v>
       </c>
-      <c r="C248" s="4" t="s">
+      <c r="C248" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D248" s="2"/>
+      <c r="D248" s="1"/>
     </row>
     <row r="249" spans="1:4">
-      <c r="A249" s="2">
+      <c r="A249" s="1">
         <v>248</v>
       </c>
-      <c r="B249" s="3" t="s">
+      <c r="B249" t="s">
         <v>495</v>
       </c>
-      <c r="C249" s="4" t="s">
+      <c r="C249" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D249" s="2"/>
+      <c r="D249" s="1"/>
     </row>
     <row r="250" spans="1:4">
-      <c r="A250" s="2">
+      <c r="A250" s="1">
         <v>249</v>
       </c>
-      <c r="B250" s="3" t="s">
+      <c r="B250" t="s">
         <v>497</v>
       </c>
-      <c r="C250" s="4" t="s">
+      <c r="C250" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D250" s="2"/>
+      <c r="D250" s="1"/>
     </row>
     <row r="251" spans="1:4">
-      <c r="A251" s="2">
+      <c r="A251" s="1">
         <v>250</v>
       </c>
-      <c r="B251" s="3" t="s">
+      <c r="B251" t="s">
         <v>499</v>
       </c>
-      <c r="C251" s="4" t="s">
+      <c r="C251" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D251" s="2"/>
+      <c r="D251" s="1"/>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="2">
+      <c r="A252" s="1">
         <v>251</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="B252" t="s">
         <v>501</v>
       </c>
-      <c r="C252" s="4" t="s">
+      <c r="C252" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D252" s="2"/>
+      <c r="D252" s="1"/>
     </row>
     <row r="253" spans="1:4">
-      <c r="A253" s="2">
+      <c r="A253" s="1">
         <v>252</v>
       </c>
-      <c r="B253" s="1" t="s">
+      <c r="B253" t="s">
         <v>503</v>
       </c>
-      <c r="C253" s="4" t="s">
+      <c r="C253" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D253" s="2"/>
+      <c r="D253" s="1"/>
     </row>
     <row r="254" spans="1:4">
-      <c r="A254" s="2">
+      <c r="A254" s="1">
         <v>253</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="B254" t="s">
         <v>505</v>
       </c>
-      <c r="C254" s="4" t="s">
+      <c r="C254" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D254" s="2"/>
+      <c r="D254" s="1"/>
     </row>
     <row r="255" spans="1:4">
-      <c r="A255" s="2">
+      <c r="A255" s="1">
         <v>254</v>
       </c>
-      <c r="B255" s="1" t="s">
+      <c r="B255" t="s">
         <v>507</v>
       </c>
-      <c r="C255" s="4" t="s">
+      <c r="C255" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="D255" s="2"/>
+      <c r="D255" s="1"/>
     </row>
     <row r="256" spans="1:4">
-      <c r="A256" s="2">
+      <c r="A256" s="1">
         <v>255</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="B256" t="s">
         <v>509</v>
       </c>
-      <c r="C256" s="4" t="s">
+      <c r="C256" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D256" s="2"/>
+      <c r="D256" s="1"/>
     </row>
     <row r="257" spans="1:4">
-      <c r="A257" s="2">
+      <c r="A257" s="1">
         <v>256</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="B257" t="s">
         <v>511</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C257" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D257" s="2"/>
+      <c r="D257" s="1"/>
     </row>
     <row r="258" spans="1:4">
-      <c r="A258" s="2">
+      <c r="A258" s="1">
         <v>257</v>
       </c>
-      <c r="B258" s="1" t="s">
+      <c r="B258" t="s">
         <v>513</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="C258" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="D258" s="2"/>
+      <c r="D258" s="1"/>
     </row>
     <row r="259" spans="1:4">
-      <c r="A259" s="2">
+      <c r="A259" s="1">
         <v>258</v>
       </c>
-      <c r="B259" s="1" t="s">
+      <c r="B259" t="s">
         <v>515</v>
       </c>
-      <c r="C259" s="4" t="s">
+      <c r="C259" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D259" s="2"/>
+      <c r="D259" s="1"/>
     </row>
     <row r="260" spans="1:4">
-      <c r="A260" s="2">
+      <c r="A260" s="1">
         <v>259</v>
       </c>
-      <c r="B260" s="1" t="s">
+      <c r="B260" t="s">
         <v>517</v>
       </c>
-      <c r="C260" s="4" t="s">
+      <c r="C260" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D260" s="2"/>
+      <c r="D260" s="1"/>
     </row>
     <row r="261" spans="1:4">
-      <c r="A261" s="2">
+      <c r="A261" s="1">
         <v>260</v>
       </c>
-      <c r="B261" s="1" t="s">
+      <c r="B261" t="s">
         <v>519</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="C261" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="D261" s="2"/>
+      <c r="D261" s="1"/>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="2">
+      <c r="A262" s="1">
         <v>261</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="B262" t="s">
         <v>521</v>
       </c>
-      <c r="C262" s="4" t="s">
+      <c r="C262" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D262" s="2"/>
+      <c r="D262" s="1"/>
     </row>
     <row r="263" spans="1:4">
-      <c r="A263" s="2">
+      <c r="A263" s="1">
         <v>262</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="B263" t="s">
         <v>523</v>
       </c>
-      <c r="C263" s="4" t="s">
+      <c r="C263" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D263" s="2"/>
+      <c r="D263" s="1"/>
     </row>
     <row r="264" spans="1:4">
-      <c r="A264" s="2">
+      <c r="A264" s="1">
         <v>263</v>
       </c>
-      <c r="B264" s="1" t="s">
+      <c r="B264" t="s">
         <v>525</v>
       </c>
-      <c r="C264" s="4" t="s">
+      <c r="C264" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="D264" s="2"/>
+      <c r="D264" s="1"/>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="2">
+      <c r="A265" s="1">
         <v>264</v>
       </c>
-      <c r="B265" s="1" t="s">
+      <c r="B265" t="s">
         <v>527</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="C265" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="D265" s="2"/>
+      <c r="D265" s="1"/>
     </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="2">
+      <c r="A266" s="1">
         <v>265</v>
       </c>
-      <c r="B266" s="1" t="s">
+      <c r="B266" t="s">
         <v>529</v>
       </c>
-      <c r="C266" s="4" t="s">
+      <c r="C266" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D266" s="2"/>
+      <c r="D266" s="1"/>
     </row>
     <row r="267" spans="1:4">
-      <c r="A267" s="2">
+      <c r="A267" s="1">
         <v>266</v>
       </c>
-      <c r="B267" s="1" t="s">
+      <c r="B267" t="s">
         <v>531</v>
       </c>
-      <c r="C267" s="4" t="s">
+      <c r="C267" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D267" s="2"/>
+      <c r="D267" s="1"/>
     </row>
     <row r="268" spans="1:4">
-      <c r="A268" s="2">
+      <c r="A268" s="1">
         <v>267</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="B268" t="s">
         <v>533</v>
       </c>
-      <c r="C268" s="4" t="s">
+      <c r="C268" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D268" s="2"/>
+      <c r="D268" s="1"/>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="2">
+      <c r="A269" s="1">
         <v>268</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="B269" t="s">
         <v>535</v>
       </c>
-      <c r="C269" s="4" t="s">
+      <c r="C269" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D269" s="2"/>
+      <c r="D269" s="1"/>
     </row>
     <row r="270" spans="1:4">
-      <c r="A270" s="2">
+      <c r="A270" s="1">
         <v>269</v>
       </c>
-      <c r="B270" s="1" t="s">
+      <c r="B270" t="s">
         <v>537</v>
       </c>
-      <c r="C270" s="4" t="s">
+      <c r="C270" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D270" s="2"/>
+      <c r="D270" s="1"/>
     </row>
     <row r="271" spans="1:4">
-      <c r="A271" s="2">
+      <c r="A271" s="1">
         <v>270</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="B271" t="s">
         <v>539</v>
       </c>
-      <c r="C271" s="4" t="s">
+      <c r="C271" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D271" s="2"/>
+      <c r="D271" s="1"/>
     </row>
     <row r="272" spans="1:4">
-      <c r="A272" s="2">
+      <c r="A272" s="1">
         <v>271</v>
       </c>
-      <c r="B272" s="1" t="s">
+      <c r="B272" t="s">
         <v>541</v>
       </c>
-      <c r="C272" s="4" t="s">
+      <c r="C272" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D272" s="2"/>
+      <c r="D272" s="1"/>
     </row>
     <row r="273" spans="1:4">
-      <c r="A273" s="2">
+      <c r="A273" s="1">
         <v>272</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="B273" t="s">
         <v>543</v>
       </c>
-      <c r="C273" s="4" t="s">
+      <c r="C273" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="D273" s="2"/>
+      <c r="D273" s="1"/>
     </row>
     <row r="274" spans="1:4">
-      <c r="A274" s="2">
+      <c r="A274" s="1">
         <v>273</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="B274" t="s">
         <v>545</v>
       </c>
-      <c r="C274" s="4" t="s">
+      <c r="C274" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D274" s="2"/>
+      <c r="D274" s="1"/>
     </row>
     <row r="275" spans="1:4">
-      <c r="A275" s="2">
+      <c r="A275" s="1">
         <v>274</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="B275" t="s">
         <v>547</v>
       </c>
-      <c r="C275" s="4" t="s">
+      <c r="C275" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D275" s="2"/>
+      <c r="D275" s="1"/>
     </row>
     <row r="276" spans="1:4">
-      <c r="A276" s="2">
+      <c r="A276" s="1">
         <v>275</v>
       </c>
-      <c r="B276" s="1" t="s">
+      <c r="B276" t="s">
         <v>549</v>
       </c>
-      <c r="C276" s="4" t="s">
+      <c r="C276" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D276" s="2"/>
+      <c r="D276" s="1"/>
     </row>
     <row r="277" spans="1:4">
-      <c r="A277" s="2">
+      <c r="A277" s="1">
         <v>276</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="B277" t="s">
         <v>551</v>
       </c>
-      <c r="C277" s="4" t="s">
+      <c r="C277" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D277" s="2"/>
+      <c r="D277" s="1"/>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" s="2">
+      <c r="A278" s="1">
         <v>277</v>
       </c>
-      <c r="B278" s="1" t="s">
+      <c r="B278" t="s">
         <v>553</v>
       </c>
-      <c r="C278" s="4" t="s">
+      <c r="C278" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D278" s="2"/>
+      <c r="D278" s="1"/>
     </row>
     <row r="279" spans="1:4">
-      <c r="A279" s="2">
+      <c r="A279" s="1">
         <v>278</v>
       </c>
-      <c r="B279" s="1" t="s">
+      <c r="B279" t="s">
         <v>555</v>
       </c>
-      <c r="C279" s="4" t="s">
+      <c r="C279" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="D279" s="2"/>
+      <c r="D279" s="1"/>
     </row>
     <row r="280" spans="1:4">
-      <c r="A280" s="2">
+      <c r="A280" s="1">
         <v>279</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="B280" t="s">
         <v>557</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="C280" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D280" s="2"/>
+      <c r="D280" s="1"/>
     </row>
     <row r="281" spans="1:4">
-      <c r="A281" s="2">
+      <c r="A281" s="1">
         <v>280</v>
       </c>
-      <c r="B281" s="1" t="s">
+      <c r="B281" t="s">
         <v>559</v>
       </c>
-      <c r="C281" s="4" t="s">
+      <c r="C281" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D281" s="2"/>
+      <c r="D281" s="1"/>
     </row>
     <row r="282" spans="1:4">
-      <c r="A282" s="2">
+      <c r="A282" s="1">
         <v>281</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="B282" t="s">
         <v>561</v>
       </c>
-      <c r="C282" s="4" t="s">
+      <c r="C282" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="D282" s="2"/>
+      <c r="D282" s="1"/>
     </row>
     <row r="283" spans="1:4">
-      <c r="A283" s="2">
+      <c r="A283" s="1">
         <v>282</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="B283" t="s">
         <v>563</v>
       </c>
-      <c r="C283" s="4" t="s">
+      <c r="C283" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="D283" s="2"/>
+      <c r="D283" s="1"/>
     </row>
     <row r="284" spans="1:4">
-      <c r="A284" s="2">
+      <c r="A284" s="1">
         <v>283</v>
       </c>
-      <c r="B284" s="1" t="s">
+      <c r="B284" t="s">
         <v>565</v>
       </c>
-      <c r="C284" s="4" t="s">
+      <c r="C284" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D284" s="2"/>
+      <c r="D284" s="1"/>
     </row>
     <row r="285" spans="1:4">
-      <c r="A285" s="2">
+      <c r="A285" s="1">
         <v>284</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="B285" t="s">
         <v>567</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="C285" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="D285" s="2"/>
+      <c r="D285" s="1"/>
     </row>
     <row r="286" spans="1:4">
-      <c r="A286" s="2">
+      <c r="A286" s="1">
         <v>285</v>
       </c>
-      <c r="B286" s="1" t="s">
+      <c r="B286" t="s">
         <v>569</v>
       </c>
-      <c r="C286" s="4" t="s">
+      <c r="C286" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D286" s="2"/>
+      <c r="D286" s="1"/>
     </row>
     <row r="287" spans="1:4">
-      <c r="A287" s="2">
+      <c r="A287" s="1">
         <v>286</v>
       </c>
-      <c r="B287" s="1" t="s">
+      <c r="B287" t="s">
         <v>571</v>
       </c>
-      <c r="C287" s="4" t="s">
+      <c r="C287" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="D287" s="2"/>
+      <c r="D287" s="1"/>
     </row>
     <row r="288" spans="1:4">
-      <c r="A288" s="2">
+      <c r="A288" s="1">
         <v>287</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="B288" t="s">
         <v>573</v>
       </c>
-      <c r="C288" s="4" t="s">
+      <c r="C288" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="D288" s="2"/>
+      <c r="D288" s="1"/>
     </row>
     <row r="289" spans="1:4">
-      <c r="A289" s="2">
+      <c r="A289" s="1">
         <v>288</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="B289" t="s">
         <v>575</v>
       </c>
-      <c r="C289" s="4" t="s">
+      <c r="C289" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="D289" s="2"/>
+      <c r="D289" s="1"/>
     </row>
     <row r="290" spans="1:4">
-      <c r="A290" s="2">
+      <c r="A290" s="1">
         <v>289</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="B290" t="s">
         <v>577</v>
       </c>
-      <c r="C290" s="4" t="s">
+      <c r="C290" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="D290" s="2"/>
+      <c r="D290" s="1"/>
     </row>
     <row r="291" spans="1:4">
-      <c r="A291" s="2">
+      <c r="A291" s="1">
         <v>290</v>
       </c>
-      <c r="B291" s="1" t="s">
+      <c r="B291" t="s">
         <v>579</v>
       </c>
-      <c r="C291" s="4" t="s">
+      <c r="C291" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="D291" s="2"/>
+      <c r="D291" s="1"/>
     </row>
     <row r="292" spans="1:4">
-      <c r="A292" s="2">
+      <c r="A292" s="1">
         <v>291</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="B292" t="s">
         <v>581</v>
       </c>
-      <c r="C292" s="4" t="s">
+      <c r="C292" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="D292" s="2"/>
+      <c r="D292" s="1"/>
     </row>
     <row r="293" spans="1:4">
-      <c r="A293" s="2">
+      <c r="A293" s="1">
         <v>292</v>
       </c>
-      <c r="B293" s="1" t="s">
+      <c r="B293" t="s">
         <v>583</v>
       </c>
-      <c r="C293" s="4" t="s">
+      <c r="C293" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="D293" s="2"/>
+      <c r="D293" s="1"/>
     </row>
     <row r="294" spans="1:4">
-      <c r="A294" s="2">
+      <c r="A294" s="1">
         <v>293</v>
       </c>
-      <c r="B294" s="1" t="s">
+      <c r="B294" t="s">
         <v>585</v>
       </c>
-      <c r="C294" s="4" t="s">
+      <c r="C294" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="D294" s="2"/>
+      <c r="D294" s="1"/>
     </row>
     <row r="295" spans="1:4">
-      <c r="A295" s="2">
+      <c r="A295" s="1">
         <v>294</v>
       </c>
-      <c r="B295" s="1" t="s">
+      <c r="B295" t="s">
         <v>587</v>
       </c>
-      <c r="C295" s="4" t="s">
+      <c r="C295" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="D295" s="2"/>
+      <c r="D295" s="1"/>
     </row>
     <row r="296" spans="1:4">
-      <c r="A296" s="2">
+      <c r="A296" s="1">
         <v>295</v>
       </c>
-      <c r="B296" s="1" t="s">
+      <c r="B296" t="s">
         <v>589</v>
       </c>
-      <c r="C296" s="4" t="s">
+      <c r="C296" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="D296" s="2"/>
+      <c r="D296" s="1"/>
     </row>
     <row r="297" spans="1:4">
-      <c r="A297" s="2">
+      <c r="A297" s="1">
         <v>296</v>
       </c>
-      <c r="B297" s="1" t="s">
+      <c r="B297" t="s">
         <v>591</v>
       </c>
-      <c r="C297" s="4" t="s">
+      <c r="C297" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="D297" s="2"/>
+      <c r="D297" s="1"/>
     </row>
     <row r="298" spans="1:4">
-      <c r="A298" s="2">
+      <c r="A298" s="1">
         <v>297</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="B298" t="s">
         <v>593</v>
       </c>
-      <c r="C298" s="4" t="s">
+      <c r="C298" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="D298" s="2"/>
+      <c r="D298" s="1"/>
     </row>
     <row r="299" spans="1:4">
-      <c r="A299" s="2">
+      <c r="A299" s="1">
         <v>298</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="B299" t="s">
         <v>595</v>
       </c>
-      <c r="C299" s="4" t="s">
+      <c r="C299" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="D299" s="2"/>
+      <c r="D299" s="1"/>
     </row>
     <row r="300" spans="1:4">
-      <c r="A300" s="2">
+      <c r="A300" s="1">
         <v>299</v>
       </c>
-      <c r="B300" s="1" t="s">
+      <c r="B300" t="s">
         <v>597</v>
       </c>
-      <c r="C300" s="4" t="s">
+      <c r="C300" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="D300" s="2"/>
+      <c r="D300" s="1"/>
     </row>
     <row r="301" spans="1:4">
-      <c r="A301" s="2">
+      <c r="A301" s="1">
         <v>300</v>
       </c>
-      <c r="B301" s="1" t="s">
+      <c r="B301" t="s">
         <v>599</v>
       </c>
-      <c r="C301" s="4" t="s">
+      <c r="C301" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="D301" s="2"/>
+      <c r="D301" s="1"/>
     </row>
     <row r="302" spans="1:4">
-      <c r="A302" s="2">
+      <c r="A302" s="1">
         <v>301</v>
       </c>
-      <c r="B302" s="1" t="s">
+      <c r="B302" t="s">
         <v>601</v>
       </c>
-      <c r="C302" s="4" t="s">
+      <c r="C302" s="2" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="303" spans="1:4">
-      <c r="A303" s="2">
+      <c r="A303" s="1">
         <v>302</v>
       </c>
-      <c r="B303" s="1" t="s">
+      <c r="B303" t="s">
         <v>603</v>
       </c>
-      <c r="C303" s="4" t="s">
+      <c r="C303" s="2" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="304" spans="1:4">
-      <c r="A304" s="2">
+      <c r="A304" s="1">
         <v>303</v>
       </c>
-      <c r="B304" s="1" t="s">
+      <c r="B304" t="s">
         <v>605</v>
       </c>
-      <c r="C304" s="4" t="s">
+      <c r="C304" s="2" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="305" spans="1:3">
-      <c r="A305" s="2">
+      <c r="A305" s="1">
         <v>304</v>
       </c>
-      <c r="B305" s="1" t="s">
+      <c r="B305" t="s">
         <v>607</v>
       </c>
-      <c r="C305" s="4" t="s">
+      <c r="C305" s="2" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="306" spans="1:3">
-      <c r="A306" s="2">
+      <c r="A306" s="1">
         <v>305</v>
       </c>
-      <c r="B306" s="1" t="s">
+      <c r="B306" t="s">
         <v>609</v>
       </c>
-      <c r="C306" s="4" t="s">
+      <c r="C306" s="2" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="307" spans="1:3">
-      <c r="A307" s="2">
+      <c r="A307" s="1">
         <v>306</v>
       </c>
-      <c r="B307" s="1" t="s">
+      <c r="B307" t="s">
         <v>611</v>
       </c>
-      <c r="C307" s="4" t="s">
+      <c r="C307" s="2" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="2">
+      <c r="A308" s="1">
         <v>307</v>
       </c>
-      <c r="B308" s="1" t="s">
+      <c r="B308" t="s">
         <v>613</v>
       </c>
-      <c r="C308" s="4" t="s">
+      <c r="C308" s="2" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="2">
+      <c r="A309" s="1">
         <v>308</v>
       </c>
-      <c r="B309" s="1" t="s">
+      <c r="B309" t="s">
         <v>615</v>
       </c>
-      <c r="C309" s="4" t="s">
+      <c r="C309" s="2" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="310" spans="1:3">
-      <c r="A310" s="2">
+      <c r="A310" s="1">
         <v>309</v>
       </c>
-      <c r="B310" s="1" t="s">
+      <c r="B310" t="s">
         <v>617</v>
       </c>
-      <c r="C310" s="4" t="s">
+      <c r="C310" s="2" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="2">
+      <c r="A311" s="1">
         <v>310</v>
       </c>
-      <c r="B311" s="1" t="s">
+      <c r="B311" t="s">
         <v>619</v>
       </c>
-      <c r="C311" s="4" t="s">
+      <c r="C311" s="2" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="2">
+      <c r="A312" s="1">
         <v>311</v>
       </c>
-      <c r="B312" s="1" t="s">
+      <c r="B312" t="s">
         <v>621</v>
       </c>
-      <c r="C312" s="4" t="s">
+      <c r="C312" s="2" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="313" spans="1:3">
-      <c r="A313" s="2">
+      <c r="A313" s="1">
         <v>312</v>
       </c>
-      <c r="B313" s="1" t="s">
+      <c r="B313" t="s">
         <v>623</v>
       </c>
-      <c r="C313" s="4" t="s">
+      <c r="C313" s="2" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="314" spans="1:3">
-      <c r="A314" s="2">
+      <c r="A314" s="1">
         <v>313</v>
       </c>
-      <c r="B314" s="1" t="s">
+      <c r="B314" t="s">
         <v>625</v>
       </c>
-      <c r="C314" s="4" t="s">
+      <c r="C314" s="2" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="315" spans="1:3">
-      <c r="A315" s="2">
+      <c r="A315" s="1">
         <v>314</v>
       </c>
-      <c r="B315" s="1" t="s">
+      <c r="B315" t="s">
         <v>627</v>
       </c>
-      <c r="C315" s="4" t="s">
+      <c r="C315" s="2" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="2">
+      <c r="A316" s="1">
         <v>315</v>
       </c>
-      <c r="B316" s="1" t="s">
+      <c r="B316" t="s">
         <v>629</v>
       </c>
-      <c r="C316" s="4" t="s">
+      <c r="C316" s="2" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="2">
+      <c r="A317" s="1">
         <v>316</v>
       </c>
-      <c r="B317" s="1" t="s">
+      <c r="B317" t="s">
         <v>631</v>
       </c>
-      <c r="C317" s="4" t="s">
+      <c r="C317" s="2" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="318" spans="1:3">
-      <c r="A318" s="2">
+      <c r="A318" s="1">
         <v>317</v>
       </c>
-      <c r="B318" s="1" t="s">
+      <c r="B318" t="s">
         <v>633</v>
       </c>
-      <c r="C318" s="4" t="s">
+      <c r="C318" s="2" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="2">
+      <c r="A319" s="1">
         <v>318</v>
       </c>
-      <c r="B319" s="1" t="s">
+      <c r="B319" t="s">
         <v>635</v>
       </c>
-      <c r="C319" s="4" t="s">
+      <c r="C319" s="2" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="2">
+      <c r="A320" s="1">
         <v>319</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="B320" t="s">
         <v>637</v>
       </c>
-      <c r="C320" s="4" t="s">
+      <c r="C320" s="2" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="321" spans="1:3">
-      <c r="A321" s="2">
+      <c r="A321" s="1">
         <v>320</v>
       </c>
-      <c r="B321" s="1" t="s">
+      <c r="B321" t="s">
         <v>639</v>
       </c>
-      <c r="C321" s="4" t="s">
+      <c r="C321" s="2" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="322" spans="1:3">
-      <c r="A322" s="2">
+      <c r="A322" s="1">
         <v>321</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="B322" t="s">
         <v>641</v>
       </c>
-      <c r="C322" s="4" t="s">
+      <c r="C322" s="2" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="323" spans="1:3">
-      <c r="A323" s="2">
+      <c r="A323" s="1">
         <v>322</v>
       </c>
-      <c r="B323" s="1" t="s">
+      <c r="B323" t="s">
         <v>643</v>
       </c>
-      <c r="C323" s="4" t="s">
+      <c r="C323" s="2" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="2">
+      <c r="A324" s="1">
         <v>323</v>
       </c>
-      <c r="B324" s="1" t="s">
+      <c r="B324" t="s">
         <v>645</v>
       </c>
-      <c r="C324" s="4" t="s">
+      <c r="C324" s="2" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="2">
+      <c r="A325" s="1">
         <v>324</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="B325" t="s">
         <v>647</v>
       </c>
-      <c r="C325" s="4" t="s">
+      <c r="C325" s="2" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="326" spans="1:3">
-      <c r="A326" s="2">
+      <c r="A326" s="1">
         <v>325</v>
       </c>
-      <c r="B326" s="1" t="s">
+      <c r="B326" t="s">
         <v>649</v>
       </c>
-      <c r="C326" s="4" t="s">
+      <c r="C326" s="2" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="327" spans="1:3">
-      <c r="A327" s="2">
+      <c r="A327" s="1">
         <v>326</v>
       </c>
-      <c r="B327" s="1" t="s">
+      <c r="B327" t="s">
         <v>651</v>
       </c>
-      <c r="C327" s="4" t="s">
+      <c r="C327" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="2">
+      <c r="A328" s="1">
         <v>327</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="B328" t="s">
         <v>653</v>
       </c>
-      <c r="C328" s="4" t="s">
+      <c r="C328" s="2" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="2">
+      <c r="A329" s="1">
         <v>328</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="B329" t="s">
         <v>655</v>
       </c>
-      <c r="C329" s="4" t="s">
+      <c r="C329" s="2" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="330" spans="1:3">
-      <c r="A330" s="2">
+      <c r="A330" s="1">
         <v>329</v>
       </c>
-      <c r="B330" s="1" t="s">
+      <c r="B330" t="s">
         <v>657</v>
       </c>
-      <c r="C330" s="4" t="s">
+      <c r="C330" s="2" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="331" spans="1:3">
-      <c r="A331" s="2">
+      <c r="A331" s="1">
         <v>330</v>
       </c>
-      <c r="B331" s="1" t="s">
+      <c r="B331" t="s">
         <v>659</v>
       </c>
-      <c r="C331" s="4" t="s">
+      <c r="C331" s="2" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="332" spans="1:3">
-      <c r="A332" s="2">
+      <c r="A332" s="1">
         <v>331</v>
       </c>
-      <c r="B332" s="1" t="s">
+      <c r="B332" t="s">
         <v>661</v>
       </c>
-      <c r="C332" s="4" t="s">
+      <c r="C332" s="2" t="s">
         <v>662</v>
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="2">
+      <c r="A333" s="1">
         <v>332</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="B333" t="s">
         <v>663</v>
       </c>
-      <c r="C333" s="4" t="s">
+      <c r="C333" s="2" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="2">
+      <c r="A334" s="1">
         <v>333</v>
       </c>
-      <c r="B334" s="1" t="s">
+      <c r="B334" t="s">
         <v>665</v>
       </c>
-      <c r="C334" s="4" t="s">
+      <c r="C334" s="2" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="335" spans="1:3">
-      <c r="A335" s="2">
+      <c r="A335" s="1">
         <v>334</v>
       </c>
-      <c r="B335" s="1" t="s">
+      <c r="B335" t="s">
         <v>667</v>
       </c>
-      <c r="C335" s="4" t="s">
+      <c r="C335" s="2" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="2">
+      <c r="A336" s="1">
         <v>335</v>
       </c>
-      <c r="B336" s="1" t="s">
+      <c r="B336" t="s">
         <v>669</v>
       </c>
-      <c r="C336" s="4" t="s">
+      <c r="C336" s="2" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="2">
+      <c r="A337" s="1">
         <v>336</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="B337" t="s">
         <v>671</v>
       </c>
-      <c r="C337" s="4" t="s">
+      <c r="C337" s="2" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="338" spans="1:3">
-      <c r="A338" s="2">
+      <c r="A338" s="1">
         <v>337</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="B338" t="s">
         <v>673</v>
       </c>
-      <c r="C338" s="4" t="s">
+      <c r="C338" s="2" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="339" spans="1:3">
-      <c r="A339" s="2">
+      <c r="A339" s="1">
         <v>338</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="B339" t="s">
         <v>675</v>
       </c>
-      <c r="C339" s="4" t="s">
+      <c r="C339" s="2" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="340" spans="1:3">
-      <c r="A340" s="2">
+      <c r="A340" s="1">
         <v>339</v>
       </c>
-      <c r="B340" s="1" t="s">
+      <c r="B340" t="s">
         <v>677</v>
       </c>
-      <c r="C340" s="4" t="s">
+      <c r="C340" s="2" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="2">
+      <c r="A341" s="1">
         <v>340</v>
       </c>
-      <c r="B341" s="1" t="s">
+      <c r="B341" t="s">
         <v>679</v>
       </c>
-      <c r="C341" s="4" t="s">
+      <c r="C341" s="2" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="2">
+      <c r="A342" s="1">
         <v>341</v>
       </c>
-      <c r="B342" s="1" t="s">
+      <c r="B342" t="s">
         <v>681</v>
       </c>
-      <c r="C342" s="4" t="s">
+      <c r="C342" s="2" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="343" spans="1:3">
-      <c r="A343" s="2">
+      <c r="A343" s="1">
         <v>342</v>
       </c>
-      <c r="B343" s="1" t="s">
+      <c r="B343" t="s">
         <v>683</v>
       </c>
-      <c r="C343" s="4" t="s">
+      <c r="C343" s="2" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="2">
+      <c r="A344" s="1">
         <v>343</v>
       </c>
-      <c r="B344" s="1" t="s">
+      <c r="B344" t="s">
         <v>685</v>
       </c>
-      <c r="C344" s="4" t="s">
+      <c r="C344" s="2" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="2">
+      <c r="A345" s="1">
         <v>344</v>
       </c>
-      <c r="B345" s="1" t="s">
+      <c r="B345" t="s">
         <v>687</v>
       </c>
-      <c r="C345" s="4" t="s">
+      <c r="C345" s="2" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="346" spans="1:3">
-      <c r="A346" s="2">
+      <c r="A346" s="1">
         <v>345</v>
       </c>
-      <c r="B346" s="1" t="s">
+      <c r="B346" t="s">
         <v>689</v>
       </c>
-      <c r="C346" s="4" t="s">
+      <c r="C346" s="2" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="347" spans="1:3">
-      <c r="A347" s="2">
+      <c r="A347" s="1">
         <v>346</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="B347" t="s">
         <v>691</v>
       </c>
-      <c r="C347" s="4" t="s">
+      <c r="C347" s="2" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="348" spans="1:3">
-      <c r="A348" s="2">
+      <c r="A348" s="1">
         <v>347</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="B348" t="s">
         <v>693</v>
       </c>
-      <c r="C348" s="4" t="s">
+      <c r="C348" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="2">
+      <c r="A349" s="1">
         <v>348</v>
       </c>
-      <c r="B349" s="1" t="s">
+      <c r="B349" t="s">
         <v>695</v>
       </c>
-      <c r="C349" s="4" t="s">
+      <c r="C349" s="2" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="2">
+      <c r="A350" s="1">
         <v>349</v>
       </c>
-      <c r="B350" s="1" t="s">
+      <c r="B350" t="s">
         <v>697</v>
       </c>
-      <c r="C350" s="4" t="s">
+      <c r="C350" s="2" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="351" spans="1:3">
-      <c r="A351" s="2">
+      <c r="A351" s="1">
         <v>350</v>
       </c>
-      <c r="B351" s="1" t="s">
+      <c r="B351" t="s">
         <v>699</v>
       </c>
-      <c r="C351" s="4" t="s">
+      <c r="C351" s="2" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="2">
+      <c r="A352" s="1">
         <v>351</v>
       </c>
-      <c r="B352" s="1" t="s">
+      <c r="B352" t="s">
         <v>701</v>
       </c>
-      <c r="C352" s="4" t="s">
+      <c r="C352" s="2" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="2">
+      <c r="A353" s="1">
         <v>352</v>
       </c>
-      <c r="B353" s="1" t="s">
+      <c r="B353" t="s">
         <v>703</v>
       </c>
-      <c r="C353" s="4" t="s">
+      <c r="C353" s="2" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="354" spans="1:3">
-      <c r="A354" s="2">
+      <c r="A354" s="1">
         <v>353</v>
       </c>
-      <c r="B354" s="1" t="s">
+      <c r="B354" t="s">
         <v>705</v>
       </c>
-      <c r="C354" s="4" t="s">
+      <c r="C354" s="2" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="355" spans="1:3">
-      <c r="A355" s="2">
+      <c r="A355" s="1">
         <v>354</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="B355" t="s">
         <v>707</v>
       </c>
-      <c r="C355" s="4" t="s">
+      <c r="C355" s="2" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="356" spans="1:3">
-      <c r="A356" s="2">
+      <c r="A356" s="1">
         <v>355</v>
       </c>
-      <c r="B356" s="1" t="s">
+      <c r="B356" t="s">
         <v>709</v>
       </c>
-      <c r="C356" s="4" t="s">
+      <c r="C356" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="2">
+      <c r="A357" s="1">
         <v>356</v>
       </c>
-      <c r="B357" s="1" t="s">
+      <c r="B357" t="s">
         <v>711</v>
       </c>
-      <c r="C357" s="4" t="s">
+      <c r="C357" s="2" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="2">
+      <c r="A358" s="1">
         <v>357</v>
       </c>
-      <c r="B358" s="1" t="s">
+      <c r="B358" t="s">
         <v>713</v>
       </c>
-      <c r="C358" s="4" t="s">
+      <c r="C358" s="2" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="359" spans="1:3">
-      <c r="A359" s="2">
+      <c r="A359" s="1">
         <v>358</v>
       </c>
-      <c r="B359" s="1" t="s">
+      <c r="B359" t="s">
         <v>715</v>
       </c>
-      <c r="C359" s="4" t="s">
+      <c r="C359" s="2" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="2">
+      <c r="A360" s="1">
         <v>359</v>
       </c>
-      <c r="B360" s="1" t="s">
+      <c r="B360" t="s">
         <v>717</v>
       </c>
-      <c r="C360" s="4" t="s">
+      <c r="C360" s="2" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="2">
+      <c r="A361" s="1">
         <v>360</v>
       </c>
-      <c r="B361" s="1" t="s">
+      <c r="B361" t="s">
         <v>719</v>
       </c>
-      <c r="C361" s="4" t="s">
+      <c r="C361" s="2" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="362" spans="1:3">
-      <c r="A362" s="2">
+      <c r="A362" s="1">
         <v>361</v>
       </c>
-      <c r="B362" s="1" t="s">
+      <c r="B362" t="s">
         <v>721</v>
       </c>
-      <c r="C362" s="4" t="s">
+      <c r="C362" s="2" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="363" spans="1:3">
-      <c r="A363" s="2">
+      <c r="A363" s="1">
         <v>362</v>
       </c>
-      <c r="B363" s="1" t="s">
+      <c r="B363" t="s">
         <v>723</v>
       </c>
-      <c r="C363" s="4" t="s">
+      <c r="C363" s="2" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="364" spans="1:3">
-      <c r="A364" s="2">
+      <c r="A364" s="1">
         <v>363</v>
       </c>
-      <c r="B364" s="1" t="s">
+      <c r="B364" t="s">
         <v>725</v>
       </c>
-      <c r="C364" s="4" t="s">
+      <c r="C364" s="2" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="2">
+      <c r="A365" s="1">
         <v>364</v>
       </c>
-      <c r="B365" s="1" t="s">
+      <c r="B365" t="s">
         <v>727</v>
       </c>
-      <c r="C365" s="4" t="s">
+      <c r="C365" s="2" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="2">
+      <c r="A366" s="1">
         <v>365</v>
       </c>
-      <c r="B366" s="1" t="s">
+      <c r="B366" t="s">
         <v>729</v>
       </c>
-      <c r="C366" s="4" t="s">
+      <c r="C366" s="2" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="367" spans="1:3">
-      <c r="A367" s="2">
+      <c r="A367" s="1">
         <v>366</v>
       </c>
-      <c r="B367" s="1" t="s">
+      <c r="B367" t="s">
         <v>731</v>
       </c>
-      <c r="C367" s="4" t="s">
+      <c r="C367" s="2" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="2">
+      <c r="A368" s="1">
         <v>367</v>
       </c>
-      <c r="B368" s="1" t="s">
+      <c r="B368" t="s">
         <v>733</v>
       </c>
-      <c r="C368" s="4" t="s">
+      <c r="C368" s="2" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="2">
+      <c r="A369" s="1">
         <v>368</v>
       </c>
-      <c r="B369" s="1" t="s">
+      <c r="B369" t="s">
         <v>735</v>
       </c>
-      <c r="C369" s="4" t="s">
+      <c r="C369" s="2" t="s">
         <v>736</v>
       </c>
     </row>
     <row r="370" spans="1:3">
-      <c r="A370" s="2">
+      <c r="A370" s="1">
         <v>369</v>
       </c>
-      <c r="B370" s="1" t="s">
+      <c r="B370" t="s">
         <v>737</v>
       </c>
-      <c r="C370" s="4" t="s">
+      <c r="C370" s="2" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="371" spans="1:3">
-      <c r="A371" s="2">
+      <c r="A371" s="1">
         <v>370</v>
       </c>
-      <c r="B371" s="1" t="s">
+      <c r="B371" t="s">
         <v>739</v>
       </c>
-      <c r="C371" s="4" t="s">
+      <c r="C371" s="2" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="372" spans="1:3">
-      <c r="A372" s="2">
+      <c r="A372" s="1">
         <v>371</v>
       </c>
-      <c r="B372" s="1" t="s">
+      <c r="B372" t="s">
         <v>741</v>
       </c>
-      <c r="C372" s="4" t="s">
+      <c r="C372" s="2" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="2">
+      <c r="A373" s="1">
         <v>372</v>
       </c>
-      <c r="B373" s="1" t="s">
+      <c r="B373" t="s">
         <v>743</v>
       </c>
-      <c r="C373" s="4" t="s">
+      <c r="C373" s="2" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="2">
+      <c r="A374" s="1">
         <v>373</v>
       </c>
-      <c r="B374" s="1" t="s">
+      <c r="B374" t="s">
         <v>745</v>
       </c>
-      <c r="C374" s="4" t="s">
+      <c r="C374" s="2" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="375" spans="1:3">
-      <c r="A375" s="2">
+      <c r="A375" s="1">
         <v>374</v>
       </c>
-      <c r="B375" s="1" t="s">
+      <c r="B375" t="s">
         <v>747</v>
       </c>
-      <c r="C375" s="4" t="s">
+      <c r="C375" s="2" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="2">
+      <c r="A376" s="1">
         <v>375</v>
       </c>
-      <c r="B376" s="1" t="s">
+      <c r="B376" t="s">
         <v>749</v>
       </c>
-      <c r="C376" s="4" t="s">
+      <c r="C376" s="2" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="2">
+      <c r="A377" s="1">
         <v>376</v>
       </c>
-      <c r="B377" s="1" t="s">
+      <c r="B377" t="s">
         <v>751</v>
       </c>
-      <c r="C377" s="4" t="s">
+      <c r="C377" s="2" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="378" spans="1:3">
-      <c r="A378" s="2">
+      <c r="A378" s="1">
         <v>377</v>
       </c>
-      <c r="B378" s="1" t="s">
+      <c r="B378" t="s">
         <v>753</v>
       </c>
-      <c r="C378" s="4" t="s">
+      <c r="C378" s="2" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="379" spans="1:3">
-      <c r="A379" s="2">
+      <c r="A379" s="1">
         <v>378</v>
       </c>
-      <c r="B379" s="1" t="s">
+      <c r="B379" t="s">
         <v>755</v>
       </c>
-      <c r="C379" s="4" t="s">
+      <c r="C379" s="2" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="380" spans="1:3">
-      <c r="A380" s="2">
+      <c r="A380" s="1">
         <v>379</v>
       </c>
-      <c r="B380" s="1" t="s">
+      <c r="B380" t="s">
         <v>757</v>
       </c>
-      <c r="C380" s="4" t="s">
+      <c r="C380" s="2" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="2">
+      <c r="A381" s="1">
         <v>380</v>
       </c>
-      <c r="B381" s="1" t="s">
+      <c r="B381" t="s">
         <v>759</v>
       </c>
-      <c r="C381" s="4" t="s">
+      <c r="C381" s="2" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="2">
+      <c r="A382" s="1">
         <v>381</v>
       </c>
-      <c r="B382" s="1" t="s">
+      <c r="B382" t="s">
         <v>761</v>
       </c>
-      <c r="C382" s="4" t="s">
+      <c r="C382" s="2" t="s">
         <v>762</v>
       </c>
     </row>
     <row r="383" spans="1:3">
-      <c r="A383" s="2">
+      <c r="A383" s="1">
         <v>382</v>
       </c>
-      <c r="B383" s="1" t="s">
+      <c r="B383" t="s">
         <v>763</v>
       </c>
-      <c r="C383" s="4" t="s">
+      <c r="C383" s="2" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="384" spans="1:3">
-      <c r="A384" s="2">
+      <c r="A384" s="1">
         <v>383</v>
       </c>
-      <c r="B384" s="1" t="s">
+      <c r="B384" t="s">
         <v>765</v>
       </c>
-      <c r="C384" s="4" t="s">
+      <c r="C384" s="2" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="2">
+      <c r="A385" s="1">
         <v>384</v>
       </c>
-      <c r="B385" s="1" t="s">
+      <c r="B385" t="s">
         <v>767</v>
       </c>
-      <c r="C385" s="4" t="s">
+      <c r="C385" s="2" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="2">
+      <c r="A386" s="1">
         <v>385</v>
       </c>
-      <c r="B386" s="1" t="s">
+      <c r="B386" t="s">
         <v>769</v>
       </c>
-      <c r="C386" s="4" t="s">
+      <c r="C386" s="2" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="387" spans="1:3">
-      <c r="A387" s="2">
+      <c r="A387" s="1">
         <v>386</v>
       </c>
-      <c r="B387" s="1" t="s">
+      <c r="B387" t="s">
         <v>771</v>
       </c>
-      <c r="C387" s="4" t="s">
+      <c r="C387" s="2" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="388" spans="1:3">
-      <c r="A388" s="2">
+      <c r="A388" s="1">
         <v>387</v>
       </c>
-      <c r="B388" s="1" t="s">
+      <c r="B388" t="s">
         <v>773</v>
       </c>
-      <c r="C388" s="4" t="s">
+      <c r="C388" s="2" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="389" spans="1:3">
-      <c r="A389" s="2">
+      <c r="A389" s="1">
         <v>388</v>
       </c>
-      <c r="B389" s="1" t="s">
+      <c r="B389" t="s">
         <v>775</v>
       </c>
-      <c r="C389" s="4" t="s">
+      <c r="C389" s="2" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="2">
+      <c r="A390" s="1">
         <v>389</v>
       </c>
-      <c r="B390" s="1" t="s">
+      <c r="B390" t="s">
         <v>777</v>
       </c>
-      <c r="C390" s="4" t="s">
+      <c r="C390" s="2" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="2">
+      <c r="A391" s="1">
         <v>390</v>
       </c>
-      <c r="B391" s="1" t="s">
+      <c r="B391" t="s">
         <v>779</v>
       </c>
-      <c r="C391" s="4" t="s">
+      <c r="C391" s="2" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="392" spans="1:3">
-      <c r="A392" s="2">
+      <c r="A392" s="1">
         <v>391</v>
       </c>
-      <c r="B392" s="1" t="s">
+      <c r="B392" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="2">
+      <c r="A393" s="1">
         <v>392</v>
       </c>
-      <c r="B393" s="1" t="s">
+      <c r="B393" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="2">
+      <c r="A394" s="1">
         <v>393</v>
       </c>
-      <c r="B394" s="1" t="s">
+      <c r="B394" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="395" spans="1:3">
-      <c r="A395" s="2">
+      <c r="A395" s="1">
         <v>394</v>
       </c>
-      <c r="B395" s="1" t="s">
+      <c r="B395" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="396" spans="1:3">
-      <c r="A396" s="2">
+      <c r="A396" s="1">
         <v>395</v>
       </c>
-      <c r="B396" s="1" t="s">
+      <c r="B396" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="397" spans="1:3">
-      <c r="A397" s="2">
+      <c r="A397" s="1">
         <v>396</v>
       </c>
-      <c r="B397" s="1" t="s">
+      <c r="B397" t="s">
         <v>786</v>
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="2">
+      <c r="A398" s="1">
         <v>397</v>
       </c>
-      <c r="B398" s="1" t="s">
+      <c r="B398" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="2">
+      <c r="A399" s="1">
         <v>398</v>
       </c>
-      <c r="B399" s="1" t="s">
+      <c r="B399" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="400" spans="1:3">
-      <c r="A400" s="2">
+      <c r="A400" s="1">
         <v>399</v>
       </c>
-      <c r="B400" s="1" t="s">
+      <c r="B400" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="2">
+      <c r="A401" s="1">
         <v>400</v>
       </c>
-      <c r="B401" s="1" t="s">
+      <c r="B401" t="s">
         <v>790</v>
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="2">
+      <c r="A402" s="1">
         <v>401</v>
       </c>
-      <c r="B402" s="1" t="s">
+      <c r="B402" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="2">
+      <c r="A403" s="1">
         <v>402</v>
       </c>
-      <c r="B403" s="1" t="s">
+      <c r="B403" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="2">
+      <c r="A404" s="1">
         <v>403</v>
       </c>
-      <c r="B404" s="1" t="s">
+      <c r="B404" t="s">
         <v>793</v>
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="2">
+      <c r="A405" s="1">
         <v>404</v>
       </c>
-      <c r="B405" s="1" t="s">
+      <c r="B405" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="2">
+      <c r="A406" s="1">
         <v>405</v>
       </c>
-      <c r="B406" s="1" t="s">
+      <c r="B406" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="2">
+      <c r="A407" s="1">
         <v>406</v>
       </c>
-      <c r="B407" s="1" t="s">
+      <c r="B407" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="2">
+      <c r="A408" s="1">
         <v>407</v>
       </c>
-      <c r="B408" s="1" t="s">
+      <c r="B408" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="2">
+      <c r="A409" s="1">
         <v>408</v>
       </c>
-      <c r="B409" s="1" t="s">
+      <c r="B409" t="s">
         <v>798</v>
       </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="2">
+      <c r="A410" s="1">
         <v>409</v>
       </c>
-      <c r="B410" s="1" t="s">
+      <c r="B410" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="2">
+      <c r="A411" s="1">
         <v>410</v>
       </c>
-      <c r="B411" s="1" t="s">
+      <c r="B411" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="2">
+      <c r="A412" s="1">
         <v>411</v>
       </c>
-      <c r="B412" s="1" t="s">
+      <c r="B412" t="s">
         <v>801</v>
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="2">
+      <c r="A413" s="1">
         <v>412</v>
       </c>
-      <c r="B413" s="1" t="s">
+      <c r="B413" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="2">
+      <c r="A414" s="1">
         <v>413</v>
       </c>
-      <c r="B414" s="1" t="s">
+      <c r="B414" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="2">
+      <c r="A415" s="1">
         <v>414</v>
       </c>
-      <c r="B415" s="1" t="s">
+      <c r="B415" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="2">
+      <c r="A416" s="1">
         <v>415</v>
       </c>
-      <c r="B416" s="1" t="s">
+      <c r="B416" t="s">
         <v>805</v>
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="2">
+      <c r="A417" s="1">
         <v>416</v>
       </c>
-      <c r="B417" s="1" t="s">
+      <c r="B417" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="2">
+      <c r="A418" s="1">
         <v>417</v>
       </c>
-      <c r="B418" s="1" t="s">
+      <c r="B418" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="2">
+      <c r="A419" s="1">
         <v>418</v>
       </c>
-      <c r="B419" s="1" t="s">
+      <c r="B419" t="s">
         <v>808</v>
       </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="2">
+      <c r="A420" s="1">
         <v>419</v>
       </c>
-      <c r="B420" s="1" t="s">
+      <c r="B420" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="2">
+      <c r="A421" s="1">
         <v>420</v>
       </c>
-      <c r="B421" s="1" t="s">
+      <c r="B421" t="s">
         <v>810</v>
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="2">
+      <c r="A422" s="1">
         <v>421</v>
       </c>
-      <c r="B422" s="1" t="s">
+      <c r="B422" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="2">
+      <c r="A423" s="1">
         <v>422</v>
       </c>
-      <c r="B423" s="1" t="s">
+      <c r="B423" t="s">
         <v>812</v>
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="2">
+      <c r="A424" s="1">
         <v>423</v>
       </c>
-      <c r="B424" s="1" t="s">
+      <c r="B424" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="2">
+      <c r="A425" s="1">
         <v>424</v>
       </c>
-      <c r="B425" s="1" t="s">
+      <c r="B425" t="s">
         <v>814</v>
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="2">
+      <c r="A426" s="1">
         <v>425</v>
       </c>
-      <c r="B426" s="1" t="s">
+      <c r="B426" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="2">
+      <c r="A427" s="1">
         <v>426</v>
       </c>
-      <c r="B427" s="1" t="s">
+      <c r="B427" t="s">
         <v>816</v>
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="2">
+      <c r="A428" s="1">
         <v>427</v>
       </c>
-      <c r="B428" s="1" t="s">
+      <c r="B428" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="2">
+      <c r="A429" s="1">
         <v>428</v>
       </c>
-      <c r="B429" s="1" t="s">
+      <c r="B429" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="2">
+      <c r="A430" s="1">
         <v>429</v>
       </c>
-      <c r="B430" s="1" t="s">
+      <c r="B430" t="s">
         <v>819</v>
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="2">
+      <c r="A431" s="1">
         <v>430</v>
       </c>
-      <c r="B431" s="1" t="s">
+      <c r="B431" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="2">
+      <c r="A432" s="1">
         <v>431</v>
       </c>
-      <c r="B432" s="1" t="s">
+      <c r="B432" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="2">
+      <c r="A433" s="1">
         <v>432</v>
       </c>
-      <c r="B433" s="1" t="s">
+      <c r="B433" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="2">
+      <c r="A434" s="1">
         <v>433</v>
       </c>
-      <c r="B434" s="1" t="s">
+      <c r="B434" t="s">
         <v>823</v>
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="2">
+      <c r="A435" s="1">
         <v>434</v>
       </c>
-      <c r="B435" s="1" t="s">
+      <c r="B435" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="2">
+      <c r="A436" s="1">
         <v>435</v>
       </c>
-      <c r="B436" s="1" t="s">
+      <c r="B436" t="s">
         <v>825</v>
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="2">
+      <c r="A437" s="1">
         <v>436</v>
       </c>
-      <c r="B437" s="1" t="s">
+      <c r="B437" t="s">
         <v>826</v>
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="2">
+      <c r="A438" s="1">
         <v>437</v>
       </c>
-      <c r="B438" s="1" t="s">
+      <c r="B438" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="2">
+      <c r="A439" s="1">
         <v>438</v>
       </c>
-      <c r="B439" s="1" t="s">
+      <c r="B439" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="2">
+      <c r="A440" s="1">
         <v>439</v>
       </c>
-      <c r="B440" s="1" t="s">
+      <c r="B440" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="2">
+      <c r="A441" s="1">
         <v>440</v>
       </c>
-      <c r="B441" s="1" t="s">
+      <c r="B441" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="2">
+      <c r="A442" s="1">
         <v>441</v>
       </c>
-      <c r="B442" s="1" t="s">
+      <c r="B442" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="2">
+      <c r="A443" s="1">
         <v>442</v>
       </c>
-      <c r="B443" s="1" t="s">
+      <c r="B443" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="2">
+      <c r="A444" s="1">
         <v>443</v>
       </c>
-      <c r="B444" s="1" t="s">
+      <c r="B444" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="2">
+      <c r="A445" s="1">
         <v>444</v>
       </c>
-      <c r="B445" s="1" t="s">
+      <c r="B445" t="s">
         <v>834</v>
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="2">
+      <c r="A446" s="1">
         <v>445</v>
       </c>
-      <c r="B446" s="1" t="s">
+      <c r="B446" t="s">
         <v>835</v>
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="2">
+      <c r="A447" s="1">
         <v>446</v>
       </c>
-      <c r="B447" s="1" t="s">
+      <c r="B447" t="s">
         <v>836</v>
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="2">
+      <c r="A448" s="1">
         <v>447</v>
       </c>
-      <c r="B448" s="1" t="s">
+      <c r="B448" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="2">
+      <c r="A449" s="1">
         <v>448</v>
       </c>
-      <c r="B449" s="1" t="s">
+      <c r="B449" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="2">
+      <c r="A450" s="1">
         <v>449</v>
       </c>
-      <c r="B450" s="1" t="s">
+      <c r="B450" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="2">
+      <c r="A451" s="1">
         <v>450</v>
       </c>
-      <c r="B451" s="1" t="s">
+      <c r="B451" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="2">
+      <c r="A452" s="1">
         <v>451</v>
       </c>
-      <c r="B452" s="1" t="s">
+      <c r="B452" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="2">
+      <c r="A453" s="1">
         <v>452</v>
       </c>
-      <c r="B453" s="1" t="s">
+      <c r="B453" t="s">
         <v>842</v>
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="2">
+      <c r="A454" s="1">
         <v>453</v>
       </c>
-      <c r="B454" s="1" t="s">
+      <c r="B454" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="2">
+      <c r="A455" s="1">
         <v>454</v>
       </c>
-      <c r="B455" s="1" t="s">
+      <c r="B455" t="s">
         <v>844</v>
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="2">
+      <c r="A456" s="1">
         <v>455</v>
       </c>
-      <c r="B456" s="1" t="s">
+      <c r="B456" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="2">
+      <c r="A457" s="1">
         <v>456</v>
       </c>
-      <c r="B457" s="1" t="s">
+      <c r="B457" t="s">
         <v>846</v>
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="2">
+      <c r="A458" s="1">
         <v>457</v>
       </c>
-      <c r="B458" s="1" t="s">
+      <c r="B458" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="2">
+      <c r="A459" s="1">
         <v>458</v>
       </c>
-      <c r="B459" s="1" t="s">
+      <c r="B459" t="s">
         <v>848</v>
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="2">
+      <c r="A460" s="1">
         <v>459</v>
       </c>
-      <c r="B460" s="1" t="s">
+      <c r="B460" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="2">
+      <c r="A461" s="1">
         <v>460</v>
       </c>
-      <c r="B461" s="1" t="s">
+      <c r="B461" t="s">
         <v>850</v>
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="2">
+      <c r="A462" s="1">
         <v>461</v>
       </c>
-      <c r="B462" s="1" t="s">
+      <c r="B462" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="2">
+      <c r="A463" s="1">
         <v>462</v>
       </c>
-      <c r="B463" s="1" t="s">
+      <c r="B463" t="s">
         <v>852</v>
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="2">
+      <c r="A464" s="1">
         <v>463</v>
       </c>
-      <c r="B464" s="1" t="s">
+      <c r="B464" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="2">
+      <c r="A465" s="1">
         <v>464</v>
       </c>
-      <c r="B465" s="1" t="s">
+      <c r="B465" t="s">
         <v>854</v>
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="2">
+      <c r="A466" s="1">
         <v>465</v>
       </c>
-      <c r="B466" s="1" t="s">
+      <c r="B466" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="467" spans="1:2">
-      <c r="A467" s="2">
+      <c r="A467" s="1">
         <v>466</v>
       </c>
-      <c r="B467" s="1" t="s">
+      <c r="B467" t="s">
         <v>856</v>
       </c>
     </row>
     <row r="468" spans="1:2">
-      <c r="A468" s="2">
+      <c r="A468" s="1">
         <v>467</v>
       </c>
-      <c r="B468" s="1" t="s">
+      <c r="B468" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="469" spans="1:2">
-      <c r="A469" s="2">
+      <c r="A469" s="1">
         <v>468</v>
       </c>
-      <c r="B469" s="1" t="s">
+      <c r="B469" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="470" spans="1:2">
-      <c r="A470" s="2">
+      <c r="A470" s="1">
         <v>469</v>
       </c>
-      <c r="B470" s="1" t="s">
+      <c r="B470" t="s">
         <v>859</v>
       </c>
     </row>
     <row r="471" spans="1:2">
-      <c r="A471" s="2">
+      <c r="A471" s="1">
         <v>470</v>
       </c>
-      <c r="B471" s="1" t="s">
+      <c r="B471" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="472" spans="1:2">
-      <c r="A472" s="2">
+      <c r="A472" s="1">
         <v>471</v>
       </c>
-      <c r="B472" s="1" t="s">
+      <c r="B472" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="473" spans="1:2">
-      <c r="A473" s="2">
+      <c r="A473" s="1">
         <v>472</v>
       </c>
-      <c r="B473" s="1" t="s">
+      <c r="B473" t="s">
         <v>862</v>
       </c>
     </row>
     <row r="474" spans="1:2">
-      <c r="A474" s="2">
+      <c r="A474" s="1">
         <v>473</v>
       </c>
-      <c r="B474" s="1" t="s">
+      <c r="B474" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="475" spans="1:2">
-      <c r="A475" s="2">
+      <c r="A475" s="1">
         <v>474</v>
       </c>
-      <c r="B475" s="1" t="s">
+      <c r="B475" t="s">
         <v>864</v>
       </c>
     </row>
     <row r="476" spans="1:2">
-      <c r="A476" s="2">
+      <c r="A476" s="1">
         <v>475</v>
       </c>
-      <c r="B476" s="1" t="s">
+      <c r="B476" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="477" spans="1:2">
-      <c r="A477" s="2">
+      <c r="A477" s="1">
         <v>476</v>
       </c>
-      <c r="B477" s="1" t="s">
+      <c r="B477" t="s">
         <v>866</v>
       </c>
     </row>
     <row r="478" spans="1:2">
-      <c r="A478" s="2">
+      <c r="A478" s="1">
         <v>477</v>
       </c>
-      <c r="B478" s="1" t="s">
+      <c r="B478" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="479" spans="1:2">
-      <c r="A479" s="2">
+      <c r="A479" s="1">
         <v>478</v>
       </c>
-      <c r="B479" s="1" t="s">
+      <c r="B479" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="480" spans="1:2">
-      <c r="A480" s="2">
+      <c r="A480" s="1">
         <v>479</v>
       </c>
-      <c r="B480" s="1" t="s">
+      <c r="B480" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="481" spans="1:2">
-      <c r="A481" s="2">
+      <c r="A481" s="1">
         <v>480</v>
       </c>
-      <c r="B481" s="1" t="s">
+      <c r="B481" t="s">
         <v>870</v>
       </c>
     </row>
     <row r="482" spans="1:2">
-      <c r="A482" s="2">
+      <c r="A482" s="1">
         <v>481</v>
       </c>
-      <c r="B482" s="1" t="s">
+      <c r="B482" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="483" spans="1:2">
-      <c r="A483" s="2">
+      <c r="A483" s="1">
         <v>482</v>
       </c>
-      <c r="B483" s="1" t="s">
+      <c r="B483" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="484" spans="1:2">
-      <c r="A484" s="2">
+      <c r="A484" s="1">
         <v>483</v>
       </c>
-      <c r="B484" s="1" t="s">
+      <c r="B484" t="s">
         <v>873</v>
       </c>
     </row>
     <row r="485" spans="1:2">
-      <c r="A485" s="2">
+      <c r="A485" s="1">
         <v>484</v>
       </c>
-      <c r="B485" s="1" t="s">
+      <c r="B485" t="s">
         <v>874</v>
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="2">
+      <c r="A486" s="1">
         <v>485</v>
       </c>
-      <c r="B486" s="1" t="s">
+      <c r="B486" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="2">
+      <c r="A487" s="1">
         <v>486</v>
       </c>
-      <c r="B487" s="1" t="s">
+      <c r="B487" t="s">
         <v>876</v>
       </c>
     </row>
     <row r="488" spans="1:2">
-      <c r="A488" s="2">
+      <c r="A488" s="1">
         <v>487</v>
       </c>
-      <c r="B488" s="1" t="s">
+      <c r="B488" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="2">
+      <c r="A489" s="1">
         <v>488</v>
       </c>
-      <c r="B489" s="1" t="s">
+      <c r="B489" t="s">
         <v>878</v>
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="2">
+      <c r="A490" s="1">
         <v>489</v>
       </c>
-      <c r="B490" s="1" t="s">
+      <c r="B490" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="2">
+      <c r="A491" s="1">
         <v>490</v>
       </c>
-      <c r="B491" s="1" t="s">
+      <c r="B491" t="s">
         <v>880</v>
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="2">
+      <c r="A492" s="1">
         <v>491</v>
       </c>
-      <c r="B492" s="1" t="s">
+      <c r="B492" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="2">
+      <c r="A493" s="1">
         <v>492</v>
       </c>
-      <c r="B493" s="1" t="s">
+      <c r="B493" t="s">
         <v>882</v>
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="2">
+      <c r="A494" s="1">
         <v>493</v>
       </c>
-      <c r="B494" s="1" t="s">
+      <c r="B494" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="2">
+      <c r="A495" s="1">
         <v>494</v>
       </c>
-      <c r="B495" s="1" t="s">
+      <c r="B495" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="2">
+      <c r="A496" s="1">
         <v>495</v>
       </c>
-      <c r="B496" s="1" t="s">
+      <c r="B496" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="2">
+      <c r="A497" s="1">
         <v>496</v>
       </c>
-      <c r="B497" s="1" t="s">
+      <c r="B497" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="2">
+      <c r="A498" s="1">
         <v>497</v>
       </c>
-      <c r="B498" s="1" t="s">
+      <c r="B498" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="2">
+      <c r="A499" s="1">
         <v>498</v>
       </c>
-      <c r="B499" s="1" t="s">
+      <c r="B499" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="2">
+      <c r="A500" s="1">
         <v>499</v>
       </c>
-      <c r="B500" s="1" t="s">
+      <c r="B500" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="2">
+      <c r="A501" s="1">
         <v>500</v>
       </c>
-      <c r="B501" s="1" t="s">
+      <c r="B501" t="s">
         <v>890</v>
       </c>
     </row>

--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BE14D5C-B0B5-478C-B07A-3118A13CE647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E36D20D-A91B-41FD-BA8B-A09800BB313E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,7 +426,7 @@
     <t>Kiedy oni uczą się migać z moim bratem?</t>
   </si>
   <si>
-    <t>ONI, KIEDY, UCZYĆ-SIĘ, MIGAĆ, MÓJ, BRAT</t>
+    <t>ONI, KIEDY, UCZYĆ-SIĘ, MIGAĆ, MÓJ, MĘŻCZYZNA, RODZEŃSTWO</t>
   </si>
   <si>
     <t>Wczoraj rano ty byłeś bardzo zmęczony.</t>

--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E36D20D-A91B-41FD-BA8B-A09800BB313E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{203CE402-0B44-4051-9DF8-87444669A50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -456,7 +456,7 @@
     <t>Ty i twój przyjaciel macie dużo pieniędzy.</t>
   </si>
   <si>
-    <t>TY+TWÓJ, PRZYJACIEL, RAZEM, PIENIĄDZE, DUŻO</t>
+    <t>TY, TWÓJ, PRZYJACIEL, RAZEM, PIENIĄDZE, DUŻO</t>
   </si>
   <si>
     <t>Ten stary kot nie chce dzisiaj jeść.</t>
@@ -516,7 +516,7 @@
     <t>Dlaczego ty dzisiaj rano nie byłeś u babci?</t>
   </si>
   <si>
-    <t>TY, DLACZEGO, DZISIAJ, RANO, U, BABCI, NIE-BYĆ</t>
+    <t>TY, DLACZEGO, DZISIAJ, RANO, U, BABCIA, NIE-BYĆ</t>
   </si>
   <si>
     <t>Kolega czeka na mnie w starym samochodzie.</t>
@@ -1434,7 +1434,7 @@
     <t>On czeka w domu na ciebie i na tatę.</t>
   </si>
   <si>
-    <t>ON, DOM, NA-CIEBIE, TATA, CZEKAĆ</t>
+    <t>ON, DOM, CIEBIE, TATA, CZEKAĆ</t>
   </si>
   <si>
     <t>Czy twój pies lubi mojego małego kota?</t>

--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{203CE402-0B44-4051-9DF8-87444669A50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94388451-74E5-40AF-AC6E-BAD0E2C2031A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
     <t>Dlaczego wczoraj nie byłeś w szkole?</t>
   </si>
   <si>
-    <t>WCZORAJ,SZKOŁA , NIE, BYŁO , DLACZEGO</t>
+    <t>WCZORAJ,SZKOŁA , NIE-BYŁO, DLACZEGO</t>
   </si>
   <si>
     <t>Mój brat ma duży dom i nowy samochód.</t>
@@ -126,7 +126,7 @@
     <t>Nie rozumiem, co ty mówisz.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA,NIE, ROZUMIEM , TY, CO , MÓWIĆ, CO </t>
+    <t xml:space="preserve">JA, NIE-ROZUMIEM , TY, CO , MÓWIĆ, CO </t>
   </si>
   <si>
     <t>Wesoła kobieta idzie do domu.</t>
@@ -174,7 +174,7 @@
     <t>Kolega nie rozumie, co ja mówię.</t>
   </si>
   <si>
-    <t xml:space="preserve">KOLEGA , NIE , ROZUMIEĆ , CO, JA, MÓWIĆ </t>
+    <t xml:space="preserve">KOLEGA , NIE -ROZUMIEĆ , CO, JA, MÓWIĆ </t>
   </si>
   <si>
     <t>Gdzie jest mój przyjaciel?</t>
@@ -216,7 +216,7 @@
     <t>On nie słyszy, ale bardzo dobrze widzi.</t>
   </si>
   <si>
-    <t xml:space="preserve">ON,NIE, SŁYSZY, ALE, WIDZI </t>
+    <t xml:space="preserve">ON,NIE-SŁYSZY, ALE, WIDZI </t>
   </si>
   <si>
     <t>Nie, ja nie chcę tego starego telefonu.</t>
@@ -684,7 +684,7 @@
     <t>Nie mam teraz czasu</t>
   </si>
   <si>
-    <t>TERAZ, JA, CZAS, NIE-MIEĆ, MIĘĆ</t>
+    <t>TERAZ, JA, CZAS, NIE-MIEĆ, MIEĆ</t>
   </si>
   <si>
     <t>Jestem zmęczony więc idę spać.</t>

--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="1001">
   <si>
     <t xml:space="preserve">Indeks zadnia </t>
   </si>
@@ -2368,331 +2368,661 @@
     <t xml:space="preserve">Chcę wiedzieć, dlaczego nie masz pieniędzy na książkę.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, CHCIEĆ, WIEDZIEĆ, DLACZEGO, TY, NIE, MIEĆ, PIENIĄDZE, NA, KSIĄŻKA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pamiętaj, żeby uczyć się w domu w dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">PAMIĘTAJ, DZIEŃ, UCZYĆ-SIĘ, W, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty zawsze masz czas, żeby pić ze mną herbatę.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, ZAWSZE, MIEĆ, CZAS, PIĆ, ZE-MNĄ, HERBATA</t>
+  </si>
+  <si>
     <t xml:space="preserve">W nocy słyszałem, jak ten kot dużo pije.</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC, JA, SŁYSZEĆ, TEN, KOT, DUŻO, PIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jesteś dzisiaj zmęczony, bo wczoraj dużo pracowałeś.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, DZISIAJ, ZMĘCZONY, BO, WCZORAJ, DUŻO, PRACOWAĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój tata nie lubi, kiedy pije gorącą wodę.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, TATA, LUBIĆ-NIE, KIEDY, PIĆ, WODA, GORĄCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">My bardzo często pijemy kawę u twojej siostry.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, CZĘSTO, PIĆ, KAWA, U, TWOJA, SIOSTRA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ta mała książka jest dla ciebie ważna?</t>
   </si>
   <si>
+    <t xml:space="preserve">DLACZEGO, KSIĄŻKA, MAŁA, TA, DLA-CIEBIE, WAŻNA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie wczoraj uczyłeś się migać z moim bratem?</t>
   </si>
   <si>
+    <t xml:space="preserve">GDZIE, WCZORAJ, TY, UCZYĆ-SIĘ, MIGAĆ, Z, MOIM, BRAT?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chcę kupić stary dom z dużym psem.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, CHCIEĆ, KUPIĆ, DOM, STARY, Z, PIES, DUŻY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie rozumiem, o czym ty do mnie rano mówiłeś.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, ROZUMIEĆ-NIE, RANO, TY, DO-MNIE, MÓWIĆ, O-CZYM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj nie mogę iść do pracy, bo chory brat jest w domu.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, JA, IŚĆ, PRACA, NIE-MOGĘ, BO, BRAT, CHORY, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czekam na moje pieniądze od poniedziałku.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, CZEKAĆ, NA, MOJE, PIENIĄDZE, OD, PONIEDZIAŁEK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj wieczorem widziałem, jak twój kolega pije kawę.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, WIDZIEĆ, TWÓJ, KOLEGA, PIĆ, KAWA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Babcia lubi, żeby kot spał rano pod domem.</t>
   </si>
   <si>
+    <t xml:space="preserve">BABCIA, LUBIĆ, ŻEBY, KOT, RANO, SPAĆ, POD, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten czas był dla mojego przyjaciela bardzo dobry.</t>
   </si>
   <si>
+    <t xml:space="preserve">TEN, CZAS, DLA, MÓJ, PRZYJACIEL, BARDZO, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kocham ten wesoły dzień w szkole z moim bratem.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, KOCHAĆ, TEN, DZIEŃ, WESOŁY, W, SZKOŁA, Z, MOIM, BRAT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego nie pamiętasz o moich urodzinach w poniedziałek?</t>
   </si>
   <si>
+    <t xml:space="preserve">DLACZEGO, TY, PAMIĘTAĆ-NIE, O, MOJE, URODZINY, PONIEDZIAŁEK?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Siostra jest często zmęczona.</t>
   </si>
   <si>
+    <t xml:space="preserve">SIOSTRA, CZĘSTO, ZMĘCZONA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Niech ta kobieta zostanie u ciebie na herbatę.</t>
   </si>
   <si>
+    <t xml:space="preserve">NIECH, KOBIETA, TA, ZOSTAĆ, U-CIEBIE, NA, HERBATA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze rano dziękuję tacie za dobrą pracę.</t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, RANO, JA, DZIĘKOWAĆ, TATA, ZA, PRACA, DOBRA</t>
+  </si>
+  <si>
     <t xml:space="preserve">W nocy mój dziadek nie słyszy, co babcia mówi.</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC, MÓJ, DZIADEK, SŁYSZEĆ-NIE, BABCIA, MÓWIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do pracy z psem?</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, KTO, MIEĆ, POMYSŁ, IŚĆ, PRACA, Z, PIES?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twój telefon był wczoraj rano w moim starym samochodzie.</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, TELEFON, WCZORAJ, RANO, BYĆ, W, MÓJ, SAMOCHÓD, STARY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie mam klucza, żeby być rano w domu u dziadka.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, NIE, MIEĆ, KLUCZ, ŻEBY, RANO, BYĆ, U, DZIADEK, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja będę na ciebie czekać z gorącą wodą rano.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, BĘDĘ, CZEKAĆ-NA-CIEBIE, Z, WODA, GORĄCA, RANO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mama musi teraz jeść.</t>
   </si>
   <si>
+    <t xml:space="preserve">MAMA, TERAZ, MUSI, JEŚĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie jest woda dla mojego nowego psa i kota?</t>
   </si>
   <si>
+    <t xml:space="preserve">GDZIE, WODA, DLA, MÓJ, PIES, NOWY, I, KOT?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj w nocy myślałem, co dzisiaj robić w szkole.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, NOC, JA, MYŚLEĆ, DZISIAJ, SZKOŁA, ROBIĆ-CO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro rano kupię dla ciebie ten stary samochód taty.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, RANO, JA, KUPIĆ, DLA-CIEBIE, TATA, SAMOCHÓD, STARY, TEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy twój przyjaciel ma czas na kawę po pracy?</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, PRZYJACIEL, MIEĆ, CZAS, NA, KAWA, PO, PRACA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Będziemy uczyć się migać o mojej starej pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, UCZYĆ-SIĘ, MIGAĆ, O, MOJA, PRACA, STARA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zostań z bratem w domu, bo on jest smutny.</t>
   </si>
   <si>
+    <t xml:space="preserve">ZOSTAŃ, Z, BRAT, W, DOM, BO, ON, SMUTNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja i ty musimy dużo pić, żeby nie być zmęczonymi.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, TY, MUSIEĆ, PIĆ, DUŻO, ŻEBY, ZMĘCZENI-NIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój nowy dom w poniedziałek rano jest bardzo zimny.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, DOM, NOWY, PONIEDZIAŁEK, RANO, BARDZO, ZIMNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego ten stary kot zawsze dużo je u babci?</t>
   </si>
   <si>
+    <t xml:space="preserve">DLACZEGO, KOT, STARY, TEN, ZAWSZE, DUŻO, JEŚĆ, U, BABCIA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mężczyzna czekał rano z psem, żeby iść do pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">MĘŻCZYZNA, CZEKAĆ, RANO, Z, PIES, ŻEBY, IŚĆ, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam, że wczoraj rano kupiłem ten nowy telefon.</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, WCZORAJ, RANO, JA, KUPIĆ, TELEFON, NOWY, TEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Często słyszę mojego psa rano, kiedy idę do pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">CZĘSTO, JA, SŁYSZEĆ, MÓJ, PIES, RANO, KIEDY, IŚĆ, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj wieczorem byłem z małym psem w starym domu dziadka.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, BYĆ, Z, PIES, MAŁY, W, DOM, STARY, DZIADEK</t>
+  </si>
+  <si>
     <t xml:space="preserve">My chcemy dużo spać, żeby nie być chorym rano.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, CHCIEĆ, DUŻO, SPAĆ, ŻEBY, RANO, CHORY-NIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">No to ile będziesz to robić? </t>
   </si>
   <si>
+    <t xml:space="preserve">NO-TO, TY, BĘDZIESZ, TO, ROBIĆ, ILE?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Niech mój przyjaciel czeka na ciebie rano u dziadka.</t>
   </si>
   <si>
+    <t xml:space="preserve">NIECH, MÓJ, PRZYJACIEL, CZEKAĆ-NA-CIEBIE, RANO, U, DZIADEK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy to jest środa, czy czwartek?</t>
   </si>
   <si>
+    <t xml:space="preserve">TO, ŚRODA, CZY, CZWARTEK?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twój wesoły tata wczoraj pił z moim dziadkiem wodę.</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, TATA, WESOŁY, WCZORAJ, PIĆ, WODA, Z, MOIM, DZIADEK</t>
+  </si>
+  <si>
     <t xml:space="preserve">My chcemy wiedzieć, gdzie wczoraj był twój samochód rano.</t>
   </si>
   <si>
+    <t xml:space="preserve">MY, CHCIEĆ, WIEDZIEĆ, GDZIE, WCZORAJ, RANO, TWÓJ, SAMOCHÓD, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro w nocy będę spać u brata z psem.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, NOC, JA, SPAĆ, U, BRAT, Z, PIES</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kiedy kupisz dla mnie tę książkę o starym domu?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, KUPIĆ, DLA-MNIE, KSIĄŻKA, O, DOM, STARY, KIEDY?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja bardzo lubię pić z tobą dobrą gorącą herbatę.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, BARDZO, LUBIĆ, PIĆ, Z-TOBĄ, HERBATA, DOBRA, GORĄCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie my wczoraj widzieliśmy ten stary samochód mojego przyjaciela?</t>
   </si>
   <si>
+    <t xml:space="preserve">GDZIE, MY, WCZORAJ, WIDZIEĆ, SAMOCHÓD, STARY, MÓJ, PRZYJACIEL?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam, ale to był taki ważny rok, czy wy to teraz rozumiecie?</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, ALE, TEN, ROK, BARDZO, WAŻNY, WY, TERAZ, ROZUMIEĆ?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój dziadek w poniedziałek wieczorem był zmęczony i smutny.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, DZIADEK, PONIEDZIAŁEK, WIECZÓR, ZMĘCZONY, I, SMUTNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie mogę dzisiaj iść po kawę z moim nowym przyjacielem.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, DZISIAJ, IŚĆ, KAWA, Z, MÓJ, PRZYJACIEL, NOWY, NIE-MOGĘ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Babcia i dziadek dzisiaj rano pili ze mną wodę.</t>
   </si>
   <si>
+    <t xml:space="preserve">BABCIA, DZIADEK, DZISIAJ, RANO, PIĆ, ZE-MNĄ, WODA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twój brat zawsze bardzo lubi mówić rano o pracy w środę?</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, BRAT, ZAWSZE, BARDZO, LUBIĆ, RANO, MÓWIĆ, O, PRACA, ŚRODA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile to było robione? </t>
   </si>
   <si>
+    <t xml:space="preserve">TO, ROBIĆ, BYŁO, ILE?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pamiętam, żeby pić zimną wodę w gorący dzień.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, PAMIĘTAĆ, PIĆ, WODA, ZIMNA, W, DZIEŃ, GORĄCY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro rano idę z małym psem do ciebie po klucz.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, RANO, JA, IŚĆ, Z, PIES, MAŁY, DO-CIEBIE, PO, KLUCZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ty nie pamiętasz, dlaczego wczoraj byłem u ciebie z bratem.</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, PAMIĘTAĆ-NIE, DLACZEGO, WCZORAJ, JA, BYĆ, U-CIEBIE, Z, BRAT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile kawy dzisiaj pijesz, żeby mieć na to czas?</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, TY, PIĆ, KAWA, ILE, ŻEBY, MIEĆ, CZAS, NA-TO?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto wesoły i zdrowy idzie z moim bratem do starej szkoły?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, WESOŁY, ZDROWY, IŚĆ, Z, MOIM, BRAT, DO, SZKOŁA, STARA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój stary pies ma dzisiaj urodziny rano.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, PIES, STARY, DZISIAJ, RANO, URODZINY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czekam rano przed twoim nowym domem z gorącą herbatą.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, CZEKAĆ, RANO, PRZED, TWÓJ, DOM, NOWY, Z, HERBATA, GORĄCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dzisiaj rano chcę uczyć się migać z twoją babcią.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZISIAJ, RANO, JA, CHCIEĆ, UCZYĆ-SIĘ, MIGAĆ, Z, TWOJA, BABCIA</t>
+  </si>
+  <si>
     <t xml:space="preserve">To było we wtorek i w środę, teraz już to rozumiem, to był taki ważny rok. </t>
   </si>
   <si>
+    <t xml:space="preserve">TO, BYĆ, WTOREK, I, ŚRODA, TERAZ, JA, ROZUMIEĆ, —, TEN, ROK, WAŻNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy wy się teraz kochacie, czy to już taki nowy pomysł na ten czwartek? </t>
   </si>
   <si>
+    <t xml:space="preserve">WY, TERAZ, KOCHAĆ-SIĘ, CZY, TO, POMYSŁ, NOWY, NA, CZWARTEK?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziadek nie słyszy, kiedy babcia mówi do kota.</t>
   </si>
   <si>
+    <t xml:space="preserve">DZIADEK, SŁYSZEĆ-NIE, KIEDY, BABCIA, MÓWIĆ, DO, KOT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj w nocy myślałem o tej książce z moim bratem.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, NOC, JA, MYŚLEĆ, O, KSIĄŻKA, TA, Z, MOIM, BRAT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zostań rano w domu u dziadka, bo jesteś bardzo chory.</t>
   </si>
   <si>
+    <t xml:space="preserve">RANO, ZOSTAŃ, U, DZIADEK, DOM, BO, TY, BARDZO, CHORY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nie mam rano klucza od twojego starego samochodu.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, NIE, MIEĆ, RANO, KLUCZ, OD, TWOJEGO, SAMOCHÓD, STARY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy wiesz, co ten duży pies jadł w poniedziałek?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, WIEDZIEĆ, CO, PIES, DUŻY, TEN, JEŚĆ, PONIEDZIAŁEK?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kocham ten czas rano, kiedy kot śpi u mnie.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, KOCHAĆ, TEN, CZAS, RANO, KIEDY, KOT, SPAĆ, U-MNIE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj wieczorem widziałem mojego psa przed szkołą.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, WIDZIEĆ, MÓJ, PIES, PRZED, SZKOŁA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pamiętam, żeby dużo pracować i mieć pieniądze na nowy dom.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, PAMIĘTAĆ:, DUŻO, PRACOWAĆ, PIENIĄDZE, MIEĆ, NA, DOM, NOWY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ten bardzo smutny mężczyzna nie lubi pić ze mną kawy.</t>
   </si>
   <si>
+    <t xml:space="preserve">TEN, MĘŻCZYZNA, BARDZO, SMUTNY, LUBIĆ-NIE, PIĆ, ZE-MNĄ, KAWA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie wczoraj kupiłeś tę książkę dla przyjaciela?</t>
   </si>
   <si>
+    <t xml:space="preserve">GDZIE, WCZORAJ, TY, KUPIĆ, KSIĄŻKA, DLA, PRZYJACIEL?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój tata bardzo kocha rano pić herbatę z wesołym psem.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, TATA, BARDZO, KOCHAĆ, RANO, PIĆ, HERBATA, Z, PIES, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze chcę być z tobą rano u ciebie w pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, JA, CHCIEĆ, BYĆ, Z-TOBĄ, RANO, U-CIEBIE, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twój pomysł na urodziny brata w poniedziałek jest bardzo dobry.</t>
   </si>
   <si>
+    <t xml:space="preserve">TWÓJ, POMYSŁ, NA, URODZINY, BRAT, PONIEDZIAŁEK, BARDZO, DOBRY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Niech kot zostanie u ciebie z moim starym tatą.</t>
   </si>
   <si>
+    <t xml:space="preserve">NIECH, KOT, ZOSTAĆ, U-CIEBIE, Z, MOIM, TATA, STARY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do nowej szkoły rano?</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, KTO, MIEĆ, POMYSŁ, IŚĆ, RANO, DO, SZKOŁA, NOWA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj rano mój tata kupił ten stary dom.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, RANO, MÓJ, TATA, KUPIĆ, DOM, STARY, TEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego zawsze pijesz gorącą wodę z mamą?</t>
   </si>
   <si>
+    <t xml:space="preserve">DLACZEGO, TY, ZAWSZE, PIĆ, WODA, GORĄCA, Z, MAMA?</t>
+  </si>
+  <si>
     <t xml:space="preserve">We wtorek rano mój brat musi iść do pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">WTOREK, RANO, MÓJ, BRAT, MUSI, IŚĆ, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">W środę ja i ty chcemy kupić nowy dom, który będzie dla nas ważny </t>
   </si>
   <si>
+    <t xml:space="preserve">ŚRODA, JA, TY, CHCIEĆ, KUPIĆ, DOM, NOWY, DLA-NAS, WAŻNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czy w czwartek twój pies był chory i kto mu pomógł? </t>
   </si>
   <si>
+    <t xml:space="preserve">CZWARTEK, TWÓJ, PIES, CHORY, BYŁ?, KTO, POMÓC-MU?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dlaczego we wtorek zawsze jesteś smutny?</t>
   </si>
   <si>
+    <t xml:space="preserve">DLACZEGO, WTOREK, TY, ZAWSZE, SMUTNY?</t>
+  </si>
+  <si>
     <t xml:space="preserve">W środę wieczorem dziadek pije gorącą herbatę, bo kocha ten zdrowy pomysł. </t>
   </si>
   <si>
+    <t xml:space="preserve">ŚRODA, WIECZÓR, DZIADEK, PIĆ, HERBATA, GORĄCA, BO, KOCHAĆ, TEN, POMYSŁ, ZDROWY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Już pamiętam że mój przyjaciel ma urodziny w czwartek</t>
   </si>
   <si>
+    <t xml:space="preserve">JUŻ, PAMIĘTAĆ:, MÓJ, PRZYJACIEL, URODZINY, CZWARTEK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wczoraj był poniedziałek, a dzisiaj jest wtorek.</t>
   </si>
   <si>
+    <t xml:space="preserve">WCZORAJ, PONIEDZIAŁEK, DZISIAJ, WTOREK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kto musi pracować w środę w nocy?</t>
   </si>
   <si>
+    <t xml:space="preserve">KTO, MUSI, ŚRODA, NOC, PRACOWAĆ?</t>
+  </si>
+  <si>
     <t xml:space="preserve">W czwartek rano babcia czeka na mój telefon.</t>
   </si>
   <si>
+    <t xml:space="preserve">CZWARTEK, RANO, BABCIA, CZEKAĆ, NA, MÓJ, TELEFON</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kobieta i mężczyzna idą do szkoły we wtorek.</t>
   </si>
   <si>
+    <t xml:space="preserve">KOBIETA, PLUS, MĘŻCZYZNA, IŚĆ, SZKOŁA, WTOREK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ja wiem, że w środę będę bardzo zmęczony.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, WIEDZIEĆ, ŚRODA, JA, BĘDĘ, BARDZO, ZMĘCZONY</t>
+  </si>
+  <si>
     <t xml:space="preserve">W czwartek siostra chce mieć nową książkę.</t>
   </si>
   <si>
+    <t xml:space="preserve">CZWARTEK, SIOSTRA, CHCIEĆ, MIEĆ, KSIĄŻKA, NOWA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gdzie ty byłeś we wtorek rano?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, BYĆ, GDZIE, WTOREK, RANO?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mój stary kot lubi spać w środę w domu.</t>
   </si>
   <si>
+    <t xml:space="preserve">MÓJ, KOT, STARY, LUBIĆ, ŚRODA, SPAĆ, DOM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ile pieniędzy musisz mieć na czwartek?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, MUSIEĆ, MIEĆ, PIENIĄDZE, ILE, NA, CZWARTEK?</t>
+  </si>
+  <si>
     <t xml:space="preserve">We wtorek my nie mamy czasu na kawę.</t>
   </si>
   <si>
+    <t xml:space="preserve">WTOREK, MY, CZAS-NIE, NA, KAWA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zawsze w środę uczę się migać, teraz już kocham to robić. </t>
   </si>
   <si>
+    <t xml:space="preserve">ZAWSZE, ŚRODA, JA, UCZYĆ-SIĘ, MIGAĆ, TERAZ, JUŻ, KOCHAĆ, TO, ROBIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">W czwartek wieczorem twój kolega jest wesoły.</t>
   </si>
   <si>
+    <t xml:space="preserve">CZWARTEK, WIECZÓR, TWÓJ, KOLEGA, WESOŁY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pamiętam, co mój tata mówił we wtorek.</t>
   </si>
   <si>
+    <t xml:space="preserve">JA, PAMIĘTAĆ, CO, MÓJ, TATA, WTOREK, MÓWIĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">W środę ten duży samochód jest mój, a wy go już kochacie. </t>
   </si>
   <si>
+    <t xml:space="preserve">ŚRODA, SAMOCHÓD, DUŻY, TEN, MÓJ, WY, JUŻ, KOCHAĆ-GO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dziękuję, że chcesz mi pomóc w czwartek, to taki zdrowy pomysł. </t>
   </si>
   <si>
+    <t xml:space="preserve">DZIĘKUJĘ, ŻE, CHCIEĆ, MI, POMÓC, CZWARTEK, —, TO, POMYSŁ, ZDROWY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jak bardzo lubisz ten wtorek?</t>
   </si>
   <si>
+    <t xml:space="preserve">TY, LUBIĆ, WTOREK, JAK-BARDZO?</t>
+  </si>
+  <si>
     <t xml:space="preserve">W środę rano muszę pić zimną wodę.</t>
   </si>
   <si>
+    <t xml:space="preserve">ŚRODA, RANO, JA, MUSI, PIĆ, WODA, ZIMNA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jutro czwartek, więc idę do pracy.</t>
   </si>
   <si>
+    <t xml:space="preserve">JUTRO, CZWARTEK, WIĘC, JA, IŚĆ, PRACA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przepraszam, że nie byłem zdrowy we wtorek.</t>
   </si>
   <si>
+    <t xml:space="preserve">PRZEPRASZAM, WTOREK, JA, ZDROWY-NIE, BYĆ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Teraz idę do pracy, bo muszę iść po klucz, który ma moja siostra. </t>
   </si>
   <si>
+    <t xml:space="preserve">TERAZ, JA, IŚĆ, PRACA, BO, MUSZĘ, IŚĆ, PO, KLUCZ, MOJA, SIOSTRA, MA</t>
+  </si>
+  <si>
     <t xml:space="preserve">On się teraz uczy, żeby rozumieć, jak pomóc chorej kobiecie. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON, TERAZ, UCZYĆ-SIĘ, ŻEBY, ROZUMIEĆ, JAK, POMÓC, KOBIETA, CHORA</t>
   </si>
 </sst>
 </file>
@@ -2713,16 +3043,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2812,37 +3145,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2915,8 +3248,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D501"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D502"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60"/>
@@ -5998,7 +6331,7 @@
       <c r="B257" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C257" s="5" t="s">
+      <c r="C257" s="4" t="s">
         <v>512</v>
       </c>
       <c r="D257" s="2"/>
@@ -6010,7 +6343,7 @@
       <c r="B258" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C258" s="5" t="s">
+      <c r="C258" s="4" t="s">
         <v>514</v>
       </c>
       <c r="D258" s="2"/>
@@ -6022,7 +6355,7 @@
       <c r="B259" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C259" s="5" t="s">
+      <c r="C259" s="4" t="s">
         <v>516</v>
       </c>
       <c r="D259" s="2"/>
@@ -6034,7 +6367,7 @@
       <c r="B260" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C260" s="5" t="s">
+      <c r="C260" s="4" t="s">
         <v>518</v>
       </c>
       <c r="D260" s="2"/>
@@ -6046,7 +6379,7 @@
       <c r="B261" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C261" s="5" t="s">
+      <c r="C261" s="4" t="s">
         <v>520</v>
       </c>
       <c r="D261" s="2"/>
@@ -6058,7 +6391,7 @@
       <c r="B262" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C262" s="5" t="s">
+      <c r="C262" s="4" t="s">
         <v>522</v>
       </c>
       <c r="D262" s="2"/>
@@ -6070,7 +6403,7 @@
       <c r="B263" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C263" s="5" t="s">
+      <c r="C263" s="4" t="s">
         <v>524</v>
       </c>
       <c r="D263" s="2"/>
@@ -6082,7 +6415,7 @@
       <c r="B264" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C264" s="5" t="s">
+      <c r="C264" s="4" t="s">
         <v>526</v>
       </c>
       <c r="D264" s="2"/>
@@ -6094,7 +6427,7 @@
       <c r="B265" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C265" s="5" t="s">
+      <c r="C265" s="4" t="s">
         <v>528</v>
       </c>
       <c r="D265" s="2"/>
@@ -6106,7 +6439,7 @@
       <c r="B266" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C266" s="5" t="s">
+      <c r="C266" s="4" t="s">
         <v>530</v>
       </c>
       <c r="D266" s="2"/>
@@ -6118,7 +6451,7 @@
       <c r="B267" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C267" s="5" t="s">
+      <c r="C267" s="4" t="s">
         <v>532</v>
       </c>
       <c r="D267" s="2"/>
@@ -6130,7 +6463,7 @@
       <c r="B268" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C268" s="5" t="s">
+      <c r="C268" s="4" t="s">
         <v>534</v>
       </c>
       <c r="D268" s="2"/>
@@ -6142,7 +6475,7 @@
       <c r="B269" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C269" s="5" t="s">
+      <c r="C269" s="4" t="s">
         <v>536</v>
       </c>
       <c r="D269" s="2"/>
@@ -6154,7 +6487,7 @@
       <c r="B270" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C270" s="5" t="s">
+      <c r="C270" s="4" t="s">
         <v>538</v>
       </c>
       <c r="D270" s="2"/>
@@ -6166,7 +6499,7 @@
       <c r="B271" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C271" s="5" t="s">
+      <c r="C271" s="4" t="s">
         <v>540</v>
       </c>
       <c r="D271" s="2"/>
@@ -6178,7 +6511,7 @@
       <c r="B272" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C272" s="5" t="s">
+      <c r="C272" s="4" t="s">
         <v>542</v>
       </c>
       <c r="D272" s="2"/>
@@ -6190,7 +6523,7 @@
       <c r="B273" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C273" s="5" t="s">
+      <c r="C273" s="4" t="s">
         <v>544</v>
       </c>
       <c r="D273" s="2"/>
@@ -6202,7 +6535,7 @@
       <c r="B274" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C274" s="5" t="s">
+      <c r="C274" s="4" t="s">
         <v>546</v>
       </c>
       <c r="D274" s="2"/>
@@ -6214,7 +6547,7 @@
       <c r="B275" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C275" s="5" t="s">
+      <c r="C275" s="4" t="s">
         <v>548</v>
       </c>
       <c r="D275" s="2"/>
@@ -6226,7 +6559,7 @@
       <c r="B276" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C276" s="5" t="s">
+      <c r="C276" s="4" t="s">
         <v>550</v>
       </c>
       <c r="D276" s="2"/>
@@ -6238,7 +6571,7 @@
       <c r="B277" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C277" s="5" t="s">
+      <c r="C277" s="4" t="s">
         <v>552</v>
       </c>
       <c r="D277" s="2"/>
@@ -6250,7 +6583,7 @@
       <c r="B278" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C278" s="5" t="s">
+      <c r="C278" s="4" t="s">
         <v>554</v>
       </c>
       <c r="D278" s="2"/>
@@ -6262,7 +6595,7 @@
       <c r="B279" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C279" s="5" t="s">
+      <c r="C279" s="4" t="s">
         <v>556</v>
       </c>
       <c r="D279" s="2"/>
@@ -6274,7 +6607,7 @@
       <c r="B280" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C280" s="5" t="s">
+      <c r="C280" s="4" t="s">
         <v>558</v>
       </c>
       <c r="D280" s="2"/>
@@ -6286,7 +6619,7 @@
       <c r="B281" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C281" s="5" t="s">
+      <c r="C281" s="4" t="s">
         <v>560</v>
       </c>
       <c r="D281" s="2"/>
@@ -6298,7 +6631,7 @@
       <c r="B282" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C282" s="5" t="s">
+      <c r="C282" s="4" t="s">
         <v>562</v>
       </c>
       <c r="D282" s="2"/>
@@ -6310,7 +6643,7 @@
       <c r="B283" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C283" s="5" t="s">
+      <c r="C283" s="4" t="s">
         <v>564</v>
       </c>
       <c r="D283" s="2"/>
@@ -6322,7 +6655,7 @@
       <c r="B284" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C284" s="5" t="s">
+      <c r="C284" s="4" t="s">
         <v>566</v>
       </c>
       <c r="D284" s="2"/>
@@ -6334,7 +6667,7 @@
       <c r="B285" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C285" s="5" t="s">
+      <c r="C285" s="4" t="s">
         <v>568</v>
       </c>
       <c r="D285" s="2"/>
@@ -6346,7 +6679,7 @@
       <c r="B286" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C286" s="5" t="s">
+      <c r="C286" s="4" t="s">
         <v>570</v>
       </c>
       <c r="D286" s="2"/>
@@ -6358,7 +6691,7 @@
       <c r="B287" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C287" s="5" t="s">
+      <c r="C287" s="4" t="s">
         <v>572</v>
       </c>
       <c r="D287" s="2"/>
@@ -6370,7 +6703,7 @@
       <c r="B288" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C288" s="5" t="s">
+      <c r="C288" s="4" t="s">
         <v>574</v>
       </c>
       <c r="D288" s="2"/>
@@ -6382,7 +6715,7 @@
       <c r="B289" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C289" s="5" t="s">
+      <c r="C289" s="4" t="s">
         <v>576</v>
       </c>
       <c r="D289" s="2"/>
@@ -6394,7 +6727,7 @@
       <c r="B290" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C290" s="5" t="s">
+      <c r="C290" s="4" t="s">
         <v>578</v>
       </c>
       <c r="D290" s="2"/>
@@ -6406,7 +6739,7 @@
       <c r="B291" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C291" s="5" t="s">
+      <c r="C291" s="4" t="s">
         <v>580</v>
       </c>
       <c r="D291" s="2"/>
@@ -6418,7 +6751,7 @@
       <c r="B292" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C292" s="5" t="s">
+      <c r="C292" s="4" t="s">
         <v>582</v>
       </c>
       <c r="D292" s="2"/>
@@ -6430,7 +6763,7 @@
       <c r="B293" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C293" s="5" t="s">
+      <c r="C293" s="4" t="s">
         <v>584</v>
       </c>
       <c r="D293" s="2"/>
@@ -6442,7 +6775,7 @@
       <c r="B294" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C294" s="5" t="s">
+      <c r="C294" s="4" t="s">
         <v>586</v>
       </c>
       <c r="D294" s="2"/>
@@ -6454,7 +6787,7 @@
       <c r="B295" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C295" s="5" t="s">
+      <c r="C295" s="4" t="s">
         <v>588</v>
       </c>
       <c r="D295" s="2"/>
@@ -6466,7 +6799,7 @@
       <c r="B296" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="C296" s="5" t="s">
+      <c r="C296" s="4" t="s">
         <v>590</v>
       </c>
       <c r="D296" s="2"/>
@@ -6478,7 +6811,7 @@
       <c r="B297" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C297" s="5" t="s">
+      <c r="C297" s="4" t="s">
         <v>592</v>
       </c>
       <c r="D297" s="2"/>
@@ -6490,7 +6823,7 @@
       <c r="B298" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="C298" s="5" t="s">
+      <c r="C298" s="4" t="s">
         <v>594</v>
       </c>
       <c r="D298" s="2"/>
@@ -6502,7 +6835,7 @@
       <c r="B299" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C299" s="5" t="s">
+      <c r="C299" s="4" t="s">
         <v>596</v>
       </c>
       <c r="D299" s="2"/>
@@ -6514,7 +6847,7 @@
       <c r="B300" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C300" s="5" t="s">
+      <c r="C300" s="4" t="s">
         <v>598</v>
       </c>
       <c r="D300" s="2"/>
@@ -6526,7 +6859,7 @@
       <c r="B301" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="C301" s="5" t="s">
+      <c r="C301" s="4" t="s">
         <v>600</v>
       </c>
       <c r="D301" s="2"/>
@@ -6538,7 +6871,7 @@
       <c r="B302" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C302" s="5" t="s">
+      <c r="C302" s="4" t="s">
         <v>602</v>
       </c>
     </row>
@@ -6549,7 +6882,7 @@
       <c r="B303" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C303" s="5" t="s">
+      <c r="C303" s="4" t="s">
         <v>604</v>
       </c>
     </row>
@@ -6560,7 +6893,7 @@
       <c r="B304" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C304" s="5" t="s">
+      <c r="C304" s="4" t="s">
         <v>606</v>
       </c>
     </row>
@@ -6571,7 +6904,7 @@
       <c r="B305" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C305" s="5" t="s">
+      <c r="C305" s="4" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6582,7 +6915,7 @@
       <c r="B306" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C306" s="5" t="s">
+      <c r="C306" s="4" t="s">
         <v>610</v>
       </c>
     </row>
@@ -6593,7 +6926,7 @@
       <c r="B307" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C307" s="5" t="s">
+      <c r="C307" s="4" t="s">
         <v>612</v>
       </c>
     </row>
@@ -6604,7 +6937,7 @@
       <c r="B308" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C308" s="5" t="s">
+      <c r="C308" s="4" t="s">
         <v>614</v>
       </c>
     </row>
@@ -6615,7 +6948,7 @@
       <c r="B309" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C309" s="5" t="s">
+      <c r="C309" s="4" t="s">
         <v>616</v>
       </c>
     </row>
@@ -6626,7 +6959,7 @@
       <c r="B310" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="C310" s="5" t="s">
+      <c r="C310" s="4" t="s">
         <v>618</v>
       </c>
     </row>
@@ -6637,7 +6970,7 @@
       <c r="B311" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C311" s="5" t="s">
+      <c r="C311" s="4" t="s">
         <v>620</v>
       </c>
     </row>
@@ -6648,7 +6981,7 @@
       <c r="B312" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="C312" s="5" t="s">
+      <c r="C312" s="4" t="s">
         <v>622</v>
       </c>
     </row>
@@ -6659,7 +6992,7 @@
       <c r="B313" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C313" s="5" t="s">
+      <c r="C313" s="4" t="s">
         <v>624</v>
       </c>
     </row>
@@ -6670,7 +7003,7 @@
       <c r="B314" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C314" s="5" t="s">
+      <c r="C314" s="4" t="s">
         <v>626</v>
       </c>
     </row>
@@ -6681,7 +7014,7 @@
       <c r="B315" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="C315" s="5" t="s">
+      <c r="C315" s="4" t="s">
         <v>628</v>
       </c>
     </row>
@@ -6692,7 +7025,7 @@
       <c r="B316" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C316" s="5" t="s">
+      <c r="C316" s="4" t="s">
         <v>630</v>
       </c>
     </row>
@@ -6703,7 +7036,7 @@
       <c r="B317" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C317" s="5" t="s">
+      <c r="C317" s="4" t="s">
         <v>632</v>
       </c>
     </row>
@@ -6714,7 +7047,7 @@
       <c r="B318" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C318" s="5" t="s">
+      <c r="C318" s="4" t="s">
         <v>634</v>
       </c>
     </row>
@@ -6725,7 +7058,7 @@
       <c r="B319" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C319" s="5" t="s">
+      <c r="C319" s="4" t="s">
         <v>636</v>
       </c>
     </row>
@@ -6736,7 +7069,7 @@
       <c r="B320" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C320" s="5" t="s">
+      <c r="C320" s="4" t="s">
         <v>638</v>
       </c>
     </row>
@@ -6747,7 +7080,7 @@
       <c r="B321" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C321" s="5" t="s">
+      <c r="C321" s="4" t="s">
         <v>640</v>
       </c>
     </row>
@@ -6758,7 +7091,7 @@
       <c r="B322" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C322" s="5" t="s">
+      <c r="C322" s="4" t="s">
         <v>642</v>
       </c>
     </row>
@@ -6769,7 +7102,7 @@
       <c r="B323" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C323" s="5" t="s">
+      <c r="C323" s="4" t="s">
         <v>644</v>
       </c>
     </row>
@@ -6780,7 +7113,7 @@
       <c r="B324" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C324" s="5" t="s">
+      <c r="C324" s="4" t="s">
         <v>646</v>
       </c>
     </row>
@@ -6791,7 +7124,7 @@
       <c r="B325" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C325" s="5" t="s">
+      <c r="C325" s="4" t="s">
         <v>648</v>
       </c>
     </row>
@@ -6802,7 +7135,7 @@
       <c r="B326" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C326" s="5" t="s">
+      <c r="C326" s="4" t="s">
         <v>650</v>
       </c>
     </row>
@@ -6813,7 +7146,7 @@
       <c r="B327" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C327" s="5" t="s">
+      <c r="C327" s="4" t="s">
         <v>652</v>
       </c>
     </row>
@@ -6824,7 +7157,7 @@
       <c r="B328" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C328" s="5" t="s">
+      <c r="C328" s="4" t="s">
         <v>654</v>
       </c>
     </row>
@@ -6835,7 +7168,7 @@
       <c r="B329" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C329" s="5" t="s">
+      <c r="C329" s="4" t="s">
         <v>656</v>
       </c>
     </row>
@@ -6846,7 +7179,7 @@
       <c r="B330" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="C330" s="5" t="s">
+      <c r="C330" s="4" t="s">
         <v>658</v>
       </c>
     </row>
@@ -6857,7 +7190,7 @@
       <c r="B331" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C331" s="5" t="s">
+      <c r="C331" s="4" t="s">
         <v>660</v>
       </c>
     </row>
@@ -6868,7 +7201,7 @@
       <c r="B332" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C332" s="5" t="s">
+      <c r="C332" s="4" t="s">
         <v>662</v>
       </c>
     </row>
@@ -6879,7 +7212,7 @@
       <c r="B333" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C333" s="5" t="s">
+      <c r="C333" s="4" t="s">
         <v>664</v>
       </c>
     </row>
@@ -6890,7 +7223,7 @@
       <c r="B334" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C334" s="5" t="s">
+      <c r="C334" s="4" t="s">
         <v>666</v>
       </c>
     </row>
@@ -6901,7 +7234,7 @@
       <c r="B335" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C335" s="5" t="s">
+      <c r="C335" s="4" t="s">
         <v>668</v>
       </c>
     </row>
@@ -6912,7 +7245,7 @@
       <c r="B336" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C336" s="5" t="s">
+      <c r="C336" s="4" t="s">
         <v>670</v>
       </c>
     </row>
@@ -6923,7 +7256,7 @@
       <c r="B337" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C337" s="5" t="s">
+      <c r="C337" s="4" t="s">
         <v>672</v>
       </c>
     </row>
@@ -6934,7 +7267,7 @@
       <c r="B338" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C338" s="5" t="s">
+      <c r="C338" s="4" t="s">
         <v>674</v>
       </c>
     </row>
@@ -6945,7 +7278,7 @@
       <c r="B339" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C339" s="5" t="s">
+      <c r="C339" s="4" t="s">
         <v>676</v>
       </c>
     </row>
@@ -6956,7 +7289,7 @@
       <c r="B340" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="C340" s="5" t="s">
+      <c r="C340" s="4" t="s">
         <v>678</v>
       </c>
     </row>
@@ -6967,7 +7300,7 @@
       <c r="B341" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C341" s="5" t="s">
+      <c r="C341" s="4" t="s">
         <v>680</v>
       </c>
     </row>
@@ -6978,7 +7311,7 @@
       <c r="B342" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C342" s="5" t="s">
+      <c r="C342" s="4" t="s">
         <v>682</v>
       </c>
     </row>
@@ -6989,7 +7322,7 @@
       <c r="B343" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="C343" s="5" t="s">
+      <c r="C343" s="4" t="s">
         <v>684</v>
       </c>
     </row>
@@ -7000,7 +7333,7 @@
       <c r="B344" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C344" s="5" t="s">
+      <c r="C344" s="4" t="s">
         <v>686</v>
       </c>
     </row>
@@ -7011,7 +7344,7 @@
       <c r="B345" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="C345" s="5" t="s">
+      <c r="C345" s="4" t="s">
         <v>688</v>
       </c>
     </row>
@@ -7022,7 +7355,7 @@
       <c r="B346" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C346" s="5" t="s">
+      <c r="C346" s="4" t="s">
         <v>690</v>
       </c>
     </row>
@@ -7033,7 +7366,7 @@
       <c r="B347" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="C347" s="5" t="s">
+      <c r="C347" s="4" t="s">
         <v>692</v>
       </c>
     </row>
@@ -7044,7 +7377,7 @@
       <c r="B348" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="C348" s="5" t="s">
+      <c r="C348" s="4" t="s">
         <v>694</v>
       </c>
     </row>
@@ -7055,7 +7388,7 @@
       <c r="B349" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C349" s="5" t="s">
+      <c r="C349" s="4" t="s">
         <v>696</v>
       </c>
     </row>
@@ -7066,7 +7399,7 @@
       <c r="B350" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="C350" s="5" t="s">
+      <c r="C350" s="4" t="s">
         <v>698</v>
       </c>
     </row>
@@ -7077,7 +7410,7 @@
       <c r="B351" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C351" s="5" t="s">
+      <c r="C351" s="4" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7088,7 +7421,7 @@
       <c r="B352" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="C352" s="5" t="s">
+      <c r="C352" s="4" t="s">
         <v>702</v>
       </c>
     </row>
@@ -7099,7 +7432,7 @@
       <c r="B353" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C353" s="5" t="s">
+      <c r="C353" s="4" t="s">
         <v>704</v>
       </c>
     </row>
@@ -7110,7 +7443,7 @@
       <c r="B354" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C354" s="5" t="s">
+      <c r="C354" s="4" t="s">
         <v>706</v>
       </c>
     </row>
@@ -7121,7 +7454,7 @@
       <c r="B355" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C355" s="5" t="s">
+      <c r="C355" s="4" t="s">
         <v>708</v>
       </c>
     </row>
@@ -7132,7 +7465,7 @@
       <c r="B356" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C356" s="5" t="s">
+      <c r="C356" s="4" t="s">
         <v>710</v>
       </c>
     </row>
@@ -7143,7 +7476,7 @@
       <c r="B357" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C357" s="5" t="s">
+      <c r="C357" s="4" t="s">
         <v>712</v>
       </c>
     </row>
@@ -7154,7 +7487,7 @@
       <c r="B358" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="C358" s="5" t="s">
+      <c r="C358" s="4" t="s">
         <v>714</v>
       </c>
     </row>
@@ -7165,7 +7498,7 @@
       <c r="B359" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="C359" s="5" t="s">
+      <c r="C359" s="4" t="s">
         <v>716</v>
       </c>
     </row>
@@ -7176,7 +7509,7 @@
       <c r="B360" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C360" s="5" t="s">
+      <c r="C360" s="4" t="s">
         <v>718</v>
       </c>
     </row>
@@ -7187,7 +7520,7 @@
       <c r="B361" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="C361" s="5" t="s">
+      <c r="C361" s="4" t="s">
         <v>720</v>
       </c>
     </row>
@@ -7198,7 +7531,7 @@
       <c r="B362" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="C362" s="5" t="s">
+      <c r="C362" s="4" t="s">
         <v>722</v>
       </c>
     </row>
@@ -7209,7 +7542,7 @@
       <c r="B363" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C363" s="5" t="s">
+      <c r="C363" s="4" t="s">
         <v>724</v>
       </c>
     </row>
@@ -7220,7 +7553,7 @@
       <c r="B364" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="C364" s="5" t="s">
+      <c r="C364" s="4" t="s">
         <v>726</v>
       </c>
     </row>
@@ -7231,7 +7564,7 @@
       <c r="B365" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C365" s="5" t="s">
+      <c r="C365" s="4" t="s">
         <v>728</v>
       </c>
     </row>
@@ -7242,7 +7575,7 @@
       <c r="B366" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="C366" s="5" t="s">
+      <c r="C366" s="4" t="s">
         <v>730</v>
       </c>
     </row>
@@ -7253,7 +7586,7 @@
       <c r="B367" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C367" s="5" t="s">
+      <c r="C367" s="4" t="s">
         <v>732</v>
       </c>
     </row>
@@ -7264,7 +7597,7 @@
       <c r="B368" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C368" s="5" t="s">
+      <c r="C368" s="4" t="s">
         <v>734</v>
       </c>
     </row>
@@ -7275,7 +7608,7 @@
       <c r="B369" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="C369" s="5" t="s">
+      <c r="C369" s="4" t="s">
         <v>736</v>
       </c>
     </row>
@@ -7286,7 +7619,7 @@
       <c r="B370" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C370" s="5" t="s">
+      <c r="C370" s="4" t="s">
         <v>738</v>
       </c>
     </row>
@@ -7297,7 +7630,7 @@
       <c r="B371" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C371" s="5" t="s">
+      <c r="C371" s="4" t="s">
         <v>740</v>
       </c>
     </row>
@@ -7308,7 +7641,7 @@
       <c r="B372" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C372" s="5" t="s">
+      <c r="C372" s="4" t="s">
         <v>742</v>
       </c>
     </row>
@@ -7319,7 +7652,7 @@
       <c r="B373" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C373" s="5" t="s">
+      <c r="C373" s="4" t="s">
         <v>744</v>
       </c>
     </row>
@@ -7330,7 +7663,7 @@
       <c r="B374" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="C374" s="5" t="s">
+      <c r="C374" s="4" t="s">
         <v>746</v>
       </c>
     </row>
@@ -7341,7 +7674,7 @@
       <c r="B375" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C375" s="5" t="s">
+      <c r="C375" s="4" t="s">
         <v>748</v>
       </c>
     </row>
@@ -7352,7 +7685,7 @@
       <c r="B376" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="C376" s="5" t="s">
+      <c r="C376" s="4" t="s">
         <v>750</v>
       </c>
     </row>
@@ -7363,7 +7696,7 @@
       <c r="B377" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C377" s="5" t="s">
+      <c r="C377" s="4" t="s">
         <v>752</v>
       </c>
     </row>
@@ -7374,7 +7707,7 @@
       <c r="B378" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C378" s="5" t="s">
+      <c r="C378" s="4" t="s">
         <v>754</v>
       </c>
     </row>
@@ -7385,7 +7718,7 @@
       <c r="B379" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="C379" s="5" t="s">
+      <c r="C379" s="4" t="s">
         <v>756</v>
       </c>
     </row>
@@ -7396,7 +7729,7 @@
       <c r="B380" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="C380" s="5" t="s">
+      <c r="C380" s="4" t="s">
         <v>758</v>
       </c>
     </row>
@@ -7407,7 +7740,7 @@
       <c r="B381" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C381" s="5" t="s">
+      <c r="C381" s="4" t="s">
         <v>760</v>
       </c>
     </row>
@@ -7418,7 +7751,7 @@
       <c r="B382" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="C382" s="5" t="s">
+      <c r="C382" s="4" t="s">
         <v>762</v>
       </c>
     </row>
@@ -7429,7 +7762,7 @@
       <c r="B383" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C383" s="5" t="s">
+      <c r="C383" s="4" t="s">
         <v>764</v>
       </c>
     </row>
@@ -7440,7 +7773,7 @@
       <c r="B384" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="C384" s="5" t="s">
+      <c r="C384" s="4" t="s">
         <v>766</v>
       </c>
     </row>
@@ -7451,7 +7784,7 @@
       <c r="B385" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="C385" s="5" t="s">
+      <c r="C385" s="4" t="s">
         <v>768</v>
       </c>
     </row>
@@ -7462,7 +7795,7 @@
       <c r="B386" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="C386" s="5" t="s">
+      <c r="C386" s="4" t="s">
         <v>770</v>
       </c>
     </row>
@@ -7473,941 +7806,1274 @@
       <c r="B387" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C387" s="5" t="s">
+      <c r="C387" s="4" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2" t="n">
         <v>387</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C388" s="5" t="s">
+      <c r="C388" s="4" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2" t="n">
         <v>388</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="C389" s="5" t="s">
+      <c r="C389" s="4" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2" t="n">
         <v>389</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="C390" s="5" t="s">
+      <c r="C390" s="4" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2" t="n">
         <v>390</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="C391" s="5" t="s">
+      <c r="C391" s="4" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2" t="n">
         <v>391</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C392" s="5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="2" t="n">
         <v>392</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>783</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="2" t="n">
         <v>393</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+      <c r="C394" s="5" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="n">
         <v>394</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>787</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2" t="n">
         <v>395</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>789</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2" t="n">
         <v>396</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>791</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2" t="n">
         <v>397</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>793</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2" t="n">
         <v>398</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>795</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2" t="n">
         <v>399</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>797</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2" t="n">
         <v>400</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>799</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="n">
         <v>401</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>801</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2" t="n">
         <v>402</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>803</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2" t="n">
         <v>403</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>805</v>
+      </c>
+      <c r="C404" s="5" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2" t="n">
         <v>404</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>807</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2" t="n">
         <v>405</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>809</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2" t="n">
         <v>406</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>811</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2" t="n">
         <v>407</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>813</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="n">
         <v>408</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>815</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2" t="n">
         <v>409</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>817</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2" t="n">
         <v>410</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>819</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2" t="n">
         <v>411</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>821</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2" t="n">
         <v>412</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>823</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2" t="n">
         <v>413</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>825</v>
+      </c>
+      <c r="C414" s="5" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2" t="n">
         <v>414</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>827</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2" t="n">
         <v>415</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>829</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2" t="n">
         <v>416</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>831</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2" t="n">
         <v>417</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>833</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2" t="n">
         <v>418</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>835</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2" t="n">
         <v>419</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>837</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="2" t="n">
         <v>420</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>839</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="n">
         <v>421</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>841</v>
+      </c>
+      <c r="C422" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2" t="n">
         <v>422</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>843</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2" t="n">
         <v>423</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>845</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="n">
         <v>424</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>847</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="n">
         <v>425</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>849</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2" t="n">
         <v>426</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>851</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2" t="n">
         <v>427</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>853</v>
+      </c>
+      <c r="C428" s="5" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2" t="n">
         <v>428</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>855</v>
+      </c>
+      <c r="C429" s="5" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2" t="n">
         <v>429</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>857</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2" t="n">
         <v>430</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>859</v>
+      </c>
+      <c r="C431" s="5" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="n">
         <v>431</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>861</v>
+      </c>
+      <c r="C432" s="5" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="n">
         <v>432</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>863</v>
+      </c>
+      <c r="C433" s="5" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2" t="n">
         <v>433</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>865</v>
+      </c>
+      <c r="C434" s="5" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="n">
         <v>434</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>867</v>
+      </c>
+      <c r="C435" s="5" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2" t="n">
         <v>435</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>869</v>
+      </c>
+      <c r="C436" s="5" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="n">
         <v>436</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>871</v>
+      </c>
+      <c r="C437" s="5" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2" t="n">
         <v>437</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>873</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2" t="n">
         <v>438</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>875</v>
+      </c>
+      <c r="C439" s="5" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2" t="n">
         <v>439</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>877</v>
+      </c>
+      <c r="C440" s="5" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2" t="n">
         <v>440</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>879</v>
+      </c>
+      <c r="C441" s="5" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2" t="n">
         <v>441</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>881</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2" t="n">
         <v>442</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>883</v>
+      </c>
+      <c r="C443" s="5" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2" t="n">
         <v>443</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>885</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2" t="n">
         <v>444</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>887</v>
+      </c>
+      <c r="C445" s="5" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2" t="n">
         <v>445</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>889</v>
+      </c>
+      <c r="C446" s="5" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2" t="n">
         <v>446</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>891</v>
+      </c>
+      <c r="C447" s="5" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="n">
         <v>447</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>893</v>
+      </c>
+      <c r="C448" s="5" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2" t="n">
         <v>448</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>895</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2" t="n">
         <v>449</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>897</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2" t="n">
         <v>450</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>899</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="n">
         <v>451</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>901</v>
+      </c>
+      <c r="C452" s="5" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="n">
         <v>452</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>903</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="n">
         <v>453</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>905</v>
+      </c>
+      <c r="C454" s="5" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="n">
         <v>454</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>907</v>
+      </c>
+      <c r="C455" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="n">
         <v>455</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>909</v>
+      </c>
+      <c r="C456" s="5" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="n">
         <v>456</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>911</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2" t="n">
         <v>457</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>913</v>
+      </c>
+      <c r="C458" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2" t="n">
         <v>458</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>915</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2" t="n">
         <v>459</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>917</v>
+      </c>
+      <c r="C460" s="5" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="2" t="n">
         <v>460</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>919</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2" t="n">
         <v>461</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>921</v>
+      </c>
+      <c r="C462" s="5" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2" t="n">
         <v>462</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>923</v>
+      </c>
+      <c r="C463" s="5" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2" t="n">
         <v>463</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>925</v>
+      </c>
+      <c r="C464" s="5" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2" t="n">
         <v>464</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>927</v>
+      </c>
+      <c r="C465" s="5" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2" t="n">
         <v>465</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>929</v>
+      </c>
+      <c r="C466" s="5" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2" t="n">
         <v>466</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>931</v>
+      </c>
+      <c r="C467" s="5" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2" t="n">
         <v>467</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>933</v>
+      </c>
+      <c r="C468" s="5" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2" t="n">
         <v>468</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>935</v>
+      </c>
+      <c r="C469" s="5" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2" t="n">
         <v>469</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>937</v>
+      </c>
+      <c r="C470" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2" t="n">
         <v>470</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>939</v>
+      </c>
+      <c r="C471" s="5" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2" t="n">
         <v>471</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>941</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="n">
         <v>472</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>943</v>
+      </c>
+      <c r="C473" s="5" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2" t="n">
         <v>473</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>945</v>
+      </c>
+      <c r="C474" s="5" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="n">
         <v>474</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>947</v>
+      </c>
+      <c r="C475" s="5" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="n">
         <v>475</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>949</v>
+      </c>
+      <c r="C476" s="5" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2" t="n">
         <v>476</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>951</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2" t="n">
         <v>477</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>953</v>
+      </c>
+      <c r="C478" s="5" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2" t="n">
         <v>478</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>955</v>
+      </c>
+      <c r="C479" s="5" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="2" t="n">
         <v>479</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>957</v>
+      </c>
+      <c r="C480" s="5" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="n">
         <v>480</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>959</v>
+      </c>
+      <c r="C481" s="5" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2" t="n">
         <v>481</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>961</v>
+      </c>
+      <c r="C482" s="5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2" t="n">
         <v>482</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>963</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2" t="n">
         <v>483</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>965</v>
+      </c>
+      <c r="C484" s="5" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2" t="n">
         <v>484</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>967</v>
+      </c>
+      <c r="C485" s="5" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2" t="n">
         <v>485</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>969</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2" t="n">
         <v>486</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>971</v>
+      </c>
+      <c r="C487" s="5" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="2" t="n">
         <v>487</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>973</v>
+      </c>
+      <c r="C488" s="5" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="2" t="n">
         <v>488</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>975</v>
+      </c>
+      <c r="C489" s="5" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2" t="n">
         <v>489</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>977</v>
+      </c>
+      <c r="C490" s="5" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2" t="n">
         <v>490</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>979</v>
+      </c>
+      <c r="C491" s="5" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2" t="n">
         <v>491</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>981</v>
+      </c>
+      <c r="C492" s="5" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2" t="n">
         <v>492</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>983</v>
+      </c>
+      <c r="C493" s="5" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2" t="n">
         <v>493</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>985</v>
+      </c>
+      <c r="C494" s="5" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2" t="n">
         <v>494</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>987</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2" t="n">
         <v>495</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>989</v>
+      </c>
+      <c r="C496" s="5" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="n">
         <v>496</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>991</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2" t="n">
         <v>497</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>993</v>
+      </c>
+      <c r="C498" s="5" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="2" t="n">
         <v>498</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>995</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="2" t="n">
         <v>499</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>997</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2" t="n">
         <v>500</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>890</v>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C502" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normalny"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normalny"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/Sentences/prepared_sentences_m.xlsx
+++ b/Sentences/prepared_sentences_m.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="891">
   <si>
     <t xml:space="preserve">Indeks zadnia </t>
   </si>
@@ -2368,661 +2368,331 @@
     <t xml:space="preserve">Chcę wiedzieć, dlaczego nie masz pieniędzy na książkę.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, CHCIEĆ, WIEDZIEĆ, DLACZEGO, TY, NIE, MIEĆ, PIENIĄDZE, NA, KSIĄŻKA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pamiętaj, żeby uczyć się w domu w dzień.</t>
   </si>
   <si>
-    <t xml:space="preserve">PAMIĘTAJ, DZIEŃ, UCZYĆ-SIĘ, W, DOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ty zawsze masz czas, żeby pić ze mną herbatę.</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, ZAWSZE, MIEĆ, CZAS, PIĆ, ZE-MNĄ, HERBATA</t>
-  </si>
-  <si>
     <t xml:space="preserve">W nocy słyszałem, jak ten kot dużo pije.</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC, JA, SŁYSZEĆ, TEN, KOT, DUŻO, PIĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jesteś dzisiaj zmęczony, bo wczoraj dużo pracowałeś.</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, DZISIAJ, ZMĘCZONY, BO, WCZORAJ, DUŻO, PRACOWAĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mój tata nie lubi, kiedy pije gorącą wodę.</t>
   </si>
   <si>
-    <t xml:space="preserve">MÓJ, TATA, LUBIĆ-NIE, KIEDY, PIĆ, WODA, GORĄCA</t>
-  </si>
-  <si>
     <t xml:space="preserve">My bardzo często pijemy kawę u twojej siostry.</t>
   </si>
   <si>
-    <t xml:space="preserve">MY, CZĘSTO, PIĆ, KAWA, U, TWOJA, SIOSTRA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dlaczego ta mała książka jest dla ciebie ważna?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, KSIĄŻKA, MAŁA, TA, DLA-CIEBIE, WAŻNA?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gdzie wczoraj uczyłeś się migać z moim bratem?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, WCZORAJ, TY, UCZYĆ-SIĘ, MIGAĆ, Z, MOIM, BRAT?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chcę kupić stary dom z dużym psem.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, CHCIEĆ, KUPIĆ, DOM, STARY, Z, PIES, DUŻY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nie rozumiem, o czym ty do mnie rano mówiłeś.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, ROZUMIEĆ-NIE, RANO, TY, DO-MNIE, MÓWIĆ, O-CZYM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dzisiaj nie mogę iść do pracy, bo chory brat jest w domu.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZISIAJ, JA, IŚĆ, PRACA, NIE-MOGĘ, BO, BRAT, CHORY, DOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czekam na moje pieniądze od poniedziałku.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, CZEKAĆ, NA, MOJE, PIENIĄDZE, OD, PONIEDZIAŁEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wczoraj wieczorem widziałem, jak twój kolega pije kawę.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, WIDZIEĆ, TWÓJ, KOLEGA, PIĆ, KAWA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Babcia lubi, żeby kot spał rano pod domem.</t>
   </si>
   <si>
-    <t xml:space="preserve">BABCIA, LUBIĆ, ŻEBY, KOT, RANO, SPAĆ, POD, DOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ten czas był dla mojego przyjaciela bardzo dobry.</t>
   </si>
   <si>
-    <t xml:space="preserve">TEN, CZAS, DLA, MÓJ, PRZYJACIEL, BARDZO, DOBRY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kocham ten wesoły dzień w szkole z moim bratem.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, KOCHAĆ, TEN, DZIEŃ, WESOŁY, W, SZKOŁA, Z, MOIM, BRAT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dlaczego nie pamiętasz o moich urodzinach w poniedziałek?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, TY, PAMIĘTAĆ-NIE, O, MOJE, URODZINY, PONIEDZIAŁEK?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Siostra jest często zmęczona.</t>
   </si>
   <si>
-    <t xml:space="preserve">SIOSTRA, CZĘSTO, ZMĘCZONA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Niech ta kobieta zostanie u ciebie na herbatę.</t>
   </si>
   <si>
-    <t xml:space="preserve">NIECH, KOBIETA, TA, ZOSTAĆ, U-CIEBIE, NA, HERBATA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zawsze rano dziękuję tacie za dobrą pracę.</t>
   </si>
   <si>
-    <t xml:space="preserve">ZAWSZE, RANO, JA, DZIĘKOWAĆ, TATA, ZA, PRACA, DOBRA</t>
-  </si>
-  <si>
     <t xml:space="preserve">W nocy mój dziadek nie słyszy, co babcia mówi.</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC, MÓJ, DZIADEK, SŁYSZEĆ-NIE, BABCIA, MÓWIĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do pracy z psem?</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, KTO, MIEĆ, POMYSŁ, IŚĆ, PRACA, Z, PIES?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Twój telefon był wczoraj rano w moim starym samochodzie.</t>
   </si>
   <si>
-    <t xml:space="preserve">TWÓJ, TELEFON, WCZORAJ, RANO, BYĆ, W, MÓJ, SAMOCHÓD, STARY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nie mam klucza, żeby być rano w domu u dziadka.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, NIE, MIEĆ, KLUCZ, ŻEBY, RANO, BYĆ, U, DZIADEK, DOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ja będę na ciebie czekać z gorącą wodą rano.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, BĘDĘ, CZEKAĆ-NA-CIEBIE, Z, WODA, GORĄCA, RANO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mama musi teraz jeść.</t>
   </si>
   <si>
-    <t xml:space="preserve">MAMA, TERAZ, MUSI, JEŚĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gdzie jest woda dla mojego nowego psa i kota?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, WODA, DLA, MÓJ, PIES, NOWY, I, KOT?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wczoraj w nocy myślałem, co dzisiaj robić w szkole.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, NOC, JA, MYŚLEĆ, DZISIAJ, SZKOŁA, ROBIĆ-CO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jutro rano kupię dla ciebie ten stary samochód taty.</t>
   </si>
   <si>
-    <t xml:space="preserve">JUTRO, RANO, JA, KUPIĆ, DLA-CIEBIE, TATA, SAMOCHÓD, STARY, TEN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czy twój przyjaciel ma czas na kawę po pracy?</t>
   </si>
   <si>
-    <t xml:space="preserve">TWÓJ, PRZYJACIEL, MIEĆ, CZAS, NA, KAWA, PO, PRACA?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Będziemy uczyć się migać o mojej starej pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">MY, UCZYĆ-SIĘ, MIGAĆ, O, MOJA, PRACA, STARA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zostań z bratem w domu, bo on jest smutny.</t>
   </si>
   <si>
-    <t xml:space="preserve">ZOSTAŃ, Z, BRAT, W, DOM, BO, ON, SMUTNY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ja i ty musimy dużo pić, żeby nie być zmęczonymi.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, TY, MUSIEĆ, PIĆ, DUŻO, ŻEBY, ZMĘCZENI-NIE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mój nowy dom w poniedziałek rano jest bardzo zimny.</t>
   </si>
   <si>
-    <t xml:space="preserve">MÓJ, DOM, NOWY, PONIEDZIAŁEK, RANO, BARDZO, ZIMNY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dlaczego ten stary kot zawsze dużo je u babci?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, KOT, STARY, TEN, ZAWSZE, DUŻO, JEŚĆ, U, BABCIA?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mężczyzna czekał rano z psem, żeby iść do pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">MĘŻCZYZNA, CZEKAĆ, RANO, Z, PIES, ŻEBY, IŚĆ, PRACA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Przepraszam, że wczoraj rano kupiłem ten nowy telefon.</t>
   </si>
   <si>
-    <t xml:space="preserve">PRZEPRASZAM, WCZORAJ, RANO, JA, KUPIĆ, TELEFON, NOWY, TEN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Często słyszę mojego psa rano, kiedy idę do pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">CZĘSTO, JA, SŁYSZEĆ, MÓJ, PIES, RANO, KIEDY, IŚĆ, PRACA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wczoraj wieczorem byłem z małym psem w starym domu dziadka.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, BYĆ, Z, PIES, MAŁY, W, DOM, STARY, DZIADEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">My chcemy dużo spać, żeby nie być chorym rano.</t>
   </si>
   <si>
-    <t xml:space="preserve">MY, CHCIEĆ, DUŻO, SPAĆ, ŻEBY, RANO, CHORY-NIE</t>
-  </si>
-  <si>
     <t xml:space="preserve">No to ile będziesz to robić? </t>
   </si>
   <si>
-    <t xml:space="preserve">NO-TO, TY, BĘDZIESZ, TO, ROBIĆ, ILE?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Niech mój przyjaciel czeka na ciebie rano u dziadka.</t>
   </si>
   <si>
-    <t xml:space="preserve">NIECH, MÓJ, PRZYJACIEL, CZEKAĆ-NA-CIEBIE, RANO, U, DZIADEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czy to jest środa, czy czwartek?</t>
   </si>
   <si>
-    <t xml:space="preserve">TO, ŚRODA, CZY, CZWARTEK?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Twój wesoły tata wczoraj pił z moim dziadkiem wodę.</t>
   </si>
   <si>
-    <t xml:space="preserve">TWÓJ, TATA, WESOŁY, WCZORAJ, PIĆ, WODA, Z, MOIM, DZIADEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">My chcemy wiedzieć, gdzie wczoraj był twój samochód rano.</t>
   </si>
   <si>
-    <t xml:space="preserve">MY, CHCIEĆ, WIEDZIEĆ, GDZIE, WCZORAJ, RANO, TWÓJ, SAMOCHÓD, BYĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jutro w nocy będę spać u brata z psem.</t>
   </si>
   <si>
-    <t xml:space="preserve">JUTRO, NOC, JA, SPAĆ, U, BRAT, Z, PIES</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kiedy kupisz dla mnie tę książkę o starym domu?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, KUPIĆ, DLA-MNIE, KSIĄŻKA, O, DOM, STARY, KIEDY?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ja bardzo lubię pić z tobą dobrą gorącą herbatę.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, BARDZO, LUBIĆ, PIĆ, Z-TOBĄ, HERBATA, DOBRA, GORĄCA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gdzie my wczoraj widzieliśmy ten stary samochód mojego przyjaciela?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, MY, WCZORAJ, WIDZIEĆ, SAMOCHÓD, STARY, MÓJ, PRZYJACIEL?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Przepraszam, ale to był taki ważny rok, czy wy to teraz rozumiecie?</t>
   </si>
   <si>
-    <t xml:space="preserve">PRZEPRASZAM, ALE, TEN, ROK, BARDZO, WAŻNY, WY, TERAZ, ROZUMIEĆ?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mój dziadek w poniedziałek wieczorem był zmęczony i smutny.</t>
   </si>
   <si>
-    <t xml:space="preserve">MÓJ, DZIADEK, PONIEDZIAŁEK, WIECZÓR, ZMĘCZONY, I, SMUTNY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nie mogę dzisiaj iść po kawę z moim nowym przyjacielem.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, DZISIAJ, IŚĆ, KAWA, Z, MÓJ, PRZYJACIEL, NOWY, NIE-MOGĘ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Babcia i dziadek dzisiaj rano pili ze mną wodę.</t>
   </si>
   <si>
-    <t xml:space="preserve">BABCIA, DZIADEK, DZISIAJ, RANO, PIĆ, ZE-MNĄ, WODA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Twój brat zawsze bardzo lubi mówić rano o pracy w środę?</t>
   </si>
   <si>
-    <t xml:space="preserve">TWÓJ, BRAT, ZAWSZE, BARDZO, LUBIĆ, RANO, MÓWIĆ, O, PRACA, ŚRODA?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ile to było robione? </t>
   </si>
   <si>
-    <t xml:space="preserve">TO, ROBIĆ, BYŁO, ILE?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pamiętam, żeby pić zimną wodę w gorący dzień.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, PAMIĘTAĆ, PIĆ, WODA, ZIMNA, W, DZIEŃ, GORĄCY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jutro rano idę z małym psem do ciebie po klucz.</t>
   </si>
   <si>
-    <t xml:space="preserve">JUTRO, RANO, JA, IŚĆ, Z, PIES, MAŁY, DO-CIEBIE, PO, KLUCZ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ty nie pamiętasz, dlaczego wczoraj byłem u ciebie z bratem.</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, PAMIĘTAĆ-NIE, DLACZEGO, WCZORAJ, JA, BYĆ, U-CIEBIE, Z, BRAT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ile kawy dzisiaj pijesz, żeby mieć na to czas?</t>
   </si>
   <si>
-    <t xml:space="preserve">DZISIAJ, TY, PIĆ, KAWA, ILE, ŻEBY, MIEĆ, CZAS, NA-TO?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kto wesoły i zdrowy idzie z moim bratem do starej szkoły?</t>
   </si>
   <si>
-    <t xml:space="preserve">KTO, WESOŁY, ZDROWY, IŚĆ, Z, MOIM, BRAT, DO, SZKOŁA, STARA?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mój stary pies ma dzisiaj urodziny rano.</t>
   </si>
   <si>
-    <t xml:space="preserve">MÓJ, PIES, STARY, DZISIAJ, RANO, URODZINY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czekam rano przed twoim nowym domem z gorącą herbatą.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, CZEKAĆ, RANO, PRZED, TWÓJ, DOM, NOWY, Z, HERBATA, GORĄCA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dzisiaj rano chcę uczyć się migać z twoją babcią.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZISIAJ, RANO, JA, CHCIEĆ, UCZYĆ-SIĘ, MIGAĆ, Z, TWOJA, BABCIA</t>
-  </si>
-  <si>
     <t xml:space="preserve">To było we wtorek i w środę, teraz już to rozumiem, to był taki ważny rok. </t>
   </si>
   <si>
-    <t xml:space="preserve">TO, BYĆ, WTOREK, I, ŚRODA, TERAZ, JA, ROZUMIEĆ, —, TEN, ROK, WAŻNY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czy wy się teraz kochacie, czy to już taki nowy pomysł na ten czwartek? </t>
   </si>
   <si>
-    <t xml:space="preserve">WY, TERAZ, KOCHAĆ-SIĘ, CZY, TO, POMYSŁ, NOWY, NA, CZWARTEK?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dziadek nie słyszy, kiedy babcia mówi do kota.</t>
   </si>
   <si>
-    <t xml:space="preserve">DZIADEK, SŁYSZEĆ-NIE, KIEDY, BABCIA, MÓWIĆ, DO, KOT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wczoraj w nocy myślałem o tej książce z moim bratem.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, NOC, JA, MYŚLEĆ, O, KSIĄŻKA, TA, Z, MOIM, BRAT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zostań rano w domu u dziadka, bo jesteś bardzo chory.</t>
   </si>
   <si>
-    <t xml:space="preserve">RANO, ZOSTAŃ, U, DZIADEK, DOM, BO, TY, BARDZO, CHORY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nie mam rano klucza od twojego starego samochodu.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, NIE, MIEĆ, RANO, KLUCZ, OD, TWOJEGO, SAMOCHÓD, STARY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czy wiesz, co ten duży pies jadł w poniedziałek?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, WIEDZIEĆ, CO, PIES, DUŻY, TEN, JEŚĆ, PONIEDZIAŁEK?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kocham ten czas rano, kiedy kot śpi u mnie.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, KOCHAĆ, TEN, CZAS, RANO, KIEDY, KOT, SPAĆ, U-MNIE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wczoraj wieczorem widziałem mojego psa przed szkołą.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, WIECZÓR, JA, WIDZIEĆ, MÓJ, PIES, PRZED, SZKOŁA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pamiętam, żeby dużo pracować i mieć pieniądze na nowy dom.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, PAMIĘTAĆ:, DUŻO, PRACOWAĆ, PIENIĄDZE, MIEĆ, NA, DOM, NOWY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ten bardzo smutny mężczyzna nie lubi pić ze mną kawy.</t>
   </si>
   <si>
-    <t xml:space="preserve">TEN, MĘŻCZYZNA, BARDZO, SMUTNY, LUBIĆ-NIE, PIĆ, ZE-MNĄ, KAWA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gdzie wczoraj kupiłeś tę książkę dla przyjaciela?</t>
   </si>
   <si>
-    <t xml:space="preserve">GDZIE, WCZORAJ, TY, KUPIĆ, KSIĄŻKA, DLA, PRZYJACIEL?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mój tata bardzo kocha rano pić herbatę z wesołym psem.</t>
   </si>
   <si>
-    <t xml:space="preserve">MÓJ, TATA, BARDZO, KOCHAĆ, RANO, PIĆ, HERBATA, Z, PIES, WESOŁY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zawsze chcę być z tobą rano u ciebie w pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">ZAWSZE, JA, CHCIEĆ, BYĆ, Z-TOBĄ, RANO, U-CIEBIE, PRACA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Twój pomysł na urodziny brata w poniedziałek jest bardzo dobry.</t>
   </si>
   <si>
-    <t xml:space="preserve">TWÓJ, POMYSŁ, NA, URODZINY, BRAT, PONIEDZIAŁEK, BARDZO, DOBRY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Niech kot zostanie u ciebie z moim starym tatą.</t>
   </si>
   <si>
-    <t xml:space="preserve">NIECH, KOT, ZOSTAĆ, U-CIEBIE, Z, MOIM, TATA, STARY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kto wczoraj miał pomysł, żeby iść do nowej szkoły rano?</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, KTO, MIEĆ, POMYSŁ, IŚĆ, RANO, DO, SZKOŁA, NOWA?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wczoraj rano mój tata kupił ten stary dom.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, RANO, MÓJ, TATA, KUPIĆ, DOM, STARY, TEN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dlaczego zawsze pijesz gorącą wodę z mamą?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, TY, ZAWSZE, PIĆ, WODA, GORĄCA, Z, MAMA?</t>
-  </si>
-  <si>
     <t xml:space="preserve">We wtorek rano mój brat musi iść do pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">WTOREK, RANO, MÓJ, BRAT, MUSI, IŚĆ, PRACA</t>
-  </si>
-  <si>
     <t xml:space="preserve">W środę ja i ty chcemy kupić nowy dom, który będzie dla nas ważny </t>
   </si>
   <si>
-    <t xml:space="preserve">ŚRODA, JA, TY, CHCIEĆ, KUPIĆ, DOM, NOWY, DLA-NAS, WAŻNY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Czy w czwartek twój pies był chory i kto mu pomógł? </t>
   </si>
   <si>
-    <t xml:space="preserve">CZWARTEK, TWÓJ, PIES, CHORY, BYŁ?, KTO, POMÓC-MU?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dlaczego we wtorek zawsze jesteś smutny?</t>
   </si>
   <si>
-    <t xml:space="preserve">DLACZEGO, WTOREK, TY, ZAWSZE, SMUTNY?</t>
-  </si>
-  <si>
     <t xml:space="preserve">W środę wieczorem dziadek pije gorącą herbatę, bo kocha ten zdrowy pomysł. </t>
   </si>
   <si>
-    <t xml:space="preserve">ŚRODA, WIECZÓR, DZIADEK, PIĆ, HERBATA, GORĄCA, BO, KOCHAĆ, TEN, POMYSŁ, ZDROWY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Już pamiętam że mój przyjaciel ma urodziny w czwartek</t>
   </si>
   <si>
-    <t xml:space="preserve">JUŻ, PAMIĘTAĆ:, MÓJ, PRZYJACIEL, URODZINY, CZWARTEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wczoraj był poniedziałek, a dzisiaj jest wtorek.</t>
   </si>
   <si>
-    <t xml:space="preserve">WCZORAJ, PONIEDZIAŁEK, DZISIAJ, WTOREK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kto musi pracować w środę w nocy?</t>
   </si>
   <si>
-    <t xml:space="preserve">KTO, MUSI, ŚRODA, NOC, PRACOWAĆ?</t>
-  </si>
-  <si>
     <t xml:space="preserve">W czwartek rano babcia czeka na mój telefon.</t>
   </si>
   <si>
-    <t xml:space="preserve">CZWARTEK, RANO, BABCIA, CZEKAĆ, NA, MÓJ, TELEFON</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kobieta i mężczyzna idą do szkoły we wtorek.</t>
   </si>
   <si>
-    <t xml:space="preserve">KOBIETA, PLUS, MĘŻCZYZNA, IŚĆ, SZKOŁA, WTOREK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ja wiem, że w środę będę bardzo zmęczony.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, WIEDZIEĆ, ŚRODA, JA, BĘDĘ, BARDZO, ZMĘCZONY</t>
-  </si>
-  <si>
     <t xml:space="preserve">W czwartek siostra chce mieć nową książkę.</t>
   </si>
   <si>
-    <t xml:space="preserve">CZWARTEK, SIOSTRA, CHCIEĆ, MIEĆ, KSIĄŻKA, NOWA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gdzie ty byłeś we wtorek rano?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, BYĆ, GDZIE, WTOREK, RANO?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mój stary kot lubi spać w środę w domu.</t>
   </si>
   <si>
-    <t xml:space="preserve">MÓJ, KOT, STARY, LUBIĆ, ŚRODA, SPAĆ, DOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ile pieniędzy musisz mieć na czwartek?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, MUSIEĆ, MIEĆ, PIENIĄDZE, ILE, NA, CZWARTEK?</t>
-  </si>
-  <si>
     <t xml:space="preserve">We wtorek my nie mamy czasu na kawę.</t>
   </si>
   <si>
-    <t xml:space="preserve">WTOREK, MY, CZAS-NIE, NA, KAWA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zawsze w środę uczę się migać, teraz już kocham to robić. </t>
   </si>
   <si>
-    <t xml:space="preserve">ZAWSZE, ŚRODA, JA, UCZYĆ-SIĘ, MIGAĆ, TERAZ, JUŻ, KOCHAĆ, TO, ROBIĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">W czwartek wieczorem twój kolega jest wesoły.</t>
   </si>
   <si>
-    <t xml:space="preserve">CZWARTEK, WIECZÓR, TWÓJ, KOLEGA, WESOŁY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pamiętam, co mój tata mówił we wtorek.</t>
   </si>
   <si>
-    <t xml:space="preserve">JA, PAMIĘTAĆ, CO, MÓJ, TATA, WTOREK, MÓWIĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">W środę ten duży samochód jest mój, a wy go już kochacie. </t>
   </si>
   <si>
-    <t xml:space="preserve">ŚRODA, SAMOCHÓD, DUŻY, TEN, MÓJ, WY, JUŻ, KOCHAĆ-GO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dziękuję, że chcesz mi pomóc w czwartek, to taki zdrowy pomysł. </t>
   </si>
   <si>
-    <t xml:space="preserve">DZIĘKUJĘ, ŻE, CHCIEĆ, MI, POMÓC, CZWARTEK, —, TO, POMYSŁ, ZDROWY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jak bardzo lubisz ten wtorek?</t>
   </si>
   <si>
-    <t xml:space="preserve">TY, LUBIĆ, WTOREK, JAK-BARDZO?</t>
-  </si>
-  <si>
     <t xml:space="preserve">W środę rano muszę pić zimną wodę.</t>
   </si>
   <si>
-    <t xml:space="preserve">ŚRODA, RANO, JA, MUSI, PIĆ, WODA, ZIMNA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jutro czwartek, więc idę do pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">JUTRO, CZWARTEK, WIĘC, JA, IŚĆ, PRACA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Przepraszam, że nie byłem zdrowy we wtorek.</t>
   </si>
   <si>
-    <t xml:space="preserve">PRZEPRASZAM, WTOREK, JA, ZDROWY-NIE, BYĆ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Teraz idę do pracy, bo muszę iść po klucz, który ma moja siostra. </t>
   </si>
   <si>
-    <t xml:space="preserve">TERAZ, JA, IŚĆ, PRACA, BO, MUSZĘ, IŚĆ, PO, KLUCZ, MOJA, SIOSTRA, MA</t>
-  </si>
-  <si>
     <t xml:space="preserve">On się teraz uczy, żeby rozumieć, jak pomóc chorej kobiecie. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON, TERAZ, UCZYĆ-SIĘ, ŻEBY, ROZUMIEĆ, JAK, POMÓC, KOBIETA, CHORA</t>
   </si>
 </sst>
 </file>
@@ -3043,19 +2713,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3145,37 +2812,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3248,8 +2915,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D502"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D501"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60"/>
@@ -6331,7 +5998,7 @@
       <c r="B257" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C257" s="5" t="s">
         <v>512</v>
       </c>
       <c r="D257" s="2"/>
@@ -6343,7 +6010,7 @@
       <c r="B258" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="C258" s="5" t="s">
         <v>514</v>
       </c>
       <c r="D258" s="2"/>
@@ -6355,7 +6022,7 @@
       <c r="B259" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C259" s="4" t="s">
+      <c r="C259" s="5" t="s">
         <v>516</v>
       </c>
       <c r="D259" s="2"/>
@@ -6367,7 +6034,7 @@
       <c r="B260" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C260" s="4" t="s">
+      <c r="C260" s="5" t="s">
         <v>518</v>
       </c>
       <c r="D260" s="2"/>
@@ -6379,7 +6046,7 @@
       <c r="B261" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="C261" s="5" t="s">
         <v>520</v>
       </c>
       <c r="D261" s="2"/>
@@ -6391,7 +6058,7 @@
       <c r="B262" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C262" s="4" t="s">
+      <c r="C262" s="5" t="s">
         <v>522</v>
       </c>
       <c r="D262" s="2"/>
@@ -6403,7 +6070,7 @@
       <c r="B263" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C263" s="4" t="s">
+      <c r="C263" s="5" t="s">
         <v>524</v>
       </c>
       <c r="D263" s="2"/>
@@ -6415,7 +6082,7 @@
       <c r="B264" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C264" s="4" t="s">
+      <c r="C264" s="5" t="s">
         <v>526</v>
       </c>
       <c r="D264" s="2"/>
@@ -6427,7 +6094,7 @@
       <c r="B265" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="C265" s="5" t="s">
         <v>528</v>
       </c>
       <c r="D265" s="2"/>
@@ -6439,7 +6106,7 @@
       <c r="B266" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C266" s="4" t="s">
+      <c r="C266" s="5" t="s">
         <v>530</v>
       </c>
       <c r="D266" s="2"/>
@@ -6451,7 +6118,7 @@
       <c r="B267" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C267" s="4" t="s">
+      <c r="C267" s="5" t="s">
         <v>532</v>
       </c>
       <c r="D267" s="2"/>
@@ -6463,7 +6130,7 @@
       <c r="B268" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C268" s="4" t="s">
+      <c r="C268" s="5" t="s">
         <v>534</v>
       </c>
       <c r="D268" s="2"/>
@@ -6475,7 +6142,7 @@
       <c r="B269" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C269" s="4" t="s">
+      <c r="C269" s="5" t="s">
         <v>536</v>
       </c>
       <c r="D269" s="2"/>
@@ -6487,7 +6154,7 @@
       <c r="B270" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C270" s="4" t="s">
+      <c r="C270" s="5" t="s">
         <v>538</v>
       </c>
       <c r="D270" s="2"/>
@@ -6499,7 +6166,7 @@
       <c r="B271" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C271" s="4" t="s">
+      <c r="C271" s="5" t="s">
         <v>540</v>
       </c>
       <c r="D271" s="2"/>
@@ -6511,7 +6178,7 @@
       <c r="B272" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C272" s="4" t="s">
+      <c r="C272" s="5" t="s">
         <v>542</v>
       </c>
       <c r="D272" s="2"/>
@@ -6523,7 +6190,7 @@
       <c r="B273" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C273" s="4" t="s">
+      <c r="C273" s="5" t="s">
         <v>544</v>
       </c>
       <c r="D273" s="2"/>
@@ -6535,7 +6202,7 @@
       <c r="B274" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C274" s="4" t="s">
+      <c r="C274" s="5" t="s">
         <v>546</v>
       </c>
       <c r="D274" s="2"/>
@@ -6547,7 +6214,7 @@
       <c r="B275" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C275" s="4" t="s">
+      <c r="C275" s="5" t="s">
         <v>548</v>
       </c>
       <c r="D275" s="2"/>
@@ -6559,7 +6226,7 @@
       <c r="B276" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C276" s="4" t="s">
+      <c r="C276" s="5" t="s">
         <v>550</v>
       </c>
       <c r="D276" s="2"/>
@@ -6571,7 +6238,7 @@
       <c r="B277" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C277" s="4" t="s">
+      <c r="C277" s="5" t="s">
         <v>552</v>
       </c>
       <c r="D277" s="2"/>
@@ -6583,7 +6250,7 @@
       <c r="B278" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C278" s="4" t="s">
+      <c r="C278" s="5" t="s">
         <v>554</v>
       </c>
       <c r="D278" s="2"/>
@@ -6595,7 +6262,7 @@
       <c r="B279" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C279" s="4" t="s">
+      <c r="C279" s="5" t="s">
         <v>556</v>
       </c>
       <c r="D279" s="2"/>
@@ -6607,7 +6274,7 @@
       <c r="B280" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="C280" s="5" t="s">
         <v>558</v>
       </c>
       <c r="D280" s="2"/>
@@ -6619,7 +6286,7 @@
       <c r="B281" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C281" s="4" t="s">
+      <c r="C281" s="5" t="s">
         <v>560</v>
       </c>
       <c r="D281" s="2"/>
@@ -6631,7 +6298,7 @@
       <c r="B282" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C282" s="4" t="s">
+      <c r="C282" s="5" t="s">
         <v>562</v>
       </c>
       <c r="D282" s="2"/>
@@ -6643,7 +6310,7 @@
       <c r="B283" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="C283" s="4" t="s">
+      <c r="C283" s="5" t="s">
         <v>564</v>
       </c>
       <c r="D283" s="2"/>
@@ -6655,7 +6322,7 @@
       <c r="B284" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C284" s="4" t="s">
+      <c r="C284" s="5" t="s">
         <v>566</v>
       </c>
       <c r="D284" s="2"/>
@@ -6667,7 +6334,7 @@
       <c r="B285" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="C285" s="5" t="s">
         <v>568</v>
       </c>
       <c r="D285" s="2"/>
@@ -6679,7 +6346,7 @@
       <c r="B286" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C286" s="4" t="s">
+      <c r="C286" s="5" t="s">
         <v>570</v>
       </c>
       <c r="D286" s="2"/>
@@ -6691,7 +6358,7 @@
       <c r="B287" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C287" s="4" t="s">
+      <c r="C287" s="5" t="s">
         <v>572</v>
       </c>
       <c r="D287" s="2"/>
@@ -6703,7 +6370,7 @@
       <c r="B288" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C288" s="4" t="s">
+      <c r="C288" s="5" t="s">
         <v>574</v>
       </c>
       <c r="D288" s="2"/>
@@ -6715,7 +6382,7 @@
       <c r="B289" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C289" s="4" t="s">
+      <c r="C289" s="5" t="s">
         <v>576</v>
       </c>
       <c r="D289" s="2"/>
@@ -6727,7 +6394,7 @@
       <c r="B290" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C290" s="4" t="s">
+      <c r="C290" s="5" t="s">
         <v>578</v>
       </c>
       <c r="D290" s="2"/>
@@ -6739,7 +6406,7 @@
       <c r="B291" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C291" s="4" t="s">
+      <c r="C291" s="5" t="s">
         <v>580</v>
       </c>
       <c r="D291" s="2"/>
@@ -6751,7 +6418,7 @@
       <c r="B292" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C292" s="4" t="s">
+      <c r="C292" s="5" t="s">
         <v>582</v>
       </c>
       <c r="D292" s="2"/>
@@ -6763,7 +6430,7 @@
       <c r="B293" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C293" s="4" t="s">
+      <c r="C293" s="5" t="s">
         <v>584</v>
       </c>
       <c r="D293" s="2"/>
@@ -6775,7 +6442,7 @@
       <c r="B294" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C294" s="4" t="s">
+      <c r="C294" s="5" t="s">
         <v>586</v>
       </c>
       <c r="D294" s="2"/>
@@ -6787,7 +6454,7 @@
       <c r="B295" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C295" s="4" t="s">
+      <c r="C295" s="5" t="s">
         <v>588</v>
       </c>
       <c r="D295" s="2"/>
@@ -6799,7 +6466,7 @@
       <c r="B296" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="C296" s="4" t="s">
+      <c r="C296" s="5" t="s">
         <v>590</v>
       </c>
       <c r="D296" s="2"/>
@@ -6811,7 +6478,7 @@
       <c r="B297" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C297" s="4" t="s">
+      <c r="C297" s="5" t="s">
         <v>592</v>
       </c>
       <c r="D297" s="2"/>
@@ -6823,7 +6490,7 @@
       <c r="B298" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="C298" s="4" t="s">
+      <c r="C298" s="5" t="s">
         <v>594</v>
       </c>
       <c r="D298" s="2"/>
@@ -6835,7 +6502,7 @@
       <c r="B299" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C299" s="4" t="s">
+      <c r="C299" s="5" t="s">
         <v>596</v>
       </c>
       <c r="D299" s="2"/>
@@ -6847,7 +6514,7 @@
       <c r="B300" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C300" s="4" t="s">
+      <c r="C300" s="5" t="s">
         <v>598</v>
       </c>
       <c r="D300" s="2"/>
@@ -6859,7 +6526,7 @@
       <c r="B301" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="C301" s="4" t="s">
+      <c r="C301" s="5" t="s">
         <v>600</v>
       </c>
       <c r="D301" s="2"/>
@@ -6871,7 +6538,7 @@
       <c r="B302" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C302" s="4" t="s">
+      <c r="C302" s="5" t="s">
         <v>602</v>
       </c>
     </row>
@@ -6882,7 +6549,7 @@
       <c r="B303" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C303" s="4" t="s">
+      <c r="C303" s="5" t="s">
         <v>604</v>
       </c>
     </row>
@@ -6893,7 +6560,7 @@
       <c r="B304" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C304" s="4" t="s">
+      <c r="C304" s="5" t="s">
         <v>606</v>
       </c>
     </row>
@@ -6904,7 +6571,7 @@
       <c r="B305" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C305" s="4" t="s">
+      <c r="C305" s="5" t="s">
         <v>608</v>
       </c>
     </row>
@@ -6915,7 +6582,7 @@
       <c r="B306" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C306" s="4" t="s">
+      <c r="C306" s="5" t="s">
         <v>610</v>
       </c>
     </row>
@@ -6926,7 +6593,7 @@
       <c r="B307" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C307" s="4" t="s">
+      <c r="C307" s="5" t="s">
         <v>612</v>
       </c>
     </row>
@@ -6937,7 +6604,7 @@
       <c r="B308" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C308" s="4" t="s">
+      <c r="C308" s="5" t="s">
         <v>614</v>
       </c>
     </row>
@@ -6948,7 +6615,7 @@
       <c r="B309" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C309" s="4" t="s">
+      <c r="C309" s="5" t="s">
         <v>616</v>
       </c>
     </row>
@@ -6959,7 +6626,7 @@
       <c r="B310" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="C310" s="4" t="s">
+      <c r="C310" s="5" t="s">
         <v>618</v>
       </c>
     </row>
@@ -6970,7 +6637,7 @@
       <c r="B311" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C311" s="4" t="s">
+      <c r="C311" s="5" t="s">
         <v>620</v>
       </c>
     </row>
@@ -6981,7 +6648,7 @@
       <c r="B312" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="C312" s="4" t="s">
+      <c r="C312" s="5" t="s">
         <v>622</v>
       </c>
     </row>
@@ -6992,7 +6659,7 @@
       <c r="B313" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C313" s="4" t="s">
+      <c r="C313" s="5" t="s">
         <v>624</v>
       </c>
     </row>
@@ -7003,7 +6670,7 @@
       <c r="B314" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C314" s="4" t="s">
+      <c r="C314" s="5" t="s">
         <v>626</v>
       </c>
     </row>
@@ -7014,7 +6681,7 @@
       <c r="B315" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="C315" s="4" t="s">
+      <c r="C315" s="5" t="s">
         <v>628</v>
       </c>
     </row>
@@ -7025,7 +6692,7 @@
       <c r="B316" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C316" s="4" t="s">
+      <c r="C316" s="5" t="s">
         <v>630</v>
       </c>
     </row>
@@ -7036,7 +6703,7 @@
       <c r="B317" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C317" s="4" t="s">
+      <c r="C317" s="5" t="s">
         <v>632</v>
       </c>
     </row>
@@ -7047,7 +6714,7 @@
       <c r="B318" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C318" s="4" t="s">
+      <c r="C318" s="5" t="s">
         <v>634</v>
       </c>
     </row>
@@ -7058,7 +6725,7 @@
       <c r="B319" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C319" s="4" t="s">
+      <c r="C319" s="5" t="s">
         <v>636</v>
       </c>
     </row>
@@ -7069,7 +6736,7 @@
       <c r="B320" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C320" s="4" t="s">
+      <c r="C320" s="5" t="s">
         <v>638</v>
       </c>
     </row>
@@ -7080,7 +6747,7 @@
       <c r="B321" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C321" s="4" t="s">
+      <c r="C321" s="5" t="s">
         <v>640</v>
       </c>
     </row>
@@ -7091,7 +6758,7 @@
       <c r="B322" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C322" s="4" t="s">
+      <c r="C322" s="5" t="s">
         <v>642</v>
       </c>
     </row>
@@ -7102,7 +6769,7 @@
       <c r="B323" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C323" s="4" t="s">
+      <c r="C323" s="5" t="s">
         <v>644</v>
       </c>
     </row>
@@ -7113,7 +6780,7 @@
       <c r="B324" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C324" s="4" t="s">
+      <c r="C324" s="5" t="s">
         <v>646</v>
       </c>
     </row>
@@ -7124,7 +6791,7 @@
       <c r="B325" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C325" s="4" t="s">
+      <c r="C325" s="5" t="s">
         <v>648</v>
       </c>
     </row>
@@ -7135,7 +6802,7 @@
       <c r="B326" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C326" s="4" t="s">
+      <c r="C326" s="5" t="s">
         <v>650</v>
       </c>
     </row>
@@ -7146,7 +6813,7 @@
       <c r="B327" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C327" s="4" t="s">
+      <c r="C327" s="5" t="s">
         <v>652</v>
       </c>
     </row>
@@ -7157,7 +6824,7 @@
       <c r="B328" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C328" s="4" t="s">
+      <c r="C328" s="5" t="s">
         <v>654</v>
       </c>
     </row>
@@ -7168,7 +6835,7 @@
       <c r="B329" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C329" s="4" t="s">
+      <c r="C329" s="5" t="s">
         <v>656</v>
       </c>
     </row>
@@ -7179,7 +6846,7 @@
       <c r="B330" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="C330" s="4" t="s">
+      <c r="C330" s="5" t="s">
         <v>658</v>
       </c>
     </row>
@@ -7190,7 +6857,7 @@
       <c r="B331" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C331" s="4" t="s">
+      <c r="C331" s="5" t="s">
         <v>660</v>
       </c>
     </row>
@@ -7201,7 +6868,7 @@
       <c r="B332" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C332" s="4" t="s">
+      <c r="C332" s="5" t="s">
         <v>662</v>
       </c>
     </row>
@@ -7212,7 +6879,7 @@
       <c r="B333" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C333" s="4" t="s">
+      <c r="C333" s="5" t="s">
         <v>664</v>
       </c>
     </row>
@@ -7223,7 +6890,7 @@
       <c r="B334" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C334" s="4" t="s">
+      <c r="C334" s="5" t="s">
         <v>666</v>
       </c>
     </row>
@@ -7234,7 +6901,7 @@
       <c r="B335" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C335" s="4" t="s">
+      <c r="C335" s="5" t="s">
         <v>668</v>
       </c>
     </row>
@@ -7245,7 +6912,7 @@
       <c r="B336" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C336" s="4" t="s">
+      <c r="C336" s="5" t="s">
         <v>670</v>
       </c>
     </row>
@@ -7256,7 +6923,7 @@
       <c r="B337" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C337" s="4" t="s">
+      <c r="C337" s="5" t="s">
         <v>672</v>
       </c>
     </row>
@@ -7267,7 +6934,7 @@
       <c r="B338" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C338" s="4" t="s">
+      <c r="C338" s="5" t="s">
         <v>674</v>
       </c>
     </row>
@@ -7278,7 +6945,7 @@
       <c r="B339" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C339" s="4" t="s">
+      <c r="C339" s="5" t="s">
         <v>676</v>
       </c>
     </row>
@@ -7289,7 +6956,7 @@
       <c r="B340" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="C340" s="4" t="s">
+      <c r="C340" s="5" t="s">
         <v>678</v>
       </c>
     </row>
@@ -7300,7 +6967,7 @@
       <c r="B341" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C341" s="4" t="s">
+      <c r="C341" s="5" t="s">
         <v>680</v>
       </c>
     </row>
@@ -7311,7 +6978,7 @@
       <c r="B342" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C342" s="4" t="s">
+      <c r="C342" s="5" t="s">
         <v>682</v>
       </c>
     </row>
@@ -7322,7 +6989,7 @@
       <c r="B343" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="C343" s="4" t="s">
+      <c r="C343" s="5" t="s">
         <v>684</v>
       </c>
     </row>
@@ -7333,7 +7000,7 @@
       <c r="B344" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C344" s="4" t="s">
+      <c r="C344" s="5" t="s">
         <v>686</v>
       </c>
     </row>
@@ -7344,7 +7011,7 @@
       <c r="B345" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="C345" s="4" t="s">
+      <c r="C345" s="5" t="s">
         <v>688</v>
       </c>
     </row>
@@ -7355,7 +7022,7 @@
       <c r="B346" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C346" s="4" t="s">
+      <c r="C346" s="5" t="s">
         <v>690</v>
       </c>
     </row>
@@ -7366,7 +7033,7 @@
       <c r="B347" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="C347" s="4" t="s">
+      <c r="C347" s="5" t="s">
         <v>692</v>
       </c>
     </row>
@@ -7377,7 +7044,7 @@
       <c r="B348" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="C348" s="4" t="s">
+      <c r="C348" s="5" t="s">
         <v>694</v>
       </c>
     </row>
@@ -7388,7 +7055,7 @@
       <c r="B349" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C349" s="4" t="s">
+      <c r="C349" s="5" t="s">
         <v>696</v>
       </c>
     </row>
@@ -7399,7 +7066,7 @@
       <c r="B350" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="C350" s="4" t="s">
+      <c r="C350" s="5" t="s">
         <v>698</v>
       </c>
     </row>
@@ -7410,7 +7077,7 @@
       <c r="B351" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C351" s="4" t="s">
+      <c r="C351" s="5" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7421,7 +7088,7 @@
       <c r="B352" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="C352" s="4" t="s">
+      <c r="C352" s="5" t="s">
         <v>702</v>
       </c>
     </row>
@@ -7432,7 +7099,7 @@
       <c r="B353" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C353" s="4" t="s">
+      <c r="C353" s="5" t="s">
         <v>704</v>
       </c>
     </row>
@@ -7443,7 +7110,7 @@
       <c r="B354" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C354" s="4" t="s">
+      <c r="C354" s="5" t="s">
         <v>706</v>
       </c>
     </row>
@@ -7454,7 +7121,7 @@
       <c r="B355" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C355" s="4" t="s">
+      <c r="C355" s="5" t="s">
         <v>708</v>
       </c>
     </row>
@@ -7465,7 +7132,7 @@
       <c r="B356" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C356" s="4" t="s">
+      <c r="C356" s="5" t="s">
         <v>710</v>
       </c>
     </row>
@@ -7476,7 +7143,7 @@
       <c r="B357" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C357" s="4" t="s">
+      <c r="C357" s="5" t="s">
         <v>712</v>
       </c>
     </row>
@@ -7487,7 +7154,7 @@
       <c r="B358" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="C358" s="4" t="s">
+      <c r="C358" s="5" t="s">
         <v>714</v>
       </c>
     </row>
@@ -7498,7 +7165,7 @@
       <c r="B359" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="C359" s="4" t="s">
+      <c r="C359" s="5" t="s">
         <v>716</v>
       </c>
     </row>
@@ -7509,7 +7176,7 @@
       <c r="B360" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C360" s="4" t="s">
+      <c r="C360" s="5" t="s">
         <v>718</v>
       </c>
     </row>
@@ -7520,7 +7187,7 @@
       <c r="B361" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="C361" s="4" t="s">
+      <c r="C361" s="5" t="s">
         <v>720</v>
       </c>
     </row>
@@ -7531,7 +7198,7 @@
       <c r="B362" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="C362" s="4" t="s">
+      <c r="C362" s="5" t="s">
         <v>722</v>
       </c>
     </row>
@@ -7542,7 +7209,7 @@
       <c r="B363" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C363" s="4" t="s">
+      <c r="C363" s="5" t="s">
         <v>724</v>
       </c>
     </row>
@@ -7553,7 +7220,7 @@
       <c r="B364" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="C364" s="4" t="s">
+      <c r="C364" s="5" t="s">
         <v>726</v>
       </c>
     </row>
@@ -7564,7 +7231,7 @@
       <c r="B365" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C365" s="4" t="s">
+      <c r="C365" s="5" t="s">
         <v>728</v>
       </c>
     </row>
@@ -7575,7 +7242,7 @@
       <c r="B366" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="C366" s="4" t="s">
+      <c r="C366" s="5" t="s">
         <v>730</v>
       </c>
     </row>
@@ -7586,7 +7253,7 @@
       <c r="B367" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C367" s="4" t="s">
+      <c r="C367" s="5" t="s">
         <v>732</v>
       </c>
     </row>
@@ -7597,7 +7264,7 @@
       <c r="B368" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C368" s="4" t="s">
+      <c r="C368" s="5" t="s">
         <v>734</v>
       </c>
     </row>
@@ -7608,7 +7275,7 @@
       <c r="B369" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="C369" s="4" t="s">
+      <c r="C369" s="5" t="s">
         <v>736</v>
       </c>
     </row>
@@ -7619,7 +7286,7 @@
       <c r="B370" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C370" s="4" t="s">
+      <c r="C370" s="5" t="s">
         <v>738</v>
       </c>
     </row>
@@ -7630,7 +7297,7 @@
       <c r="B371" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C371" s="4" t="s">
+      <c r="C371" s="5" t="s">
         <v>740</v>
       </c>
     </row>
@@ -7641,7 +7308,7 @@
       <c r="B372" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C372" s="4" t="s">
+      <c r="C372" s="5" t="s">
         <v>742</v>
       </c>
     </row>
@@ -7652,7 +7319,7 @@
       <c r="B373" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C373" s="4" t="s">
+      <c r="C373" s="5" t="s">
         <v>744</v>
       </c>
     </row>
@@ -7663,7 +7330,7 @@
       <c r="B374" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="C374" s="4" t="s">
+      <c r="C374" s="5" t="s">
         <v>746</v>
       </c>
     </row>
@@ -7674,7 +7341,7 @@
       <c r="B375" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C375" s="4" t="s">
+      <c r="C375" s="5" t="s">
         <v>748</v>
       </c>
     </row>
@@ -7685,7 +7352,7 @@
       <c r="B376" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="C376" s="4" t="s">
+      <c r="C376" s="5" t="s">
         <v>750</v>
       </c>
     </row>
@@ -7696,7 +7363,7 @@
       <c r="B377" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C377" s="4" t="s">
+      <c r="C377" s="5" t="s">
         <v>752</v>
       </c>
     </row>
@@ -7707,7 +7374,7 @@
       <c r="B378" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C378" s="4" t="s">
+      <c r="C378" s="5" t="s">
         <v>754</v>
       </c>
     </row>
@@ -7718,7 +7385,7 @@
       <c r="B379" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="C379" s="4" t="s">
+      <c r="C379" s="5" t="s">
         <v>756</v>
       </c>
     </row>
@@ -7729,7 +7396,7 @@
       <c r="B380" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="C380" s="4" t="s">
+      <c r="C380" s="5" t="s">
         <v>758</v>
       </c>
     </row>
@@ -7740,7 +7407,7 @@
       <c r="B381" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C381" s="4" t="s">
+      <c r="C381" s="5" t="s">
         <v>760</v>
       </c>
     </row>
@@ -7751,7 +7418,7 @@
       <c r="B382" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="C382" s="4" t="s">
+      <c r="C382" s="5" t="s">
         <v>762</v>
       </c>
     </row>
@@ -7762,7 +7429,7 @@
       <c r="B383" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C383" s="4" t="s">
+      <c r="C383" s="5" t="s">
         <v>764</v>
       </c>
     </row>
@@ -7773,7 +7440,7 @@
       <c r="B384" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="C384" s="4" t="s">
+      <c r="C384" s="5" t="s">
         <v>766</v>
       </c>
     </row>
@@ -7784,7 +7451,7 @@
       <c r="B385" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="C385" s="4" t="s">
+      <c r="C385" s="5" t="s">
         <v>768</v>
       </c>
     </row>
@@ -7795,7 +7462,7 @@
       <c r="B386" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="C386" s="4" t="s">
+      <c r="C386" s="5" t="s">
         <v>770</v>
       </c>
     </row>
@@ -7806,1274 +7473,941 @@
       <c r="B387" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C387" s="4" t="s">
+      <c r="C387" s="5" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2" t="n">
         <v>387</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C388" s="4" t="s">
+      <c r="C388" s="5" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2" t="n">
         <v>388</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="C389" s="4" t="s">
+      <c r="C389" s="5" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2" t="n">
         <v>389</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="C390" s="4" t="s">
+      <c r="C390" s="5" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2" t="n">
         <v>390</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="C391" s="4" t="s">
+      <c r="C391" s="5" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2" t="n">
         <v>391</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="C392" s="5" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="2" t="n">
         <v>392</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="C393" s="5" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="2" t="n">
         <v>393</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="C394" s="5" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="n">
         <v>394</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2" t="n">
         <v>395</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="C396" s="5" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2" t="n">
         <v>396</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="C397" s="5" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2" t="n">
         <v>397</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="C398" s="5" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2" t="n">
         <v>398</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="C399" s="5" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2" t="n">
         <v>399</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="C400" s="5" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2" t="n">
         <v>400</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="C401" s="5" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="n">
         <v>401</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C402" s="5" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2" t="n">
         <v>402</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="C403" s="5" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2" t="n">
         <v>403</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="C404" s="5" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2" t="n">
         <v>404</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="C405" s="5" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2" t="n">
         <v>405</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="C406" s="5" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2" t="n">
         <v>406</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="C407" s="5" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2" t="n">
         <v>407</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="C408" s="5" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="n">
         <v>408</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="C409" s="5" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2" t="n">
         <v>409</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="C410" s="5" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2" t="n">
         <v>410</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="C411" s="5" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2" t="n">
         <v>411</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C412" s="5" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2" t="n">
         <v>412</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="C413" s="5" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2" t="n">
         <v>413</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="C414" s="5" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2" t="n">
         <v>414</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="C415" s="5" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2" t="n">
         <v>415</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="C416" s="5" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2" t="n">
         <v>416</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2" t="n">
         <v>417</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="C418" s="5" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2" t="n">
         <v>418</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="C419" s="5" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2" t="n">
         <v>419</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="C420" s="5" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="2" t="n">
         <v>420</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="C421" s="5" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="n">
         <v>421</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="C422" s="5" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2" t="n">
         <v>422</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="C423" s="5" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2" t="n">
         <v>423</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="C424" s="5" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="n">
         <v>424</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="C425" s="5" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="n">
         <v>425</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="C426" s="5" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2" t="n">
         <v>426</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="C427" s="5" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2" t="n">
         <v>427</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="C428" s="5" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2" t="n">
         <v>428</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C429" s="5" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2" t="n">
         <v>429</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="C430" s="5" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2" t="n">
         <v>430</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="C431" s="5" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="n">
         <v>431</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="C432" s="5" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="n">
         <v>432</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="C433" s="5" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2" t="n">
         <v>433</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="C434" s="5" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="n">
         <v>434</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="C435" s="5" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2" t="n">
         <v>435</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>869</v>
-      </c>
-      <c r="C436" s="5" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="n">
         <v>436</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="C437" s="5" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2" t="n">
         <v>437</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="C438" s="5" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2" t="n">
         <v>438</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="C439" s="5" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2" t="n">
         <v>439</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="C440" s="5" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2" t="n">
         <v>440</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="C441" s="5" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2" t="n">
         <v>441</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="C442" s="5" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2" t="n">
         <v>442</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C443" s="5" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2" t="n">
         <v>443</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="C444" s="5" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2" t="n">
         <v>444</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="C445" s="5" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2" t="n">
         <v>445</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="C446" s="5" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2" t="n">
         <v>446</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="C447" s="5" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="n">
         <v>447</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="C448" s="5" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2" t="n">
         <v>448</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="C449" s="5" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2" t="n">
         <v>449</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2" t="n">
         <v>450</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="n">
         <v>451</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="C452" s="5" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="n">
         <v>452</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="n">
         <v>453</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="C454" s="5" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="n">
         <v>454</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="C455" s="5" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="n">
         <v>455</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C456" s="5" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="n">
         <v>456</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="C457" s="5" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2" t="n">
         <v>457</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="C458" s="5" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2" t="n">
         <v>458</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="C459" s="5" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2" t="n">
         <v>459</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="C460" s="5" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="2" t="n">
         <v>460</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="C461" s="5" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2" t="n">
         <v>461</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>921</v>
-      </c>
-      <c r="C462" s="5" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2" t="n">
         <v>462</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>923</v>
-      </c>
-      <c r="C463" s="5" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2" t="n">
         <v>463</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="C464" s="5" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2" t="n">
         <v>464</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="C465" s="5" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2" t="n">
         <v>465</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>929</v>
-      </c>
-      <c r="C466" s="5" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2" t="n">
         <v>466</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="C467" s="5" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2" t="n">
         <v>467</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>933</v>
-      </c>
-      <c r="C468" s="5" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2" t="n">
         <v>468</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C469" s="5" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2" t="n">
         <v>469</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="C470" s="5" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2" t="n">
         <v>470</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="C471" s="5" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2" t="n">
         <v>471</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="C472" s="5" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="n">
         <v>472</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>943</v>
-      </c>
-      <c r="C473" s="5" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2" t="n">
         <v>473</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C474" s="5" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="n">
         <v>474</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C475" s="5" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="n">
         <v>475</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="C476" s="5" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2" t="n">
         <v>476</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="C477" s="5" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2" t="n">
         <v>477</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="C478" s="5" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2" t="n">
         <v>478</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="C479" s="5" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="2" t="n">
         <v>479</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="C480" s="5" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="n">
         <v>480</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="C481" s="5" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2" t="n">
         <v>481</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="C482" s="5" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2" t="n">
         <v>482</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>963</v>
-      </c>
-      <c r="C483" s="5" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2" t="n">
         <v>483</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="C484" s="5" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2" t="n">
         <v>484</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="C485" s="5" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2" t="n">
         <v>485</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="C486" s="5" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2" t="n">
         <v>486</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="C487" s="5" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="2" t="n">
         <v>487</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="C488" s="5" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="2" t="n">
         <v>488</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>975</v>
-      </c>
-      <c r="C489" s="5" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2" t="n">
         <v>489</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="C490" s="5" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2" t="n">
         <v>490</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="C491" s="5" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2" t="n">
         <v>491</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="C492" s="5" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2" t="n">
         <v>492</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>983</v>
-      </c>
-      <c r="C493" s="5" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2" t="n">
         <v>493</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="C494" s="5" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2" t="n">
         <v>494</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="C495" s="5" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2" t="n">
         <v>495</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="C496" s="5" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="n">
         <v>496</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="C497" s="5" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2" t="n">
         <v>497</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="C498" s="5" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="2" t="n">
         <v>498</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="C499" s="5" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="2" t="n">
         <v>499</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="C500" s="5" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2" t="n">
         <v>500</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>999</v>
-      </c>
-      <c r="C501" s="5" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C502" s="0"/>
+        <v>890</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normalny"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normalny"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>